--- a/presentations/Analiz_SUOT_podpisanty_skvoznaya.xlsx
+++ b/presentations/Analiz_SUOT_podpisanty_skvoznaya.xlsx
@@ -560,7 +560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L306"/>
+  <dimension ref="A1:L345"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8"/>
   <cols>
     <col width="10" customWidth="1" style="14" min="1" max="1"/>
@@ -19543,6 +19543,2424 @@
         </is>
       </c>
     </row>
+    <row r="307">
+      <c r="A307" s="16" t="inlineStr">
+        <is>
+          <t>Расследование несчастных случаев</t>
+        </is>
+      </c>
+      <c r="B307" s="16" t="inlineStr">
+        <is>
+          <t>Приказ Минтруда России от 20.04.2022 № 223н "Об утверждении Положения об особенностях расследования несчастных случаев на производстве в отдельных отраслях и организациях, форм документов, соответствующих классификаторов, необходимых для расследования несчастных случаев на производстве"</t>
+        </is>
+      </c>
+      <c r="C307" s="16" t="inlineStr">
+        <is>
+          <t>п. 22 Положения (приложение № 1 к приказу № 223н)</t>
+        </is>
+      </c>
+      <c r="D307" s="16" t="inlineStr">
+        <is>
+          <t>Приказ (распоряжение) о создании комиссии по расследованию несчастного случая</t>
+        </is>
+      </c>
+      <c r="E307" s="16" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F307" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G307" s="16" t="inlineStr">
+        <is>
+          <t>Создание комиссии по расследованию несчастного случая; состав комиссии (включая председателя) из нечетного числа членов; сроки расследования исчисляются в календарных днях начиная со дня издания приказа</t>
+        </is>
+      </c>
+      <c r="H307" s="16" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I307" s="16" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J307" s="16" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K307" s="16" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L307" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="16" t="inlineStr">
+        <is>
+          <t>Расследование несчастных случаев</t>
+        </is>
+      </c>
+      <c r="B308" s="16" t="inlineStr">
+        <is>
+          <t>Приказ Минтруда России от 20.04.2022 № 223н "Об утверждении Положения об особенностях расследования несчастных случаев на производстве в отдельных отраслях и организациях, форм документов, соответствующих классификаторов, необходимых для расследования несчастных случаев на производстве"</t>
+        </is>
+      </c>
+      <c r="C308" s="16" t="inlineStr">
+        <is>
+          <t>приложение № 2 к приказу № 223н (форма № 1)</t>
+        </is>
+      </c>
+      <c r="D308" s="16" t="inlineStr">
+        <is>
+          <t>Извещение о несчастном случае на производстве (групповом, тяжелом несчастном случае, несчастном случае со смертельным исходом)</t>
+        </is>
+      </c>
+      <c r="E308" s="16" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="F308" s="16" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="G308" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H308" s="16" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I308" s="16" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J308" s="16" t="inlineStr">
+        <is>
+          <t>Уведомление</t>
+        </is>
+      </c>
+      <c r="K308" s="16" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L308" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="16" t="inlineStr">
+        <is>
+          <t>Расследование несчастных случаев</t>
+        </is>
+      </c>
+      <c r="B309" s="16" t="inlineStr">
+        <is>
+          <t>Приказ Минтруда России от 20.04.2022 № 223н "Об утверждении Положения об особенностях расследования несчастных случаев на производстве в отдельных отраслях и организациях, форм документов, соответствующих классификаторов, необходимых для расследования несчастных случаев на производстве"</t>
+        </is>
+      </c>
+      <c r="C309" s="16" t="inlineStr">
+        <is>
+          <t>приложение № 2 к приказу № 223н (форма № 1)</t>
+        </is>
+      </c>
+      <c r="D309" s="16" t="inlineStr">
+        <is>
+          <t>Извещение о несчастном случае на производстве (групповом, тяжелом несчастном случае, несчастном случае со смертельным исходом)</t>
+        </is>
+      </c>
+      <c r="E309" s="16" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="F309" s="16" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="G309" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H309" s="16" t="inlineStr">
+        <is>
+          <t>Лицо, передавшее извещение</t>
+        </is>
+      </c>
+      <c r="I309" s="16" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J309" s="16" t="inlineStr">
+        <is>
+          <t>Уведомление</t>
+        </is>
+      </c>
+      <c r="K309" s="16" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L309" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="16" t="inlineStr">
+        <is>
+          <t>Расследование несчастных случаев</t>
+        </is>
+      </c>
+      <c r="B310" s="16" t="inlineStr">
+        <is>
+          <t>Приказ Минтруда России от 20.04.2022 № 223н "Об утверждении Положения об особенностях расследования несчастных случаев на производстве в отдельных отраслях и организациях, форм документов, соответствующих классификаторов, необходимых для расследования несчастных случаев на производстве"</t>
+        </is>
+      </c>
+      <c r="C310" s="16" t="inlineStr">
+        <is>
+          <t>приложение № 2 к приказу № 223н (форма № 1)</t>
+        </is>
+      </c>
+      <c r="D310" s="16" t="inlineStr">
+        <is>
+          <t>Извещение о несчастном случае на производстве (групповом, тяжелом несчастном случае, несчастном случае со смертельным исходом)</t>
+        </is>
+      </c>
+      <c r="E310" s="16" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="F310" s="16" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="G310" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H310" s="16" t="inlineStr">
+        <is>
+          <t>Лицо, принявшее извещение</t>
+        </is>
+      </c>
+      <c r="I310" s="16" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J310" s="16" t="inlineStr">
+        <is>
+          <t>Подтверждение (?)</t>
+        </is>
+      </c>
+      <c r="K310" s="16" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L310" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="16" t="inlineStr">
+        <is>
+          <t>Расследование несчастных случаев</t>
+        </is>
+      </c>
+      <c r="B311" s="16" t="inlineStr">
+        <is>
+          <t>Приказ Минздрава России от 11.04.2025 № 196н "Об утверждении учетной формы N 315-1/у "Медицинское заключение о характере полученных повреждений здоровья в результате несчастного случая на производстве и степени их тяжести", учетной формы N 316-1/у "Медицинское заключение об установлении заключительного диагноза пострадавшего в результате несчастного случая на производстве"</t>
+        </is>
+      </c>
+      <c r="C311" s="16" t="inlineStr">
+        <is>
+          <t>приложение № 1, приложение № 2 к приказу № 196н</t>
+        </is>
+      </c>
+      <c r="D311" s="16" t="inlineStr">
+        <is>
+          <t>Запрос работодателя о выдаче медицинского заключения (учетные формы N 315-1/у, N 316-1/у)</t>
+        </is>
+      </c>
+      <c r="E311" s="16" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F311" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G311" s="16" t="inlineStr">
+        <is>
+          <t>Запрос организации (индивидуального предпринимателя), работодателя - физического лица, по которому выдается медицинское заключение</t>
+        </is>
+      </c>
+      <c r="H311" s="16" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I311" s="16" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J311" s="16" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K311" s="16" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L311" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="16" t="inlineStr">
+        <is>
+          <t>Расследование несчастных случаев</t>
+        </is>
+      </c>
+      <c r="B312" s="16" t="inlineStr">
+        <is>
+          <t>Приказ Минздрава России от 11.04.2025 № 196н "Об утверждении учетной формы N 315-1/у "Медицинское заключение о характере полученных повреждений здоровья в результате несчастного случая на производстве и степени их тяжести", учетной формы N 316-1/у "Медицинское заключение об установлении заключительного диагноза пострадавшего в результате несчастного случая на производстве"</t>
+        </is>
+      </c>
+      <c r="C312" s="16" t="inlineStr">
+        <is>
+          <t>приложение № 1 к приказу № 196н (учетная форма N 315-1/у)</t>
+        </is>
+      </c>
+      <c r="D312" s="16" t="inlineStr">
+        <is>
+          <t>Медицинское заключение о характере полученных повреждений здоровья в результате несчастного случая на производстве и степени их тяжести</t>
+        </is>
+      </c>
+      <c r="E312" s="16" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="F312" s="16" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="G312" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H312" s="16" t="inlineStr">
+        <is>
+          <t>Руководитель медицинской организации (уполномоченное должностное лицо)</t>
+        </is>
+      </c>
+      <c r="I312" s="16" t="inlineStr">
+        <is>
+          <t>собственноручная или УКЭП</t>
+        </is>
+      </c>
+      <c r="J312" s="16" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K312" s="16" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="L312" s="16" t="inlineStr">
+        <is>
+          <t>Печать организации</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="16" t="inlineStr">
+        <is>
+          <t>Расследование несчастных случаев</t>
+        </is>
+      </c>
+      <c r="B313" s="16" t="inlineStr">
+        <is>
+          <t>Приказ Минздрава России от 11.04.2025 № 196н "Об утверждении учетной формы N 315-1/у "Медицинское заключение о характере полученных повреждений здоровья в результате несчастного случая на производстве и степени их тяжести", учетной формы N 316-1/у "Медицинское заключение об установлении заключительного диагноза пострадавшего в результате несчастного случая на производстве"</t>
+        </is>
+      </c>
+      <c r="C313" s="16" t="inlineStr">
+        <is>
+          <t>приложение № 2 к приказу № 196н (учетная форма N 316-1/у)</t>
+        </is>
+      </c>
+      <c r="D313" s="16" t="inlineStr">
+        <is>
+          <t>Медицинское заключение об установлении заключительного диагноза пострадавшего в результате несчастного случая на производстве</t>
+        </is>
+      </c>
+      <c r="E313" s="16" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="F313" s="16" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="G313" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H313" s="16" t="inlineStr">
+        <is>
+          <t>Руководитель медицинской организации (уполномоченное должностное лицо)</t>
+        </is>
+      </c>
+      <c r="I313" s="16" t="inlineStr">
+        <is>
+          <t>собственноручная или УКЭП</t>
+        </is>
+      </c>
+      <c r="J313" s="16" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K313" s="16" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="L313" s="16" t="inlineStr">
+        <is>
+          <t>Печать организации</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="16" t="inlineStr">
+        <is>
+          <t>Расследование несчастных случаев</t>
+        </is>
+      </c>
+      <c r="B314" s="16" t="inlineStr">
+        <is>
+          <t>Приказ Минтруда России от 20.04.2022 № 223н "Об утверждении Положения об особенностях расследования несчастных случаев на производстве в отдельных отраслях и организациях, форм документов, соответствующих классификаторов, необходимых для расследования несчастных случаев на производстве"</t>
+        </is>
+      </c>
+      <c r="C314" s="16" t="inlineStr">
+        <is>
+          <t>приложение № 2 к приказу № 223н (форма № 2, форма Н-1)</t>
+        </is>
+      </c>
+      <c r="D314" s="16" t="inlineStr">
+        <is>
+          <t>Акт о несчастном случае на производстве (форма Н-1)</t>
+        </is>
+      </c>
+      <c r="E314" s="16" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="F314" s="16" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="G314" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H314" s="16" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I314" s="16" t="inlineStr">
+        <is>
+          <t>собственноручная</t>
+        </is>
+      </c>
+      <c r="J314" s="16" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K314" s="16" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="L314" s="16" t="inlineStr">
+        <is>
+          <t>Печать организации</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="16" t="inlineStr">
+        <is>
+          <t>Расследование несчастных случаев</t>
+        </is>
+      </c>
+      <c r="B315" s="16" t="inlineStr">
+        <is>
+          <t>Приказ Минтруда России от 20.04.2022 № 223н "Об утверждении Положения об особенностях расследования несчастных случаев на производстве в отдельных отраслях и организациях, форм документов, соответствующих классификаторов, необходимых для расследования несчастных случаев на производстве"</t>
+        </is>
+      </c>
+      <c r="C315" s="16" t="inlineStr">
+        <is>
+          <t>приложение № 2 к приказу № 223н (форма № 2, форма Н-1)</t>
+        </is>
+      </c>
+      <c r="D315" s="16" t="inlineStr">
+        <is>
+          <t>Акт о несчастном случае на производстве (форма Н-1)</t>
+        </is>
+      </c>
+      <c r="E315" s="16" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="F315" s="16" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="G315" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H315" s="16" t="inlineStr">
+        <is>
+          <t>Лицо, проводившее расследование несчастного случая (член комиссии / председатель комиссии)</t>
+        </is>
+      </c>
+      <c r="I315" s="16" t="inlineStr">
+        <is>
+          <t>собственноручная</t>
+        </is>
+      </c>
+      <c r="J315" s="16" t="inlineStr">
+        <is>
+          <t>Подтверждение (?)</t>
+        </is>
+      </c>
+      <c r="K315" s="16" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="L315" s="16" t="inlineStr">
+        <is>
+          <t>Печать организации</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="16" t="inlineStr">
+        <is>
+          <t>Расследование несчастных случаев</t>
+        </is>
+      </c>
+      <c r="B316" s="16" t="inlineStr">
+        <is>
+          <t>Приказ Минтруда России от 20.04.2022 № 223н "Об утверждении Положения об особенностях расследования несчастных случаев на производстве в отдельных отраслях и организациях, форм документов, соответствующих классификаторов, необходимых для расследования несчастных случаев на производстве"</t>
+        </is>
+      </c>
+      <c r="C316" s="16" t="inlineStr">
+        <is>
+          <t>приложение № 2 к приказу № 223н (форма № 2, форма Н-1)</t>
+        </is>
+      </c>
+      <c r="D316" s="16" t="inlineStr">
+        <is>
+          <t>Акт о несчастном случае на производстве (форма Н-1)</t>
+        </is>
+      </c>
+      <c r="E316" s="16" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="F316" s="16" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="G316" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H316" s="16" t="inlineStr">
+        <is>
+          <t>Пострадавший (законный представитель или иное доверенное лицо)</t>
+        </is>
+      </c>
+      <c r="I316" s="16" t="inlineStr">
+        <is>
+          <t>собственноручная</t>
+        </is>
+      </c>
+      <c r="J316" s="16" t="inlineStr">
+        <is>
+          <t>Ознакомление</t>
+        </is>
+      </c>
+      <c r="K316" s="16" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="L316" s="16" t="inlineStr">
+        <is>
+          <t>Печать организации</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="16" t="inlineStr">
+        <is>
+          <t>Расследование несчастных случаев</t>
+        </is>
+      </c>
+      <c r="B317" s="16" t="inlineStr">
+        <is>
+          <t>Приказ Минтруда России от 20.04.2022 № 223н "Об утверждении Положения об особенностях расследования несчастных случаев на производстве в отдельных отраслях и организациях, форм документов, соответствующих классификаторов, необходимых для расследования несчастных случаев на производстве"</t>
+        </is>
+      </c>
+      <c r="C317" s="16" t="inlineStr">
+        <is>
+          <t>приложение № 2 к приказу № 223н (форма № 3, форма Н-1ПС); п. 16–18 Положения (приложение № 1 к приказу № 223н)</t>
+        </is>
+      </c>
+      <c r="D317" s="16" t="inlineStr">
+        <is>
+          <t>Акт о несчастном случае на производстве (форма Н-1ПС)</t>
+        </is>
+      </c>
+      <c r="E317" s="16" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="F317" s="16" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="G317" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H317" s="16" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I317" s="16" t="inlineStr">
+        <is>
+          <t>собственноручная</t>
+        </is>
+      </c>
+      <c r="J317" s="16" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K317" s="16" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="L317" s="16" t="inlineStr">
+        <is>
+          <t>Печать организации</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="16" t="inlineStr">
+        <is>
+          <t>Расследование несчастных случаев</t>
+        </is>
+      </c>
+      <c r="B318" s="16" t="inlineStr">
+        <is>
+          <t>Приказ Минтруда России от 20.04.2022 № 223н "Об утверждении Положения об особенностях расследования несчастных случаев на производстве в отдельных отраслях и организациях, форм документов, соответствующих классификаторов, необходимых для расследования несчастных случаев на производстве"</t>
+        </is>
+      </c>
+      <c r="C318" s="16" t="inlineStr">
+        <is>
+          <t>приложение № 2 к приказу № 223н (форма № 3, форма Н-1ПС); п. 16–18 Положения (приложение № 1 к приказу № 223н)</t>
+        </is>
+      </c>
+      <c r="D318" s="16" t="inlineStr">
+        <is>
+          <t>Акт о несчастном случае на производстве (форма Н-1ПС)</t>
+        </is>
+      </c>
+      <c r="E318" s="16" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="F318" s="16" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="G318" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H318" s="16" t="inlineStr">
+        <is>
+          <t>Лицо, проводившее расследование несчастного случая</t>
+        </is>
+      </c>
+      <c r="I318" s="16" t="inlineStr">
+        <is>
+          <t>собственноручная</t>
+        </is>
+      </c>
+      <c r="J318" s="16" t="inlineStr">
+        <is>
+          <t>Подтверждение (?)</t>
+        </is>
+      </c>
+      <c r="K318" s="16" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="L318" s="16" t="inlineStr">
+        <is>
+          <t>Печать организации</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="16" t="inlineStr">
+        <is>
+          <t>Расследование несчастных случаев</t>
+        </is>
+      </c>
+      <c r="B319" s="16" t="inlineStr">
+        <is>
+          <t>Приказ Минтруда России от 20.04.2022 № 223н "Об утверждении Положения об особенностях расследования несчастных случаев на производстве в отдельных отраслях и организациях, форм документов, соответствующих классификаторов, необходимых для расследования несчастных случаев на производстве"</t>
+        </is>
+      </c>
+      <c r="C319" s="16" t="inlineStr">
+        <is>
+          <t>приложение № 2 к приказу № 223н (форма № 4, форма Н-1ЧС); п. 21.1–21.4 Положения (приложение № 1 к приказу № 223н)</t>
+        </is>
+      </c>
+      <c r="D319" s="16" t="inlineStr">
+        <is>
+          <t>Акт о несчастном случае на производстве (форма Н-1ЧС)</t>
+        </is>
+      </c>
+      <c r="E319" s="16" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="F319" s="16" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="G319" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H319" s="16" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I319" s="16" t="inlineStr">
+        <is>
+          <t>собственноручная</t>
+        </is>
+      </c>
+      <c r="J319" s="16" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K319" s="16" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="L319" s="16" t="inlineStr">
+        <is>
+          <t>Печать организации</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="16" t="inlineStr">
+        <is>
+          <t>Расследование несчастных случаев</t>
+        </is>
+      </c>
+      <c r="B320" s="16" t="inlineStr">
+        <is>
+          <t>Приказ Минтруда России от 20.04.2022 № 223н "Об утверждении Положения об особенностях расследования несчастных случаев на производстве в отдельных отраслях и организациях, форм документов, соответствующих классификаторов, необходимых для расследования несчастных случаев на производстве"</t>
+        </is>
+      </c>
+      <c r="C320" s="16" t="inlineStr">
+        <is>
+          <t>приложение № 2 к приказу № 223н (форма № 4, форма Н-1ЧС); п. 21.1–21.4 Положения (приложение № 1 к приказу № 223н)</t>
+        </is>
+      </c>
+      <c r="D320" s="16" t="inlineStr">
+        <is>
+          <t>Акт о несчастном случае на производстве (форма Н-1ЧС)</t>
+        </is>
+      </c>
+      <c r="E320" s="16" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="F320" s="16" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="G320" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H320" s="16" t="inlineStr">
+        <is>
+          <t>Лицо, проводившее расследование несчастного случая</t>
+        </is>
+      </c>
+      <c r="I320" s="16" t="inlineStr">
+        <is>
+          <t>собственноручная</t>
+        </is>
+      </c>
+      <c r="J320" s="16" t="inlineStr">
+        <is>
+          <t>Подтверждение (?)</t>
+        </is>
+      </c>
+      <c r="K320" s="16" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="L320" s="16" t="inlineStr">
+        <is>
+          <t>Печать организации</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="16" t="inlineStr">
+        <is>
+          <t>Расследование несчастных случаев</t>
+        </is>
+      </c>
+      <c r="B321" s="16" t="inlineStr">
+        <is>
+          <t>Приказ Минтруда России от 20.04.2022 № 223н "Об утверждении Положения об особенностях расследования несчастных случаев на производстве в отдельных отраслях и организациях, форм документов, соответствующих классификаторов, необходимых для расследования несчастных случаев на производстве"</t>
+        </is>
+      </c>
+      <c r="C321" s="16" t="inlineStr">
+        <is>
+          <t>приложение № 2 к приказу № 223н (форма № 5)</t>
+        </is>
+      </c>
+      <c r="D321" s="16" t="inlineStr">
+        <is>
+          <t>Акт о расследовании группового несчастного случая (легкого несчастного случая, тяжелого несчастного случая, несчастного случая со смертельным исходом)</t>
+        </is>
+      </c>
+      <c r="E321" s="16" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="F321" s="16" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="G321" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H321" s="16" t="inlineStr">
+        <is>
+          <t>Председатель комиссии по расследованию несчастного случая</t>
+        </is>
+      </c>
+      <c r="I321" s="16" t="inlineStr">
+        <is>
+          <t>собственноручная</t>
+        </is>
+      </c>
+      <c r="J321" s="16" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K321" s="16" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L321" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="16" t="inlineStr">
+        <is>
+          <t>Расследование несчастных случаев</t>
+        </is>
+      </c>
+      <c r="B322" s="16" t="inlineStr">
+        <is>
+          <t>Приказ Минтруда России от 20.04.2022 № 223н "Об утверждении Положения об особенностях расследования несчастных случаев на производстве в отдельных отраслях и организациях, форм документов, соответствующих классификаторов, необходимых для расследования несчастных случаев на производстве"</t>
+        </is>
+      </c>
+      <c r="C322" s="16" t="inlineStr">
+        <is>
+          <t>приложение № 2 к приказу № 223н (форма № 5)</t>
+        </is>
+      </c>
+      <c r="D322" s="16" t="inlineStr">
+        <is>
+          <t>Акт о расследовании группового несчастного случая (легкого несчастного случая, тяжелого несчастного случая, несчастного случая со смертельным исходом)</t>
+        </is>
+      </c>
+      <c r="E322" s="16" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="F322" s="16" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="G322" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H322" s="16" t="inlineStr">
+        <is>
+          <t>Член комиссии по расследованию несчастного случая</t>
+        </is>
+      </c>
+      <c r="I322" s="16" t="inlineStr">
+        <is>
+          <t>собственноручная</t>
+        </is>
+      </c>
+      <c r="J322" s="16" t="inlineStr">
+        <is>
+          <t>Подтверждение (?)</t>
+        </is>
+      </c>
+      <c r="K322" s="16" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L322" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="16" t="inlineStr">
+        <is>
+          <t>Расследование несчастных случаев</t>
+        </is>
+      </c>
+      <c r="B323" s="16" t="inlineStr">
+        <is>
+          <t>Приказ Минтруда России от 20.04.2022 № 223н "Об утверждении Положения об особенностях расследования несчастных случаев на производстве в отдельных отраслях и организациях, форм документов, соответствующих классификаторов, необходимых для расследования несчастных случаев на производстве"</t>
+        </is>
+      </c>
+      <c r="C323" s="16" t="inlineStr">
+        <is>
+          <t>приложение № 2 к приказу № 223н (форма № 6)</t>
+        </is>
+      </c>
+      <c r="D323" s="16" t="inlineStr">
+        <is>
+          <t>Акт о расследовании обстоятельств происшествия, предполагающего гибель работника в результате несчастного случая</t>
+        </is>
+      </c>
+      <c r="E323" s="16" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="F323" s="16" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="G323" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H323" s="16" t="inlineStr">
+        <is>
+          <t>Председатель комиссии по расследованию несчастного случая</t>
+        </is>
+      </c>
+      <c r="I323" s="16" t="inlineStr">
+        <is>
+          <t>собственноручная</t>
+        </is>
+      </c>
+      <c r="J323" s="16" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K323" s="16" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L323" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="16" t="inlineStr">
+        <is>
+          <t>Расследование несчастных случаев</t>
+        </is>
+      </c>
+      <c r="B324" s="16" t="inlineStr">
+        <is>
+          <t>Приказ Минтруда России от 20.04.2022 № 223н "Об утверждении Положения об особенностях расследования несчастных случаев на производстве в отдельных отраслях и организациях, форм документов, соответствующих классификаторов, необходимых для расследования несчастных случаев на производстве"</t>
+        </is>
+      </c>
+      <c r="C324" s="16" t="inlineStr">
+        <is>
+          <t>приложение № 2 к приказу № 223н (форма № 6)</t>
+        </is>
+      </c>
+      <c r="D324" s="16" t="inlineStr">
+        <is>
+          <t>Акт о расследовании обстоятельств происшествия, предполагающего гибель работника в результате несчастного случая</t>
+        </is>
+      </c>
+      <c r="E324" s="16" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="F324" s="16" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="G324" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H324" s="16" t="inlineStr">
+        <is>
+          <t>Член комиссии по расследованию несчастного случая</t>
+        </is>
+      </c>
+      <c r="I324" s="16" t="inlineStr">
+        <is>
+          <t>собственноручная</t>
+        </is>
+      </c>
+      <c r="J324" s="16" t="inlineStr">
+        <is>
+          <t>Подтверждение (?)</t>
+        </is>
+      </c>
+      <c r="K324" s="16" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L324" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="16" t="inlineStr">
+        <is>
+          <t>Расследование несчастных случаев</t>
+        </is>
+      </c>
+      <c r="B325" s="16" t="inlineStr">
+        <is>
+          <t>Приказ Минтруда России от 20.04.2022 № 223н "Об утверждении Положения об особенностях расследования несчастных случаев на производстве в отдельных отраслях и организациях, форм документов, соответствующих классификаторов, необходимых для расследования несчастных случаев на производстве"</t>
+        </is>
+      </c>
+      <c r="C325" s="16" t="inlineStr">
+        <is>
+          <t>приложение № 2 к приказу № 223н (форма № 7)</t>
+        </is>
+      </c>
+      <c r="D325" s="16" t="inlineStr">
+        <is>
+          <t>Заключение государственного инспектора труда</t>
+        </is>
+      </c>
+      <c r="E325" s="16" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="F325" s="16" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="G325" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H325" s="16" t="inlineStr">
+        <is>
+          <t>Государственный инспектор труда</t>
+        </is>
+      </c>
+      <c r="I325" s="16" t="inlineStr">
+        <is>
+          <t>собственноручная</t>
+        </is>
+      </c>
+      <c r="J325" s="16" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K325" s="16" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="L325" s="16" t="inlineStr">
+        <is>
+          <t>Печать / именной штамп государственного инспектора труда</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="16" t="inlineStr">
+        <is>
+          <t>Расследование несчастных случаев</t>
+        </is>
+      </c>
+      <c r="B326" s="16" t="inlineStr">
+        <is>
+          <t>Приказ Минтруда России от 20.04.2022 № 223н "Об утверждении Положения об особенностях расследования несчастных случаев на производстве в отдельных отраслях и организациях, форм документов, соответствующих классификаторов, необходимых для расследования несчастных случаев на производстве"</t>
+        </is>
+      </c>
+      <c r="C326" s="16" t="inlineStr">
+        <is>
+          <t>приложение № 2 к приказу № 223н (форма № 8); п. 25 Положения (приложение № 1 к приказу № 223н)</t>
+        </is>
+      </c>
+      <c r="D326" s="16" t="inlineStr">
+        <is>
+          <t>Протокол опроса пострадавшего при несчастном случае (очевидца несчастного случая, должностного лица)</t>
+        </is>
+      </c>
+      <c r="E326" s="16" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="F326" s="16" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="G326" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H326" s="16" t="inlineStr">
+        <is>
+          <t>Председатель (член) комиссии по расследованию несчастного случая</t>
+        </is>
+      </c>
+      <c r="I326" s="16" t="inlineStr">
+        <is>
+          <t>собственноручная</t>
+        </is>
+      </c>
+      <c r="J326" s="16" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K326" s="16" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L326" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="16" t="inlineStr">
+        <is>
+          <t>Расследование несчастных случаев</t>
+        </is>
+      </c>
+      <c r="B327" s="16" t="inlineStr">
+        <is>
+          <t>Приказ Минтруда России от 20.04.2022 № 223н "Об утверждении Положения об особенностях расследования несчастных случаев на производстве в отдельных отраслях и организациях, форм документов, соответствующих классификаторов, необходимых для расследования несчастных случаев на производстве"</t>
+        </is>
+      </c>
+      <c r="C327" s="16" t="inlineStr">
+        <is>
+          <t>приложение № 2 к приказу № 223н (форма № 8); п. 25 Положения (приложение № 1 к приказу № 223н)</t>
+        </is>
+      </c>
+      <c r="D327" s="16" t="inlineStr">
+        <is>
+          <t>Протокол опроса пострадавшего при несчастном случае (очевидца несчастного случая, должностного лица)</t>
+        </is>
+      </c>
+      <c r="E327" s="16" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="F327" s="16" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="G327" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H327" s="16" t="inlineStr">
+        <is>
+          <t>Опрашиваемое лицо (пострадавший / очевидец / должностное лицо)</t>
+        </is>
+      </c>
+      <c r="I327" s="16" t="inlineStr">
+        <is>
+          <t>собственноручная</t>
+        </is>
+      </c>
+      <c r="J327" s="16" t="inlineStr">
+        <is>
+          <t>Подтверждение (?)</t>
+        </is>
+      </c>
+      <c r="K327" s="16" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L327" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="16" t="inlineStr">
+        <is>
+          <t>Расследование несчастных случаев</t>
+        </is>
+      </c>
+      <c r="B328" s="16" t="inlineStr">
+        <is>
+          <t>Приказ Минтруда России от 20.04.2022 № 223н "Об утверждении Положения об особенностях расследования несчастных случаев на производстве в отдельных отраслях и организациях, форм документов, соответствующих классификаторов, необходимых для расследования несчастных случаев на производстве"</t>
+        </is>
+      </c>
+      <c r="C328" s="16" t="inlineStr">
+        <is>
+          <t>приложение № 2 к приказу № 223н (форма № 9); п. 25 Положения (приложение № 1 к приказу № 223н)</t>
+        </is>
+      </c>
+      <c r="D328" s="16" t="inlineStr">
+        <is>
+          <t>Протокол осмотра места несчастного случая</t>
+        </is>
+      </c>
+      <c r="E328" s="16" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="F328" s="16" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="G328" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H328" s="16" t="inlineStr">
+        <is>
+          <t>Председатель (член) комиссии по расследованию несчастного случая</t>
+        </is>
+      </c>
+      <c r="I328" s="16" t="inlineStr">
+        <is>
+          <t>собственноручная</t>
+        </is>
+      </c>
+      <c r="J328" s="16" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K328" s="16" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L328" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="16" t="inlineStr">
+        <is>
+          <t>Расследование несчастных случаев</t>
+        </is>
+      </c>
+      <c r="B329" s="16" t="inlineStr">
+        <is>
+          <t>Приказ Минтруда России от 20.04.2022 № 223н "Об утверждении Положения об особенностях расследования несчастных случаев на производстве в отдельных отраслях и организациях, форм документов, соответствующих классификаторов, необходимых для расследования несчастных случаев на производстве"</t>
+        </is>
+      </c>
+      <c r="C329" s="16" t="inlineStr">
+        <is>
+          <t>приложение № 2 к приказу № 223н (форма № 9); п. 25 Положения (приложение № 1 к приказу № 223н)</t>
+        </is>
+      </c>
+      <c r="D329" s="16" t="inlineStr">
+        <is>
+          <t>Протокол осмотра места несчастного случая</t>
+        </is>
+      </c>
+      <c r="E329" s="16" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="F329" s="16" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="G329" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H329" s="16" t="inlineStr">
+        <is>
+          <t>Лицо, участвовавшее в осмотре места несчастного случая</t>
+        </is>
+      </c>
+      <c r="I329" s="16" t="inlineStr">
+        <is>
+          <t>собственноручная</t>
+        </is>
+      </c>
+      <c r="J329" s="16" t="inlineStr">
+        <is>
+          <t>Подтверждение (?)</t>
+        </is>
+      </c>
+      <c r="K329" s="16" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L329" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="16" t="inlineStr">
+        <is>
+          <t>Расследование несчастных случаев</t>
+        </is>
+      </c>
+      <c r="B330" s="16" t="inlineStr">
+        <is>
+          <t>Приказ Минтруда России от 20.04.2022 № 223н "Об утверждении Положения об особенностях расследования несчастных случаев на производстве в отдельных отраслях и организациях, форм документов, соответствующих классификаторов, необходимых для расследования несчастных случаев на производстве"</t>
+        </is>
+      </c>
+      <c r="C330" s="16" t="inlineStr">
+        <is>
+          <t>приложение № 2 к приказу № 223н (форма № 10)</t>
+        </is>
+      </c>
+      <c r="D330" s="16" t="inlineStr">
+        <is>
+          <t>Сообщение о последствиях несчастного случая на производстве и принятых мерах</t>
+        </is>
+      </c>
+      <c r="E330" s="16" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="F330" s="16" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="G330" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H330" s="16" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I330" s="16" t="inlineStr">
+        <is>
+          <t>собственноручная</t>
+        </is>
+      </c>
+      <c r="J330" s="16" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K330" s="16" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L330" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="16" t="inlineStr">
+        <is>
+          <t>Расследование несчастных случаев</t>
+        </is>
+      </c>
+      <c r="B331" s="16" t="inlineStr">
+        <is>
+          <t>Приказ Минтруда России от 20.04.2022 № 223н "Об утверждении Положения об особенностях расследования несчастных случаев на производстве в отдельных отраслях и организациях, форм документов, соответствующих классификаторов, необходимых для расследования несчастных случаев на производстве"</t>
+        </is>
+      </c>
+      <c r="C331" s="16" t="inlineStr">
+        <is>
+          <t>приложение № 2 к приказу № 223н (форма № 10)</t>
+        </is>
+      </c>
+      <c r="D331" s="16" t="inlineStr">
+        <is>
+          <t>Сообщение о последствиях несчастного случая на производстве и принятых мерах</t>
+        </is>
+      </c>
+      <c r="E331" s="16" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="F331" s="16" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="G331" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H331" s="16" t="inlineStr">
+        <is>
+          <t>Главный бухгалтер</t>
+        </is>
+      </c>
+      <c r="I331" s="16" t="inlineStr">
+        <is>
+          <t>собственноручная</t>
+        </is>
+      </c>
+      <c r="J331" s="16" t="inlineStr">
+        <is>
+          <t>Подтверждение (?)</t>
+        </is>
+      </c>
+      <c r="K331" s="16" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L331" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="16" t="inlineStr">
+        <is>
+          <t>Расследование несчастных случаев</t>
+        </is>
+      </c>
+      <c r="B332" s="16" t="inlineStr">
+        <is>
+          <t>Приказ Минтруда России от 20.04.2022 № 223н "Об утверждении Положения об особенностях расследования несчастных случаев на производстве в отдельных отраслях и организациях, форм документов, соответствующих классификаторов, необходимых для расследования несчастных случаев на производстве"</t>
+        </is>
+      </c>
+      <c r="C332" s="16" t="inlineStr">
+        <is>
+          <t>приложение № 2 к приказу № 223н (форма № 11)</t>
+        </is>
+      </c>
+      <c r="D332" s="16" t="inlineStr">
+        <is>
+          <t>Журнал регистрации несчастных случаев на производстве</t>
+        </is>
+      </c>
+      <c r="E332" s="16" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="F332" s="16" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="G332" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H332" s="16" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I332" s="16" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J332" s="16" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K332" s="16" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L332" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="16" t="inlineStr">
+        <is>
+          <t>Расследование несчастных случаев</t>
+        </is>
+      </c>
+      <c r="B333" s="16" t="inlineStr">
+        <is>
+          <t>Приказ Минтруда России от 20.04.2022 № 223н "Об утверждении Положения об особенностях расследования несчастных случаев на производстве в отдельных отраслях и организациях, форм документов, соответствующих классификаторов, необходимых для расследования несчастных случаев на производстве"</t>
+        </is>
+      </c>
+      <c r="C333" s="16" t="inlineStr">
+        <is>
+          <t>п. 23 Положения (приложение № 1 к приказу № 223н)</t>
+        </is>
+      </c>
+      <c r="D333" s="16" t="inlineStr">
+        <is>
+          <t>Письменное уведомление об отзыве (замене) члена комиссии или председателя комиссии по расследованию несчастного случая</t>
+        </is>
+      </c>
+      <c r="E333" s="16" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F333" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G333" s="16" t="inlineStr">
+        <is>
+          <t>Письменное уведомление работодателя, образовавшего комиссию, руководителем органа (организации), направившего представителя, об отзыве члена комиссии или председателя и направлении другого представителя</t>
+        </is>
+      </c>
+      <c r="H333" s="16" t="inlineStr">
+        <is>
+          <t>Руководитель органа (организации), направившего члена комиссии</t>
+        </is>
+      </c>
+      <c r="I333" s="16" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J333" s="16" t="inlineStr">
+        <is>
+          <t>Уведомление</t>
+        </is>
+      </c>
+      <c r="K333" s="16" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L333" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="16" t="inlineStr">
+        <is>
+          <t>Расследование несчастных случаев</t>
+        </is>
+      </c>
+      <c r="B334" s="16" t="inlineStr">
+        <is>
+          <t>Приказ Минтруда России от 20.04.2022 № 223н "Об утверждении Положения об особенностях расследования несчастных случаев на производстве в отдельных отраслях и организациях, форм документов, соответствующих классификаторов, необходимых для расследования несчастных случаев на производстве"</t>
+        </is>
+      </c>
+      <c r="C334" s="16" t="inlineStr">
+        <is>
+          <t>п. 23 Положения (приложение № 1 к приказу № 223н)</t>
+        </is>
+      </c>
+      <c r="D334" s="16" t="inlineStr">
+        <is>
+          <t>Документы, подтверждающие замену члена комиссии или председателя комиссии</t>
+        </is>
+      </c>
+      <c r="E334" s="16" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F334" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G334" s="16" t="inlineStr">
+        <is>
+          <t>Документы, подтверждающие замену члена комиссии или председателя комиссии, с указанием причины принятого решения; приобщаются к материалам расследования</t>
+        </is>
+      </c>
+      <c r="H334" s="16" t="inlineStr">
+        <is>
+          <t>Руководитель органа (организации), направившего члена комиссии</t>
+        </is>
+      </c>
+      <c r="I334" s="16" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J334" s="16" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K334" s="16" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L334" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="16" t="inlineStr">
+        <is>
+          <t>Расследование несчастных случаев</t>
+        </is>
+      </c>
+      <c r="B335" s="16" t="inlineStr">
+        <is>
+          <t>Приказ Минтруда России от 20.04.2022 № 223н "Об утверждении Положения об особенностях расследования несчастных случаев на производстве в отдельных отраслях и организациях, форм документов, соответствующих классификаторов, необходимых для расследования несчастных случаев на производстве"</t>
+        </is>
+      </c>
+      <c r="C335" s="16" t="inlineStr">
+        <is>
+          <t>п. 23 Положения (приложение № 1 к приказу № 223н)</t>
+        </is>
+      </c>
+      <c r="D335" s="16" t="inlineStr">
+        <is>
+          <t>Изменения в приказ (распоряжение) об образовании комиссии по расследованию несчастного случая</t>
+        </is>
+      </c>
+      <c r="E335" s="16" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F335" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G335" s="16" t="inlineStr">
+        <is>
+          <t>Изменения в приказ (распоряжение) об образовании комиссии, вносимые работодателем в течение 24 часов после получения письменного уведомления о замене; приобщаются к материалам расследования</t>
+        </is>
+      </c>
+      <c r="H335" s="16" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I335" s="16" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J335" s="16" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K335" s="16" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L335" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="16" t="inlineStr">
+        <is>
+          <t>Расследование несчастных случаев</t>
+        </is>
+      </c>
+      <c r="B336" s="16" t="inlineStr">
+        <is>
+          <t>Приказ Минтруда России от 20.04.2022 № 223н "Об утверждении Положения об особенностях расследования несчастных случаев на производстве в отдельных отраслях и организациях, форм документов, соответствующих классификаторов, необходимых для расследования несчастных случаев на производстве"</t>
+        </is>
+      </c>
+      <c r="C336" s="16" t="inlineStr">
+        <is>
+          <t>п. 24 Положения (приложение № 1 к приказу № 223н)</t>
+        </is>
+      </c>
+      <c r="D336" s="16" t="inlineStr">
+        <is>
+          <t>Заявление пострадавшего или его доверенного лица о расследовании несчастного случая (о котором не было своевременно сообщено работодателю или нетрудоспособность наступила не сразу)</t>
+        </is>
+      </c>
+      <c r="E336" s="16" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F336" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G336" s="16" t="inlineStr">
+        <is>
+          <t>Заявление пострадавшего или его доверенного лица о расследовании несчастного случая, о котором не было своевременно (в течение 24 часов) сообщено работодателю или в результате которого нетрудоспособность наступила не сразу</t>
+        </is>
+      </c>
+      <c r="H336" s="16" t="inlineStr">
+        <is>
+          <t>Пострадавший (доверенное лицо)</t>
+        </is>
+      </c>
+      <c r="I336" s="16" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J336" s="16" t="inlineStr">
+        <is>
+          <t>Заявление</t>
+        </is>
+      </c>
+      <c r="K336" s="16" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L336" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="16" t="inlineStr">
+        <is>
+          <t>Расследование несчастных случаев</t>
+        </is>
+      </c>
+      <c r="B337" s="16" t="inlineStr">
+        <is>
+          <t>Приказ Минтруда России от 20.04.2022 № 223н "Об утверждении Положения об особенностях расследования несчастных случаев на производстве в отдельных отраслях и организациях, форм документов, соответствующих классификаторов, необходимых для расследования несчастных случаев на производстве"</t>
+        </is>
+      </c>
+      <c r="C337" s="16" t="inlineStr">
+        <is>
+          <t>п. 26 Положения (приложение № 1 к приказу № 223н)</t>
+        </is>
+      </c>
+      <c r="D337" s="16" t="inlineStr">
+        <is>
+          <t>Протокол заседания комиссии по расследованию несчастного случая</t>
+        </is>
+      </c>
+      <c r="E337" s="16" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F337" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G337" s="16" t="inlineStr">
+        <is>
+          <t>Протокол заседания комиссии в произвольной форме (заседание может проводиться с использованием средств связи, в том числе видео-конференц-связи); приобщается к материалам расследования</t>
+        </is>
+      </c>
+      <c r="H337" s="16" t="inlineStr">
+        <is>
+          <t>Председатель комиссии по расследованию несчастного случая</t>
+        </is>
+      </c>
+      <c r="I337" s="16" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J337" s="16" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K337" s="16" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L337" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="16" t="inlineStr">
+        <is>
+          <t>Расследование несчастных случаев</t>
+        </is>
+      </c>
+      <c r="B338" s="16" t="inlineStr">
+        <is>
+          <t>Приказ Минтруда России от 20.04.2022 № 223н "Об утверждении Положения об особенностях расследования несчастных случаев на производстве в отдельных отраслях и организациях, форм документов, соответствующих классификаторов, необходимых для расследования несчастных случаев на производстве"</t>
+        </is>
+      </c>
+      <c r="C338" s="16" t="inlineStr">
+        <is>
+          <t>п. 26 Положения (приложение № 1 к приказу № 223н)</t>
+        </is>
+      </c>
+      <c r="D338" s="16" t="inlineStr">
+        <is>
+          <t>Протокол заседания комиссии по расследованию несчастного случая</t>
+        </is>
+      </c>
+      <c r="E338" s="16" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F338" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G338" s="16" t="inlineStr">
+        <is>
+          <t>Протокол заседания комиссии в произвольной форме (заседание может проводиться с использованием средств связи, в том числе видео-конференц-связи); приобщается к материалам расследования</t>
+        </is>
+      </c>
+      <c r="H338" s="16" t="inlineStr">
+        <is>
+          <t>Член комиссии по расследованию несчастного случая</t>
+        </is>
+      </c>
+      <c r="I338" s="16" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J338" s="16" t="inlineStr">
+        <is>
+          <t>Подтверждение (?)</t>
+        </is>
+      </c>
+      <c r="K338" s="16" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L338" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="16" t="inlineStr">
+        <is>
+          <t>Расследование несчастных случаев</t>
+        </is>
+      </c>
+      <c r="B339" s="16" t="inlineStr">
+        <is>
+          <t>Приказ Минтруда России от 20.04.2022 № 223н "Об утверждении Положения об особенностях расследования несчастных случаев на производстве в отдельных отраслях и организациях, форм документов, соответствующих классификаторов, необходимых для расследования несчастных случаев на производстве"</t>
+        </is>
+      </c>
+      <c r="C339" s="16" t="inlineStr">
+        <is>
+          <t>п. 30–31 Положения (приложение № 1 к приказу № 223н)</t>
+        </is>
+      </c>
+      <c r="D339" s="16" t="inlineStr">
+        <is>
+          <t>Протокол заседания комиссии по расследованию несчастного случая (при разногласиях или отказе от подписания актов)</t>
+        </is>
+      </c>
+      <c r="E339" s="16" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F339" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G339" s="16" t="inlineStr">
+        <is>
+          <t>Протокол в произвольной форме: при разногласиях — решение большинством голосов; при отказе членов комиссии (включая председателя) от подписания актов — с указанием причины отказа; копия направляется в соответствующую государственную инспекцию труда / орган (организацию)</t>
+        </is>
+      </c>
+      <c r="H339" s="16" t="inlineStr">
+        <is>
+          <t>Председатель комиссии по расследованию несчастного случая</t>
+        </is>
+      </c>
+      <c r="I339" s="16" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J339" s="16" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K339" s="16" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L339" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="16" t="inlineStr">
+        <is>
+          <t>Расследование несчастных случаев</t>
+        </is>
+      </c>
+      <c r="B340" s="16" t="inlineStr">
+        <is>
+          <t>Приказ Минтруда России от 20.04.2022 № 223н "Об утверждении Положения об особенностях расследования несчастных случаев на производстве в отдельных отраслях и организациях, форм документов, соответствующих классификаторов, необходимых для расследования несчастных случаев на производстве"</t>
+        </is>
+      </c>
+      <c r="C340" s="16" t="inlineStr">
+        <is>
+          <t>п. 30–31 Положения (приложение № 1 к приказу № 223н)</t>
+        </is>
+      </c>
+      <c r="D340" s="16" t="inlineStr">
+        <is>
+          <t>Протокол заседания комиссии по расследованию несчастного случая (при разногласиях или отказе от подписания актов)</t>
+        </is>
+      </c>
+      <c r="E340" s="16" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F340" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G340" s="16" t="inlineStr">
+        <is>
+          <t>Протокол в произвольной форме: при разногласиях — решение большинством голосов; при отказе членов комиссии (включая председателя) от подписания актов — с указанием причины отказа; копия направляется в соответствующую государственную инспекцию труда / орган (организацию)</t>
+        </is>
+      </c>
+      <c r="H340" s="16" t="inlineStr">
+        <is>
+          <t>Член комиссии по расследованию несчастного случая</t>
+        </is>
+      </c>
+      <c r="I340" s="16" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J340" s="16" t="inlineStr">
+        <is>
+          <t>Подтверждение (?)</t>
+        </is>
+      </c>
+      <c r="K340" s="16" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L340" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="16" t="inlineStr">
+        <is>
+          <t>Расследование несчастных случаев</t>
+        </is>
+      </c>
+      <c r="B341" s="16" t="inlineStr">
+        <is>
+          <t>Приказ Минтруда России от 20.04.2022 № 223н "Об утверждении Положения об особенностях расследования несчастных случаев на производстве в отдельных отраслях и организациях, форм документов, соответствующих классификаторов, необходимых для расследования несчастных случаев на производстве"</t>
+        </is>
+      </c>
+      <c r="C341" s="16" t="inlineStr">
+        <is>
+          <t>п. 30 Положения (приложение № 1 к приказу № 223н)</t>
+        </is>
+      </c>
+      <c r="D341" s="16" t="inlineStr">
+        <is>
+          <t>Аргументированное особое мнение члена комиссии (включая председателя комиссии)</t>
+        </is>
+      </c>
+      <c r="E341" s="16" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F341" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G341" s="16" t="inlineStr">
+        <is>
+          <t>Аргументированное особое мнение члена комиссии (включая председателя), не согласного с принятым решением; приобщается к материалам расследования</t>
+        </is>
+      </c>
+      <c r="H341" s="16" t="inlineStr">
+        <is>
+          <t>Член комиссии (включая председателя комиссии) по расследованию несчастного случая</t>
+        </is>
+      </c>
+      <c r="I341" s="16" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J341" s="16" t="inlineStr">
+        <is>
+          <t>Подтверждение (?)</t>
+        </is>
+      </c>
+      <c r="K341" s="16" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L341" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="16" t="inlineStr">
+        <is>
+          <t>Расследование несчастных случаев</t>
+        </is>
+      </c>
+      <c r="B342" s="16" t="inlineStr">
+        <is>
+          <t>Приказ Минтруда России от 20.04.2022 № 223н "Об утверждении Положения об особенностях расследования несчастных случаев на производстве в отдельных отраслях и организациях, форм документов, соответствующих классификаторов, необходимых для расследования несчастных случаев на производстве"</t>
+        </is>
+      </c>
+      <c r="C342" s="16" t="inlineStr">
+        <is>
+          <t>п. 25 Положения (приложение № 1 к приказу № 223н)</t>
+        </is>
+      </c>
+      <c r="D342" s="16" t="inlineStr">
+        <is>
+          <t>Мотивированное требование члена комиссии о направлении запроса в федеральный орган исполнительной власти (его территориальный орган)</t>
+        </is>
+      </c>
+      <c r="E342" s="16" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F342" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G342" s="16" t="inlineStr">
+        <is>
+          <t>Мотивированное требование члена комиссии о направлении запроса в целях получения заключения федерального органа исполнительной власти, осуществляющего государственный контроль (надзор) в установленной сфере деятельности (его территориального органа)</t>
+        </is>
+      </c>
+      <c r="H342" s="16" t="inlineStr">
+        <is>
+          <t>Член комиссии по расследованию несчастного случая</t>
+        </is>
+      </c>
+      <c r="I342" s="16" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J342" s="16" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K342" s="16" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L342" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="16" t="inlineStr">
+        <is>
+          <t>Расследование несчастных случаев</t>
+        </is>
+      </c>
+      <c r="B343" s="16" t="inlineStr">
+        <is>
+          <t>Приказ Минтруда России от 20.04.2022 № 223н "Об утверждении Положения об особенностях расследования несчастных случаев на производстве в отдельных отраслях и организациях, форм документов, соответствующих классификаторов, необходимых для расследования несчастных случаев на производстве"</t>
+        </is>
+      </c>
+      <c r="C343" s="16" t="inlineStr">
+        <is>
+          <t>п. 25 Положения (приложение № 1 к приказу № 223н)</t>
+        </is>
+      </c>
+      <c r="D343" s="16" t="inlineStr">
+        <is>
+          <t>Запрос председателя комиссии в федеральный орган исполнительной власти (его территориальный орган) о выдаче заключения</t>
+        </is>
+      </c>
+      <c r="E343" s="16" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F343" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G343" s="16" t="inlineStr">
+        <is>
+          <t>Запрос председателя комиссии (в установленных случаях — государственного инспектора труда) в соответствующий федеральный орган исполнительной власти (его территориальный орган) в целях получения заключения, в компетенции которого находится запрашиваемое исследование</t>
+        </is>
+      </c>
+      <c r="H343" s="16" t="inlineStr">
+        <is>
+          <t>Председатель комиссии по расследованию несчастного случая</t>
+        </is>
+      </c>
+      <c r="I343" s="16" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J343" s="16" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K343" s="16" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L343" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="16" t="inlineStr">
+        <is>
+          <t>Расследование несчастных случаев</t>
+        </is>
+      </c>
+      <c r="B344" s="16" t="inlineStr">
+        <is>
+          <t>Приказ Минтруда России от 20.04.2022 № 223н "Об утверждении Положения об особенностях расследования несчастных случаев на производстве в отдельных отраслях и организациях, форм документов, соответствующих классификаторов, необходимых для расследования несчастных случаев на производстве"</t>
+        </is>
+      </c>
+      <c r="C344" s="16" t="inlineStr">
+        <is>
+          <t>п. 27 Положения (приложение № 1 к приказу № 223н)</t>
+        </is>
+      </c>
+      <c r="D344" s="16" t="inlineStr">
+        <is>
+          <t>Экспертное заключение о причине смерти пострадавшего и (или) его нахождении в момент несчастного случая в состоянии алкогольного, наркотического или иного токсического опьянения</t>
+        </is>
+      </c>
+      <c r="E344" s="16" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F344" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G344" s="16" t="inlineStr">
+        <is>
+          <t>Экспертное заключение о причине смерти пострадавшего и его нахождении в момент несчастного случая в состоянии алкогольного, наркотического или иного токсического опьянения; включается в материалы расследования случая гибели работника; обеспечивается работодателем за счет собственных средств по требованию комиссии</t>
+        </is>
+      </c>
+      <c r="H344" s="16" t="inlineStr">
+        <is>
+          <t>Эксперт (специалист)</t>
+        </is>
+      </c>
+      <c r="I344" s="16" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J344" s="16" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K344" s="16" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L344" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="16" t="inlineStr">
+        <is>
+          <t>Расследование несчастных случаев</t>
+        </is>
+      </c>
+      <c r="B345" s="16" t="inlineStr">
+        <is>
+          <t>Приказ Минтруда России от 20.04.2022 № 223н "Об утверждении Положения об особенностях расследования несчастных случаев на производстве в отдельных отраслях и организациях, форм документов, соответствующих классификаторов, необходимых для расследования несчастных случаев на производстве"</t>
+        </is>
+      </c>
+      <c r="C345" s="16" t="inlineStr">
+        <is>
+          <t>п. 21.2 Положения (приложение № 1 к приказу № 223н)</t>
+        </is>
+      </c>
+      <c r="D345" s="16" t="inlineStr">
+        <is>
+          <t>Документы, подтверждающие причинно-следственную связь между гибелью (травмой) работника и исполнением им трудовых обязанностей (при оформлении акта формы Н-1ЧС)</t>
+        </is>
+      </c>
+      <c r="E345" s="16" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F345" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G345" s="16" t="inlineStr">
+        <is>
+          <t>Документы, подтверждающие причинно-следственную связь между гибелью (травмой) работника и исполнением им трудовых обязанностей; направляются вместе с актами формы Н-1ЧС в исполнительный орган страховщика</t>
+        </is>
+      </c>
+      <c r="H345" s="16" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I345" s="16" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J345" s="16" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K345" s="16" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L345" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:L195"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/presentations/Analiz_SUOT_podpisanty_skvoznaya.xlsx
+++ b/presentations/Analiz_SUOT_podpisanty_skvoznaya.xlsx
@@ -9,7 +9,7 @@
     <sheet name="Подписанты СОУТ сквозная" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Подписанты СОУТ сквозная'!$A$1:$L$195</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Подписанты СОУТ сквозная'!$A$1:$L$299</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -560,7 +560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L345"/>
+  <dimension ref="A1:L324"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8"/>
   <cols>
     <col width="10" customWidth="1" style="14" min="1" max="1"/>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="D65" s="13" t="inlineStr">
         <is>
-          <t>Мотивированное особое мнение члена комиссии по проведению специальной оценки условий труда</t>
+          <t>Мотивированное особое мнение члена комиссии</t>
         </is>
       </c>
       <c r="E65" s="13" t="inlineStr">
@@ -17311,2783 +17311,2783 @@
         </is>
       </c>
     </row>
-    <row r="271" customFormat="1" s="14">
-      <c r="A271" s="16" t="inlineStr">
+    <row r="271" ht="55.2" customFormat="1" customHeight="1" s="14">
+      <c r="A271" s="15" t="inlineStr">
         <is>
           <t>Расследование профзаболеваний</t>
         </is>
       </c>
-      <c r="B271" s="16" t="inlineStr">
+      <c r="B271" s="15" t="inlineStr">
         <is>
           <t>Постановление Правительства РФ от 05.07.2022 № 1206 "О порядке расследования и учета случаев профессиональных заболеваний работников"</t>
         </is>
       </c>
-      <c r="C271" s="16" t="inlineStr">
-        <is>
-          <t>п. 4, 9 Правил (постановление № 1206)</t>
-        </is>
-      </c>
-      <c r="D271" s="16" t="inlineStr">
-        <is>
-          <t>Сведения, необходимые для составления санитарно-гигиенической характеристики условий труда работника</t>
-        </is>
-      </c>
-      <c r="E271" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="F271" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G271" s="16" t="inlineStr">
-        <is>
-          <t>Сведения, предусмотренные формой и порядком составления санитарно-гигиенической характеристики условий труда работника (направляются работодателем в орган государственного санитарно-эпидемиологического контроля (надзора))</t>
-        </is>
-      </c>
-      <c r="H271" s="16" t="inlineStr">
+      <c r="C271" s="15" t="inlineStr">
+        <is>
+          <t>п. 5 Правил (постановление № 1206)</t>
+        </is>
+      </c>
+      <c r="D271" s="15" t="inlineStr">
+        <is>
+          <t>Направление на экспертизу связи заболевания с профессией</t>
+        </is>
+      </c>
+      <c r="E271" s="15" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F271" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G271" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H271" s="15" t="inlineStr">
+        <is>
+          <t>Медицинская организация</t>
+        </is>
+      </c>
+      <c r="I271" s="15" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J271" s="15" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K271" s="15" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L271" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="272" ht="55.2" customFormat="1" customHeight="1" s="14">
+      <c r="A272" s="15" t="inlineStr">
+        <is>
+          <t>Расследование профзаболеваний</t>
+        </is>
+      </c>
+      <c r="B272" s="15" t="inlineStr">
+        <is>
+          <t>Постановление Правительства РФ от 05.07.2022 № 1206 "О порядке расследования и учета случаев профессиональных заболеваний работников"</t>
+        </is>
+      </c>
+      <c r="C272" s="15" t="inlineStr">
+        <is>
+          <t>п. 7 Правил (постановление № 1206)</t>
+        </is>
+      </c>
+      <c r="D272" s="15" t="inlineStr">
+        <is>
+          <t>Возражения к санитарно-гигиенической характеристике условий труда работника</t>
+        </is>
+      </c>
+      <c r="E272" s="15" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F272" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G272" s="15" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="H272" s="15" t="inlineStr">
         <is>
           <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
         </is>
       </c>
-      <c r="I271" s="16" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J271" s="16" t="inlineStr">
+      <c r="I272" s="15" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J272" s="15" t="inlineStr">
+        <is>
+          <t>Заявление</t>
+        </is>
+      </c>
+      <c r="K272" s="15" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L272" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="273" ht="55.2" customFormat="1" customHeight="1" s="14">
+      <c r="A273" s="15" t="inlineStr">
+        <is>
+          <t>Расследование профзаболеваний</t>
+        </is>
+      </c>
+      <c r="B273" s="15" t="inlineStr">
+        <is>
+          <t>Постановление Правительства РФ от 05.07.2022 № 1206 "О порядке расследования и учета случаев профессиональных заболеваний работников"</t>
+        </is>
+      </c>
+      <c r="C273" s="15" t="inlineStr">
+        <is>
+          <t>п. 7 Правил (постановление № 1206)</t>
+        </is>
+      </c>
+      <c r="D273" s="15" t="inlineStr">
+        <is>
+          <t>Возражения к санитарно-гигиенической характеристике условий труда работника</t>
+        </is>
+      </c>
+      <c r="E273" s="15" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F273" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G273" s="15" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="H273" s="15" t="inlineStr">
+        <is>
+          <t>Работник</t>
+        </is>
+      </c>
+      <c r="I273" s="15" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J273" s="15" t="inlineStr">
+        <is>
+          <t>Заявление</t>
+        </is>
+      </c>
+      <c r="K273" s="15" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L273" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="274" ht="55.2" customFormat="1" customHeight="1" s="14">
+      <c r="A274" s="15" t="inlineStr">
+        <is>
+          <t>Расследование профзаболеваний</t>
+        </is>
+      </c>
+      <c r="B274" s="15" t="inlineStr">
+        <is>
+          <t>Постановление Правительства РФ от 05.07.2022 № 1206 "О порядке расследования и учета случаев профессиональных заболеваний работников"</t>
+        </is>
+      </c>
+      <c r="C274" s="15" t="inlineStr">
+        <is>
+          <t>п. 8 Правил (постановление № 1206)</t>
+        </is>
+      </c>
+      <c r="D274" s="15" t="inlineStr">
+        <is>
+          <t>Извещение об установлении предварительного диагноза - хроническое профессиональное заболевание</t>
+        </is>
+      </c>
+      <c r="E274" s="15" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="F274" s="15" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="G274" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H274" s="15" t="inlineStr">
+        <is>
+          <t>Медицинская организация</t>
+        </is>
+      </c>
+      <c r="I274" s="15" t="inlineStr">
+        <is>
+          <t>собственноручная или УКЭП</t>
+        </is>
+      </c>
+      <c r="J274" s="15" t="inlineStr">
         <is>
           <t>Утверждение</t>
         </is>
       </c>
-      <c r="K271" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="L271" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="272" customFormat="1" s="14">
-      <c r="A272" s="16" t="inlineStr">
+      <c r="K274" s="15" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="L274" s="15" t="inlineStr">
+        <is>
+          <t>Печать организации</t>
+        </is>
+      </c>
+    </row>
+    <row r="275" ht="55.2" customFormat="1" customHeight="1" s="14">
+      <c r="A275" s="15" t="inlineStr">
         <is>
           <t>Расследование профзаболеваний</t>
         </is>
       </c>
-      <c r="B272" s="16" t="inlineStr">
+      <c r="B275" s="15" t="inlineStr">
         <is>
           <t>Постановление Правительства РФ от 05.07.2022 № 1206 "О порядке расследования и учета случаев профессиональных заболеваний работников"</t>
         </is>
       </c>
-      <c r="C272" s="16" t="inlineStr">
-        <is>
-          <t>п. 7 Правил (постановление № 1206)</t>
-        </is>
-      </c>
-      <c r="D272" s="16" t="inlineStr">
-        <is>
-          <t>Возражения к санитарно-гигиенической характеристике условий труда работника</t>
-        </is>
-      </c>
-      <c r="E272" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="F272" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G272" s="16" t="inlineStr">
-        <is>
-          <t>Письменные возражения к содержанию санитарно-гигиенической характеристики условий труда работника (прилагаются к характеристике)</t>
-        </is>
-      </c>
-      <c r="H272" s="16" t="inlineStr">
+      <c r="C275" s="15" t="inlineStr">
+        <is>
+          <t>п. 11, 12 Правил (постановление № 1206)</t>
+        </is>
+      </c>
+      <c r="D275" s="15" t="inlineStr">
+        <is>
+          <t>Медицинское заключение о наличии или об отсутствии профессионального заболевания</t>
+        </is>
+      </c>
+      <c r="E275" s="15" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="F275" s="15" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="G275" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H275" s="15" t="inlineStr">
+        <is>
+          <t>Председатель врачебной комиссии</t>
+        </is>
+      </c>
+      <c r="I275" s="15" t="inlineStr">
+        <is>
+          <t>собственноручная или УКЭП</t>
+        </is>
+      </c>
+      <c r="J275" s="15" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K275" s="15" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="L275" s="15" t="inlineStr">
+        <is>
+          <t>Печать организации</t>
+        </is>
+      </c>
+    </row>
+    <row r="276" ht="55.2" customFormat="1" customHeight="1" s="14">
+      <c r="A276" s="15" t="inlineStr">
+        <is>
+          <t>Расследование профзаболеваний</t>
+        </is>
+      </c>
+      <c r="B276" s="15" t="inlineStr">
+        <is>
+          <t>Постановление Правительства РФ от 05.07.2022 № 1206 "О порядке расследования и учета случаев профессиональных заболеваний работников"</t>
+        </is>
+      </c>
+      <c r="C276" s="15" t="inlineStr">
+        <is>
+          <t>п. 11, 12 Правил (постановление № 1206)</t>
+        </is>
+      </c>
+      <c r="D276" s="15" t="inlineStr">
+        <is>
+          <t>Медицинское заключение о наличии или об отсутствии профессионального заболевания</t>
+        </is>
+      </c>
+      <c r="E276" s="15" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="F276" s="15" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="G276" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H276" s="15" t="inlineStr">
+        <is>
+          <t>Член врачебной комиссии</t>
+        </is>
+      </c>
+      <c r="I276" s="15" t="inlineStr">
+        <is>
+          <t>собственноручная или УКЭП</t>
+        </is>
+      </c>
+      <c r="J276" s="15" t="inlineStr">
+        <is>
+          <t>Подтверждение (?)</t>
+        </is>
+      </c>
+      <c r="K276" s="15" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="L276" s="15" t="inlineStr">
+        <is>
+          <t>Печать организации</t>
+        </is>
+      </c>
+    </row>
+    <row r="277" ht="55.2" customFormat="1" customHeight="1" s="14">
+      <c r="A277" s="15" t="inlineStr">
+        <is>
+          <t>Расследование профзаболеваний</t>
+        </is>
+      </c>
+      <c r="B277" s="15" t="inlineStr">
+        <is>
+          <t>Постановление Правительства РФ от 05.07.2022 № 1206 "О порядке расследования и учета случаев профессиональных заболеваний работников"</t>
+        </is>
+      </c>
+      <c r="C277" s="15" t="inlineStr">
+        <is>
+          <t>п. 12 Правил (постановление № 1206)</t>
+        </is>
+      </c>
+      <c r="D277" s="15" t="inlineStr">
+        <is>
+          <t>Медицинское заключение о наличии или об отсутствии профессионального заболевания</t>
+        </is>
+      </c>
+      <c r="E277" s="15" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="F277" s="15" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="G277" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H277" s="15" t="inlineStr">
+        <is>
+          <t>Работник</t>
+        </is>
+      </c>
+      <c r="I277" s="15" t="inlineStr">
+        <is>
+          <t>собственноручная</t>
+        </is>
+      </c>
+      <c r="J277" s="15" t="inlineStr">
+        <is>
+          <t>Ознакомление</t>
+        </is>
+      </c>
+      <c r="K277" s="15" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="L277" s="15" t="inlineStr">
+        <is>
+          <t>Выдается под расписку</t>
+        </is>
+      </c>
+    </row>
+    <row r="278" ht="69" customFormat="1" customHeight="1" s="14">
+      <c r="A278" s="15" t="inlineStr">
+        <is>
+          <t>Расследование профзаболеваний</t>
+        </is>
+      </c>
+      <c r="B278" s="15" t="inlineStr">
+        <is>
+          <t>Постановление Правительства РФ от 05.07.2022 № 1206 "О порядке расследования и учета случаев профессиональных заболеваний работников"</t>
+        </is>
+      </c>
+      <c r="C278" s="15" t="inlineStr">
+        <is>
+          <t>п. 11, 14 Правил (постановление № 1206)</t>
+        </is>
+      </c>
+      <c r="D278" s="15" t="inlineStr">
+        <is>
+          <t>Извещение об установлении заключительного диагноза - острое профессиональное заболевание или хроническое профессиональное заболевание, его уточнении или отмене</t>
+        </is>
+      </c>
+      <c r="E278" s="15" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="F278" s="15" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="G278" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H278" s="15" t="inlineStr">
+        <is>
+          <t>Центр профессиональной патологии</t>
+        </is>
+      </c>
+      <c r="I278" s="15" t="inlineStr">
+        <is>
+          <t>собственноручная или УКЭП</t>
+        </is>
+      </c>
+      <c r="J278" s="15" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K278" s="15" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="L278" s="15" t="inlineStr">
+        <is>
+          <t>Печать организации</t>
+        </is>
+      </c>
+    </row>
+    <row r="279" ht="55.2" customFormat="1" customHeight="1" s="14">
+      <c r="A279" s="15" t="inlineStr">
+        <is>
+          <t>Расследование профзаболеваний</t>
+        </is>
+      </c>
+      <c r="B279" s="15" t="inlineStr">
+        <is>
+          <t>Постановление Правительства РФ от 05.07.2022 № 1206 "О порядке расследования и учета случаев профессиональных заболеваний работников"</t>
+        </is>
+      </c>
+      <c r="C279" s="15" t="inlineStr">
+        <is>
+          <t>п. 13 Правил (постановление № 1206)</t>
+        </is>
+      </c>
+      <c r="D279" s="15" t="inlineStr">
+        <is>
+          <t>Заявление о проведении экспертизы связи заболевания с профессией</t>
+        </is>
+      </c>
+      <c r="E279" s="15" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F279" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G279" s="15" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="H279" s="15" t="inlineStr">
         <is>
           <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
         </is>
       </c>
-      <c r="I272" s="16" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J272" s="16" t="inlineStr">
+      <c r="I279" s="15" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J279" s="15" t="inlineStr">
+        <is>
+          <t>Заявление</t>
+        </is>
+      </c>
+      <c r="K279" s="15" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L279" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="280" ht="55.2" customFormat="1" customHeight="1" s="14">
+      <c r="A280" s="15" t="inlineStr">
+        <is>
+          <t>Расследование профзаболеваний</t>
+        </is>
+      </c>
+      <c r="B280" s="15" t="inlineStr">
+        <is>
+          <t>Постановление Правительства РФ от 05.07.2022 № 1206 "О порядке расследования и учета случаев профессиональных заболеваний работников"</t>
+        </is>
+      </c>
+      <c r="C280" s="15" t="inlineStr">
+        <is>
+          <t>п. 13 Правил (постановление № 1206)</t>
+        </is>
+      </c>
+      <c r="D280" s="15" t="inlineStr">
+        <is>
+          <t>Заявление о проведении экспертизы связи заболевания с профессией (в целях изменения или отмены диагноза профессионального заболевания)</t>
+        </is>
+      </c>
+      <c r="E280" s="15" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F280" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G280" s="15" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="H280" s="15" t="inlineStr">
+        <is>
+          <t>Работник</t>
+        </is>
+      </c>
+      <c r="I280" s="15" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J280" s="15" t="inlineStr">
+        <is>
+          <t>Заявление</t>
+        </is>
+      </c>
+      <c r="K280" s="15" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L280" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="281" ht="55.2" customFormat="1" customHeight="1" s="14">
+      <c r="A281" s="15" t="inlineStr">
+        <is>
+          <t>Расследование профзаболеваний</t>
+        </is>
+      </c>
+      <c r="B281" s="15" t="inlineStr">
+        <is>
+          <t>Постановление Правительства РФ от 05.07.2022 № 1206 "О порядке расследования и учета случаев профессиональных заболеваний работников"</t>
+        </is>
+      </c>
+      <c r="C281" s="15" t="inlineStr">
+        <is>
+          <t>п. 13 Правил (постановление № 1206)</t>
+        </is>
+      </c>
+      <c r="D281" s="15" t="inlineStr">
+        <is>
+          <t>Заявление о проведении экспертизы связи заболевания с профессией (в целях изменения или отмены диагноза профессионального заболевания)</t>
+        </is>
+      </c>
+      <c r="E281" s="15" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F281" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G281" s="15" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="H281" s="15" t="inlineStr">
+        <is>
+          <t>Медицинская организация</t>
+        </is>
+      </c>
+      <c r="I281" s="15" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J281" s="15" t="inlineStr">
+        <is>
+          <t>Заявление</t>
+        </is>
+      </c>
+      <c r="K281" s="15" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L281" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="282" ht="55.2" customFormat="1" customHeight="1" s="14">
+      <c r="A282" s="15" t="inlineStr">
+        <is>
+          <t>Расследование профзаболеваний</t>
+        </is>
+      </c>
+      <c r="B282" s="15" t="inlineStr">
+        <is>
+          <t>Постановление Правительства РФ от 05.07.2022 № 1206 "О порядке расследования и учета случаев профессиональных заболеваний работников"</t>
+        </is>
+      </c>
+      <c r="C282" s="15" t="inlineStr">
+        <is>
+          <t>п. 15, 23 «а» Правил (постановление № 1206)</t>
+        </is>
+      </c>
+      <c r="D282" s="15" t="inlineStr">
+        <is>
+          <t>Приказ (распоряжение) о создании комиссии по расследованию случая профессионального заболевания</t>
+        </is>
+      </c>
+      <c r="E282" s="15" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F282" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G282" s="15" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="H282" s="15" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I282" s="15" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J282" s="15" t="inlineStr">
         <is>
           <t>Утверждение</t>
         </is>
       </c>
-      <c r="K272" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="L272" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" s="16" t="inlineStr">
+      <c r="K282" s="15" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L282" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="283" ht="55.2" customFormat="1" customHeight="1" s="14">
+      <c r="A283" s="15" t="inlineStr">
         <is>
           <t>Расследование профзаболеваний</t>
         </is>
       </c>
-      <c r="B273" s="16" t="inlineStr">
+      <c r="B283" s="15" t="inlineStr">
         <is>
           <t>Постановление Правительства РФ от 05.07.2022 № 1206 "О порядке расследования и учета случаев профессиональных заболеваний работников"</t>
         </is>
       </c>
-      <c r="C273" s="16" t="inlineStr">
-        <is>
-          <t>п. 7 Правил (постановление № 1206)</t>
-        </is>
-      </c>
-      <c r="D273" s="16" t="inlineStr">
-        <is>
-          <t>Возражения к санитарно-гигиенической характеристике условий труда работника</t>
-        </is>
-      </c>
-      <c r="E273" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="F273" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G273" s="16" t="inlineStr">
-        <is>
-          <t>Письменные возражения к содержанию санитарно-гигиенической характеристики условий труда работника (прилагаются к характеристике)</t>
-        </is>
-      </c>
-      <c r="H273" s="16" t="inlineStr">
-        <is>
-          <t>Работник (его представитель)</t>
-        </is>
-      </c>
-      <c r="I273" s="16" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J273" s="16" t="inlineStr">
+      <c r="C283" s="15" t="inlineStr">
+        <is>
+          <t>п. 22, 23 «ж» Правил (постановление № 1206)</t>
+        </is>
+      </c>
+      <c r="D283" s="15" t="inlineStr">
+        <is>
+          <t>Протокол опроса работника, иных лиц</t>
+        </is>
+      </c>
+      <c r="E283" s="15" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F283" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G283" s="15" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="H283" s="15" t="inlineStr">
+        <is>
+          <t>Член комиссии по расследованию случая профессионального заболевания</t>
+        </is>
+      </c>
+      <c r="I283" s="15" t="inlineStr">
+        <is>
+          <t>собственноручная или ЭП</t>
+        </is>
+      </c>
+      <c r="J283" s="15" t="inlineStr">
         <is>
           <t>Утверждение</t>
         </is>
       </c>
-      <c r="K273" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="L273" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" s="16" t="inlineStr">
+      <c r="K283" s="15" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L283" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="284" ht="55.2" customFormat="1" customHeight="1" s="14">
+      <c r="A284" s="15" t="inlineStr">
         <is>
           <t>Расследование профзаболеваний</t>
         </is>
       </c>
-      <c r="B274" s="16" t="inlineStr">
+      <c r="B284" s="15" t="inlineStr">
         <is>
           <t>Постановление Правительства РФ от 05.07.2022 № 1206 "О порядке расследования и учета случаев профессиональных заболеваний работников"</t>
         </is>
       </c>
-      <c r="C274" s="16" t="inlineStr">
-        <is>
-          <t>п. 8 Правил (постановление № 1206)</t>
-        </is>
-      </c>
-      <c r="D274" s="16" t="inlineStr">
-        <is>
-          <t>Извещение об установлении предварительного диагноза - хроническое профессиональное заболевание</t>
-        </is>
-      </c>
-      <c r="E274" s="16" t="inlineStr">
+      <c r="C284" s="15" t="inlineStr">
+        <is>
+          <t>п. 22, 23 «ж» Правил (постановление № 1206)</t>
+        </is>
+      </c>
+      <c r="D284" s="15" t="inlineStr">
+        <is>
+          <t>Протокол опроса работника, иных лиц</t>
+        </is>
+      </c>
+      <c r="E284" s="15" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F284" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G284" s="15" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="H284" s="15" t="inlineStr">
+        <is>
+          <t>Работник</t>
+        </is>
+      </c>
+      <c r="I284" s="15" t="inlineStr">
+        <is>
+          <t>собственноручная или ЭП</t>
+        </is>
+      </c>
+      <c r="J284" s="15" t="inlineStr">
+        <is>
+          <t>Подтверждение (?)</t>
+        </is>
+      </c>
+      <c r="K284" s="15" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L284" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="285" ht="69" customFormat="1" customHeight="1" s="14">
+      <c r="A285" s="15" t="inlineStr">
+        <is>
+          <t>Расследование профзаболеваний</t>
+        </is>
+      </c>
+      <c r="B285" s="15" t="inlineStr">
+        <is>
+          <t>Постановление Правительства РФ от 05.07.2022 № 1206 "О порядке расследования и учета случаев профессиональных заболеваний работников"</t>
+        </is>
+      </c>
+      <c r="C285" s="15" t="inlineStr">
+        <is>
+          <t>п. 25, 31 Правил (постановление № 1206)</t>
+        </is>
+      </c>
+      <c r="D285" s="15" t="inlineStr">
+        <is>
+          <t>Мотивированное мнение выборного органа первичной профсоюзной организации (иного представительного органа работников)</t>
+        </is>
+      </c>
+      <c r="E285" s="15" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F285" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G285" s="15" t="inlineStr">
+        <is>
+          <t>Мотивированное мнение о степени вины работника (в процентах) при установлении факта грубой неосторожности работника, содействовавшей возникновению или увеличению вреда, причиненного его здоровью</t>
+        </is>
+      </c>
+      <c r="H285" s="15" t="inlineStr">
+        <is>
+          <t>Выборный орган первичной профсоюзной организации или иного представительного органа работников</t>
+        </is>
+      </c>
+      <c r="I285" s="15" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J285" s="15" t="inlineStr">
+        <is>
+          <t>Согласование</t>
+        </is>
+      </c>
+      <c r="K285" s="15" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L285" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="286" ht="55.2" customFormat="1" customHeight="1" s="14">
+      <c r="A286" s="15" t="inlineStr">
+        <is>
+          <t>Расследование профзаболеваний</t>
+        </is>
+      </c>
+      <c r="B286" s="15" t="inlineStr">
+        <is>
+          <t>Постановление Правительства РФ от 05.07.2022 № 1206 "О порядке расследования и учета случаев профессиональных заболеваний работников"</t>
+        </is>
+      </c>
+      <c r="C286" s="15" t="inlineStr">
+        <is>
+          <t>п. 26 Правил (постановление № 1206)</t>
+        </is>
+      </c>
+      <c r="D286" s="15" t="inlineStr">
+        <is>
+          <t>Протокол заседания комиссии по расследованию случая профессионального заболевания</t>
+        </is>
+      </c>
+      <c r="E286" s="15" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F286" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G286" s="15" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="H286" s="15" t="inlineStr">
+        <is>
+          <t>Председатель комиссии по расследованию случая профессионального заболевания</t>
+        </is>
+      </c>
+      <c r="I286" s="15" t="inlineStr">
+        <is>
+          <t>собственноручная или ЭП</t>
+        </is>
+      </c>
+      <c r="J286" s="15" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K286" s="15" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L286" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="287" ht="55.2" customFormat="1" customHeight="1" s="14">
+      <c r="A287" s="15" t="inlineStr">
+        <is>
+          <t>Расследование профзаболеваний</t>
+        </is>
+      </c>
+      <c r="B287" s="15" t="inlineStr">
+        <is>
+          <t>Постановление Правительства РФ от 05.07.2022 № 1206 "О порядке расследования и учета случаев профессиональных заболеваний работников"</t>
+        </is>
+      </c>
+      <c r="C287" s="15" t="inlineStr">
+        <is>
+          <t>п. 26 Правил (постановление № 1206)</t>
+        </is>
+      </c>
+      <c r="D287" s="15" t="inlineStr">
+        <is>
+          <t>Мотивированное особое мнение члена комиссии</t>
+        </is>
+      </c>
+      <c r="E287" s="15" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F287" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G287" s="15" t="inlineStr">
+        <is>
+          <t>Особое мнение члена комиссии, не согласного с решением в рамках расследования случая профессионального заболевания</t>
+        </is>
+      </c>
+      <c r="H287" s="15" t="inlineStr">
+        <is>
+          <t>Член комиссии по расследованию случая профессионального заболевания</t>
+        </is>
+      </c>
+      <c r="I287" s="15" t="inlineStr">
+        <is>
+          <t>собственноручная или ЭП</t>
+        </is>
+      </c>
+      <c r="J287" s="15" t="inlineStr">
+        <is>
+          <t>Заявление</t>
+        </is>
+      </c>
+      <c r="K287" s="15" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L287" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="288" ht="55.2" customFormat="1" customHeight="1" s="14">
+      <c r="A288" s="15" t="inlineStr">
+        <is>
+          <t>Расследование профзаболеваний</t>
+        </is>
+      </c>
+      <c r="B288" s="15" t="inlineStr">
+        <is>
+          <t>Постановление Правительства РФ от 05.07.2022 № 1206 "О порядке расследования и учета случаев профессиональных заболеваний работников"</t>
+        </is>
+      </c>
+      <c r="C288" s="15" t="inlineStr">
+        <is>
+          <t>п. 26, 29–31 Правил (постановление № 1206); приложение к Правилам</t>
+        </is>
+      </c>
+      <c r="D288" s="15" t="inlineStr">
+        <is>
+          <t>Акт о случае профессионального заболевания</t>
+        </is>
+      </c>
+      <c r="E288" s="15" t="inlineStr">
         <is>
           <t>ДА</t>
         </is>
       </c>
-      <c r="F274" s="16" t="inlineStr">
+      <c r="F288" s="15" t="inlineStr">
         <is>
           <t>ДА</t>
         </is>
       </c>
-      <c r="G274" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H274" s="16" t="inlineStr">
-        <is>
-          <t>Медицинская организация</t>
-        </is>
-      </c>
-      <c r="I274" s="16" t="inlineStr">
-        <is>
-          <t>собственноручная или УКЭП</t>
-        </is>
-      </c>
-      <c r="J274" s="16" t="inlineStr">
+      <c r="G288" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H288" s="15" t="inlineStr">
+        <is>
+          <t>Главный государственный санитарный врач в субъекте РФ</t>
+        </is>
+      </c>
+      <c r="I288" s="15" t="inlineStr">
+        <is>
+          <t>собственноручная</t>
+        </is>
+      </c>
+      <c r="J288" s="15" t="inlineStr">
         <is>
           <t>Утверждение</t>
         </is>
       </c>
-      <c r="K274" s="16" t="inlineStr">
+      <c r="K288" s="15" t="inlineStr">
         <is>
           <t>УСЛОВНО</t>
         </is>
       </c>
-      <c r="L274" s="16" t="inlineStr">
+      <c r="L288" s="15" t="inlineStr">
         <is>
           <t>Печать организации</t>
         </is>
       </c>
     </row>
-    <row r="275">
-      <c r="A275" s="16" t="inlineStr">
+    <row r="289" ht="55.2" customFormat="1" customHeight="1" s="14">
+      <c r="A289" s="15" t="inlineStr">
         <is>
           <t>Расследование профзаболеваний</t>
         </is>
       </c>
-      <c r="B275" s="16" t="inlineStr">
+      <c r="B289" s="15" t="inlineStr">
         <is>
           <t>Постановление Правительства РФ от 05.07.2022 № 1206 "О порядке расследования и учета случаев профессиональных заболеваний работников"</t>
         </is>
       </c>
-      <c r="C275" s="16" t="inlineStr">
-        <is>
-          <t>п. 10 «г» Правил (постановление № 1206)</t>
-        </is>
-      </c>
-      <c r="D275" s="16" t="inlineStr">
-        <is>
-          <t>Копия трудовой книжки и (или) сведения о трудовой деятельности работника</t>
-        </is>
-      </c>
-      <c r="E275" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="F275" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G275" s="16" t="inlineStr">
-        <is>
-          <t>Копия трудовой книжки и (или) сведения о трудовой деятельности, предусмотренные статьей 66.1 Трудового кодекса Российской Федерации</t>
-        </is>
-      </c>
-      <c r="H275" s="16" t="inlineStr">
+      <c r="C289" s="15" t="inlineStr">
+        <is>
+          <t>п. 26, 29–31 Правил (постановление № 1206); приложение к Правилам</t>
+        </is>
+      </c>
+      <c r="D289" s="15" t="inlineStr">
+        <is>
+          <t>Акт о случае профессионального заболевания</t>
+        </is>
+      </c>
+      <c r="E289" s="15" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="F289" s="15" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="G289" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H289" s="15" t="inlineStr">
+        <is>
+          <t>Член комиссии по расследованию случая профессионального заболевания</t>
+        </is>
+      </c>
+      <c r="I289" s="15" t="inlineStr">
+        <is>
+          <t>собственноручная</t>
+        </is>
+      </c>
+      <c r="J289" s="15" t="inlineStr">
+        <is>
+          <t>Подтверждение (?)</t>
+        </is>
+      </c>
+      <c r="K289" s="15" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="L289" s="15" t="inlineStr">
+        <is>
+          <t>Печать организации</t>
+        </is>
+      </c>
+    </row>
+    <row r="290" ht="151.8" customFormat="1" customHeight="1" s="14">
+      <c r="A290" s="15" t="inlineStr">
+        <is>
+          <t>Расследование профзаболеваний</t>
+        </is>
+      </c>
+      <c r="B290" s="15" t="inlineStr">
+        <is>
+          <t>Постановление Правительства РФ от 05.07.2022 № 1206 "О порядке расследования и учета случаев профессиональных заболеваний работников"</t>
+        </is>
+      </c>
+      <c r="C290" s="15" t="inlineStr">
+        <is>
+          <t>п. 26 Правил (постановление № 1206)</t>
+        </is>
+      </c>
+      <c r="D290" s="15" t="inlineStr">
+        <is>
+          <t>Протокол заседания комиссии по расследованию случая профессионального заболевания (заболевание работника не связано с воздействием вредного производственного фактора (факторов) на рабочем месте, и (или) было получено работником не при исполнении трудовых обязанностей по определенной условиями трудового договора профессии (должности))</t>
+        </is>
+      </c>
+      <c r="E290" s="15" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="F290" s="15" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="G290" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H290" s="15" t="inlineStr">
+        <is>
+          <t>Председатель комиссии по расследованию случая профессионального заболевания</t>
+        </is>
+      </c>
+      <c r="I290" s="15" t="inlineStr">
+        <is>
+          <t>собственноручная</t>
+        </is>
+      </c>
+      <c r="J290" s="15" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K290" s="15" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="L290" s="15" t="inlineStr">
+        <is>
+          <t>Печать организации</t>
+        </is>
+      </c>
+    </row>
+    <row r="291" ht="151.8" customFormat="1" customHeight="1" s="14">
+      <c r="A291" s="15" t="inlineStr">
+        <is>
+          <t>Расследование профзаболеваний</t>
+        </is>
+      </c>
+      <c r="B291" s="15" t="inlineStr">
+        <is>
+          <t>Постановление Правительства РФ от 05.07.2022 № 1206 "О порядке расследования и учета случаев профессиональных заболеваний работников"</t>
+        </is>
+      </c>
+      <c r="C291" s="15" t="inlineStr">
+        <is>
+          <t>п. 26 Правил (постановление № 1206)</t>
+        </is>
+      </c>
+      <c r="D291" s="15" t="inlineStr">
+        <is>
+          <t>Протокол заседания комиссии по расследованию случая профессионального заболевания (заболевание работника не связано с воздействием вредного производственного фактора (факторов) на рабочем месте, и (или) было получено работником не при исполнении трудовых обязанностей по определенной условиями трудового договора профессии (должности))</t>
+        </is>
+      </c>
+      <c r="E291" s="15" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="F291" s="15" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="G291" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H291" s="15" t="inlineStr">
+        <is>
+          <t>Член комиссии по расследованию случая профессионального заболевания</t>
+        </is>
+      </c>
+      <c r="I291" s="15" t="inlineStr">
+        <is>
+          <t>собственноручная</t>
+        </is>
+      </c>
+      <c r="J291" s="15" t="inlineStr">
+        <is>
+          <t>Подтверждение (?)</t>
+        </is>
+      </c>
+      <c r="K291" s="15" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="L291" s="15" t="inlineStr">
+        <is>
+          <t>Печать организации</t>
+        </is>
+      </c>
+    </row>
+    <row r="292" ht="55.2" customFormat="1" customHeight="1" s="14">
+      <c r="A292" s="15" t="inlineStr">
+        <is>
+          <t>Расследование профзаболеваний</t>
+        </is>
+      </c>
+      <c r="B292" s="15" t="inlineStr">
+        <is>
+          <t>Постановление Правительства РФ от 05.07.2022 № 1206 "О порядке расследования и учета случаев профессиональных заболеваний работников"</t>
+        </is>
+      </c>
+      <c r="C292" s="15" t="inlineStr">
+        <is>
+          <t>п. 28 Правил (постановление № 1206)</t>
+        </is>
+      </c>
+      <c r="D292" s="15" t="inlineStr">
+        <is>
+          <t>Локальный нормативный акт о конкретных мерах по предупреждению профессиональных заболеваний</t>
+        </is>
+      </c>
+      <c r="E292" s="15" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F292" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G292" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H292" s="15" t="inlineStr">
         <is>
           <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
         </is>
       </c>
-      <c r="I275" s="16" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J275" s="16" t="inlineStr">
+      <c r="I292" s="15" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J292" s="15" t="inlineStr">
         <is>
           <t>Утверждение</t>
         </is>
       </c>
-      <c r="K275" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="L275" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" s="16" t="inlineStr">
+      <c r="K292" s="15" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L292" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="293" ht="55.2" customFormat="1" customHeight="1" s="14">
+      <c r="A293" s="15" t="inlineStr">
         <is>
           <t>Расследование профзаболеваний</t>
         </is>
       </c>
-      <c r="B276" s="16" t="inlineStr">
+      <c r="B293" s="15" t="inlineStr">
         <is>
           <t>Постановление Правительства РФ от 05.07.2022 № 1206 "О порядке расследования и учета случаев профессиональных заболеваний работников"</t>
         </is>
       </c>
-      <c r="C276" s="16" t="inlineStr">
-        <is>
-          <t>п. 10 «е» Правил (постановление № 1206)</t>
-        </is>
-      </c>
-      <c r="D276" s="16" t="inlineStr">
-        <is>
-          <t>Копии протоколов лабораторных испытаний, выполненных в ходе осуществления производственного контроля на рабочем месте работника</t>
-        </is>
-      </c>
-      <c r="E276" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="F276" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G276" s="16" t="inlineStr">
-        <is>
-          <t>Копии протоколов лабораторных испытаний производственного контроля на рабочем месте работника (при наличии у работодателя)</t>
-        </is>
-      </c>
-      <c r="H276" s="16" t="inlineStr">
+      <c r="C293" s="15" t="inlineStr">
+        <is>
+          <t>п. 28 Правил (постановление № 1206)</t>
+        </is>
+      </c>
+      <c r="D293" s="15" t="inlineStr">
+        <is>
+          <t>Сообщение об исполнении решений комиссии по расследованию случая профессионального заболевания</t>
+        </is>
+      </c>
+      <c r="E293" s="15" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F293" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G293" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H293" s="15" t="inlineStr">
         <is>
           <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
         </is>
       </c>
-      <c r="I276" s="16" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J276" s="16" t="inlineStr">
+      <c r="I293" s="15" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J293" s="15" t="inlineStr">
+        <is>
+          <t>Уведомление</t>
+        </is>
+      </c>
+      <c r="K293" s="15" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L293" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="294" ht="55.2" customFormat="1" customHeight="1" s="14">
+      <c r="A294" s="15" t="inlineStr">
+        <is>
+          <t>Расследование профзаболеваний</t>
+        </is>
+      </c>
+      <c r="B294" s="15" t="inlineStr">
+        <is>
+          <t>Постановление Правительства РФ от 05.07.2022 № 1206 "О порядке расследования и учета случаев профессиональных заболеваний работников"</t>
+        </is>
+      </c>
+      <c r="C294" s="15" t="inlineStr">
+        <is>
+          <t>п. 34, 35 Правил (постановление № 1206)</t>
+        </is>
+      </c>
+      <c r="D294" s="15" t="inlineStr">
+        <is>
+          <t>Заявление о рассмотрении разногласий по вопросам установления диагноза профессионального заболевания и его расследования</t>
+        </is>
+      </c>
+      <c r="E294" s="15" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F294" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G294" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H294" s="15" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I294" s="15" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J294" s="15" t="inlineStr">
+        <is>
+          <t>Заявление</t>
+        </is>
+      </c>
+      <c r="K294" s="15" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L294" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="295" ht="55.2" customFormat="1" customHeight="1" s="14">
+      <c r="A295" s="15" t="inlineStr">
+        <is>
+          <t>Расследование профзаболеваний</t>
+        </is>
+      </c>
+      <c r="B295" s="15" t="inlineStr">
+        <is>
+          <t>Постановление Правительства РФ от 05.07.2022 № 1206 "О порядке расследования и учета случаев профессиональных заболеваний работников"</t>
+        </is>
+      </c>
+      <c r="C295" s="15" t="inlineStr">
+        <is>
+          <t>п. 34, 35 Правил (постановление № 1206)</t>
+        </is>
+      </c>
+      <c r="D295" s="15" t="inlineStr">
+        <is>
+          <t>Заявление о рассмотрении разногласий по вопросам установления диагноза профессионального заболевания и его расследования</t>
+        </is>
+      </c>
+      <c r="E295" s="15" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F295" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G295" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H295" s="15" t="inlineStr">
+        <is>
+          <t>Работник</t>
+        </is>
+      </c>
+      <c r="I295" s="15" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J295" s="15" t="inlineStr">
+        <is>
+          <t>Заявление</t>
+        </is>
+      </c>
+      <c r="K295" s="15" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L295" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="296" ht="179.4" customFormat="1" customHeight="1" s="14">
+      <c r="A296" s="15" t="inlineStr">
+        <is>
+          <t>Расследование профзаболеваний</t>
+        </is>
+      </c>
+      <c r="B296" s="15" t="inlineStr">
+        <is>
+          <t>Приказ Минздрава России от 29.04.2025 № 258н "Об утверждении порядка проведения экспертизы связи заболевания с профессией, учетной формы извещения об установлении диагноза - острое (хроническое) профессиональное заболевание, уточнении или отмене диагноза - острое (хроническое) профессиональное заболевание, учетной формы медицинского заключения о наличии или об отсутствии профессионального заболевания, порядка учета профессионального заболевания органом государственного санитарно-эпидемиологического контроля (надзора), проводившим расследование обстоятельств и причин возникновения у работника профессионального заболевания, формы протокола заседания комиссии по расследованию случая профессионального заболевания"</t>
+        </is>
+      </c>
+      <c r="C296" s="15" t="inlineStr">
+        <is>
+          <t>п. 9-10 Порядка (приказ № 258н)</t>
+        </is>
+      </c>
+      <c r="D296" s="15" t="inlineStr">
+        <is>
+          <t>Приказ о создании врачебной комиссии по экспертизе связи заболевания с профессией</t>
+        </is>
+      </c>
+      <c r="E296" s="15" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F296" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G296" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H296" s="15" t="inlineStr">
+        <is>
+          <t>Центр профессиональной патологии</t>
+        </is>
+      </c>
+      <c r="I296" s="15" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J296" s="15" t="inlineStr">
         <is>
           <t>Утверждение</t>
         </is>
       </c>
-      <c r="K276" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="L276" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" s="16" t="inlineStr">
+      <c r="K296" s="15" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L296" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="297" ht="179.4" customFormat="1" customHeight="1" s="14">
+      <c r="A297" s="15" t="inlineStr">
         <is>
           <t>Расследование профзаболеваний</t>
         </is>
       </c>
-      <c r="B277" s="16" t="inlineStr">
-        <is>
-          <t>Постановление Правительства РФ от 05.07.2022 № 1206 "О порядке расследования и учета случаев профессиональных заболеваний работников"</t>
-        </is>
-      </c>
-      <c r="C277" s="16" t="inlineStr">
-        <is>
-          <t>п. 11, 12 Правил (постановление № 1206)</t>
-        </is>
-      </c>
-      <c r="D277" s="16" t="inlineStr">
-        <is>
-          <t>Медицинское заключение о наличии или об отсутствии профессионального заболевания</t>
-        </is>
-      </c>
-      <c r="E277" s="16" t="inlineStr">
+      <c r="B297" s="15" t="inlineStr">
+        <is>
+          <t>Приказ Минздрава России от 29.04.2025 № 258н "Об утверждении порядка проведения экспертизы связи заболевания с профессией, учетной формы извещения об установлении диагноза - острое (хроническое) профессиональное заболевание, уточнении или отмене диагноза - острое (хроническое) профессиональное заболевание, учетной формы медицинского заключения о наличии или об отсутствии профессионального заболевания, порядка учета профессионального заболевания органом государственного санитарно-эпидемиологического контроля (надзора), проводившим расследование обстоятельств и причин возникновения у работника профессионального заболевания, формы протокола заседания комиссии по расследованию случая профессионального заболевания"</t>
+        </is>
+      </c>
+      <c r="C297" s="15" t="inlineStr">
+        <is>
+          <t>п. 18 Порядка (приказ № 258н)</t>
+        </is>
+      </c>
+      <c r="D297" s="15" t="inlineStr">
+        <is>
+          <t>Протокол врачебной комиссии по экспертизе связи заболевания с профессией</t>
+        </is>
+      </c>
+      <c r="E297" s="15" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F297" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G297" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H297" s="15" t="inlineStr">
+        <is>
+          <t>Председатель врачебной комиссии</t>
+        </is>
+      </c>
+      <c r="I297" s="15" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J297" s="15" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K297" s="15" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L297" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="298" ht="179.4" customFormat="1" customHeight="1" s="14">
+      <c r="A298" s="15" t="inlineStr">
+        <is>
+          <t>Расследование профзаболеваний</t>
+        </is>
+      </c>
+      <c r="B298" s="15" t="inlineStr">
+        <is>
+          <t>Приказ Минздрава России от 29.04.2025 № 258н "Об утверждении порядка проведения экспертизы связи заболевания с профессией, учетной формы извещения об установлении диагноза - острое (хроническое) профессиональное заболевание, уточнении или отмене диагноза - острое (хроническое) профессиональное заболевание, учетной формы медицинского заключения о наличии или об отсутствии профессионального заболевания, порядка учета профессионального заболевания органом государственного санитарно-эпидемиологического контроля (надзора), проводившим расследование обстоятельств и причин возникновения у работника профессионального заболевания, формы протокола заседания комиссии по расследованию случая профессионального заболевания"</t>
+        </is>
+      </c>
+      <c r="C298" s="15" t="inlineStr">
+        <is>
+          <t>п. 18 Порядка (приказ № 258н)</t>
+        </is>
+      </c>
+      <c r="D298" s="15" t="inlineStr">
+        <is>
+          <t>Протокол врачебной комиссии по экспертизе связи заболевания с профессией</t>
+        </is>
+      </c>
+      <c r="E298" s="15" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F298" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G298" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H298" s="15" t="inlineStr">
+        <is>
+          <t>Член врачебной комиссии</t>
+        </is>
+      </c>
+      <c r="I298" s="15" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J298" s="15" t="inlineStr">
+        <is>
+          <t>Подтверждение (?)</t>
+        </is>
+      </c>
+      <c r="K298" s="15" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L298" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="299" ht="179.4" customFormat="1" customHeight="1" s="14">
+      <c r="A299" s="15" t="inlineStr">
+        <is>
+          <t>Расследование профзаболеваний</t>
+        </is>
+      </c>
+      <c r="B299" s="15" t="inlineStr">
+        <is>
+          <t>Приказ Минздрава России от 29.04.2025 № 258н "Об утверждении порядка проведения экспертизы связи заболевания с профессией, учетной формы извещения об установлении диагноза - острое (хроническое) профессиональное заболевание, уточнении или отмене диагноза - острое (хроническое) профессиональное заболевание, учетной формы медицинского заключения о наличии или об отсутствии профессионального заболевания, порядка учета профессионального заболевания органом государственного санитарно-эпидемиологического контроля (надзора), проводившим расследование обстоятельств и причин возникновения у работника профессионального заболевания, формы протокола заседания комиссии по расследованию случая профессионального заболевания"</t>
+        </is>
+      </c>
+      <c r="C299" s="15" t="inlineStr">
+        <is>
+          <t>п. 35 Порядка (приказ № 258н)</t>
+        </is>
+      </c>
+      <c r="D299" s="15" t="inlineStr">
+        <is>
+          <t>Журнал учета выданных медицинских заключений о наличии или об отсутствии профессионального заболевания</t>
+        </is>
+      </c>
+      <c r="E299" s="15" t="inlineStr">
         <is>
           <t>ДА</t>
         </is>
       </c>
-      <c r="F277" s="16" t="inlineStr">
+      <c r="F299" s="15" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="G299" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H299" s="15" t="inlineStr">
+        <is>
+          <t>Центр профессиональной патологии</t>
+        </is>
+      </c>
+      <c r="I299" s="15" t="inlineStr">
+        <is>
+          <t>собственноручная или ЭП</t>
+        </is>
+      </c>
+      <c r="J299" s="15" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K299" s="15" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L299" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="300" customFormat="1" s="14">
+      <c r="A300" s="16" t="inlineStr">
+        <is>
+          <t>Социальное страхование</t>
+        </is>
+      </c>
+      <c r="B300" s="16" t="inlineStr">
+        <is>
+          <t>ФЗ от 24.07.1998 № 125-ФЗ; ПП РФ от 30.05.2012 № 524; приказ Минтруда от 01.08.2012 № 39н; приказ Минтруда от 11.07.2024 № 347н; приказ Минтруда от 29.10.2021 № 771н</t>
+        </is>
+      </c>
+      <c r="C300" s="16" t="inlineStr">
+        <is>
+          <t>ст. 6, 17 125-ФЗ</t>
+        </is>
+      </c>
+      <c r="D300" s="16" t="inlineStr">
+        <is>
+          <t>Документы (заявление) о регистрации страхователя / сведения для постановки на учет</t>
+        </is>
+      </c>
+      <c r="E300" s="16" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F300" s="16" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="G300" s="16" t="inlineStr">
+        <is>
+          <t>Наименование (ФИО) страхователя; место нахождения; виды экономической деятельности; банковские реквизиты; иные сведения, необходимые для учета страхователя</t>
+        </is>
+      </c>
+      <c r="H300" s="16" t="inlineStr">
+        <is>
+          <t>Руководитель организации (страхователь) / уполномоченное лицо</t>
+        </is>
+      </c>
+      <c r="I300" s="16" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J300" s="16" t="inlineStr">
+        <is>
+          <t>Заявление</t>
+        </is>
+      </c>
+      <c r="K300" s="16" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="L300" s="16" t="inlineStr">
+        <is>
+          <t>Нет ограничений</t>
+        </is>
+      </c>
+    </row>
+    <row r="301" customFormat="1" s="14">
+      <c r="A301" s="16" t="inlineStr">
+        <is>
+          <t>Социальное страхование</t>
+        </is>
+      </c>
+      <c r="B301" s="16" t="inlineStr">
+        <is>
+          <t>ФЗ от 24.07.1998 № 125-ФЗ; ПП РФ от 30.05.2012 № 524; приказ Минтруда от 01.08.2012 № 39н; приказ Минтруда от 11.07.2024 № 347н; приказ Минтруда от 29.10.2021 № 771н</t>
+        </is>
+      </c>
+      <c r="C301" s="16" t="inlineStr">
+        <is>
+          <t>ст. 17 125-ФЗ</t>
+        </is>
+      </c>
+      <c r="D301" s="16" t="inlineStr">
+        <is>
+          <t>Уведомление страховщика об изменении места нахождения / места жительства страхователя</t>
+        </is>
+      </c>
+      <c r="E301" s="16" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F301" s="16" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="G301" s="16" t="inlineStr">
+        <is>
+          <t>Сведения об изменении места нахождения (места жительства) страхователя; дата изменения</t>
+        </is>
+      </c>
+      <c r="H301" s="16" t="inlineStr">
+        <is>
+          <t>Руководитель организации (страхователь) / уполномоченное лицо</t>
+        </is>
+      </c>
+      <c r="I301" s="16" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J301" s="16" t="inlineStr">
+        <is>
+          <t>Уведомление</t>
+        </is>
+      </c>
+      <c r="K301" s="16" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="L301" s="16" t="inlineStr">
+        <is>
+          <t>Нет ограничений</t>
+        </is>
+      </c>
+    </row>
+    <row r="302" customFormat="1" s="14">
+      <c r="A302" s="16" t="inlineStr">
+        <is>
+          <t>Социальное страхование</t>
+        </is>
+      </c>
+      <c r="B302" s="16" t="inlineStr">
+        <is>
+          <t>ФЗ от 24.07.1998 № 125-ФЗ; ПП РФ от 30.05.2012 № 524; приказ Минтруда от 01.08.2012 № 39н; приказ Минтруда от 11.07.2024 № 347н; приказ Минтруда от 29.10.2021 № 771н</t>
+        </is>
+      </c>
+      <c r="C302" s="16" t="inlineStr">
+        <is>
+          <t>ст. 17 125-ФЗ</t>
+        </is>
+      </c>
+      <c r="D302" s="16" t="inlineStr">
+        <is>
+          <t>Сообщение о страховом случае (несчастный случай / профзаболевание)</t>
+        </is>
+      </c>
+      <c r="E302" s="16" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F302" s="16" t="inlineStr">
         <is>
           <t>ДА</t>
         </is>
       </c>
-      <c r="G277" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H277" s="16" t="inlineStr">
-        <is>
-          <t>Центр профессиональной патологии</t>
-        </is>
-      </c>
-      <c r="I277" s="16" t="inlineStr">
-        <is>
-          <t>собственноручная или УКЭП</t>
-        </is>
-      </c>
-      <c r="J277" s="16" t="inlineStr">
+      <c r="G302" s="16" t="inlineStr">
+        <is>
+          <t>Факт и обстоятельства страхового случая; сведения о пострадавшем работнике; дата и характер события; иные сведения, необходимые страховщику</t>
+        </is>
+      </c>
+      <c r="H302" s="16" t="inlineStr">
+        <is>
+          <t>Работодатель (страхователь) / уполномоченное лицо</t>
+        </is>
+      </c>
+      <c r="I302" s="16" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J302" s="16" t="inlineStr">
+        <is>
+          <t>Уведомление</t>
+        </is>
+      </c>
+      <c r="K302" s="16" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="L302" s="16" t="inlineStr">
+        <is>
+          <t>Нет ограничений</t>
+        </is>
+      </c>
+    </row>
+    <row r="303" customFormat="1" s="14">
+      <c r="A303" s="16" t="inlineStr">
+        <is>
+          <t>Социальное страхование</t>
+        </is>
+      </c>
+      <c r="B303" s="16" t="inlineStr">
+        <is>
+          <t>ФЗ от 24.07.1998 № 125-ФЗ; ПП РФ от 30.05.2012 № 524; приказ Минтруда от 01.08.2012 № 39н; приказ Минтруда от 11.07.2024 № 347н; приказ Минтруда от 29.10.2021 № 771н</t>
+        </is>
+      </c>
+      <c r="C303" s="16" t="inlineStr">
+        <is>
+          <t>ст. 17, 22, 24 125-ФЗ</t>
+        </is>
+      </c>
+      <c r="D303" s="16" t="inlineStr">
+        <is>
+          <t>Сведения о начисленных страховых взносах и документы, подтверждающие уплату страховых взносов</t>
+        </is>
+      </c>
+      <c r="E303" s="16" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F303" s="16" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="G303" s="16" t="inlineStr">
+        <is>
+          <t>Суммы начисленных и уплаченных страховых взносов; расчетный (отчетный) период; сведения, подтверждающие правильность исчисления и своевременность уплаты</t>
+        </is>
+      </c>
+      <c r="H303" s="16" t="inlineStr">
+        <is>
+          <t>Руководитель организации / уполномоченное лицо; главный бухгалтер (при наличии)</t>
+        </is>
+      </c>
+      <c r="I303" s="16" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J303" s="16" t="inlineStr">
+        <is>
+          <t>Подтверждение</t>
+        </is>
+      </c>
+      <c r="K303" s="16" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="L303" s="16" t="inlineStr">
+        <is>
+          <t>Нет ограничений</t>
+        </is>
+      </c>
+    </row>
+    <row r="304" customFormat="1" s="14">
+      <c r="A304" s="16" t="inlineStr">
+        <is>
+          <t>Социальное страхование</t>
+        </is>
+      </c>
+      <c r="B304" s="16" t="inlineStr">
+        <is>
+          <t>ФЗ от 24.07.1998 № 125-ФЗ; ПП РФ от 30.05.2012 № 524; приказ Минтруда от 01.08.2012 № 39н; приказ Минтруда от 11.07.2024 № 347н; приказ Минтруда от 29.10.2021 № 771н</t>
+        </is>
+      </c>
+      <c r="C304" s="16" t="inlineStr">
+        <is>
+          <t>ст. 17, 24 125-ФЗ; приказы СФР об отчетности</t>
+        </is>
+      </c>
+      <c r="D304" s="16" t="inlineStr">
+        <is>
+          <t>Сведения по форме ЕФС-1 (раздел по взносам на травматизм) / расчет по страховым взносам</t>
+        </is>
+      </c>
+      <c r="E304" s="16" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="F304" s="16" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="G304" s="16" t="inlineStr">
+        <is>
+          <t>Сведения о страхователе; расчетная база; страховой тариф; суммы начисленных взносов; сведения о застрахованных; иные показатели формы</t>
+        </is>
+      </c>
+      <c r="H304" s="16" t="inlineStr">
+        <is>
+          <t>Руководитель организации / уполномоченное лицо</t>
+        </is>
+      </c>
+      <c r="I304" s="16" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J304" s="16" t="inlineStr">
+        <is>
+          <t>Подтверждение</t>
+        </is>
+      </c>
+      <c r="K304" s="16" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="L304" s="16" t="inlineStr">
+        <is>
+          <t>Нет ограничений</t>
+        </is>
+      </c>
+    </row>
+    <row r="305" customFormat="1" s="14">
+      <c r="A305" s="16" t="inlineStr">
+        <is>
+          <t>Социальное страхование</t>
+        </is>
+      </c>
+      <c r="B305" s="16" t="inlineStr">
+        <is>
+          <t>ФЗ от 24.07.1998 № 125-ФЗ; ПП РФ от 30.05.2012 № 524; приказ Минтруда от 01.08.2012 № 39н; приказ Минтруда от 11.07.2024 № 347н; приказ Минтруда от 29.10.2021 № 771н</t>
+        </is>
+      </c>
+      <c r="C305" s="16" t="inlineStr">
+        <is>
+          <t>п. 3 Правил (ПП РФ № 524); п. 5–8 Методики (приказ № 39н)</t>
+        </is>
+      </c>
+      <c r="D305" s="16" t="inlineStr">
+        <is>
+          <t>Сведения, подтверждающие основной вид экономической деятельности страхователя</t>
+        </is>
+      </c>
+      <c r="E305" s="16" t="inlineStr">
+        <is>
+          <t>ДА (по формам, установленным для подтверждения ОВЭД)</t>
+        </is>
+      </c>
+      <c r="F305" s="16" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="G305" s="16" t="inlineStr">
+        <is>
+          <t>Основной вид экономической деятельности; доля доходов по видам деятельности; расчетная справка; копия пояснительной записки к балансу (при необходимости)</t>
+        </is>
+      </c>
+      <c r="H305" s="16" t="inlineStr">
+        <is>
+          <t>Руководитель организации / уполномоченное лицо</t>
+        </is>
+      </c>
+      <c r="I305" s="16" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J305" s="16" t="inlineStr">
+        <is>
+          <t>Подтверждение</t>
+        </is>
+      </c>
+      <c r="K305" s="16" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="L305" s="16" t="inlineStr">
+        <is>
+          <t>Нет ограничений</t>
+        </is>
+      </c>
+    </row>
+    <row r="306" customFormat="1" s="14">
+      <c r="A306" s="16" t="inlineStr">
+        <is>
+          <t>Социальное страхование</t>
+        </is>
+      </c>
+      <c r="B306" s="16" t="inlineStr">
+        <is>
+          <t>ФЗ от 24.07.1998 № 125-ФЗ; ПП РФ от 30.05.2012 № 524; приказ Минтруда от 01.08.2012 № 39н; приказ Минтруда от 11.07.2024 № 347н; приказ Минтруда от 29.10.2021 № 771н</t>
+        </is>
+      </c>
+      <c r="C306" s="16" t="inlineStr">
+        <is>
+          <t>п. 3 Правил (ПП РФ № 524); п. 5–7, 11 Методики (приказ № 39н)</t>
+        </is>
+      </c>
+      <c r="D306" s="16" t="inlineStr">
+        <is>
+          <t>Сведения о результатах проведения специальной оценки условий труда</t>
+        </is>
+      </c>
+      <c r="E306" s="16" t="inlineStr">
+        <is>
+          <t>ДА (отчет о проведении СОУТ / сведения из него)</t>
+        </is>
+      </c>
+      <c r="F306" s="16" t="inlineStr">
+        <is>
+          <t>ДА (для скидки)</t>
+        </is>
+      </c>
+      <c r="G306" s="16" t="inlineStr">
+        <is>
+          <t>Сведения о рабочих местах; классы (подклассы) условий труда; доля рабочих мест с СОУТ; показатели, используемые при расчете скидки</t>
+        </is>
+      </c>
+      <c r="H306" s="16" t="inlineStr">
+        <is>
+          <t>Работодатель (как сторона передачи сведений страховщику)</t>
+        </is>
+      </c>
+      <c r="I306" s="16" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J306" s="16" t="inlineStr">
+        <is>
+          <t>Подтверждение</t>
+        </is>
+      </c>
+      <c r="K306" s="16" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="L306" s="16" t="inlineStr">
+        <is>
+          <t>Нет ограничений</t>
+        </is>
+      </c>
+    </row>
+    <row r="307" customFormat="1" s="14">
+      <c r="A307" s="16" t="inlineStr">
+        <is>
+          <t>Социальное страхование</t>
+        </is>
+      </c>
+      <c r="B307" s="16" t="inlineStr">
+        <is>
+          <t>ФЗ от 24.07.1998 № 125-ФЗ; ПП РФ от 30.05.2012 № 524; приказ Минтруда от 01.08.2012 № 39н; приказ Минтруда от 11.07.2024 № 347н; приказ Минтруда от 29.10.2021 № 771н</t>
+        </is>
+      </c>
+      <c r="C307" s="16" t="inlineStr">
+        <is>
+          <t>п. 3 Правил (ПП РФ № 524); п. 5–7, 11 Методики (приказ № 39н)</t>
+        </is>
+      </c>
+      <c r="D307" s="16" t="inlineStr">
+        <is>
+          <t>Сведения о проведенных обязательных предварительных и периодических медицинских осмотрах</t>
+        </is>
+      </c>
+      <c r="E307" s="16" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F307" s="16" t="inlineStr">
+        <is>
+          <t>ДА (для скидки)</t>
+        </is>
+      </c>
+      <c r="G307" s="16" t="inlineStr">
+        <is>
+          <t>Сведения о численности работников, подлежащих медосмотрам; о прошедших медосмотры; показатели охвата медосмотрами для расчета скидки</t>
+        </is>
+      </c>
+      <c r="H307" s="16" t="inlineStr">
+        <is>
+          <t>Работодатель (как сторона передачи сведений страховщику)</t>
+        </is>
+      </c>
+      <c r="I307" s="16" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J307" s="16" t="inlineStr">
+        <is>
+          <t>Подтверждение</t>
+        </is>
+      </c>
+      <c r="K307" s="16" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="L307" s="16" t="inlineStr">
+        <is>
+          <t>Нет ограничений</t>
+        </is>
+      </c>
+    </row>
+    <row r="308" customFormat="1" s="14">
+      <c r="A308" s="16" t="inlineStr">
+        <is>
+          <t>Социальное страхование</t>
+        </is>
+      </c>
+      <c r="B308" s="16" t="inlineStr">
+        <is>
+          <t>ФЗ от 24.07.1998 № 125-ФЗ; ПП РФ от 30.05.2012 № 524; приказ Минтруда от 01.08.2012 № 39н; приказ Минтруда от 11.07.2024 № 347н; приказ Минтруда от 29.10.2021 № 771н</t>
+        </is>
+      </c>
+      <c r="C308" s="16" t="inlineStr">
+        <is>
+          <t>п. 3, 7 Правил (ПП РФ № 524); п. 5–11 Методики (приказ № 39н)</t>
+        </is>
+      </c>
+      <c r="D308" s="16" t="inlineStr">
+        <is>
+          <t>Заявление об установлении скидки к страховому тарифу</t>
+        </is>
+      </c>
+      <c r="E308" s="16" t="inlineStr">
+        <is>
+          <t>ДА (форма заявления, установленная страховщиком / для подачи в СФР)</t>
+        </is>
+      </c>
+      <c r="F308" s="16" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="G308" s="16" t="inlineStr">
+        <is>
+          <t>Наименование страхователя; регистрационный номер; расчетные показатели a, b, c и сравнение со среднеотраслевыми; сведения о СОУТ и медосмотрах; период, на который запрашивается скидка</t>
+        </is>
+      </c>
+      <c r="H308" s="16" t="inlineStr">
+        <is>
+          <t>Руководитель организации (страхователь) / уполномоченное лицо</t>
+        </is>
+      </c>
+      <c r="I308" s="16" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J308" s="16" t="inlineStr">
+        <is>
+          <t>Заявление</t>
+        </is>
+      </c>
+      <c r="K308" s="16" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="L308" s="16" t="inlineStr">
+        <is>
+          <t>Нет ограничений</t>
+        </is>
+      </c>
+    </row>
+    <row r="309" customFormat="1" s="14">
+      <c r="A309" s="16" t="inlineStr">
+        <is>
+          <t>Социальное страхование</t>
+        </is>
+      </c>
+      <c r="B309" s="16" t="inlineStr">
+        <is>
+          <t>ФЗ от 24.07.1998 № 125-ФЗ; ПП РФ от 30.05.2012 № 524; приказ Минтруда от 01.08.2012 № 39н; приказ Минтруда от 11.07.2024 № 347н; приказ Минтруда от 29.10.2021 № 771н</t>
+        </is>
+      </c>
+      <c r="C309" s="16" t="inlineStr">
+        <is>
+          <t>п. 4–7, 9–10 Правил (ПП РФ № 524); п. 5–12 Методики (приказ № 39н)</t>
+        </is>
+      </c>
+      <c r="D309" s="16" t="inlineStr">
+        <is>
+          <t>Решение страховщика об установлении скидки (надбавки) к страховому тарифу (получаемое страхователем)</t>
+        </is>
+      </c>
+      <c r="E309" s="16" t="inlineStr">
+        <is>
+          <t>ДА (форма решения страховщика)</t>
+        </is>
+      </c>
+      <c r="F309" s="16" t="inlineStr">
+        <is>
+          <t>— (документ страховщика)</t>
+        </is>
+      </c>
+      <c r="G309" s="16" t="inlineStr">
+        <is>
+          <t>Размер скидки или надбавки; обоснование; период применения; реквизиты страхователя</t>
+        </is>
+      </c>
+      <c r="H309" s="16" t="inlineStr">
+        <is>
+          <t>Уполномоченное должностное лицо страховщика (СФР)</t>
+        </is>
+      </c>
+      <c r="I309" s="16" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J309" s="16" t="inlineStr">
+        <is>
+          <t>Уведомление</t>
+        </is>
+      </c>
+      <c r="K309" s="16" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="L309" s="16" t="inlineStr">
+        <is>
+          <t>Нет ограничений</t>
+        </is>
+      </c>
+    </row>
+    <row r="310" customFormat="1" s="14">
+      <c r="A310" s="16" t="inlineStr">
+        <is>
+          <t>Социальное страхование</t>
+        </is>
+      </c>
+      <c r="B310" s="16" t="inlineStr">
+        <is>
+          <t>ФЗ от 24.07.1998 № 125-ФЗ; ПП РФ от 30.05.2012 № 524; приказ Минтруда от 01.08.2012 № 39н; приказ Минтруда от 11.07.2024 № 347н; приказ Минтруда от 29.10.2021 № 771н</t>
+        </is>
+      </c>
+      <c r="C310" s="16" t="inlineStr">
+        <is>
+          <t>п. 10 Правил (ПП РФ № 524)</t>
+        </is>
+      </c>
+      <c r="D310" s="16" t="inlineStr">
+        <is>
+          <t>Заявление (жалоба) страхователя об обжаловании решения об установлении надбавки</t>
+        </is>
+      </c>
+      <c r="E310" s="16" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F310" s="16" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="G310" s="16" t="inlineStr">
+        <is>
+          <t>Реквизиты обжалуемого решения; доводы страхователя; просьба о пересмотре; приложения</t>
+        </is>
+      </c>
+      <c r="H310" s="16" t="inlineStr">
+        <is>
+          <t>Руководитель организации (страхователь) / уполномоченное лицо</t>
+        </is>
+      </c>
+      <c r="I310" s="16" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J310" s="16" t="inlineStr">
+        <is>
+          <t>Заявление</t>
+        </is>
+      </c>
+      <c r="K310" s="16" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="L310" s="16" t="inlineStr">
+        <is>
+          <t>Нет ограничений</t>
+        </is>
+      </c>
+    </row>
+    <row r="311" customFormat="1" s="14">
+      <c r="A311" s="16" t="inlineStr">
+        <is>
+          <t>Социальное страхование</t>
+        </is>
+      </c>
+      <c r="B311" s="16" t="inlineStr">
+        <is>
+          <t>ФЗ от 24.07.1998 № 125-ФЗ; ПП РФ от 30.05.2012 № 524; приказ Минтруда от 01.08.2012 № 39н; приказ Минтруда от 11.07.2024 № 347н; приказ Минтруда от 29.10.2021 № 771н</t>
+        </is>
+      </c>
+      <c r="C311" s="16" t="inlineStr">
+        <is>
+          <t>п. 5 Примерного перечня (приказ № 771н); ст. 17 125-ФЗ</t>
+        </is>
+      </c>
+      <c r="D311" s="16" t="inlineStr">
+        <is>
+          <t>Перечень ежегодно реализуемых мероприятий по улучшению условий и охраны труда (в части социального страхования / предупредительных мер)</t>
+        </is>
+      </c>
+      <c r="E311" s="16" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F311" s="16" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="G311" s="16" t="inlineStr">
+        <is>
+          <t>Мероприятия по улучшению условий и охраны труда, снижению профрисков; в т.ч. мероприятия, финансируемые за счет взносов на травматизм</t>
+        </is>
+      </c>
+      <c r="H311" s="16" t="inlineStr">
+        <is>
+          <t>Работодатель; руководитель организации (при утверждении перечня)</t>
+        </is>
+      </c>
+      <c r="I311" s="16" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J311" s="16" t="inlineStr">
         <is>
           <t>Утверждение</t>
         </is>
       </c>
-      <c r="K277" s="16" t="inlineStr">
-        <is>
-          <t>УСЛОВНО</t>
-        </is>
-      </c>
-      <c r="L277" s="16" t="inlineStr">
-        <is>
-          <t>Печать организации</t>
-        </is>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" s="16" t="inlineStr">
-        <is>
-          <t>Расследование профзаболеваний</t>
-        </is>
-      </c>
-      <c r="B278" s="16" t="inlineStr">
-        <is>
-          <t>Постановление Правительства РФ от 05.07.2022 № 1206 "О порядке расследования и учета случаев профессиональных заболеваний работников"</t>
-        </is>
-      </c>
-      <c r="C278" s="16" t="inlineStr">
-        <is>
-          <t>п. 12 Правил (постановление № 1206)</t>
-        </is>
-      </c>
-      <c r="D278" s="16" t="inlineStr">
-        <is>
-          <t>Медицинское заключение о наличии или об отсутствии профессионального заболевания</t>
-        </is>
-      </c>
-      <c r="E278" s="16" t="inlineStr">
-        <is>
-          <t>ДА</t>
-        </is>
-      </c>
-      <c r="F278" s="16" t="inlineStr">
-        <is>
-          <t>ДА</t>
-        </is>
-      </c>
-      <c r="G278" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H278" s="16" t="inlineStr">
-        <is>
-          <t>Работник</t>
-        </is>
-      </c>
-      <c r="I278" s="16" t="inlineStr">
-        <is>
-          <t>собственноручная</t>
-        </is>
-      </c>
-      <c r="J278" s="16" t="inlineStr">
-        <is>
-          <t>Ознакомление</t>
-        </is>
-      </c>
-      <c r="K278" s="16" t="inlineStr">
-        <is>
-          <t>УСЛОВНО</t>
-        </is>
-      </c>
-      <c r="L278" s="16" t="inlineStr">
-        <is>
-          <t>Печать организации</t>
-        </is>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" s="16" t="inlineStr">
-        <is>
-          <t>Расследование профзаболеваний</t>
-        </is>
-      </c>
-      <c r="B279" s="16" t="inlineStr">
-        <is>
-          <t>Постановление Правительства РФ от 05.07.2022 № 1206 "О порядке расследования и учета случаев профессиональных заболеваний работников"</t>
-        </is>
-      </c>
-      <c r="C279" s="16" t="inlineStr">
-        <is>
-          <t>п. 11, 14 Правил (постановление № 1206)</t>
-        </is>
-      </c>
-      <c r="D279" s="16" t="inlineStr">
-        <is>
-          <t>Извещение об установлении заключительного диагноза - острое профессиональное заболевание или хроническое профессиональное заболевание, его уточнении или отмене</t>
-        </is>
-      </c>
-      <c r="E279" s="16" t="inlineStr">
-        <is>
-          <t>ДА</t>
-        </is>
-      </c>
-      <c r="F279" s="16" t="inlineStr">
-        <is>
-          <t>ДА</t>
-        </is>
-      </c>
-      <c r="G279" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H279" s="16" t="inlineStr">
-        <is>
-          <t>Центр профессиональной патологии</t>
-        </is>
-      </c>
-      <c r="I279" s="16" t="inlineStr">
-        <is>
-          <t>собственноручная или УКЭП</t>
-        </is>
-      </c>
-      <c r="J279" s="16" t="inlineStr">
+      <c r="K311" s="16" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="L311" s="16" t="inlineStr">
+        <is>
+          <t>Нет ограничений</t>
+        </is>
+      </c>
+    </row>
+    <row r="312" customFormat="1" s="14">
+      <c r="A312" s="16" t="inlineStr">
+        <is>
+          <t>Социальное страхование</t>
+        </is>
+      </c>
+      <c r="B312" s="16" t="inlineStr">
+        <is>
+          <t>ФЗ от 24.07.1998 № 125-ФЗ; ПП РФ от 30.05.2012 № 524; приказ Минтруда от 01.08.2012 № 39н; приказ Минтруда от 11.07.2024 № 347н; приказ Минтруда от 29.10.2021 № 771н</t>
+        </is>
+      </c>
+      <c r="C312" s="16" t="inlineStr">
+        <is>
+          <t>п. 4, 8–10 Правил (приказ № 347н)</t>
+        </is>
+      </c>
+      <c r="D312" s="16" t="inlineStr">
+        <is>
+          <t>Заявление о финансовом обеспечении предупредительных мер</t>
+        </is>
+      </c>
+      <c r="E312" s="16" t="inlineStr">
+        <is>
+          <t>ДА (рекомендуемый образец — приложение № 1 к Правилам)</t>
+        </is>
+      </c>
+      <c r="F312" s="16" t="inlineStr">
+        <is>
+          <t>ДА (при обращении за финансированием)</t>
+        </is>
+      </c>
+      <c r="G312" s="16" t="inlineStr">
+        <is>
+          <t>Наименование страхователя; регистрационный номер; год; заявляемый объем средств; перечень прилагаемых документов; сведения о расчетном счете (при возмещении)</t>
+        </is>
+      </c>
+      <c r="H312" s="16" t="inlineStr">
+        <is>
+          <t>Руководитель организации (страхователь) / уполномоченный представитель</t>
+        </is>
+      </c>
+      <c r="I312" s="16" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J312" s="16" t="inlineStr">
+        <is>
+          <t>Заявление</t>
+        </is>
+      </c>
+      <c r="K312" s="16" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="L312" s="16" t="inlineStr">
+        <is>
+          <t>Нет ограничений</t>
+        </is>
+      </c>
+    </row>
+    <row r="313" customFormat="1" s="14">
+      <c r="A313" s="16" t="inlineStr">
+        <is>
+          <t>Социальное страхование</t>
+        </is>
+      </c>
+      <c r="B313" s="16" t="inlineStr">
+        <is>
+          <t>ФЗ от 24.07.1998 № 125-ФЗ; ПП РФ от 30.05.2012 № 524; приказ Минтруда от 01.08.2012 № 39н; приказ Минтруда от 11.07.2024 № 347н; приказ Минтруда от 29.10.2021 № 771н</t>
+        </is>
+      </c>
+      <c r="C313" s="16" t="inlineStr">
+        <is>
+          <t>п. 8–10, 13 Правил (приказ № 347н)</t>
+        </is>
+      </c>
+      <c r="D313" s="16" t="inlineStr">
+        <is>
+          <t>План финансового обеспечения предупредительных мер</t>
+        </is>
+      </c>
+      <c r="E313" s="16" t="inlineStr">
+        <is>
+          <t>ДА (рекомендуемый образец — приложение № 2 к Правилам)</t>
+        </is>
+      </c>
+      <c r="F313" s="16" t="inlineStr">
+        <is>
+          <t>ДА (при обращении за финансированием)</t>
+        </is>
+      </c>
+      <c r="G313" s="16" t="inlineStr">
+        <is>
+          <t>Мероприятия; срок исполнения; количество работников; стоимость; ОКОФ; обосновывающие документы; итоговая сумма; сведения о страхователе</t>
+        </is>
+      </c>
+      <c r="H313" s="16" t="inlineStr">
+        <is>
+          <t>Руководитель организации (страхователь)</t>
+        </is>
+      </c>
+      <c r="I313" s="16" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J313" s="16" t="inlineStr">
         <is>
           <t>Утверждение</t>
         </is>
       </c>
-      <c r="K279" s="16" t="inlineStr">
-        <is>
-          <t>УСЛОВНО</t>
-        </is>
-      </c>
-      <c r="L279" s="16" t="inlineStr">
-        <is>
-          <t>Печать организации</t>
-        </is>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" s="16" t="inlineStr">
-        <is>
-          <t>Расследование профзаболеваний</t>
-        </is>
-      </c>
-      <c r="B280" s="16" t="inlineStr">
-        <is>
-          <t>Постановление Правительства РФ от 05.07.2022 № 1206 "О порядке расследования и учета случаев профессиональных заболеваний работников"</t>
-        </is>
-      </c>
-      <c r="C280" s="16" t="inlineStr">
-        <is>
-          <t>п. 13 Правил (постановление № 1206)</t>
-        </is>
-      </c>
-      <c r="D280" s="16" t="inlineStr">
-        <is>
-          <t>Заявление о проведении экспертизы связи заболевания с профессией (в целях изменения или отмены диагноза профессионального заболевания)</t>
-        </is>
-      </c>
-      <c r="E280" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="F280" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G280" s="16" t="inlineStr">
-        <is>
-          <t>Заявление о проведении экспертизы связи заболевания с профессией в свободной форме; приложение документов, указанных в п. 5 и 10 Правил; при подаче работником — согласие на запрос документации, необходимой для проведения экспертизы</t>
-        </is>
-      </c>
-      <c r="H280" s="16" t="inlineStr">
-        <is>
-          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
-        </is>
-      </c>
-      <c r="I280" s="16" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J280" s="16" t="inlineStr">
-        <is>
-          <t>Заявление</t>
-        </is>
-      </c>
-      <c r="K280" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="L280" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" s="16" t="inlineStr">
-        <is>
-          <t>Расследование профзаболеваний</t>
-        </is>
-      </c>
-      <c r="B281" s="16" t="inlineStr">
-        <is>
-          <t>Постановление Правительства РФ от 05.07.2022 № 1206 "О порядке расследования и учета случаев профессиональных заболеваний работников"</t>
-        </is>
-      </c>
-      <c r="C281" s="16" t="inlineStr">
-        <is>
-          <t>п. 13 Правил (постановление № 1206)</t>
-        </is>
-      </c>
-      <c r="D281" s="16" t="inlineStr">
-        <is>
-          <t>Заявление о проведении экспертизы связи заболевания с профессией (в целях изменения или отмены диагноза профессионального заболевания)</t>
-        </is>
-      </c>
-      <c r="E281" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="F281" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G281" s="16" t="inlineStr">
-        <is>
-          <t>Заявление о проведении экспертизы связи заболевания с профессией в свободной форме; приложение документов, указанных в п. 5 и 10 Правил; при подаче работником — согласие на запрос документации, необходимой для проведения экспертизы</t>
-        </is>
-      </c>
-      <c r="H281" s="16" t="inlineStr">
-        <is>
-          <t>Работник (его представитель)</t>
-        </is>
-      </c>
-      <c r="I281" s="16" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J281" s="16" t="inlineStr">
-        <is>
-          <t>Заявление</t>
-        </is>
-      </c>
-      <c r="K281" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="L281" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" s="16" t="inlineStr">
-        <is>
-          <t>Расследование профзаболеваний</t>
-        </is>
-      </c>
-      <c r="B282" s="16" t="inlineStr">
-        <is>
-          <t>Постановление Правительства РФ от 05.07.2022 № 1206 "О порядке расследования и учета случаев профессиональных заболеваний работников"</t>
-        </is>
-      </c>
-      <c r="C282" s="16" t="inlineStr">
-        <is>
-          <t>п. 15, 23 «а» Правил (постановление № 1206)</t>
-        </is>
-      </c>
-      <c r="D282" s="16" t="inlineStr">
-        <is>
-          <t>Приказ (распоряжение) о создании комиссии по расследованию случая профессионального заболевания</t>
-        </is>
-      </c>
-      <c r="E282" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="F282" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G282" s="16" t="inlineStr">
-        <is>
-          <t>Создание комиссии в течение 10 рабочих дней со дня получения извещения о заключительном диагнозе; председатель — руководитель (заместитель руководителя) органа государственного санитарно-эпидемиологического контроля (надзора); состав: представитель работодателя, специалист по охране труда (или лицо, ответственное за организацию работы по охране труда), представитель центра профессиональной патологии, представитель выборного органа первичной профсоюзной организации или иного уполномоченного работниками представительного органа (при наличии), страховщик (по согласованию); при необходимости — представители работодателей по прежним местам работы; число членов комиссии — нечетное</t>
-        </is>
-      </c>
-      <c r="H282" s="16" t="inlineStr">
-        <is>
-          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
-        </is>
-      </c>
-      <c r="I282" s="16" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J282" s="16" t="inlineStr">
+      <c r="K313" s="16" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="L313" s="16" t="inlineStr">
+        <is>
+          <t>Нет ограничений</t>
+        </is>
+      </c>
+    </row>
+    <row r="314" customFormat="1" s="14">
+      <c r="A314" s="16" t="inlineStr">
+        <is>
+          <t>Социальное страхование</t>
+        </is>
+      </c>
+      <c r="B314" s="16" t="inlineStr">
+        <is>
+          <t>ФЗ от 24.07.1998 № 125-ФЗ; ПП РФ от 30.05.2012 № 524; приказ Минтруда от 01.08.2012 № 39н; приказ Минтруда от 11.07.2024 № 347н; приказ Минтруда от 29.10.2021 № 771н</t>
+        </is>
+      </c>
+      <c r="C314" s="16" t="inlineStr">
+        <is>
+          <t>п. 6, 9 Правил (приказ № 347н)</t>
+        </is>
+      </c>
+      <c r="D314" s="16" t="inlineStr">
+        <is>
+          <t>Перечень мероприятий, планируемых к реализации в рамках финансового обеспечения предупредительных мер (как часть комплекта / плана)</t>
+        </is>
+      </c>
+      <c r="E314" s="16" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F314" s="16" t="inlineStr">
+        <is>
+          <t>ДА (в составе плана)</t>
+        </is>
+      </c>
+      <c r="G314" s="16" t="inlineStr">
+        <is>
+          <t>Конкретные предупредительные меры из п. 2 Правил; сроки; стоимость; связь с улучшением условий труда</t>
+        </is>
+      </c>
+      <c r="H314" s="16" t="inlineStr">
+        <is>
+          <t>Руководитель организации (страхователь)</t>
+        </is>
+      </c>
+      <c r="I314" s="16" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J314" s="16" t="inlineStr">
         <is>
           <t>Утверждение</t>
         </is>
       </c>
-      <c r="K282" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="L282" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" s="16" t="inlineStr">
-        <is>
-          <t>Расследование профзаболеваний</t>
-        </is>
-      </c>
-      <c r="B283" s="16" t="inlineStr">
-        <is>
-          <t>Постановление Правительства РФ от 05.07.2022 № 1206 "О порядке расследования и учета случаев профессиональных заболеваний работников"</t>
-        </is>
-      </c>
-      <c r="C283" s="16" t="inlineStr">
-        <is>
-          <t>п. 17 Правил (постановление № 1206)</t>
-        </is>
-      </c>
-      <c r="D283" s="16" t="inlineStr">
-        <is>
-          <t>Документы, подтверждающие замену члена комиссии (включая председателя комиссии)</t>
-        </is>
-      </c>
-      <c r="E283" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="F283" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G283" s="16" t="inlineStr">
-        <is>
-          <t>Документы, подтверждающие замену члена комиссии (включая председателя), с указанием причины принятого решения; приобщаются к материалам расследования</t>
-        </is>
-      </c>
-      <c r="H283" s="16" t="inlineStr">
-        <is>
-          <t>Организация (орган), направившая члена комиссии</t>
-        </is>
-      </c>
-      <c r="I283" s="16" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J283" s="16" t="inlineStr">
-        <is>
-          <t>Утверждение</t>
-        </is>
-      </c>
-      <c r="K283" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="L283" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" s="16" t="inlineStr">
-        <is>
-          <t>Расследование профзаболеваний</t>
-        </is>
-      </c>
-      <c r="B284" s="16" t="inlineStr">
-        <is>
-          <t>Постановление Правительства РФ от 05.07.2022 № 1206 "О порядке расследования и учета случаев профессиональных заболеваний работников"</t>
-        </is>
-      </c>
-      <c r="C284" s="16" t="inlineStr">
-        <is>
-          <t>п. 17 Правил (постановление № 1206)</t>
-        </is>
-      </c>
-      <c r="D284" s="16" t="inlineStr">
-        <is>
-          <t>Изменения в приказ (распоряжение) об образовании комиссии по расследованию случая профессионального заболевания</t>
-        </is>
-      </c>
-      <c r="E284" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="F284" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G284" s="16" t="inlineStr">
-        <is>
-          <t>Изменения в приказ (распоряжение) об образовании комиссии, вносимые работодателем в течение суток после получения письменного уведомления о замене члена комиссии; приобщаются к материалам расследования</t>
-        </is>
-      </c>
-      <c r="H284" s="16" t="inlineStr">
-        <is>
-          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
-        </is>
-      </c>
-      <c r="I284" s="16" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J284" s="16" t="inlineStr">
-        <is>
-          <t>Утверждение</t>
-        </is>
-      </c>
-      <c r="K284" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="L284" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" s="16" t="inlineStr">
-        <is>
-          <t>Расследование профзаболеваний</t>
-        </is>
-      </c>
-      <c r="B285" s="16" t="inlineStr">
-        <is>
-          <t>Постановление Правительства РФ от 05.07.2022 № 1206 "О порядке расследования и учета случаев профессиональных заболеваний работников"</t>
-        </is>
-      </c>
-      <c r="C285" s="16" t="inlineStr">
-        <is>
-          <t>п. 17 Правил (постановление № 1206)</t>
-        </is>
-      </c>
-      <c r="D285" s="16" t="inlineStr">
-        <is>
-          <t>Письменное уведомление о замене члена комиссии (включая председателя комиссии)</t>
-        </is>
-      </c>
-      <c r="E285" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="F285" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G285" s="16" t="inlineStr">
-        <is>
-          <t>Письменное уведомление о замене члена комиссии (включая председателя комиссии)</t>
-        </is>
-      </c>
-      <c r="H285" s="16" t="inlineStr">
-        <is>
-          <t>Организация (орган), направившая члена комиссии</t>
-        </is>
-      </c>
-      <c r="I285" s="16" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J285" s="16" t="inlineStr">
-        <is>
-          <t>Уведомление</t>
-        </is>
-      </c>
-      <c r="K285" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="L285" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" s="16" t="inlineStr">
-        <is>
-          <t>Расследование профзаболеваний</t>
-        </is>
-      </c>
-      <c r="B286" s="16" t="inlineStr">
-        <is>
-          <t>Постановление Правительства РФ от 05.07.2022 № 1206 "О порядке расследования и учета случаев профессиональных заболеваний работников"</t>
-        </is>
-      </c>
-      <c r="C286" s="16" t="inlineStr">
-        <is>
-          <t>п. 22, 23 «ж» Правил (постановление № 1206)</t>
-        </is>
-      </c>
-      <c r="D286" s="16" t="inlineStr">
-        <is>
-          <t>Протокол объяснений работника, опросов лиц, работавших с ним, и других лиц</t>
-        </is>
-      </c>
-      <c r="E286" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="F286" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G286" s="16" t="inlineStr">
-        <is>
-          <t>Результаты объяснений работника, опросов лиц, работавших с ним, и других лиц</t>
-        </is>
-      </c>
-      <c r="H286" s="16" t="inlineStr">
-        <is>
-          <t>Член комиссии по расследованию случая профессионального заболевания</t>
-        </is>
-      </c>
-      <c r="I286" s="16" t="inlineStr">
-        <is>
-          <t>собственноручная или ЭП</t>
-        </is>
-      </c>
-      <c r="J286" s="16" t="inlineStr">
-        <is>
-          <t>Утверждение</t>
-        </is>
-      </c>
-      <c r="K286" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="L286" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" s="16" t="inlineStr">
-        <is>
-          <t>Расследование профзаболеваний</t>
-        </is>
-      </c>
-      <c r="B287" s="16" t="inlineStr">
-        <is>
-          <t>Постановление Правительства РФ от 05.07.2022 № 1206 "О порядке расследования и учета случаев профессиональных заболеваний работников"</t>
-        </is>
-      </c>
-      <c r="C287" s="16" t="inlineStr">
-        <is>
-          <t>п. 22, 23 «ж» Правил (постановление № 1206)</t>
-        </is>
-      </c>
-      <c r="D287" s="16" t="inlineStr">
-        <is>
-          <t>Протокол объяснений работника, опросов лиц, работавших с ним, и других лиц</t>
-        </is>
-      </c>
-      <c r="E287" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="F287" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G287" s="16" t="inlineStr">
-        <is>
-          <t>Результаты объяснений работника, опросов лиц, работавших с ним, и других лиц</t>
-        </is>
-      </c>
-      <c r="H287" s="16" t="inlineStr">
-        <is>
-          <t>Работник (опрашиваемое лицо)</t>
-        </is>
-      </c>
-      <c r="I287" s="16" t="inlineStr">
-        <is>
-          <t>собственноручная или ЭП</t>
-        </is>
-      </c>
-      <c r="J287" s="16" t="inlineStr">
-        <is>
-          <t>Подтверждение (?)</t>
-        </is>
-      </c>
-      <c r="K287" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="L287" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" s="16" t="inlineStr">
-        <is>
-          <t>Расследование профзаболеваний</t>
-        </is>
-      </c>
-      <c r="B288" s="16" t="inlineStr">
-        <is>
-          <t>Постановление Правительства РФ от 05.07.2022 № 1206 "О порядке расследования и учета случаев профессиональных заболеваний работников"</t>
-        </is>
-      </c>
-      <c r="C288" s="16" t="inlineStr">
-        <is>
-          <t>п. 21 «а», 23 «а»–«л» Правил (постановление № 1206)</t>
-        </is>
-      </c>
-      <c r="D288" s="16" t="inlineStr">
-        <is>
-          <t>Документы и материалы, характеризующие условия труда на рабочем месте (участке, в цехе), в том числе архивные</t>
-        </is>
-      </c>
-      <c r="E288" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="F288" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G288" s="16" t="inlineStr">
-        <is>
-          <t>Документы и материалы, в том числе архивные, характеризующие условия труда на рабочем месте (участке, в цехе), представляемые работодателем для проведения расследования</t>
-        </is>
-      </c>
-      <c r="H288" s="16" t="inlineStr">
-        <is>
-          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
-        </is>
-      </c>
-      <c r="I288" s="16" t="inlineStr">
-        <is>
-          <t>собственноручная или ЭП</t>
-        </is>
-      </c>
-      <c r="J288" s="16" t="inlineStr">
-        <is>
-          <t>Утверждение</t>
-        </is>
-      </c>
-      <c r="K288" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="L288" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" s="16" t="inlineStr">
-        <is>
-          <t>Расследование профзаболеваний</t>
-        </is>
-      </c>
-      <c r="B289" s="16" t="inlineStr">
-        <is>
-          <t>Постановление Правительства РФ от 05.07.2022 № 1206 "О порядке расследования и учета случаев профессиональных заболеваний работников"</t>
-        </is>
-      </c>
-      <c r="C289" s="16" t="inlineStr">
-        <is>
-          <t>п. 23 «е» Правил (постановление № 1206)</t>
-        </is>
-      </c>
-      <c r="D289" s="16" t="inlineStr">
-        <is>
-          <t>Выписка из журналов регистрации инструктажей и протоколов проверки знаний работника по охране труда</t>
-        </is>
-      </c>
-      <c r="E289" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="F289" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G289" s="16" t="inlineStr">
-        <is>
-          <t>Выписка из журналов регистрации инструктажей и протоколов проверки знаний работника по охране труда</t>
-        </is>
-      </c>
-      <c r="H289" s="16" t="inlineStr">
-        <is>
-          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
-        </is>
-      </c>
-      <c r="I289" s="16" t="inlineStr">
-        <is>
-          <t>собственноручная или ЭП</t>
-        </is>
-      </c>
-      <c r="J289" s="16" t="inlineStr">
-        <is>
-          <t>Утверждение</t>
-        </is>
-      </c>
-      <c r="K289" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="L289" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" s="16" t="inlineStr">
-        <is>
-          <t>Расследование профзаболеваний</t>
-        </is>
-      </c>
-      <c r="B290" s="16" t="inlineStr">
-        <is>
-          <t>Постановление Правительства РФ от 05.07.2022 № 1206 "О порядке расследования и учета случаев профессиональных заболеваний работников"</t>
-        </is>
-      </c>
-      <c r="C290" s="16" t="inlineStr">
-        <is>
-          <t>п. 23 «д» Правил (постановление № 1206)</t>
-        </is>
-      </c>
-      <c r="D290" s="16" t="inlineStr">
-        <is>
-          <t>Медицинские заключения по результатам обязательных предварительных и периодических медицинских осмотров</t>
-        </is>
-      </c>
-      <c r="E290" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="F290" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G290" s="16" t="inlineStr">
-        <is>
-          <t>Медицинские заключения по результатам обязательных предварительных и периодических медицинских осмотров</t>
-        </is>
-      </c>
-      <c r="H290" s="16" t="inlineStr">
-        <is>
-          <t>Медицинская организация</t>
-        </is>
-      </c>
-      <c r="I290" s="16" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J290" s="16" t="inlineStr">
-        <is>
-          <t>Утверждение</t>
-        </is>
-      </c>
-      <c r="K290" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="L290" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" s="16" t="inlineStr">
-        <is>
-          <t>Расследование профзаболеваний</t>
-        </is>
-      </c>
-      <c r="B291" s="16" t="inlineStr">
-        <is>
-          <t>Постановление Правительства РФ от 05.07.2022 № 1206 "О порядке расследования и учета случаев профессиональных заболеваний работников"</t>
-        </is>
-      </c>
-      <c r="C291" s="16" t="inlineStr">
-        <is>
-          <t>п. 23 «з» Правил (постановление № 1206)</t>
-        </is>
-      </c>
-      <c r="D291" s="16" t="inlineStr">
-        <is>
-          <t>Экспертные заключения специалистов, результаты исследований и экспериментов</t>
-        </is>
-      </c>
-      <c r="E291" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="F291" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G291" s="16" t="inlineStr">
-        <is>
-          <t>Экспертные заключения специалистов, результаты исследований и экспериментов (в том числе проводимых по требованию членов комиссии за счет средств работодателя)</t>
-        </is>
-      </c>
-      <c r="H291" s="16" t="inlineStr">
-        <is>
-          <t>Эксперт (специалист)</t>
-        </is>
-      </c>
-      <c r="I291" s="16" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J291" s="16" t="inlineStr">
-        <is>
-          <t>Утверждение</t>
-        </is>
-      </c>
-      <c r="K291" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="L291" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" s="16" t="inlineStr">
-        <is>
-          <t>Расследование профзаболеваний</t>
-        </is>
-      </c>
-      <c r="B292" s="16" t="inlineStr">
-        <is>
-          <t>Постановление Правительства РФ от 05.07.2022 № 1206 "О порядке расследования и учета случаев профессиональных заболеваний работников"</t>
-        </is>
-      </c>
-      <c r="C292" s="16" t="inlineStr">
-        <is>
-          <t>п. 23 «и» Правил (постановление № 1206)</t>
-        </is>
-      </c>
-      <c r="D292" s="16" t="inlineStr">
-        <is>
-          <t>Копии документов, подтверждающих выдачу работнику средств индивидуальной защиты</t>
-        </is>
-      </c>
-      <c r="E292" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="F292" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G292" s="16" t="inlineStr">
-        <is>
-          <t>Копии документов, подтверждающих выдачу работнику средств индивидуальной защиты</t>
-        </is>
-      </c>
-      <c r="H292" s="16" t="inlineStr">
-        <is>
-          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
-        </is>
-      </c>
-      <c r="I292" s="16" t="inlineStr">
-        <is>
-          <t>собственноручная или ЭП</t>
-        </is>
-      </c>
-      <c r="J292" s="16" t="inlineStr">
-        <is>
-          <t>Утверждение</t>
-        </is>
-      </c>
-      <c r="K292" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="L292" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" s="16" t="inlineStr">
-        <is>
-          <t>Расследование профзаболеваний</t>
-        </is>
-      </c>
-      <c r="B293" s="16" t="inlineStr">
-        <is>
-          <t>Постановление Правительства РФ от 05.07.2022 № 1206 "О порядке расследования и учета случаев профессиональных заболеваний работников"</t>
-        </is>
-      </c>
-      <c r="C293" s="16" t="inlineStr">
-        <is>
-          <t>п. 23 «к» Правил (постановление № 1206)</t>
-        </is>
-      </c>
-      <c r="D293" s="16" t="inlineStr">
-        <is>
-          <t>Выписки из ранее выданных по данному производству (объекту) предписаний органа государственного санитарно-эпидемиологического контроля (надзора)</t>
-        </is>
-      </c>
-      <c r="E293" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="F293" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G293" s="16" t="inlineStr">
-        <is>
-          <t>Выписки из ранее выданных по данному производству (объекту) предписаний органа государственного санитарно-эпидемиологического контроля (надзора)</t>
-        </is>
-      </c>
-      <c r="H293" s="16" t="inlineStr">
-        <is>
-          <t>Орган государственного санитарно-эпидемиологического контроля (надзора)</t>
-        </is>
-      </c>
-      <c r="I293" s="16" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J293" s="16" t="inlineStr">
-        <is>
-          <t>Утверждение</t>
-        </is>
-      </c>
-      <c r="K293" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="L293" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" s="16" t="inlineStr">
-        <is>
-          <t>Расследование профзаболеваний</t>
-        </is>
-      </c>
-      <c r="B294" s="16" t="inlineStr">
-        <is>
-          <t>Постановление Правительства РФ от 05.07.2022 № 1206 "О порядке расследования и учета случаев профессиональных заболеваний работников"</t>
-        </is>
-      </c>
-      <c r="C294" s="16" t="inlineStr">
-        <is>
-          <t>п. 25, 31 Правил (постановление № 1206)</t>
-        </is>
-      </c>
-      <c r="D294" s="16" t="inlineStr">
-        <is>
-          <t>Мотивированное мнение (заключение) выборного органа первичной профсоюзной организации или иного уполномоченного работниками представительного органа о степени вины работника</t>
-        </is>
-      </c>
-      <c r="E294" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="F294" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G294" s="16" t="inlineStr">
-        <is>
-          <t>Мотивированное мнение (заключение) о степени вины работника (в процентах) при установлении факта грубой неосторожности работника, содействовавшей возникновению или увеличению вреда, причиненного его здоровью; копия заключения прилагается к акту</t>
-        </is>
-      </c>
-      <c r="H294" s="16" t="inlineStr">
-        <is>
-          <t>Выборный орган первичной профсоюзной организации или иного уполномоченного работниками представительного органа</t>
-        </is>
-      </c>
-      <c r="I294" s="16" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J294" s="16" t="inlineStr">
-        <is>
-          <t>Согласование</t>
-        </is>
-      </c>
-      <c r="K294" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="L294" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" s="16" t="inlineStr">
-        <is>
-          <t>Расследование профзаболеваний</t>
-        </is>
-      </c>
-      <c r="B295" s="16" t="inlineStr">
-        <is>
-          <t>Постановление Правительства РФ от 05.07.2022 № 1206 "О порядке расследования и учета случаев профессиональных заболеваний работников"</t>
-        </is>
-      </c>
-      <c r="C295" s="16" t="inlineStr">
-        <is>
-          <t>п. 26 Правил (постановление № 1206)</t>
-        </is>
-      </c>
-      <c r="D295" s="16" t="inlineStr">
-        <is>
-          <t>Протокол заседания комиссии по расследованию случая профессионального заболевания</t>
-        </is>
-      </c>
-      <c r="E295" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="F295" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G295" s="16" t="inlineStr">
-        <is>
-          <t>Итоги заседания комиссии по расследованию случая профессионального заболевания (заседание может проходить в очной форме или с использованием средств дистанционного взаимодействия)</t>
-        </is>
-      </c>
-      <c r="H295" s="16" t="inlineStr">
-        <is>
-          <t>Председатель комиссии по расследованию случая профессионального заболевания</t>
-        </is>
-      </c>
-      <c r="I295" s="16" t="inlineStr">
-        <is>
-          <t>собственноручная или ЭП</t>
-        </is>
-      </c>
-      <c r="J295" s="16" t="inlineStr">
-        <is>
-          <t>Утверждение</t>
-        </is>
-      </c>
-      <c r="K295" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="L295" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" s="16" t="inlineStr">
-        <is>
-          <t>Расследование профзаболеваний</t>
-        </is>
-      </c>
-      <c r="B296" s="16" t="inlineStr">
-        <is>
-          <t>Постановление Правительства РФ от 05.07.2022 № 1206 "О порядке расследования и учета случаев профессиональных заболеваний работников"</t>
-        </is>
-      </c>
-      <c r="C296" s="16" t="inlineStr">
-        <is>
-          <t>п. 26 Правил (постановление № 1206)</t>
-        </is>
-      </c>
-      <c r="D296" s="16" t="inlineStr">
-        <is>
-          <t>Протокол заседания комиссии по расследованию случая профессионального заболевания (при разногласиях или отказе от подписания (утверждения) документов)</t>
-        </is>
-      </c>
-      <c r="E296" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="F296" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G296" s="16" t="inlineStr">
-        <is>
-          <t>Протокол в произвольной форме: при разногласиях — решение большинством голосов; при отказе члена комиссии (включая председателя) от подписания или утверждения документов — с указанием причины отказа; копия протокола направляется в организацию (орган), представителем которого является лицо, участвующее в работе комиссии</t>
-        </is>
-      </c>
-      <c r="H296" s="16" t="inlineStr">
-        <is>
-          <t>Председатель комиссии по расследованию случая профессионального заболевания</t>
-        </is>
-      </c>
-      <c r="I296" s="16" t="inlineStr">
-        <is>
-          <t>собственноручная или ЭП</t>
-        </is>
-      </c>
-      <c r="J296" s="16" t="inlineStr">
-        <is>
-          <t>Утверждение</t>
-        </is>
-      </c>
-      <c r="K296" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="L296" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" s="16" t="inlineStr">
-        <is>
-          <t>Расследование профзаболеваний</t>
-        </is>
-      </c>
-      <c r="B297" s="16" t="inlineStr">
-        <is>
-          <t>Постановление Правительства РФ от 05.07.2022 № 1206 "О порядке расследования и учета случаев профессиональных заболеваний работников"</t>
-        </is>
-      </c>
-      <c r="C297" s="16" t="inlineStr">
-        <is>
-          <t>п. 26 Правил (постановление № 1206)</t>
-        </is>
-      </c>
-      <c r="D297" s="16" t="inlineStr">
-        <is>
-          <t>Протокол заседания комиссии по расследованию случая профессионального заболевания (при разногласиях или отказе от подписания (утверждения) документов)</t>
-        </is>
-      </c>
-      <c r="E297" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="F297" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G297" s="16" t="inlineStr">
-        <is>
-          <t>Протокол в произвольной форме: при разногласиях — решение большинством голосов; при отказе члена комиссии (включая председателя) от подписания или утверждения документов — с указанием причины отказа; копия протокола направляется в организацию (орган), представителем которого является лицо, участвующее в работе комиссии</t>
-        </is>
-      </c>
-      <c r="H297" s="16" t="inlineStr">
-        <is>
-          <t>Член комиссии по расследованию случая профессионального заболевания</t>
-        </is>
-      </c>
-      <c r="I297" s="16" t="inlineStr">
-        <is>
-          <t>собственноручная или ЭП</t>
-        </is>
-      </c>
-      <c r="J297" s="16" t="inlineStr">
-        <is>
-          <t>Подтверждение (?)</t>
-        </is>
-      </c>
-      <c r="K297" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="L297" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" s="16" t="inlineStr">
-        <is>
-          <t>Расследование профзаболеваний</t>
-        </is>
-      </c>
-      <c r="B298" s="16" t="inlineStr">
-        <is>
-          <t>Постановление Правительства РФ от 05.07.2022 № 1206 "О порядке расследования и учета случаев профессиональных заболеваний работников"</t>
-        </is>
-      </c>
-      <c r="C298" s="16" t="inlineStr">
-        <is>
-          <t>п. 26 Правил (постановление № 1206)</t>
-        </is>
-      </c>
-      <c r="D298" s="16" t="inlineStr">
-        <is>
-          <t>Протокол заседания комиссии по расследованию случая профессионального заболевания (при заключении о том, что заболевание не связано с воздействием вредного производственного фактора (факторов) и (или) получено не при исполнении трудовых обязанностей)</t>
-        </is>
-      </c>
-      <c r="E298" s="16" t="inlineStr">
-        <is>
-          <t>ДА</t>
-        </is>
-      </c>
-      <c r="F298" s="16" t="inlineStr">
-        <is>
-          <t>ДА</t>
-        </is>
-      </c>
-      <c r="G298" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H298" s="16" t="inlineStr">
-        <is>
-          <t>Председатель комиссии по расследованию случая профессионального заболевания</t>
-        </is>
-      </c>
-      <c r="I298" s="16" t="inlineStr">
-        <is>
-          <t>собственноручная или ЭП</t>
-        </is>
-      </c>
-      <c r="J298" s="16" t="inlineStr">
-        <is>
-          <t>Утверждение</t>
-        </is>
-      </c>
-      <c r="K298" s="16" t="inlineStr">
-        <is>
-          <t>УСЛОВНО</t>
-        </is>
-      </c>
-      <c r="L298" s="16" t="inlineStr">
-        <is>
-          <t>Печать организации</t>
-        </is>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" s="16" t="inlineStr">
-        <is>
-          <t>Расследование профзаболеваний</t>
-        </is>
-      </c>
-      <c r="B299" s="16" t="inlineStr">
-        <is>
-          <t>Постановление Правительства РФ от 05.07.2022 № 1206 "О порядке расследования и учета случаев профессиональных заболеваний работников"</t>
-        </is>
-      </c>
-      <c r="C299" s="16" t="inlineStr">
-        <is>
-          <t>п. 26 Правил (постановление № 1206)</t>
-        </is>
-      </c>
-      <c r="D299" s="16" t="inlineStr">
-        <is>
-          <t>Протокол заседания комиссии по расследованию случая профессионального заболевания (при заключении о том, что заболевание не связано с воздействием вредного производственного фактора (факторов) и (или) получено не при исполнении трудовых обязанностей)</t>
-        </is>
-      </c>
-      <c r="E299" s="16" t="inlineStr">
-        <is>
-          <t>ДА</t>
-        </is>
-      </c>
-      <c r="F299" s="16" t="inlineStr">
-        <is>
-          <t>ДА</t>
-        </is>
-      </c>
-      <c r="G299" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H299" s="16" t="inlineStr">
-        <is>
-          <t>Член комиссии по расследованию случая профессионального заболевания</t>
-        </is>
-      </c>
-      <c r="I299" s="16" t="inlineStr">
-        <is>
-          <t>собственноручная или ЭП</t>
-        </is>
-      </c>
-      <c r="J299" s="16" t="inlineStr">
-        <is>
-          <t>Подтверждение (?)</t>
-        </is>
-      </c>
-      <c r="K299" s="16" t="inlineStr">
-        <is>
-          <t>УСЛОВНО</t>
-        </is>
-      </c>
-      <c r="L299" s="16" t="inlineStr">
-        <is>
-          <t>Печать организации</t>
-        </is>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" s="16" t="inlineStr">
-        <is>
-          <t>Расследование профзаболеваний</t>
-        </is>
-      </c>
-      <c r="B300" s="16" t="inlineStr">
-        <is>
-          <t>Постановление Правительства РФ от 05.07.2022 № 1206 "О порядке расследования и учета случаев профессиональных заболеваний работников"</t>
-        </is>
-      </c>
-      <c r="C300" s="16" t="inlineStr">
-        <is>
-          <t>п. 26 Правил (постановление № 1206)</t>
-        </is>
-      </c>
-      <c r="D300" s="16" t="inlineStr">
-        <is>
-          <t>Аргументированное особое мнение члена комиссии (включая председателя комиссии)</t>
-        </is>
-      </c>
-      <c r="E300" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="F300" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G300" s="16" t="inlineStr">
-        <is>
-          <t>Аргументированное особое мнение члена комиссии (включая председателя), не согласного с принятым решением; приобщается к материалам расследования</t>
-        </is>
-      </c>
-      <c r="H300" s="16" t="inlineStr">
-        <is>
-          <t>Член комиссии (включая председателя комиссии) по расследованию случая профессионального заболевания</t>
-        </is>
-      </c>
-      <c r="I300" s="16" t="inlineStr">
-        <is>
-          <t>собственноручная или ЭП</t>
-        </is>
-      </c>
-      <c r="J300" s="16" t="inlineStr">
-        <is>
-          <t>Подтверждение (?)</t>
-        </is>
-      </c>
-      <c r="K300" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="L300" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" s="16" t="inlineStr">
-        <is>
-          <t>Расследование профзаболеваний</t>
-        </is>
-      </c>
-      <c r="B301" s="16" t="inlineStr">
-        <is>
-          <t>Постановление Правительства РФ от 05.07.2022 № 1206 "О порядке расследования и учета случаев профессиональных заболеваний работников"</t>
-        </is>
-      </c>
-      <c r="C301" s="16" t="inlineStr">
-        <is>
-          <t>п. 26, 29–31 Правил (постановление № 1206); приложение к Правилам</t>
-        </is>
-      </c>
-      <c r="D301" s="16" t="inlineStr">
-        <is>
-          <t>Акт о случае профессионального заболевания</t>
-        </is>
-      </c>
-      <c r="E301" s="16" t="inlineStr">
-        <is>
-          <t>ДА</t>
-        </is>
-      </c>
-      <c r="F301" s="16" t="inlineStr">
-        <is>
-          <t>ДА</t>
-        </is>
-      </c>
-      <c r="G301" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H301" s="16" t="inlineStr">
-        <is>
-          <t>Председатель комиссии по расследованию случая профессионального заболевания (руководитель (заместитель руководителя) органа государственного санитарно-эпидемиологического контроля (надзора))</t>
-        </is>
-      </c>
-      <c r="I301" s="16" t="inlineStr">
-        <is>
-          <t>собственноручная</t>
-        </is>
-      </c>
-      <c r="J301" s="16" t="inlineStr">
-        <is>
-          <t>Утверждение</t>
-        </is>
-      </c>
-      <c r="K301" s="16" t="inlineStr">
-        <is>
-          <t>УСЛОВНО</t>
-        </is>
-      </c>
-      <c r="L301" s="16" t="inlineStr">
-        <is>
-          <t>Печать организации</t>
-        </is>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" s="16" t="inlineStr">
-        <is>
-          <t>Расследование профзаболеваний</t>
-        </is>
-      </c>
-      <c r="B302" s="16" t="inlineStr">
-        <is>
-          <t>Постановление Правительства РФ от 05.07.2022 № 1206 "О порядке расследования и учета случаев профессиональных заболеваний работников"</t>
-        </is>
-      </c>
-      <c r="C302" s="16" t="inlineStr">
-        <is>
-          <t>п. 26, 29–31 Правил (постановление № 1206); приложение к Правилам</t>
-        </is>
-      </c>
-      <c r="D302" s="16" t="inlineStr">
-        <is>
-          <t>Акт о случае профессионального заболевания</t>
-        </is>
-      </c>
-      <c r="E302" s="16" t="inlineStr">
-        <is>
-          <t>ДА</t>
-        </is>
-      </c>
-      <c r="F302" s="16" t="inlineStr">
-        <is>
-          <t>ДА</t>
-        </is>
-      </c>
-      <c r="G302" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H302" s="16" t="inlineStr">
-        <is>
-          <t>Член комиссии по расследованию случая профессионального заболевания</t>
-        </is>
-      </c>
-      <c r="I302" s="16" t="inlineStr">
-        <is>
-          <t>собственноручная</t>
-        </is>
-      </c>
-      <c r="J302" s="16" t="inlineStr">
-        <is>
-          <t>Подтверждение (?)</t>
-        </is>
-      </c>
-      <c r="K302" s="16" t="inlineStr">
-        <is>
-          <t>УСЛОВНО</t>
-        </is>
-      </c>
-      <c r="L302" s="16" t="inlineStr">
-        <is>
-          <t>Печать организации</t>
-        </is>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" s="16" t="inlineStr">
-        <is>
-          <t>Расследование профзаболеваний</t>
-        </is>
-      </c>
-      <c r="B303" s="16" t="inlineStr">
-        <is>
-          <t>Постановление Правительства РФ от 05.07.2022 № 1206 "О порядке расследования и учета случаев профессиональных заболеваний работников"</t>
-        </is>
-      </c>
-      <c r="C303" s="16" t="inlineStr">
-        <is>
-          <t>п. 28 Правил (постановление № 1206)</t>
-        </is>
-      </c>
-      <c r="D303" s="16" t="inlineStr">
-        <is>
-          <t>Организационно-распорядительный документ о конкретных мерах по предупреждению профессиональных заболеваний</t>
-        </is>
-      </c>
-      <c r="E303" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="F303" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G303" s="16" t="inlineStr">
-        <is>
-          <t>Конкретные меры по предупреждению профессиональных заболеваний на основании акта о случае профессионального заболевания; издается работодателем в месячный срок со дня составления комиссией акта</t>
-        </is>
-      </c>
-      <c r="H303" s="16" t="inlineStr">
-        <is>
-          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
-        </is>
-      </c>
-      <c r="I303" s="16" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J303" s="16" t="inlineStr">
-        <is>
-          <t>Утверждение</t>
-        </is>
-      </c>
-      <c r="K303" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="L303" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" s="16" t="inlineStr">
-        <is>
-          <t>Расследование профзаболеваний</t>
-        </is>
-      </c>
-      <c r="B304" s="16" t="inlineStr">
-        <is>
-          <t>Постановление Правительства РФ от 05.07.2022 № 1206 "О порядке расследования и учета случаев профессиональных заболеваний работников"</t>
-        </is>
-      </c>
-      <c r="C304" s="16" t="inlineStr">
-        <is>
-          <t>п. 28 Правил (постановление № 1206)</t>
-        </is>
-      </c>
-      <c r="D304" s="16" t="inlineStr">
-        <is>
-          <t>Письменное сообщение об исполнении решений комиссии по расследованию случая профессионального заболевания</t>
-        </is>
-      </c>
-      <c r="E304" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="F304" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G304" s="16" t="inlineStr">
-        <is>
-          <t>Письменное сообщение работодателя в орган государственного санитарно-эпидемиологического контроля (надзора) об исполнении решений комиссии</t>
-        </is>
-      </c>
-      <c r="H304" s="16" t="inlineStr">
-        <is>
-          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
-        </is>
-      </c>
-      <c r="I304" s="16" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J304" s="16" t="inlineStr">
-        <is>
-          <t>Уведомление</t>
-        </is>
-      </c>
-      <c r="K304" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="L304" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" s="16" t="inlineStr">
-        <is>
-          <t>Расследование профзаболеваний</t>
-        </is>
-      </c>
-      <c r="B305" s="16" t="inlineStr">
-        <is>
-          <t>Постановление Правительства РФ от 05.07.2022 № 1206 "О порядке расследования и учета случаев профессиональных заболеваний работников"</t>
-        </is>
-      </c>
-      <c r="C305" s="16" t="inlineStr">
-        <is>
-          <t>п. 34, 35 Правил (постановление № 1206)</t>
-        </is>
-      </c>
-      <c r="D305" s="16" t="inlineStr">
-        <is>
-          <t>Заявление о рассмотрении разногласий по вопросам установления диагноза профессионального заболевания и его расследования</t>
-        </is>
-      </c>
-      <c r="E305" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="F305" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G305" s="16" t="inlineStr">
-        <is>
-          <t>Заявление о рассмотрении разногласий по вопросам установления диагноза профессионального заболевания и его расследования</t>
-        </is>
-      </c>
-      <c r="H305" s="16" t="inlineStr">
-        <is>
-          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
-        </is>
-      </c>
-      <c r="I305" s="16" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J305" s="16" t="inlineStr">
-        <is>
-          <t>Заявление</t>
-        </is>
-      </c>
-      <c r="K305" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="L305" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" s="16" t="inlineStr">
-        <is>
-          <t>Расследование профзаболеваний</t>
-        </is>
-      </c>
-      <c r="B306" s="16" t="inlineStr">
-        <is>
-          <t>Постановление Правительства РФ от 05.07.2022 № 1206 "О порядке расследования и учета случаев профессиональных заболеваний работников"</t>
-        </is>
-      </c>
-      <c r="C306" s="16" t="inlineStr">
-        <is>
-          <t>п. 34, 35 Правил (постановление № 1206)</t>
-        </is>
-      </c>
-      <c r="D306" s="16" t="inlineStr">
-        <is>
-          <t>Заявление о рассмотрении разногласий по вопросам установления диагноза профессионального заболевания и его расследования</t>
-        </is>
-      </c>
-      <c r="E306" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="F306" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G306" s="16" t="inlineStr">
-        <is>
-          <t>Заявление о рассмотрении разногласий по вопросам установления диагноза профессионального заболевания и его расследования</t>
-        </is>
-      </c>
-      <c r="H306" s="16" t="inlineStr">
-        <is>
-          <t>Работник</t>
-        </is>
-      </c>
-      <c r="I306" s="16" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J306" s="16" t="inlineStr">
-        <is>
-          <t>Заявление</t>
-        </is>
-      </c>
-      <c r="K306" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="L306" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" s="16" t="inlineStr">
-        <is>
-          <t>Расследование несчастных случаев</t>
-        </is>
-      </c>
-      <c r="B307" s="16" t="inlineStr">
-        <is>
-          <t>Приказ Минтруда России от 20.04.2022 № 223н "Об утверждении Положения об особенностях расследования несчастных случаев на производстве в отдельных отраслях и организациях, форм документов, соответствующих классификаторов, необходимых для расследования несчастных случаев на производстве"</t>
-        </is>
-      </c>
-      <c r="C307" s="16" t="inlineStr">
-        <is>
-          <t>п. 22 Положения (приложение № 1 к приказу № 223н)</t>
-        </is>
-      </c>
-      <c r="D307" s="16" t="inlineStr">
-        <is>
-          <t>Приказ (распоряжение) о создании комиссии по расследованию несчастного случая</t>
-        </is>
-      </c>
-      <c r="E307" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="F307" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G307" s="16" t="inlineStr">
-        <is>
-          <t>Создание комиссии по расследованию несчастного случая; состав комиссии (включая председателя) из нечетного числа членов; сроки расследования исчисляются в календарных днях начиная со дня издания приказа</t>
-        </is>
-      </c>
-      <c r="H307" s="16" t="inlineStr">
-        <is>
-          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
-        </is>
-      </c>
-      <c r="I307" s="16" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J307" s="16" t="inlineStr">
-        <is>
-          <t>Утверждение</t>
-        </is>
-      </c>
-      <c r="K307" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="L307" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308" s="16" t="inlineStr">
-        <is>
-          <t>Расследование несчастных случаев</t>
-        </is>
-      </c>
-      <c r="B308" s="16" t="inlineStr">
-        <is>
-          <t>Приказ Минтруда России от 20.04.2022 № 223н "Об утверждении Положения об особенностях расследования несчастных случаев на производстве в отдельных отраслях и организациях, форм документов, соответствующих классификаторов, необходимых для расследования несчастных случаев на производстве"</t>
-        </is>
-      </c>
-      <c r="C308" s="16" t="inlineStr">
-        <is>
-          <t>приложение № 2 к приказу № 223н (форма № 1)</t>
-        </is>
-      </c>
-      <c r="D308" s="16" t="inlineStr">
-        <is>
-          <t>Извещение о несчастном случае на производстве (групповом, тяжелом несчастном случае, несчастном случае со смертельным исходом)</t>
-        </is>
-      </c>
-      <c r="E308" s="16" t="inlineStr">
-        <is>
-          <t>ДА</t>
-        </is>
-      </c>
-      <c r="F308" s="16" t="inlineStr">
-        <is>
-          <t>ДА</t>
-        </is>
-      </c>
-      <c r="G308" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H308" s="16" t="inlineStr">
-        <is>
-          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
-        </is>
-      </c>
-      <c r="I308" s="16" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J308" s="16" t="inlineStr">
-        <is>
-          <t>Уведомление</t>
-        </is>
-      </c>
-      <c r="K308" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="L308" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="309">
-      <c r="A309" s="16" t="inlineStr">
-        <is>
-          <t>Расследование несчастных случаев</t>
-        </is>
-      </c>
-      <c r="B309" s="16" t="inlineStr">
-        <is>
-          <t>Приказ Минтруда России от 20.04.2022 № 223н "Об утверждении Положения об особенностях расследования несчастных случаев на производстве в отдельных отраслях и организациях, форм документов, соответствующих классификаторов, необходимых для расследования несчастных случаев на производстве"</t>
-        </is>
-      </c>
-      <c r="C309" s="16" t="inlineStr">
-        <is>
-          <t>приложение № 2 к приказу № 223н (форма № 1)</t>
-        </is>
-      </c>
-      <c r="D309" s="16" t="inlineStr">
-        <is>
-          <t>Извещение о несчастном случае на производстве (групповом, тяжелом несчастном случае, несчастном случае со смертельным исходом)</t>
-        </is>
-      </c>
-      <c r="E309" s="16" t="inlineStr">
-        <is>
-          <t>ДА</t>
-        </is>
-      </c>
-      <c r="F309" s="16" t="inlineStr">
-        <is>
-          <t>ДА</t>
-        </is>
-      </c>
-      <c r="G309" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H309" s="16" t="inlineStr">
-        <is>
-          <t>Лицо, передавшее извещение</t>
-        </is>
-      </c>
-      <c r="I309" s="16" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J309" s="16" t="inlineStr">
-        <is>
-          <t>Уведомление</t>
-        </is>
-      </c>
-      <c r="K309" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="L309" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="310">
-      <c r="A310" s="16" t="inlineStr">
-        <is>
-          <t>Расследование несчастных случаев</t>
-        </is>
-      </c>
-      <c r="B310" s="16" t="inlineStr">
-        <is>
-          <t>Приказ Минтруда России от 20.04.2022 № 223н "Об утверждении Положения об особенностях расследования несчастных случаев на производстве в отдельных отраслях и организациях, форм документов, соответствующих классификаторов, необходимых для расследования несчастных случаев на производстве"</t>
-        </is>
-      </c>
-      <c r="C310" s="16" t="inlineStr">
-        <is>
-          <t>приложение № 2 к приказу № 223н (форма № 1)</t>
-        </is>
-      </c>
-      <c r="D310" s="16" t="inlineStr">
-        <is>
-          <t>Извещение о несчастном случае на производстве (групповом, тяжелом несчастном случае, несчастном случае со смертельным исходом)</t>
-        </is>
-      </c>
-      <c r="E310" s="16" t="inlineStr">
-        <is>
-          <t>ДА</t>
-        </is>
-      </c>
-      <c r="F310" s="16" t="inlineStr">
-        <is>
-          <t>ДА</t>
-        </is>
-      </c>
-      <c r="G310" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H310" s="16" t="inlineStr">
-        <is>
-          <t>Лицо, принявшее извещение</t>
-        </is>
-      </c>
-      <c r="I310" s="16" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J310" s="16" t="inlineStr">
-        <is>
-          <t>Подтверждение (?)</t>
-        </is>
-      </c>
-      <c r="K310" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="L310" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="311">
-      <c r="A311" s="16" t="inlineStr">
-        <is>
-          <t>Расследование несчастных случаев</t>
-        </is>
-      </c>
-      <c r="B311" s="16" t="inlineStr">
-        <is>
-          <t>Приказ Минздрава России от 11.04.2025 № 196н "Об утверждении учетной формы N 315-1/у "Медицинское заключение о характере полученных повреждений здоровья в результате несчастного случая на производстве и степени их тяжести", учетной формы N 316-1/у "Медицинское заключение об установлении заключительного диагноза пострадавшего в результате несчастного случая на производстве"</t>
-        </is>
-      </c>
-      <c r="C311" s="16" t="inlineStr">
-        <is>
-          <t>приложение № 1, приложение № 2 к приказу № 196н</t>
-        </is>
-      </c>
-      <c r="D311" s="16" t="inlineStr">
-        <is>
-          <t>Запрос работодателя о выдаче медицинского заключения (учетные формы N 315-1/у, N 316-1/у)</t>
-        </is>
-      </c>
-      <c r="E311" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="F311" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G311" s="16" t="inlineStr">
-        <is>
-          <t>Запрос организации (индивидуального предпринимателя), работодателя - физического лица, по которому выдается медицинское заключение</t>
-        </is>
-      </c>
-      <c r="H311" s="16" t="inlineStr">
-        <is>
-          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
-        </is>
-      </c>
-      <c r="I311" s="16" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J311" s="16" t="inlineStr">
-        <is>
-          <t>Утверждение</t>
-        </is>
-      </c>
-      <c r="K311" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="L311" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="312">
-      <c r="A312" s="16" t="inlineStr">
-        <is>
-          <t>Расследование несчастных случаев</t>
-        </is>
-      </c>
-      <c r="B312" s="16" t="inlineStr">
-        <is>
-          <t>Приказ Минздрава России от 11.04.2025 № 196н "Об утверждении учетной формы N 315-1/у "Медицинское заключение о характере полученных повреждений здоровья в результате несчастного случая на производстве и степени их тяжести", учетной формы N 316-1/у "Медицинское заключение об установлении заключительного диагноза пострадавшего в результате несчастного случая на производстве"</t>
-        </is>
-      </c>
-      <c r="C312" s="16" t="inlineStr">
-        <is>
-          <t>приложение № 1 к приказу № 196н (учетная форма N 315-1/у)</t>
-        </is>
-      </c>
-      <c r="D312" s="16" t="inlineStr">
-        <is>
-          <t>Медицинское заключение о характере полученных повреждений здоровья в результате несчастного случая на производстве и степени их тяжести</t>
-        </is>
-      </c>
-      <c r="E312" s="16" t="inlineStr">
-        <is>
-          <t>ДА</t>
-        </is>
-      </c>
-      <c r="F312" s="16" t="inlineStr">
-        <is>
-          <t>ДА</t>
-        </is>
-      </c>
-      <c r="G312" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H312" s="16" t="inlineStr">
-        <is>
-          <t>Руководитель медицинской организации (уполномоченное должностное лицо)</t>
-        </is>
-      </c>
-      <c r="I312" s="16" t="inlineStr">
-        <is>
-          <t>собственноручная или УКЭП</t>
-        </is>
-      </c>
-      <c r="J312" s="16" t="inlineStr">
-        <is>
-          <t>Утверждение</t>
-        </is>
-      </c>
-      <c r="K312" s="16" t="inlineStr">
-        <is>
-          <t>УСЛОВНО</t>
-        </is>
-      </c>
-      <c r="L312" s="16" t="inlineStr">
-        <is>
-          <t>Печать организации</t>
-        </is>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" s="16" t="inlineStr">
-        <is>
-          <t>Расследование несчастных случаев</t>
-        </is>
-      </c>
-      <c r="B313" s="16" t="inlineStr">
-        <is>
-          <t>Приказ Минздрава России от 11.04.2025 № 196н "Об утверждении учетной формы N 315-1/у "Медицинское заключение о характере полученных повреждений здоровья в результате несчастного случая на производстве и степени их тяжести", учетной формы N 316-1/у "Медицинское заключение об установлении заключительного диагноза пострадавшего в результате несчастного случая на производстве"</t>
-        </is>
-      </c>
-      <c r="C313" s="16" t="inlineStr">
-        <is>
-          <t>приложение № 2 к приказу № 196н (учетная форма N 316-1/у)</t>
-        </is>
-      </c>
-      <c r="D313" s="16" t="inlineStr">
-        <is>
-          <t>Медицинское заключение об установлении заключительного диагноза пострадавшего в результате несчастного случая на производстве</t>
-        </is>
-      </c>
-      <c r="E313" s="16" t="inlineStr">
-        <is>
-          <t>ДА</t>
-        </is>
-      </c>
-      <c r="F313" s="16" t="inlineStr">
-        <is>
-          <t>ДА</t>
-        </is>
-      </c>
-      <c r="G313" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H313" s="16" t="inlineStr">
-        <is>
-          <t>Руководитель медицинской организации (уполномоченное должностное лицо)</t>
-        </is>
-      </c>
-      <c r="I313" s="16" t="inlineStr">
-        <is>
-          <t>собственноручная или УКЭП</t>
-        </is>
-      </c>
-      <c r="J313" s="16" t="inlineStr">
-        <is>
-          <t>Утверждение</t>
-        </is>
-      </c>
-      <c r="K313" s="16" t="inlineStr">
-        <is>
-          <t>УСЛОВНО</t>
-        </is>
-      </c>
-      <c r="L313" s="16" t="inlineStr">
-        <is>
-          <t>Печать организации</t>
-        </is>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" s="16" t="inlineStr">
-        <is>
-          <t>Расследование несчастных случаев</t>
-        </is>
-      </c>
-      <c r="B314" s="16" t="inlineStr">
-        <is>
-          <t>Приказ Минтруда России от 20.04.2022 № 223н "Об утверждении Положения об особенностях расследования несчастных случаев на производстве в отдельных отраслях и организациях, форм документов, соответствующих классификаторов, необходимых для расследования несчастных случаев на производстве"</t>
-        </is>
-      </c>
-      <c r="C314" s="16" t="inlineStr">
-        <is>
-          <t>приложение № 2 к приказу № 223н (форма № 2, форма Н-1)</t>
-        </is>
-      </c>
-      <c r="D314" s="16" t="inlineStr">
-        <is>
-          <t>Акт о несчастном случае на производстве (форма Н-1)</t>
-        </is>
-      </c>
-      <c r="E314" s="16" t="inlineStr">
-        <is>
-          <t>ДА</t>
-        </is>
-      </c>
-      <c r="F314" s="16" t="inlineStr">
-        <is>
-          <t>ДА</t>
-        </is>
-      </c>
-      <c r="G314" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H314" s="16" t="inlineStr">
-        <is>
-          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
-        </is>
-      </c>
-      <c r="I314" s="16" t="inlineStr">
-        <is>
-          <t>собственноручная</t>
-        </is>
-      </c>
-      <c r="J314" s="16" t="inlineStr">
-        <is>
-          <t>Утверждение</t>
-        </is>
-      </c>
       <c r="K314" s="16" t="inlineStr">
         <is>
-          <t>УСЛОВНО</t>
+          <t>Нет требований</t>
         </is>
       </c>
       <c r="L314" s="16" t="inlineStr">
         <is>
-          <t>Печать организации</t>
+          <t>Нет ограничений</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="16" t="inlineStr">
         <is>
-          <t>Расследование несчастных случаев</t>
+          <t>Социальное страхование</t>
         </is>
       </c>
       <c r="B315" s="16" t="inlineStr">
         <is>
-          <t>Приказ Минтруда России от 20.04.2022 № 223н "Об утверждении Положения об особенностях расследования несчастных случаев на производстве в отдельных отраслях и организациях, форм документов, соответствующих классификаторов, необходимых для расследования несчастных случаев на производстве"</t>
+          <t>ФЗ от 24.07.1998 № 125-ФЗ; ПП РФ от 30.05.2012 № 524; приказ Минтруда от 01.08.2012 № 39н; приказ Минтруда от 11.07.2024 № 347н; приказ Минтруда от 29.10.2021 № 771н</t>
         </is>
       </c>
       <c r="C315" s="16" t="inlineStr">
         <is>
-          <t>приложение № 2 к приказу № 223н (форма № 2, форма Н-1)</t>
+          <t>п. 9–10, 16 Правил (приказ № 347н)</t>
         </is>
       </c>
       <c r="D315" s="16" t="inlineStr">
         <is>
-          <t>Акт о несчастном случае на производстве (форма Н-1)</t>
+          <t>Комплект документов, обосновывающих необходимость финансирования предупредительных мер</t>
         </is>
       </c>
       <c r="E315" s="16" t="inlineStr">
         <is>
-          <t>ДА</t>
+          <t>НЕТ</t>
         </is>
       </c>
       <c r="F315" s="16" t="inlineStr">
         <is>
-          <t>ДА</t>
+          <t>ДА (при обращении)</t>
         </is>
       </c>
       <c r="G315" s="16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>По видам мер п. 2 Правил: копии актов, перечней, договоров, счетов, заключений, списков работников, лицензий и иных документов, предусмотренных п. 9–10 Правил</t>
         </is>
       </c>
       <c r="H315" s="16" t="inlineStr">
         <is>
-          <t>Лицо, проводившее расследование несчастного случая (член комиссии / председатель комиссии)</t>
+          <t>Руководитель организации / уполномоченное лицо (заверение копий)</t>
         </is>
       </c>
       <c r="I315" s="16" t="inlineStr">
         <is>
-          <t>собственноручная</t>
+          <t>Нет требований</t>
         </is>
       </c>
       <c r="J315" s="16" t="inlineStr">
         <is>
-          <t>Подтверждение (?)</t>
+          <t>Подтверждение</t>
         </is>
       </c>
       <c r="K315" s="16" t="inlineStr">
@@ -20097,307 +20097,307 @@
       </c>
       <c r="L315" s="16" t="inlineStr">
         <is>
-          <t>Печать организации</t>
+          <t>Печать организации (на копиях документов)</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="16" t="inlineStr">
         <is>
-          <t>Расследование несчастных случаев</t>
+          <t>Социальное страхование</t>
         </is>
       </c>
       <c r="B316" s="16" t="inlineStr">
         <is>
-          <t>Приказ Минтруда России от 20.04.2022 № 223н "Об утверждении Положения об особенностях расследования несчастных случаев на производстве в отдельных отраслях и организациях, форм документов, соответствующих классификаторов, необходимых для расследования несчастных случаев на производстве"</t>
+          <t>ФЗ от 24.07.1998 № 125-ФЗ; ПП РФ от 30.05.2012 № 524; приказ Минтруда от 01.08.2012 № 39н; приказ Минтруда от 11.07.2024 № 347н; приказ Минтруда от 29.10.2021 № 771н</t>
         </is>
       </c>
       <c r="C316" s="16" t="inlineStr">
         <is>
-          <t>приложение № 2 к приказу № 223н (форма № 2, форма Н-1)</t>
+          <t>п. 6, 13, 16 Правил (приказ № 347н)</t>
         </is>
       </c>
       <c r="D316" s="16" t="inlineStr">
         <is>
-          <t>Акт о несчастном случае на производстве (форма Н-1)</t>
+          <t>Приказ (распоряжение) о направлении работников на санаторно-курортное лечение / о реализации конкретных предупредительных мер</t>
         </is>
       </c>
       <c r="E316" s="16" t="inlineStr">
         <is>
-          <t>ДА</t>
+          <t>НЕТ</t>
         </is>
       </c>
       <c r="F316" s="16" t="inlineStr">
         <is>
-          <t>ДА</t>
+          <t>УСЛОВНО</t>
         </is>
       </c>
       <c r="G316" s="16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Перечень работников; основание направления; срок; вид мероприятия; ответственные</t>
         </is>
       </c>
       <c r="H316" s="16" t="inlineStr">
         <is>
-          <t>Пострадавший (законный представитель или иное доверенное лицо)</t>
+          <t>Руководитель организации / уполномоченное лицо</t>
         </is>
       </c>
       <c r="I316" s="16" t="inlineStr">
         <is>
-          <t>собственноручная</t>
+          <t>Нет требований</t>
         </is>
       </c>
       <c r="J316" s="16" t="inlineStr">
         <is>
-          <t>Ознакомление</t>
+          <t>Утверждение</t>
         </is>
       </c>
       <c r="K316" s="16" t="inlineStr">
         <is>
-          <t>УСЛОВНО</t>
+          <t>Нет требований</t>
         </is>
       </c>
       <c r="L316" s="16" t="inlineStr">
         <is>
-          <t>Печать организации</t>
+          <t>Нет ограничений</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="16" t="inlineStr">
         <is>
-          <t>Расследование несчастных случаев</t>
+          <t>Социальное страхование</t>
         </is>
       </c>
       <c r="B317" s="16" t="inlineStr">
         <is>
-          <t>Приказ Минтруда России от 20.04.2022 № 223н "Об утверждении Положения об особенностях расследования несчастных случаев на производстве в отдельных отраслях и организациях, форм документов, соответствующих классификаторов, необходимых для расследования несчастных случаев на производстве"</t>
+          <t>ФЗ от 24.07.1998 № 125-ФЗ; ПП РФ от 30.05.2012 № 524; приказ Минтруда от 01.08.2012 № 39н; приказ Минтруда от 11.07.2024 № 347н; приказ Минтруда от 29.10.2021 № 771н</t>
         </is>
       </c>
       <c r="C317" s="16" t="inlineStr">
         <is>
-          <t>приложение № 2 к приказу № 223н (форма № 3, форма Н-1ПС); п. 16–18 Положения (приложение № 1 к приказу № 223н)</t>
+          <t>п. 9–10 Правил (приказ № 347н)</t>
         </is>
       </c>
       <c r="D317" s="16" t="inlineStr">
         <is>
-          <t>Акт о несчастном случае на производстве (форма Н-1ПС)</t>
+          <t>Список работников, направляемых на санаторно-курортное лечение, с указанием рекомендаций</t>
         </is>
       </c>
       <c r="E317" s="16" t="inlineStr">
         <is>
-          <t>ДА</t>
+          <t>НЕТ</t>
         </is>
       </c>
       <c r="F317" s="16" t="inlineStr">
         <is>
-          <t>ДА</t>
+          <t>УСЛОВНО</t>
         </is>
       </c>
       <c r="G317" s="16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ФИО работников; вредные/опасные факторы; рекомендации по санаторно-курортному лечению; период лечения</t>
         </is>
       </c>
       <c r="H317" s="16" t="inlineStr">
         <is>
-          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+          <t>Работодатель / уполномоченное лицо</t>
         </is>
       </c>
       <c r="I317" s="16" t="inlineStr">
         <is>
-          <t>собственноручная</t>
+          <t>Нет требований</t>
         </is>
       </c>
       <c r="J317" s="16" t="inlineStr">
         <is>
-          <t>Утверждение</t>
+          <t>Подтверждение</t>
         </is>
       </c>
       <c r="K317" s="16" t="inlineStr">
         <is>
-          <t>УСЛОВНО</t>
+          <t>Нет требований</t>
         </is>
       </c>
       <c r="L317" s="16" t="inlineStr">
         <is>
-          <t>Печать организации</t>
+          <t>Нет ограничений</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="16" t="inlineStr">
         <is>
-          <t>Расследование несчастных случаев</t>
+          <t>Социальное страхование</t>
         </is>
       </c>
       <c r="B318" s="16" t="inlineStr">
         <is>
-          <t>Приказ Минтруда России от 20.04.2022 № 223н "Об утверждении Положения об особенностях расследования несчастных случаев на производстве в отдельных отраслях и организациях, форм документов, соответствующих классификаторов, необходимых для расследования несчастных случаев на производстве"</t>
+          <t>ФЗ от 24.07.1998 № 125-ФЗ; ПП РФ от 30.05.2012 № 524; приказ Минтруда от 01.08.2012 № 39н; приказ Минтруда от 11.07.2024 № 347н; приказ Минтруда от 29.10.2021 № 771н</t>
         </is>
       </c>
       <c r="C318" s="16" t="inlineStr">
         <is>
-          <t>приложение № 2 к приказу № 223н (форма № 3, форма Н-1ПС); п. 16–18 Положения (приложение № 1 к приказу № 223н)</t>
+          <t>п. 13–16 Правил (приказ № 347н)</t>
         </is>
       </c>
       <c r="D318" s="16" t="inlineStr">
         <is>
-          <t>Акт о несчастном случае на производстве (форма Н-1ПС)</t>
+          <t>Решение территориального органа СФР о финансовом обеспечении предупредительных мер либо об отказе (получаемое страхователем)</t>
         </is>
       </c>
       <c r="E318" s="16" t="inlineStr">
         <is>
-          <t>ДА</t>
+          <t>НЕТ</t>
         </is>
       </c>
       <c r="F318" s="16" t="inlineStr">
         <is>
-          <t>ДА</t>
+          <t>— (документ страховщика)</t>
         </is>
       </c>
       <c r="G318" s="16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Объем средств; перечень согласованных мер либо мотивы отказа; срок сообщения страхователю</t>
         </is>
       </c>
       <c r="H318" s="16" t="inlineStr">
         <is>
-          <t>Лицо, проводившее расследование несчастного случая</t>
+          <t>Уполномоченное должностное лицо территориального органа СФР</t>
         </is>
       </c>
       <c r="I318" s="16" t="inlineStr">
         <is>
-          <t>собственноручная</t>
+          <t>Нет требований</t>
         </is>
       </c>
       <c r="J318" s="16" t="inlineStr">
         <is>
-          <t>Подтверждение (?)</t>
+          <t>Уведомление</t>
         </is>
       </c>
       <c r="K318" s="16" t="inlineStr">
         <is>
-          <t>УСЛОВНО</t>
+          <t>Нет требований</t>
         </is>
       </c>
       <c r="L318" s="16" t="inlineStr">
         <is>
-          <t>Печать организации</t>
+          <t>Нет ограничений</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="16" t="inlineStr">
         <is>
-          <t>Расследование несчастных случаев</t>
+          <t>Социальное страхование</t>
         </is>
       </c>
       <c r="B319" s="16" t="inlineStr">
         <is>
-          <t>Приказ Минтруда России от 20.04.2022 № 223н "Об утверждении Положения об особенностях расследования несчастных случаев на производстве в отдельных отраслях и организациях, форм документов, соответствующих классификаторов, необходимых для расследования несчастных случаев на производстве"</t>
+          <t>ФЗ от 24.07.1998 № 125-ФЗ; ПП РФ от 30.05.2012 № 524; приказ Минтруда от 01.08.2012 № 39н; приказ Минтруда от 11.07.2024 № 347н; приказ Минтруда от 29.10.2021 № 771н</t>
         </is>
       </c>
       <c r="C319" s="16" t="inlineStr">
         <is>
-          <t>приложение № 2 к приказу № 223н (форма № 4, форма Н-1ЧС); п. 21.1–21.4 Положения (приложение № 1 к приказу № 223н)</t>
+          <t>п. 16 Правил (приказ № 347н)</t>
         </is>
       </c>
       <c r="D319" s="16" t="inlineStr">
         <is>
-          <t>Акт о несчастном случае на производстве (форма Н-1ЧС)</t>
+          <t>Отчет о результатах финансового обеспечения предупредительных мер</t>
         </is>
       </c>
       <c r="E319" s="16" t="inlineStr">
         <is>
-          <t>ДА</t>
+          <t>НЕТ</t>
         </is>
       </c>
       <c r="F319" s="16" t="inlineStr">
         <is>
-          <t>ДА</t>
+          <t>ДА (после реализации мер)</t>
         </is>
       </c>
       <c r="G319" s="16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Фактически реализованные мероприятия; израсходованные суммы; количество работников; подтверждающие документы; период</t>
         </is>
       </c>
       <c r="H319" s="16" t="inlineStr">
         <is>
-          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+          <t>Руководитель организации (страхователь) / уполномоченное лицо</t>
         </is>
       </c>
       <c r="I319" s="16" t="inlineStr">
         <is>
-          <t>собственноручная</t>
+          <t>Нет требований</t>
         </is>
       </c>
       <c r="J319" s="16" t="inlineStr">
         <is>
-          <t>Утверждение</t>
+          <t>Подтверждение</t>
         </is>
       </c>
       <c r="K319" s="16" t="inlineStr">
         <is>
-          <t>УСЛОВНО</t>
+          <t>Нет требований</t>
         </is>
       </c>
       <c r="L319" s="16" t="inlineStr">
         <is>
-          <t>Печать организации</t>
+          <t>Нет ограничений</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="16" t="inlineStr">
         <is>
-          <t>Расследование несчастных случаев</t>
+          <t>Социальное страхование</t>
         </is>
       </c>
       <c r="B320" s="16" t="inlineStr">
         <is>
-          <t>Приказ Минтруда России от 20.04.2022 № 223н "Об утверждении Положения об особенностях расследования несчастных случаев на производстве в отдельных отраслях и организациях, форм документов, соответствующих классификаторов, необходимых для расследования несчастных случаев на производстве"</t>
+          <t>ФЗ от 24.07.1998 № 125-ФЗ; ПП РФ от 30.05.2012 № 524; приказ Минтруда от 01.08.2012 № 39н; приказ Минтруда от 11.07.2024 № 347н; приказ Минтруда от 29.10.2021 № 771н</t>
         </is>
       </c>
       <c r="C320" s="16" t="inlineStr">
         <is>
-          <t>приложение № 2 к приказу № 223н (форма № 4, форма Н-1ЧС); п. 21.1–21.4 Положения (приложение № 1 к приказу № 223н)</t>
+          <t>п. 16 Правил (приказ № 347н)</t>
         </is>
       </c>
       <c r="D320" s="16" t="inlineStr">
         <is>
-          <t>Акт о несчастном случае на производстве (форма Н-1ЧС)</t>
+          <t>Документы, подтверждающие расходы на предупредительные меры (договоры, счета, платежные поручения, акты)</t>
         </is>
       </c>
       <c r="E320" s="16" t="inlineStr">
         <is>
-          <t>ДА</t>
+          <t>НЕТ</t>
         </is>
       </c>
       <c r="F320" s="16" t="inlineStr">
         <is>
-          <t>ДА</t>
+          <t>ДА (при отчете / возмещении)</t>
         </is>
       </c>
       <c r="G320" s="16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Предмет и стоимость работ (услуг); реквизиты сторон; факт оплаты; период; соответствие плану финансового обеспечения</t>
         </is>
       </c>
       <c r="H320" s="16" t="inlineStr">
         <is>
-          <t>Лицо, проводившее расследование несчастного случая</t>
+          <t>Руководитель организации / уполномоченное лицо; главный бухгалтер (платежные документы)</t>
         </is>
       </c>
       <c r="I320" s="16" t="inlineStr">
         <is>
-          <t>собственноручная</t>
+          <t>Нет требований</t>
         </is>
       </c>
       <c r="J320" s="16" t="inlineStr">
         <is>
-          <t>Подтверждение (?)</t>
+          <t>Подтверждение</t>
         </is>
       </c>
       <c r="K320" s="16" t="inlineStr">
@@ -20407,1562 +20407,260 @@
       </c>
       <c r="L320" s="16" t="inlineStr">
         <is>
-          <t>Печать организации</t>
+          <t>Печать организации (на копиях)</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="16" t="inlineStr">
         <is>
-          <t>Расследование несчастных случаев</t>
+          <t>Социальное страхование</t>
         </is>
       </c>
       <c r="B321" s="16" t="inlineStr">
         <is>
-          <t>Приказ Минтруда России от 20.04.2022 № 223н "Об утверждении Положения об особенностях расследования несчастных случаев на производстве в отдельных отраслях и организациях, форм документов, соответствующих классификаторов, необходимых для расследования несчастных случаев на производстве"</t>
+          <t>ФЗ от 24.07.1998 № 125-ФЗ; ПП РФ от 30.05.2012 № 524; приказ Минтруда от 01.08.2012 № 39н; приказ Минтруда от 11.07.2024 № 347н; приказ Минтруда от 29.10.2021 № 771н</t>
         </is>
       </c>
       <c r="C321" s="16" t="inlineStr">
         <is>
-          <t>приложение № 2 к приказу № 223н (форма № 5)</t>
+          <t>п. 16 Правил (приказ № 347н)</t>
         </is>
       </c>
       <c r="D321" s="16" t="inlineStr">
         <is>
-          <t>Акт о расследовании группового несчастного случая (легкого несчастного случая, тяжелого несчастного случая, несчастного случая со смертельным исходом)</t>
+          <t>Выписки из локальных нормативных актов (приказов), подтверждающих приобретение СИЗ / реализацию мер</t>
         </is>
       </c>
       <c r="E321" s="16" t="inlineStr">
         <is>
-          <t>ДА</t>
+          <t>НЕТ</t>
         </is>
       </c>
       <c r="F321" s="16" t="inlineStr">
         <is>
-          <t>ДА</t>
+          <t>УСЛОВНО</t>
         </is>
       </c>
       <c r="G321" s="16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Реквизиты ЛНА (приказа); перечень приобретенного / выполненного; работники; даты</t>
         </is>
       </c>
       <c r="H321" s="16" t="inlineStr">
         <is>
-          <t>Председатель комиссии по расследованию несчастного случая</t>
+          <t>Руководитель организации / лицо, подписавшее ЛНА</t>
         </is>
       </c>
       <c r="I321" s="16" t="inlineStr">
         <is>
-          <t>собственноручная</t>
+          <t>Нет требований</t>
         </is>
       </c>
       <c r="J321" s="16" t="inlineStr">
         <is>
-          <t>Утверждение</t>
+          <t>Подтверждение</t>
         </is>
       </c>
       <c r="K321" s="16" t="inlineStr">
         <is>
-          <t>НЕТ</t>
+          <t>УСЛОВНО</t>
         </is>
       </c>
       <c r="L321" s="16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Печать организации (на копиях)</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="16" t="inlineStr">
         <is>
-          <t>Расследование несчастных случаев</t>
+          <t>Социальное страхование</t>
         </is>
       </c>
       <c r="B322" s="16" t="inlineStr">
         <is>
-          <t>Приказ Минтруда России от 20.04.2022 № 223н "Об утверждении Положения об особенностях расследования несчастных случаев на производстве в отдельных отраслях и организациях, форм документов, соответствующих классификаторов, необходимых для расследования несчастных случаев на производстве"</t>
+          <t>ФЗ от 24.07.1998 № 125-ФЗ; ПП РФ от 30.05.2012 № 524; приказ Минтруда от 01.08.2012 № 39н; приказ Минтруда от 11.07.2024 № 347н; приказ Минтруда от 29.10.2021 № 771н</t>
         </is>
       </c>
       <c r="C322" s="16" t="inlineStr">
         <is>
-          <t>приложение № 2 к приказу № 223н (форма № 5)</t>
+          <t>п. 16–17 Правил (приказ № 347н)</t>
         </is>
       </c>
       <c r="D322" s="16" t="inlineStr">
         <is>
-          <t>Акт о расследовании группового несчастного случая (легкого несчастного случая, тяжелого несчастного случая, несчастного случая со смертельным исходом)</t>
+          <t>Заявление о возмещении произведенных расходов на предупредительные меры</t>
         </is>
       </c>
       <c r="E322" s="16" t="inlineStr">
         <is>
-          <t>ДА</t>
+          <t>НЕТ</t>
         </is>
       </c>
       <c r="F322" s="16" t="inlineStr">
         <is>
-          <t>ДА</t>
+          <t>УСЛОВНО</t>
         </is>
       </c>
       <c r="G322" s="16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Сумма к возмещению; период; реквизиты счета; ссылка на решение о финансовом обеспечении; перечень приложений</t>
         </is>
       </c>
       <c r="H322" s="16" t="inlineStr">
         <is>
-          <t>Член комиссии по расследованию несчастного случая</t>
+          <t>Руководитель организации (страхователь) / уполномоченное лицо</t>
         </is>
       </c>
       <c r="I322" s="16" t="inlineStr">
         <is>
-          <t>собственноручная</t>
+          <t>Нет требований</t>
         </is>
       </c>
       <c r="J322" s="16" t="inlineStr">
         <is>
-          <t>Подтверждение (?)</t>
+          <t>Заявление</t>
         </is>
       </c>
       <c r="K322" s="16" t="inlineStr">
         <is>
-          <t>НЕТ</t>
+          <t>Нет требований</t>
         </is>
       </c>
       <c r="L322" s="16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Нет ограничений</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="16" t="inlineStr">
         <is>
-          <t>Расследование несчастных случаев</t>
+          <t>Социальное страхование</t>
         </is>
       </c>
       <c r="B323" s="16" t="inlineStr">
         <is>
-          <t>Приказ Минтруда России от 20.04.2022 № 223н "Об утверждении Положения об особенностях расследования несчастных случаев на производстве в отдельных отраслях и организациях, форм документов, соответствующих классификаторов, необходимых для расследования несчастных случаев на производстве"</t>
+          <t>ФЗ от 24.07.1998 № 125-ФЗ; ПП РФ от 30.05.2012 № 524; приказ Минтруда от 01.08.2012 № 39н; приказ Минтруда от 11.07.2024 № 347н; приказ Минтруда от 29.10.2021 № 771н</t>
         </is>
       </c>
       <c r="C323" s="16" t="inlineStr">
         <is>
-          <t>приложение № 2 к приказу № 223н (форма № 6)</t>
+          <t>п. 17 Правил (приказ № 347н)</t>
         </is>
       </c>
       <c r="D323" s="16" t="inlineStr">
         <is>
-          <t>Акт о расследовании обстоятельств происшествия, предполагающего гибель работника в результате несчастного случая</t>
+          <t>Решение территориального органа СФР о возмещении расходов либо об отказе в возмещении (получаемое страхователем)</t>
         </is>
       </c>
       <c r="E323" s="16" t="inlineStr">
         <is>
-          <t>ДА</t>
+          <t>НЕТ</t>
         </is>
       </c>
       <c r="F323" s="16" t="inlineStr">
         <is>
-          <t>ДА</t>
+          <t>— (документ страховщика)</t>
         </is>
       </c>
       <c r="G323" s="16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Сумма возмещения либо мотивы отказа; срок перечисления</t>
         </is>
       </c>
       <c r="H323" s="16" t="inlineStr">
         <is>
-          <t>Председатель комиссии по расследованию несчастного случая</t>
+          <t>Уполномоченное должностное лицо территориального органа СФР</t>
         </is>
       </c>
       <c r="I323" s="16" t="inlineStr">
         <is>
-          <t>собственноручная</t>
+          <t>Нет требований</t>
         </is>
       </c>
       <c r="J323" s="16" t="inlineStr">
         <is>
-          <t>Утверждение</t>
+          <t>Уведомление</t>
         </is>
       </c>
       <c r="K323" s="16" t="inlineStr">
         <is>
-          <t>НЕТ</t>
+          <t>Нет требований</t>
         </is>
       </c>
       <c r="L323" s="16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Нет ограничений</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="16" t="inlineStr">
         <is>
-          <t>Расследование несчастных случаев</t>
+          <t>Социальное страхование</t>
         </is>
       </c>
       <c r="B324" s="16" t="inlineStr">
         <is>
-          <t>Приказ Минтруда России от 20.04.2022 № 223н "Об утверждении Положения об особенностях расследования несчастных случаев на производстве в отдельных отраслях и организациях, форм документов, соответствующих классификаторов, необходимых для расследования несчастных случаев на производстве"</t>
+          <t>ФЗ от 24.07.1998 № 125-ФЗ; ПП РФ от 30.05.2012 № 524; приказ Минтруда от 01.08.2012 № 39н; приказ Минтруда от 11.07.2024 № 347н; приказ Минтруда от 29.10.2021 № 771н</t>
         </is>
       </c>
       <c r="C324" s="16" t="inlineStr">
         <is>
-          <t>приложение № 2 к приказу № 223н (форма № 6)</t>
+          <t>ст. 17 125-ФЗ; п. 16 Правил (приказ № 347н)</t>
         </is>
       </c>
       <c r="D324" s="16" t="inlineStr">
         <is>
-          <t>Акт о расследовании обстоятельств происшествия, предполагающего гибель работника в результате несчастного случая</t>
+          <t>Документы (акты, договоры, счета), подтверждающие расходы страхователя на предупреждение травматизма и профзаболеваний (для учета и контроля)</t>
         </is>
       </c>
       <c r="E324" s="16" t="inlineStr">
         <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F324" s="16" t="inlineStr">
+        <is>
           <t>ДА</t>
         </is>
       </c>
-      <c r="F324" s="16" t="inlineStr">
-        <is>
-          <t>ДА</t>
-        </is>
-      </c>
       <c r="G324" s="16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Вид расходов; сумма; период; связь с обеспечением безопасных условий труда и предупреждением НС/ПЗ</t>
         </is>
       </c>
       <c r="H324" s="16" t="inlineStr">
         <is>
-          <t>Член комиссии по расследованию несчастного случая</t>
+          <t>Руководитель организации / уполномоченное лицо</t>
         </is>
       </c>
       <c r="I324" s="16" t="inlineStr">
         <is>
-          <t>собственноручная</t>
+          <t>Нет требований</t>
         </is>
       </c>
       <c r="J324" s="16" t="inlineStr">
         <is>
-          <t>Подтверждение (?)</t>
+          <t>Подтверждение</t>
         </is>
       </c>
       <c r="K324" s="16" t="inlineStr">
         <is>
-          <t>НЕТ</t>
+          <t>Нет требований</t>
         </is>
       </c>
       <c r="L324" s="16" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="325">
-      <c r="A325" s="16" t="inlineStr">
-        <is>
-          <t>Расследование несчастных случаев</t>
-        </is>
-      </c>
-      <c r="B325" s="16" t="inlineStr">
-        <is>
-          <t>Приказ Минтруда России от 20.04.2022 № 223н "Об утверждении Положения об особенностях расследования несчастных случаев на производстве в отдельных отраслях и организациях, форм документов, соответствующих классификаторов, необходимых для расследования несчастных случаев на производстве"</t>
-        </is>
-      </c>
-      <c r="C325" s="16" t="inlineStr">
-        <is>
-          <t>приложение № 2 к приказу № 223н (форма № 7)</t>
-        </is>
-      </c>
-      <c r="D325" s="16" t="inlineStr">
-        <is>
-          <t>Заключение государственного инспектора труда</t>
-        </is>
-      </c>
-      <c r="E325" s="16" t="inlineStr">
-        <is>
-          <t>ДА</t>
-        </is>
-      </c>
-      <c r="F325" s="16" t="inlineStr">
-        <is>
-          <t>ДА</t>
-        </is>
-      </c>
-      <c r="G325" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H325" s="16" t="inlineStr">
-        <is>
-          <t>Государственный инспектор труда</t>
-        </is>
-      </c>
-      <c r="I325" s="16" t="inlineStr">
-        <is>
-          <t>собственноручная</t>
-        </is>
-      </c>
-      <c r="J325" s="16" t="inlineStr">
-        <is>
-          <t>Утверждение</t>
-        </is>
-      </c>
-      <c r="K325" s="16" t="inlineStr">
-        <is>
-          <t>УСЛОВНО</t>
-        </is>
-      </c>
-      <c r="L325" s="16" t="inlineStr">
-        <is>
-          <t>Печать / именной штамп государственного инспектора труда</t>
-        </is>
-      </c>
-    </row>
-    <row r="326">
-      <c r="A326" s="16" t="inlineStr">
-        <is>
-          <t>Расследование несчастных случаев</t>
-        </is>
-      </c>
-      <c r="B326" s="16" t="inlineStr">
-        <is>
-          <t>Приказ Минтруда России от 20.04.2022 № 223н "Об утверждении Положения об особенностях расследования несчастных случаев на производстве в отдельных отраслях и организациях, форм документов, соответствующих классификаторов, необходимых для расследования несчастных случаев на производстве"</t>
-        </is>
-      </c>
-      <c r="C326" s="16" t="inlineStr">
-        <is>
-          <t>приложение № 2 к приказу № 223н (форма № 8); п. 25 Положения (приложение № 1 к приказу № 223н)</t>
-        </is>
-      </c>
-      <c r="D326" s="16" t="inlineStr">
-        <is>
-          <t>Протокол опроса пострадавшего при несчастном случае (очевидца несчастного случая, должностного лица)</t>
-        </is>
-      </c>
-      <c r="E326" s="16" t="inlineStr">
-        <is>
-          <t>ДА</t>
-        </is>
-      </c>
-      <c r="F326" s="16" t="inlineStr">
-        <is>
-          <t>ДА</t>
-        </is>
-      </c>
-      <c r="G326" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H326" s="16" t="inlineStr">
-        <is>
-          <t>Председатель (член) комиссии по расследованию несчастного случая</t>
-        </is>
-      </c>
-      <c r="I326" s="16" t="inlineStr">
-        <is>
-          <t>собственноручная</t>
-        </is>
-      </c>
-      <c r="J326" s="16" t="inlineStr">
-        <is>
-          <t>Утверждение</t>
-        </is>
-      </c>
-      <c r="K326" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="L326" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="327">
-      <c r="A327" s="16" t="inlineStr">
-        <is>
-          <t>Расследование несчастных случаев</t>
-        </is>
-      </c>
-      <c r="B327" s="16" t="inlineStr">
-        <is>
-          <t>Приказ Минтруда России от 20.04.2022 № 223н "Об утверждении Положения об особенностях расследования несчастных случаев на производстве в отдельных отраслях и организациях, форм документов, соответствующих классификаторов, необходимых для расследования несчастных случаев на производстве"</t>
-        </is>
-      </c>
-      <c r="C327" s="16" t="inlineStr">
-        <is>
-          <t>приложение № 2 к приказу № 223н (форма № 8); п. 25 Положения (приложение № 1 к приказу № 223н)</t>
-        </is>
-      </c>
-      <c r="D327" s="16" t="inlineStr">
-        <is>
-          <t>Протокол опроса пострадавшего при несчастном случае (очевидца несчастного случая, должностного лица)</t>
-        </is>
-      </c>
-      <c r="E327" s="16" t="inlineStr">
-        <is>
-          <t>ДА</t>
-        </is>
-      </c>
-      <c r="F327" s="16" t="inlineStr">
-        <is>
-          <t>ДА</t>
-        </is>
-      </c>
-      <c r="G327" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H327" s="16" t="inlineStr">
-        <is>
-          <t>Опрашиваемое лицо (пострадавший / очевидец / должностное лицо)</t>
-        </is>
-      </c>
-      <c r="I327" s="16" t="inlineStr">
-        <is>
-          <t>собственноручная</t>
-        </is>
-      </c>
-      <c r="J327" s="16" t="inlineStr">
-        <is>
-          <t>Подтверждение (?)</t>
-        </is>
-      </c>
-      <c r="K327" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="L327" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="328">
-      <c r="A328" s="16" t="inlineStr">
-        <is>
-          <t>Расследование несчастных случаев</t>
-        </is>
-      </c>
-      <c r="B328" s="16" t="inlineStr">
-        <is>
-          <t>Приказ Минтруда России от 20.04.2022 № 223н "Об утверждении Положения об особенностях расследования несчастных случаев на производстве в отдельных отраслях и организациях, форм документов, соответствующих классификаторов, необходимых для расследования несчастных случаев на производстве"</t>
-        </is>
-      </c>
-      <c r="C328" s="16" t="inlineStr">
-        <is>
-          <t>приложение № 2 к приказу № 223н (форма № 9); п. 25 Положения (приложение № 1 к приказу № 223н)</t>
-        </is>
-      </c>
-      <c r="D328" s="16" t="inlineStr">
-        <is>
-          <t>Протокол осмотра места несчастного случая</t>
-        </is>
-      </c>
-      <c r="E328" s="16" t="inlineStr">
-        <is>
-          <t>ДА</t>
-        </is>
-      </c>
-      <c r="F328" s="16" t="inlineStr">
-        <is>
-          <t>ДА</t>
-        </is>
-      </c>
-      <c r="G328" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H328" s="16" t="inlineStr">
-        <is>
-          <t>Председатель (член) комиссии по расследованию несчастного случая</t>
-        </is>
-      </c>
-      <c r="I328" s="16" t="inlineStr">
-        <is>
-          <t>собственноручная</t>
-        </is>
-      </c>
-      <c r="J328" s="16" t="inlineStr">
-        <is>
-          <t>Утверждение</t>
-        </is>
-      </c>
-      <c r="K328" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="L328" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="329">
-      <c r="A329" s="16" t="inlineStr">
-        <is>
-          <t>Расследование несчастных случаев</t>
-        </is>
-      </c>
-      <c r="B329" s="16" t="inlineStr">
-        <is>
-          <t>Приказ Минтруда России от 20.04.2022 № 223н "Об утверждении Положения об особенностях расследования несчастных случаев на производстве в отдельных отраслях и организациях, форм документов, соответствующих классификаторов, необходимых для расследования несчастных случаев на производстве"</t>
-        </is>
-      </c>
-      <c r="C329" s="16" t="inlineStr">
-        <is>
-          <t>приложение № 2 к приказу № 223н (форма № 9); п. 25 Положения (приложение № 1 к приказу № 223н)</t>
-        </is>
-      </c>
-      <c r="D329" s="16" t="inlineStr">
-        <is>
-          <t>Протокол осмотра места несчастного случая</t>
-        </is>
-      </c>
-      <c r="E329" s="16" t="inlineStr">
-        <is>
-          <t>ДА</t>
-        </is>
-      </c>
-      <c r="F329" s="16" t="inlineStr">
-        <is>
-          <t>ДА</t>
-        </is>
-      </c>
-      <c r="G329" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H329" s="16" t="inlineStr">
-        <is>
-          <t>Лицо, участвовавшее в осмотре места несчастного случая</t>
-        </is>
-      </c>
-      <c r="I329" s="16" t="inlineStr">
-        <is>
-          <t>собственноручная</t>
-        </is>
-      </c>
-      <c r="J329" s="16" t="inlineStr">
-        <is>
-          <t>Подтверждение (?)</t>
-        </is>
-      </c>
-      <c r="K329" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="L329" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="330">
-      <c r="A330" s="16" t="inlineStr">
-        <is>
-          <t>Расследование несчастных случаев</t>
-        </is>
-      </c>
-      <c r="B330" s="16" t="inlineStr">
-        <is>
-          <t>Приказ Минтруда России от 20.04.2022 № 223н "Об утверждении Положения об особенностях расследования несчастных случаев на производстве в отдельных отраслях и организациях, форм документов, соответствующих классификаторов, необходимых для расследования несчастных случаев на производстве"</t>
-        </is>
-      </c>
-      <c r="C330" s="16" t="inlineStr">
-        <is>
-          <t>приложение № 2 к приказу № 223н (форма № 10)</t>
-        </is>
-      </c>
-      <c r="D330" s="16" t="inlineStr">
-        <is>
-          <t>Сообщение о последствиях несчастного случая на производстве и принятых мерах</t>
-        </is>
-      </c>
-      <c r="E330" s="16" t="inlineStr">
-        <is>
-          <t>ДА</t>
-        </is>
-      </c>
-      <c r="F330" s="16" t="inlineStr">
-        <is>
-          <t>ДА</t>
-        </is>
-      </c>
-      <c r="G330" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H330" s="16" t="inlineStr">
-        <is>
-          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
-        </is>
-      </c>
-      <c r="I330" s="16" t="inlineStr">
-        <is>
-          <t>собственноручная</t>
-        </is>
-      </c>
-      <c r="J330" s="16" t="inlineStr">
-        <is>
-          <t>Утверждение</t>
-        </is>
-      </c>
-      <c r="K330" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="L330" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="331">
-      <c r="A331" s="16" t="inlineStr">
-        <is>
-          <t>Расследование несчастных случаев</t>
-        </is>
-      </c>
-      <c r="B331" s="16" t="inlineStr">
-        <is>
-          <t>Приказ Минтруда России от 20.04.2022 № 223н "Об утверждении Положения об особенностях расследования несчастных случаев на производстве в отдельных отраслях и организациях, форм документов, соответствующих классификаторов, необходимых для расследования несчастных случаев на производстве"</t>
-        </is>
-      </c>
-      <c r="C331" s="16" t="inlineStr">
-        <is>
-          <t>приложение № 2 к приказу № 223н (форма № 10)</t>
-        </is>
-      </c>
-      <c r="D331" s="16" t="inlineStr">
-        <is>
-          <t>Сообщение о последствиях несчастного случая на производстве и принятых мерах</t>
-        </is>
-      </c>
-      <c r="E331" s="16" t="inlineStr">
-        <is>
-          <t>ДА</t>
-        </is>
-      </c>
-      <c r="F331" s="16" t="inlineStr">
-        <is>
-          <t>ДА</t>
-        </is>
-      </c>
-      <c r="G331" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H331" s="16" t="inlineStr">
-        <is>
-          <t>Главный бухгалтер</t>
-        </is>
-      </c>
-      <c r="I331" s="16" t="inlineStr">
-        <is>
-          <t>собственноручная</t>
-        </is>
-      </c>
-      <c r="J331" s="16" t="inlineStr">
-        <is>
-          <t>Подтверждение (?)</t>
-        </is>
-      </c>
-      <c r="K331" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="L331" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="332">
-      <c r="A332" s="16" t="inlineStr">
-        <is>
-          <t>Расследование несчастных случаев</t>
-        </is>
-      </c>
-      <c r="B332" s="16" t="inlineStr">
-        <is>
-          <t>Приказ Минтруда России от 20.04.2022 № 223н "Об утверждении Положения об особенностях расследования несчастных случаев на производстве в отдельных отраслях и организациях, форм документов, соответствующих классификаторов, необходимых для расследования несчастных случаев на производстве"</t>
-        </is>
-      </c>
-      <c r="C332" s="16" t="inlineStr">
-        <is>
-          <t>приложение № 2 к приказу № 223н (форма № 11)</t>
-        </is>
-      </c>
-      <c r="D332" s="16" t="inlineStr">
-        <is>
-          <t>Журнал регистрации несчастных случаев на производстве</t>
-        </is>
-      </c>
-      <c r="E332" s="16" t="inlineStr">
-        <is>
-          <t>ДА</t>
-        </is>
-      </c>
-      <c r="F332" s="16" t="inlineStr">
-        <is>
-          <t>ДА</t>
-        </is>
-      </c>
-      <c r="G332" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H332" s="16" t="inlineStr">
-        <is>
-          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
-        </is>
-      </c>
-      <c r="I332" s="16" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J332" s="16" t="inlineStr">
-        <is>
-          <t>Утверждение</t>
-        </is>
-      </c>
-      <c r="K332" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="L332" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="333">
-      <c r="A333" s="16" t="inlineStr">
-        <is>
-          <t>Расследование несчастных случаев</t>
-        </is>
-      </c>
-      <c r="B333" s="16" t="inlineStr">
-        <is>
-          <t>Приказ Минтруда России от 20.04.2022 № 223н "Об утверждении Положения об особенностях расследования несчастных случаев на производстве в отдельных отраслях и организациях, форм документов, соответствующих классификаторов, необходимых для расследования несчастных случаев на производстве"</t>
-        </is>
-      </c>
-      <c r="C333" s="16" t="inlineStr">
-        <is>
-          <t>п. 23 Положения (приложение № 1 к приказу № 223н)</t>
-        </is>
-      </c>
-      <c r="D333" s="16" t="inlineStr">
-        <is>
-          <t>Письменное уведомление об отзыве (замене) члена комиссии или председателя комиссии по расследованию несчастного случая</t>
-        </is>
-      </c>
-      <c r="E333" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="F333" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G333" s="16" t="inlineStr">
-        <is>
-          <t>Письменное уведомление работодателя, образовавшего комиссию, руководителем органа (организации), направившего представителя, об отзыве члена комиссии или председателя и направлении другого представителя</t>
-        </is>
-      </c>
-      <c r="H333" s="16" t="inlineStr">
-        <is>
-          <t>Руководитель органа (организации), направившего члена комиссии</t>
-        </is>
-      </c>
-      <c r="I333" s="16" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J333" s="16" t="inlineStr">
-        <is>
-          <t>Уведомление</t>
-        </is>
-      </c>
-      <c r="K333" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="L333" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334" s="16" t="inlineStr">
-        <is>
-          <t>Расследование несчастных случаев</t>
-        </is>
-      </c>
-      <c r="B334" s="16" t="inlineStr">
-        <is>
-          <t>Приказ Минтруда России от 20.04.2022 № 223н "Об утверждении Положения об особенностях расследования несчастных случаев на производстве в отдельных отраслях и организациях, форм документов, соответствующих классификаторов, необходимых для расследования несчастных случаев на производстве"</t>
-        </is>
-      </c>
-      <c r="C334" s="16" t="inlineStr">
-        <is>
-          <t>п. 23 Положения (приложение № 1 к приказу № 223н)</t>
-        </is>
-      </c>
-      <c r="D334" s="16" t="inlineStr">
-        <is>
-          <t>Документы, подтверждающие замену члена комиссии или председателя комиссии</t>
-        </is>
-      </c>
-      <c r="E334" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="F334" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G334" s="16" t="inlineStr">
-        <is>
-          <t>Документы, подтверждающие замену члена комиссии или председателя комиссии, с указанием причины принятого решения; приобщаются к материалам расследования</t>
-        </is>
-      </c>
-      <c r="H334" s="16" t="inlineStr">
-        <is>
-          <t>Руководитель органа (организации), направившего члена комиссии</t>
-        </is>
-      </c>
-      <c r="I334" s="16" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J334" s="16" t="inlineStr">
-        <is>
-          <t>Утверждение</t>
-        </is>
-      </c>
-      <c r="K334" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="L334" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" s="16" t="inlineStr">
-        <is>
-          <t>Расследование несчастных случаев</t>
-        </is>
-      </c>
-      <c r="B335" s="16" t="inlineStr">
-        <is>
-          <t>Приказ Минтруда России от 20.04.2022 № 223н "Об утверждении Положения об особенностях расследования несчастных случаев на производстве в отдельных отраслях и организациях, форм документов, соответствующих классификаторов, необходимых для расследования несчастных случаев на производстве"</t>
-        </is>
-      </c>
-      <c r="C335" s="16" t="inlineStr">
-        <is>
-          <t>п. 23 Положения (приложение № 1 к приказу № 223н)</t>
-        </is>
-      </c>
-      <c r="D335" s="16" t="inlineStr">
-        <is>
-          <t>Изменения в приказ (распоряжение) об образовании комиссии по расследованию несчастного случая</t>
-        </is>
-      </c>
-      <c r="E335" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="F335" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G335" s="16" t="inlineStr">
-        <is>
-          <t>Изменения в приказ (распоряжение) об образовании комиссии, вносимые работодателем в течение 24 часов после получения письменного уведомления о замене; приобщаются к материалам расследования</t>
-        </is>
-      </c>
-      <c r="H335" s="16" t="inlineStr">
-        <is>
-          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
-        </is>
-      </c>
-      <c r="I335" s="16" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J335" s="16" t="inlineStr">
-        <is>
-          <t>Утверждение</t>
-        </is>
-      </c>
-      <c r="K335" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="L335" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" s="16" t="inlineStr">
-        <is>
-          <t>Расследование несчастных случаев</t>
-        </is>
-      </c>
-      <c r="B336" s="16" t="inlineStr">
-        <is>
-          <t>Приказ Минтруда России от 20.04.2022 № 223н "Об утверждении Положения об особенностях расследования несчастных случаев на производстве в отдельных отраслях и организациях, форм документов, соответствующих классификаторов, необходимых для расследования несчастных случаев на производстве"</t>
-        </is>
-      </c>
-      <c r="C336" s="16" t="inlineStr">
-        <is>
-          <t>п. 24 Положения (приложение № 1 к приказу № 223н)</t>
-        </is>
-      </c>
-      <c r="D336" s="16" t="inlineStr">
-        <is>
-          <t>Заявление пострадавшего или его доверенного лица о расследовании несчастного случая (о котором не было своевременно сообщено работодателю или нетрудоспособность наступила не сразу)</t>
-        </is>
-      </c>
-      <c r="E336" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="F336" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G336" s="16" t="inlineStr">
-        <is>
-          <t>Заявление пострадавшего или его доверенного лица о расследовании несчастного случая, о котором не было своевременно (в течение 24 часов) сообщено работодателю или в результате которого нетрудоспособность наступила не сразу</t>
-        </is>
-      </c>
-      <c r="H336" s="16" t="inlineStr">
-        <is>
-          <t>Пострадавший (доверенное лицо)</t>
-        </is>
-      </c>
-      <c r="I336" s="16" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J336" s="16" t="inlineStr">
-        <is>
-          <t>Заявление</t>
-        </is>
-      </c>
-      <c r="K336" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="L336" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" s="16" t="inlineStr">
-        <is>
-          <t>Расследование несчастных случаев</t>
-        </is>
-      </c>
-      <c r="B337" s="16" t="inlineStr">
-        <is>
-          <t>Приказ Минтруда России от 20.04.2022 № 223н "Об утверждении Положения об особенностях расследования несчастных случаев на производстве в отдельных отраслях и организациях, форм документов, соответствующих классификаторов, необходимых для расследования несчастных случаев на производстве"</t>
-        </is>
-      </c>
-      <c r="C337" s="16" t="inlineStr">
-        <is>
-          <t>п. 26 Положения (приложение № 1 к приказу № 223н)</t>
-        </is>
-      </c>
-      <c r="D337" s="16" t="inlineStr">
-        <is>
-          <t>Протокол заседания комиссии по расследованию несчастного случая</t>
-        </is>
-      </c>
-      <c r="E337" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="F337" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G337" s="16" t="inlineStr">
-        <is>
-          <t>Протокол заседания комиссии в произвольной форме (заседание может проводиться с использованием средств связи, в том числе видео-конференц-связи); приобщается к материалам расследования</t>
-        </is>
-      </c>
-      <c r="H337" s="16" t="inlineStr">
-        <is>
-          <t>Председатель комиссии по расследованию несчастного случая</t>
-        </is>
-      </c>
-      <c r="I337" s="16" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J337" s="16" t="inlineStr">
-        <is>
-          <t>Утверждение</t>
-        </is>
-      </c>
-      <c r="K337" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="L337" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="338">
-      <c r="A338" s="16" t="inlineStr">
-        <is>
-          <t>Расследование несчастных случаев</t>
-        </is>
-      </c>
-      <c r="B338" s="16" t="inlineStr">
-        <is>
-          <t>Приказ Минтруда России от 20.04.2022 № 223н "Об утверждении Положения об особенностях расследования несчастных случаев на производстве в отдельных отраслях и организациях, форм документов, соответствующих классификаторов, необходимых для расследования несчастных случаев на производстве"</t>
-        </is>
-      </c>
-      <c r="C338" s="16" t="inlineStr">
-        <is>
-          <t>п. 26 Положения (приложение № 1 к приказу № 223н)</t>
-        </is>
-      </c>
-      <c r="D338" s="16" t="inlineStr">
-        <is>
-          <t>Протокол заседания комиссии по расследованию несчастного случая</t>
-        </is>
-      </c>
-      <c r="E338" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="F338" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G338" s="16" t="inlineStr">
-        <is>
-          <t>Протокол заседания комиссии в произвольной форме (заседание может проводиться с использованием средств связи, в том числе видео-конференц-связи); приобщается к материалам расследования</t>
-        </is>
-      </c>
-      <c r="H338" s="16" t="inlineStr">
-        <is>
-          <t>Член комиссии по расследованию несчастного случая</t>
-        </is>
-      </c>
-      <c r="I338" s="16" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J338" s="16" t="inlineStr">
-        <is>
-          <t>Подтверждение (?)</t>
-        </is>
-      </c>
-      <c r="K338" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="L338" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="339">
-      <c r="A339" s="16" t="inlineStr">
-        <is>
-          <t>Расследование несчастных случаев</t>
-        </is>
-      </c>
-      <c r="B339" s="16" t="inlineStr">
-        <is>
-          <t>Приказ Минтруда России от 20.04.2022 № 223н "Об утверждении Положения об особенностях расследования несчастных случаев на производстве в отдельных отраслях и организациях, форм документов, соответствующих классификаторов, необходимых для расследования несчастных случаев на производстве"</t>
-        </is>
-      </c>
-      <c r="C339" s="16" t="inlineStr">
-        <is>
-          <t>п. 30–31 Положения (приложение № 1 к приказу № 223н)</t>
-        </is>
-      </c>
-      <c r="D339" s="16" t="inlineStr">
-        <is>
-          <t>Протокол заседания комиссии по расследованию несчастного случая (при разногласиях или отказе от подписания актов)</t>
-        </is>
-      </c>
-      <c r="E339" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="F339" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G339" s="16" t="inlineStr">
-        <is>
-          <t>Протокол в произвольной форме: при разногласиях — решение большинством голосов; при отказе членов комиссии (включая председателя) от подписания актов — с указанием причины отказа; копия направляется в соответствующую государственную инспекцию труда / орган (организацию)</t>
-        </is>
-      </c>
-      <c r="H339" s="16" t="inlineStr">
-        <is>
-          <t>Председатель комиссии по расследованию несчастного случая</t>
-        </is>
-      </c>
-      <c r="I339" s="16" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J339" s="16" t="inlineStr">
-        <is>
-          <t>Утверждение</t>
-        </is>
-      </c>
-      <c r="K339" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="L339" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="340">
-      <c r="A340" s="16" t="inlineStr">
-        <is>
-          <t>Расследование несчастных случаев</t>
-        </is>
-      </c>
-      <c r="B340" s="16" t="inlineStr">
-        <is>
-          <t>Приказ Минтруда России от 20.04.2022 № 223н "Об утверждении Положения об особенностях расследования несчастных случаев на производстве в отдельных отраслях и организациях, форм документов, соответствующих классификаторов, необходимых для расследования несчастных случаев на производстве"</t>
-        </is>
-      </c>
-      <c r="C340" s="16" t="inlineStr">
-        <is>
-          <t>п. 30–31 Положения (приложение № 1 к приказу № 223н)</t>
-        </is>
-      </c>
-      <c r="D340" s="16" t="inlineStr">
-        <is>
-          <t>Протокол заседания комиссии по расследованию несчастного случая (при разногласиях или отказе от подписания актов)</t>
-        </is>
-      </c>
-      <c r="E340" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="F340" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G340" s="16" t="inlineStr">
-        <is>
-          <t>Протокол в произвольной форме: при разногласиях — решение большинством голосов; при отказе членов комиссии (включая председателя) от подписания актов — с указанием причины отказа; копия направляется в соответствующую государственную инспекцию труда / орган (организацию)</t>
-        </is>
-      </c>
-      <c r="H340" s="16" t="inlineStr">
-        <is>
-          <t>Член комиссии по расследованию несчастного случая</t>
-        </is>
-      </c>
-      <c r="I340" s="16" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J340" s="16" t="inlineStr">
-        <is>
-          <t>Подтверждение (?)</t>
-        </is>
-      </c>
-      <c r="K340" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="L340" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="341">
-      <c r="A341" s="16" t="inlineStr">
-        <is>
-          <t>Расследование несчастных случаев</t>
-        </is>
-      </c>
-      <c r="B341" s="16" t="inlineStr">
-        <is>
-          <t>Приказ Минтруда России от 20.04.2022 № 223н "Об утверждении Положения об особенностях расследования несчастных случаев на производстве в отдельных отраслях и организациях, форм документов, соответствующих классификаторов, необходимых для расследования несчастных случаев на производстве"</t>
-        </is>
-      </c>
-      <c r="C341" s="16" t="inlineStr">
-        <is>
-          <t>п. 30 Положения (приложение № 1 к приказу № 223н)</t>
-        </is>
-      </c>
-      <c r="D341" s="16" t="inlineStr">
-        <is>
-          <t>Аргументированное особое мнение члена комиссии (включая председателя комиссии)</t>
-        </is>
-      </c>
-      <c r="E341" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="F341" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G341" s="16" t="inlineStr">
-        <is>
-          <t>Аргументированное особое мнение члена комиссии (включая председателя), не согласного с принятым решением; приобщается к материалам расследования</t>
-        </is>
-      </c>
-      <c r="H341" s="16" t="inlineStr">
-        <is>
-          <t>Член комиссии (включая председателя комиссии) по расследованию несчастного случая</t>
-        </is>
-      </c>
-      <c r="I341" s="16" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J341" s="16" t="inlineStr">
-        <is>
-          <t>Подтверждение (?)</t>
-        </is>
-      </c>
-      <c r="K341" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="L341" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="342">
-      <c r="A342" s="16" t="inlineStr">
-        <is>
-          <t>Расследование несчастных случаев</t>
-        </is>
-      </c>
-      <c r="B342" s="16" t="inlineStr">
-        <is>
-          <t>Приказ Минтруда России от 20.04.2022 № 223н "Об утверждении Положения об особенностях расследования несчастных случаев на производстве в отдельных отраслях и организациях, форм документов, соответствующих классификаторов, необходимых для расследования несчастных случаев на производстве"</t>
-        </is>
-      </c>
-      <c r="C342" s="16" t="inlineStr">
-        <is>
-          <t>п. 25 Положения (приложение № 1 к приказу № 223н)</t>
-        </is>
-      </c>
-      <c r="D342" s="16" t="inlineStr">
-        <is>
-          <t>Мотивированное требование члена комиссии о направлении запроса в федеральный орган исполнительной власти (его территориальный орган)</t>
-        </is>
-      </c>
-      <c r="E342" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="F342" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G342" s="16" t="inlineStr">
-        <is>
-          <t>Мотивированное требование члена комиссии о направлении запроса в целях получения заключения федерального органа исполнительной власти, осуществляющего государственный контроль (надзор) в установленной сфере деятельности (его территориального органа)</t>
-        </is>
-      </c>
-      <c r="H342" s="16" t="inlineStr">
-        <is>
-          <t>Член комиссии по расследованию несчастного случая</t>
-        </is>
-      </c>
-      <c r="I342" s="16" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J342" s="16" t="inlineStr">
-        <is>
-          <t>Утверждение</t>
-        </is>
-      </c>
-      <c r="K342" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="L342" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="343">
-      <c r="A343" s="16" t="inlineStr">
-        <is>
-          <t>Расследование несчастных случаев</t>
-        </is>
-      </c>
-      <c r="B343" s="16" t="inlineStr">
-        <is>
-          <t>Приказ Минтруда России от 20.04.2022 № 223н "Об утверждении Положения об особенностях расследования несчастных случаев на производстве в отдельных отраслях и организациях, форм документов, соответствующих классификаторов, необходимых для расследования несчастных случаев на производстве"</t>
-        </is>
-      </c>
-      <c r="C343" s="16" t="inlineStr">
-        <is>
-          <t>п. 25 Положения (приложение № 1 к приказу № 223н)</t>
-        </is>
-      </c>
-      <c r="D343" s="16" t="inlineStr">
-        <is>
-          <t>Запрос председателя комиссии в федеральный орган исполнительной власти (его территориальный орган) о выдаче заключения</t>
-        </is>
-      </c>
-      <c r="E343" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="F343" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G343" s="16" t="inlineStr">
-        <is>
-          <t>Запрос председателя комиссии (в установленных случаях — государственного инспектора труда) в соответствующий федеральный орган исполнительной власти (его территориальный орган) в целях получения заключения, в компетенции которого находится запрашиваемое исследование</t>
-        </is>
-      </c>
-      <c r="H343" s="16" t="inlineStr">
-        <is>
-          <t>Председатель комиссии по расследованию несчастного случая</t>
-        </is>
-      </c>
-      <c r="I343" s="16" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J343" s="16" t="inlineStr">
-        <is>
-          <t>Утверждение</t>
-        </is>
-      </c>
-      <c r="K343" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="L343" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="344">
-      <c r="A344" s="16" t="inlineStr">
-        <is>
-          <t>Расследование несчастных случаев</t>
-        </is>
-      </c>
-      <c r="B344" s="16" t="inlineStr">
-        <is>
-          <t>Приказ Минтруда России от 20.04.2022 № 223н "Об утверждении Положения об особенностях расследования несчастных случаев на производстве в отдельных отраслях и организациях, форм документов, соответствующих классификаторов, необходимых для расследования несчастных случаев на производстве"</t>
-        </is>
-      </c>
-      <c r="C344" s="16" t="inlineStr">
-        <is>
-          <t>п. 27 Положения (приложение № 1 к приказу № 223н)</t>
-        </is>
-      </c>
-      <c r="D344" s="16" t="inlineStr">
-        <is>
-          <t>Экспертное заключение о причине смерти пострадавшего и (или) его нахождении в момент несчастного случая в состоянии алкогольного, наркотического или иного токсического опьянения</t>
-        </is>
-      </c>
-      <c r="E344" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="F344" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G344" s="16" t="inlineStr">
-        <is>
-          <t>Экспертное заключение о причине смерти пострадавшего и его нахождении в момент несчастного случая в состоянии алкогольного, наркотического или иного токсического опьянения; включается в материалы расследования случая гибели работника; обеспечивается работодателем за счет собственных средств по требованию комиссии</t>
-        </is>
-      </c>
-      <c r="H344" s="16" t="inlineStr">
-        <is>
-          <t>Эксперт (специалист)</t>
-        </is>
-      </c>
-      <c r="I344" s="16" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J344" s="16" t="inlineStr">
-        <is>
-          <t>Утверждение</t>
-        </is>
-      </c>
-      <c r="K344" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="L344" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="345">
-      <c r="A345" s="16" t="inlineStr">
-        <is>
-          <t>Расследование несчастных случаев</t>
-        </is>
-      </c>
-      <c r="B345" s="16" t="inlineStr">
-        <is>
-          <t>Приказ Минтруда России от 20.04.2022 № 223н "Об утверждении Положения об особенностях расследования несчастных случаев на производстве в отдельных отраслях и организациях, форм документов, соответствующих классификаторов, необходимых для расследования несчастных случаев на производстве"</t>
-        </is>
-      </c>
-      <c r="C345" s="16" t="inlineStr">
-        <is>
-          <t>п. 21.2 Положения (приложение № 1 к приказу № 223н)</t>
-        </is>
-      </c>
-      <c r="D345" s="16" t="inlineStr">
-        <is>
-          <t>Документы, подтверждающие причинно-следственную связь между гибелью (травмой) работника и исполнением им трудовых обязанностей (при оформлении акта формы Н-1ЧС)</t>
-        </is>
-      </c>
-      <c r="E345" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="F345" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G345" s="16" t="inlineStr">
-        <is>
-          <t>Документы, подтверждающие причинно-следственную связь между гибелью (травмой) работника и исполнением им трудовых обязанностей; направляются вместе с актами формы Н-1ЧС в исполнительный орган страховщика</t>
-        </is>
-      </c>
-      <c r="H345" s="16" t="inlineStr">
-        <is>
-          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
-        </is>
-      </c>
-      <c r="I345" s="16" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J345" s="16" t="inlineStr">
-        <is>
-          <t>Утверждение</t>
-        </is>
-      </c>
-      <c r="K345" s="16" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="L345" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Нет ограничений</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L195"/>
+  <autoFilter ref="A1:L299"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>

--- a/presentations/Analiz_SUOT_podpisanty_skvoznaya.xlsx
+++ b/presentations/Analiz_SUOT_podpisanty_skvoznaya.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -64,6 +64,10 @@
       <sz val="10"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -84,7 +88,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -142,11 +146,17 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -193,6 +203,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -560,7 +573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L324"/>
+  <dimension ref="A1:L347"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8"/>
   <cols>
     <col width="10" customWidth="1" style="14" min="1" max="1"/>
@@ -20659,6 +20672,1432 @@
         </is>
       </c>
     </row>
+    <row r="325">
+      <c r="A325" s="20" t="inlineStr">
+        <is>
+          <t>Взаимодействие с надзорными органами</t>
+        </is>
+      </c>
+      <c r="B325" s="20" t="inlineStr">
+        <is>
+          <t>Федеральный закон от 12.01.1996 № 10-ФЗ; Федеральный закон от 26.12.2008 № 294-ФЗ; Постановление Правительства РФ от 21.07.2021 № 1230</t>
+        </is>
+      </c>
+      <c r="C325" s="20" t="inlineStr">
+        <is>
+          <t>п. 35–49 Положения (ПП РФ № 1230); ст. 25 Федерального закона № 294-ФЗ (права юридического лица / ИП при проведении проверки)</t>
+        </is>
+      </c>
+      <c r="D325" s="20" t="inlineStr">
+        <is>
+          <t>Приказ (распоряжение) о назначении уполномоченного представителя контролируемого лица для взаимодействия с органами государственного контроля (надзора) в сфере труда (ГИТ / Роструд)</t>
+        </is>
+      </c>
+      <c r="E325" s="20" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F325" s="20" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="G325" s="20" t="inlineStr">
+        <is>
+          <t>ФИО и должность уполномоченного представителя; объем полномочий при контрольных (надзорных) и профилактических мероприятиях; срок полномочий; порядок взаимодействия с должностными лицами контрольного органа</t>
+        </is>
+      </c>
+      <c r="H325" s="20" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I325" s="20" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J325" s="20" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K325" s="20" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L325" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="20" t="inlineStr">
+        <is>
+          <t>Взаимодействие с надзорными органами</t>
+        </is>
+      </c>
+      <c r="B326" s="20" t="inlineStr">
+        <is>
+          <t>Федеральный закон от 12.01.1996 № 10-ФЗ; Федеральный закон от 26.12.2008 № 294-ФЗ; Постановление Правительства РФ от 21.07.2021 № 1230</t>
+        </is>
+      </c>
+      <c r="C326" s="20" t="inlineStr">
+        <is>
+          <t>ст. 25 Федерального закона № 294-ФЗ; п. 35–49 Положения (ПП РФ № 1230)</t>
+        </is>
+      </c>
+      <c r="D326" s="20" t="inlineStr">
+        <is>
+          <t>Доверенность на представление интересов контролируемого лица при проведении контрольного (надзорного) мероприятия / профилактического визита</t>
+        </is>
+      </c>
+      <c r="E326" s="20" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F326" s="20" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="G326" s="20" t="inlineStr">
+        <is>
+          <t>Сведения о доверителе и представителе; перечень полномочий (ознакомление с решением и актом, представление документов и объяснений, подписание документов, подача возражений / жалоб); срок действия</t>
+        </is>
+      </c>
+      <c r="H326" s="20" t="inlineStr">
+        <is>
+          <t>Руководитель организации (доверитель); представитель (при принятии доверенности)</t>
+        </is>
+      </c>
+      <c r="I326" s="20" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J326" s="20" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K326" s="20" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L326" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="20" t="inlineStr">
+        <is>
+          <t>Взаимодействие с надзорными органами</t>
+        </is>
+      </c>
+      <c r="B327" s="20" t="inlineStr">
+        <is>
+          <t>Федеральный закон от 12.01.1996 № 10-ФЗ; Федеральный закон от 26.12.2008 № 294-ФЗ; Постановление Правительства РФ от 21.07.2021 № 1230</t>
+        </is>
+      </c>
+      <c r="C327" s="20" t="inlineStr">
+        <is>
+          <t>ч. 8–11 ст. 16 Федерального закона № 294-ФЗ; типовая форма — приказ Минэкономразвития России от 30.04.2009 № 141</t>
+        </is>
+      </c>
+      <c r="D327" s="20" t="inlineStr">
+        <is>
+          <t>Журнал учета проверок юридического лица / индивидуального предпринимателя</t>
+        </is>
+      </c>
+      <c r="E327" s="20" t="inlineStr">
+        <is>
+          <t>ДА (типовая форма, утв. приказом Минэкономразвития № 141)</t>
+        </is>
+      </c>
+      <c r="F327" s="20" t="inlineStr">
+        <is>
+          <t>УСЛОВНО (право, а не обязанность)</t>
+        </is>
+      </c>
+      <c r="G327" s="20" t="inlineStr">
+        <is>
+          <t>Наименование контрольного органа; даты и время проверки; правовые основания, цели, задачи и предмет; выявленные нарушения; выданные предписания; ФИО и должности проверяющих; подписи должностных лиц, проводивших проверку. Журнал прошивается, нумеруется и удостоверяется печатью (при наличии)</t>
+        </is>
+      </c>
+      <c r="H327" s="20" t="inlineStr">
+        <is>
+          <t>Должностное лицо органа контроля (надзора) — запись о проверке; ответственный работник организации — ведение журнала</t>
+        </is>
+      </c>
+      <c r="I327" s="20" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J327" s="20" t="inlineStr">
+        <is>
+          <t>Подтверждение</t>
+        </is>
+      </c>
+      <c r="K327" s="20" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="L327" s="20" t="inlineStr">
+        <is>
+          <t>Прошивка, нумерация и удостоверение печатью юридического лица / ИП (при наличии печати) — ч. 10 ст. 16 Федерального закона № 294-ФЗ</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="20" t="inlineStr">
+        <is>
+          <t>Взаимодействие с надзорными органами</t>
+        </is>
+      </c>
+      <c r="B328" s="20" t="inlineStr">
+        <is>
+          <t>Федеральный закон от 12.01.1996 № 10-ФЗ; Федеральный закон от 26.12.2008 № 294-ФЗ; Постановление Правительства РФ от 21.07.2021 № 1230</t>
+        </is>
+      </c>
+      <c r="C328" s="20" t="inlineStr">
+        <is>
+          <t>ч. 8–10 ст. 16 Федерального закона № 294-ФЗ</t>
+        </is>
+      </c>
+      <c r="D328" s="20" t="inlineStr">
+        <is>
+          <t>Приказ о назначении ответственного за ведение журнала учета проверок</t>
+        </is>
+      </c>
+      <c r="E328" s="20" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F328" s="20" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="G328" s="20" t="inlineStr">
+        <is>
+          <t>ФИО и должность ответственного; порядок замещения на период отсутствия; обязанность обеспечивать предъявление журнала должностным лицам контрольного органа</t>
+        </is>
+      </c>
+      <c r="H328" s="20" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I328" s="20" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J328" s="20" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K328" s="20" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L328" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="20" t="inlineStr">
+        <is>
+          <t>Взаимодействие с надзорными органами</t>
+        </is>
+      </c>
+      <c r="B329" s="20" t="inlineStr">
+        <is>
+          <t>Федеральный закон от 12.01.1996 № 10-ФЗ; Федеральный закон от 26.12.2008 № 294-ФЗ; Постановление Правительства РФ от 21.07.2021 № 1230</t>
+        </is>
+      </c>
+      <c r="C329" s="20" t="inlineStr">
+        <is>
+          <t>п. 35, 40, 49 Положения (ПП РФ № 1230)</t>
+        </is>
+      </c>
+      <c r="D329" s="20" t="inlineStr">
+        <is>
+          <t>Решение (копия решения) о проведении контрольного (надзорного) мероприятия</t>
+        </is>
+      </c>
+      <c r="E329" s="20" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F329" s="20" t="inlineStr">
+        <is>
+          <t>— (документ контрольного органа)</t>
+        </is>
+      </c>
+      <c r="G329" s="20" t="inlineStr">
+        <is>
+          <t>Вид КНМ; предмет; сроки; перечень должностных лиц; перечень мероприятий; перечень документов, подлежащих истребованию (при наличии); реквизиты решения</t>
+        </is>
+      </c>
+      <c r="H329" s="20" t="inlineStr">
+        <is>
+          <t>Уполномоченное должностное лицо Роструда / ГИТ</t>
+        </is>
+      </c>
+      <c r="I329" s="20" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J329" s="20" t="inlineStr">
+        <is>
+          <t>Уведомление</t>
+        </is>
+      </c>
+      <c r="K329" s="20" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="L329" s="20" t="inlineStr">
+        <is>
+          <t>Нет ограничений</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="20" t="inlineStr">
+        <is>
+          <t>Взаимодействие с надзорными органами</t>
+        </is>
+      </c>
+      <c r="B330" s="20" t="inlineStr">
+        <is>
+          <t>Федеральный закон от 12.01.1996 № 10-ФЗ; Федеральный закон от 26.12.2008 № 294-ФЗ; Постановление Правительства РФ от 21.07.2021 № 1230</t>
+        </is>
+      </c>
+      <c r="C330" s="20" t="inlineStr">
+        <is>
+          <t>п. 37–39, 41–42, 44, 46–49 Положения (ПП РФ № 1230)</t>
+        </is>
+      </c>
+      <c r="D330" s="20" t="inlineStr">
+        <is>
+          <t>Требование контрольного (надзорного) органа о представлении документов и (или) сведений</t>
+        </is>
+      </c>
+      <c r="E330" s="20" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F330" s="20" t="inlineStr">
+        <is>
+          <t>— (документ контрольного органа)</t>
+        </is>
+      </c>
+      <c r="G330" s="20" t="inlineStr">
+        <is>
+          <t>Перечень истребуемых документов / сведений; срок представления; реквизиты КНМ; последствия непредставления</t>
+        </is>
+      </c>
+      <c r="H330" s="20" t="inlineStr">
+        <is>
+          <t>Уполномоченное должностное лицо Роструда / ГИТ</t>
+        </is>
+      </c>
+      <c r="I330" s="20" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J330" s="20" t="inlineStr">
+        <is>
+          <t>Уведомление</t>
+        </is>
+      </c>
+      <c r="K330" s="20" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="L330" s="20" t="inlineStr">
+        <is>
+          <t>Нет ограничений</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="20" t="inlineStr">
+        <is>
+          <t>Взаимодействие с надзорными органами</t>
+        </is>
+      </c>
+      <c r="B331" s="20" t="inlineStr">
+        <is>
+          <t>Федеральный закон от 12.01.1996 № 10-ФЗ; Федеральный закон от 26.12.2008 № 294-ФЗ; Постановление Правительства РФ от 21.07.2021 № 1230</t>
+        </is>
+      </c>
+      <c r="C331" s="20" t="inlineStr">
+        <is>
+          <t>п. 44, 46–49 Положения (ПП РФ № 1230); ст. 25 Федерального закона № 294-ФЗ</t>
+        </is>
+      </c>
+      <c r="D331" s="20" t="inlineStr">
+        <is>
+          <t>Ответ на требование / комплект документов и сведений, представленных в контрольный (надзорный) орган</t>
+        </is>
+      </c>
+      <c r="E331" s="20" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F331" s="20" t="inlineStr">
+        <is>
+          <t>ДА (при поступлении требования)</t>
+        </is>
+      </c>
+      <c r="G331" s="20" t="inlineStr">
+        <is>
+          <t>Сопроводительное письмо; опись документов; копии (выписки) локальных актов, кадровых и иных документов по предмету КНМ; пояснения о полноте представленного комплекта</t>
+        </is>
+      </c>
+      <c r="H331" s="20" t="inlineStr">
+        <is>
+          <t>Руководитель организации / уполномоченный представитель контролируемого лица</t>
+        </is>
+      </c>
+      <c r="I331" s="20" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J331" s="20" t="inlineStr">
+        <is>
+          <t>Подтверждение</t>
+        </is>
+      </c>
+      <c r="K331" s="20" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L331" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="20" t="inlineStr">
+        <is>
+          <t>Взаимодействие с надзорными органами</t>
+        </is>
+      </c>
+      <c r="B332" s="20" t="inlineStr">
+        <is>
+          <t>Федеральный закон от 12.01.1996 № 10-ФЗ; Федеральный закон от 26.12.2008 № 294-ФЗ; Постановление Правительства РФ от 21.07.2021 № 1230</t>
+        </is>
+      </c>
+      <c r="C332" s="20" t="inlineStr">
+        <is>
+          <t>п. 37–39, 41–42, 44, 47–49 Положения (ПП РФ № 1230)</t>
+        </is>
+      </c>
+      <c r="D332" s="20" t="inlineStr">
+        <is>
+          <t>Письменные объяснения контролируемого лица (его представителя) по вопросам предмета контрольного (надзорного) мероприятия</t>
+        </is>
+      </c>
+      <c r="E332" s="20" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F332" s="20" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="G332" s="20" t="inlineStr">
+        <is>
+          <t>Обстоятельства, по которым запрошены объяснения; позиция контролируемого лица; ссылки на документы; дата и подпись</t>
+        </is>
+      </c>
+      <c r="H332" s="20" t="inlineStr">
+        <is>
+          <t>Руководитель организации / уполномоченный представитель / иное лицо, давшее объяснения</t>
+        </is>
+      </c>
+      <c r="I332" s="20" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J332" s="20" t="inlineStr">
+        <is>
+          <t>Подтверждение</t>
+        </is>
+      </c>
+      <c r="K332" s="20" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L332" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="20" t="inlineStr">
+        <is>
+          <t>Взаимодействие с надзорными органами</t>
+        </is>
+      </c>
+      <c r="B333" s="20" t="inlineStr">
+        <is>
+          <t>Федеральный закон от 12.01.1996 № 10-ФЗ; Федеральный закон от 26.12.2008 № 294-ФЗ; Постановление Правительства РФ от 21.07.2021 № 1230</t>
+        </is>
+      </c>
+      <c r="C333" s="20" t="inlineStr">
+        <is>
+          <t>п. 50–51 Положения (ПП РФ № 1230); ст. 16 Федерального закона № 294-ФЗ (акт проверки — в рамках сферы действия 294-ФЗ)</t>
+        </is>
+      </c>
+      <c r="D333" s="20" t="inlineStr">
+        <is>
+          <t>Акт контрольного (надзорного) мероприятия</t>
+        </is>
+      </c>
+      <c r="E333" s="20" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F333" s="20" t="inlineStr">
+        <is>
+          <t>— (документ контрольного органа)</t>
+        </is>
+      </c>
+      <c r="G333" s="20" t="inlineStr">
+        <is>
+          <t>Дата, время, место составления; сведения о контролируемом лице; предмет и результаты КНМ; выявленные нарушения либо отсутствие нарушений; сведения о приложениях</t>
+        </is>
+      </c>
+      <c r="H333" s="20" t="inlineStr">
+        <is>
+          <t>Уполномоченное должностное лицо Роструда / ГИТ; представитель контролируемого лица (при ознакомлении / получении)</t>
+        </is>
+      </c>
+      <c r="I333" s="20" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J333" s="20" t="inlineStr">
+        <is>
+          <t>Уведомление</t>
+        </is>
+      </c>
+      <c r="K333" s="20" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="L333" s="20" t="inlineStr">
+        <is>
+          <t>Нет ограничений</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="20" t="inlineStr">
+        <is>
+          <t>Взаимодействие с надзорными органами</t>
+        </is>
+      </c>
+      <c r="B334" s="20" t="inlineStr">
+        <is>
+          <t>Федеральный закон от 12.01.1996 № 10-ФЗ; Федеральный закон от 26.12.2008 № 294-ФЗ; Постановление Правительства РФ от 21.07.2021 № 1230</t>
+        </is>
+      </c>
+      <c r="C334" s="20" t="inlineStr">
+        <is>
+          <t>п. 50–51 Положения (ПП РФ № 1230)</t>
+        </is>
+      </c>
+      <c r="D334" s="20" t="inlineStr">
+        <is>
+          <t>Акт о проведении обязательного профилактического визита</t>
+        </is>
+      </c>
+      <c r="E334" s="20" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F334" s="20" t="inlineStr">
+        <is>
+          <t>— (документ контрольного органа)</t>
+        </is>
+      </c>
+      <c r="G334" s="20" t="inlineStr">
+        <is>
+          <t>Сведения о контролируемом лице; дата и формат визита; доведенная информация об обязательных требованиях и категории риска; результаты оценки уровня соблюдения обязательных требований</t>
+        </is>
+      </c>
+      <c r="H334" s="20" t="inlineStr">
+        <is>
+          <t>Уполномоченное должностное лицо Роструда / ГИТ</t>
+        </is>
+      </c>
+      <c r="I334" s="20" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J334" s="20" t="inlineStr">
+        <is>
+          <t>Уведомление</t>
+        </is>
+      </c>
+      <c r="K334" s="20" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="L334" s="20" t="inlineStr">
+        <is>
+          <t>Нет ограничений</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="20" t="inlineStr">
+        <is>
+          <t>Взаимодействие с надзорными органами</t>
+        </is>
+      </c>
+      <c r="B335" s="20" t="inlineStr">
+        <is>
+          <t>Федеральный закон от 12.01.1996 № 10-ФЗ; Федеральный закон от 26.12.2008 № 294-ФЗ; Постановление Правительства РФ от 21.07.2021 № 1230</t>
+        </is>
+      </c>
+      <c r="C335" s="20" t="inlineStr">
+        <is>
+          <t>п. 50–51 Положения (ПП РФ № 1230); ст. 21, 25 Федерального закона № 294-ФЗ (в части возражений на акт — при применении 294-ФЗ)</t>
+        </is>
+      </c>
+      <c r="D335" s="20" t="inlineStr">
+        <is>
+          <t>Возражения на акт контрольного (надзорного) мероприятия / акт обязательного профилактического визита</t>
+        </is>
+      </c>
+      <c r="E335" s="20" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F335" s="20" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="G335" s="20" t="inlineStr">
+        <is>
+          <t>Реквизиты акта; доводы несогласия; ссылки на нормы и доказательства; перечень приложений; просьба учесть возражения</t>
+        </is>
+      </c>
+      <c r="H335" s="20" t="inlineStr">
+        <is>
+          <t>Руководитель организации / уполномоченный представитель контролируемого лица</t>
+        </is>
+      </c>
+      <c r="I335" s="20" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J335" s="20" t="inlineStr">
+        <is>
+          <t>Заявление</t>
+        </is>
+      </c>
+      <c r="K335" s="20" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L335" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="20" t="inlineStr">
+        <is>
+          <t>Взаимодействие с надзорными органами</t>
+        </is>
+      </c>
+      <c r="B336" s="20" t="inlineStr">
+        <is>
+          <t>Федеральный закон от 12.01.1996 № 10-ФЗ; Федеральный закон от 26.12.2008 № 294-ФЗ; Постановление Правительства РФ от 21.07.2021 № 1230</t>
+        </is>
+      </c>
+      <c r="C336" s="20" t="inlineStr">
+        <is>
+          <t>п. 50–51 Положения (ПП РФ № 1230); ст. 17 Федерального закона № 294-ФЗ (предписание — в рамках сферы действия 294-ФЗ)</t>
+        </is>
+      </c>
+      <c r="D336" s="20" t="inlineStr">
+        <is>
+          <t>Предписание об устранении выявленных нарушений обязательных требований</t>
+        </is>
+      </c>
+      <c r="E336" s="20" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F336" s="20" t="inlineStr">
+        <is>
+          <t>— (документ контрольного органа)</t>
+        </is>
+      </c>
+      <c r="G336" s="20" t="inlineStr">
+        <is>
+          <t>Перечень нарушений; сроки устранения; требования о представлении информации об исполнении; реквизиты предписания</t>
+        </is>
+      </c>
+      <c r="H336" s="20" t="inlineStr">
+        <is>
+          <t>Уполномоченное должностное лицо Роструда / ГИТ</t>
+        </is>
+      </c>
+      <c r="I336" s="20" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J336" s="20" t="inlineStr">
+        <is>
+          <t>Уведомление</t>
+        </is>
+      </c>
+      <c r="K336" s="20" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="L336" s="20" t="inlineStr">
+        <is>
+          <t>Нет ограничений</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="20" t="inlineStr">
+        <is>
+          <t>Взаимодействие с надзорными органами</t>
+        </is>
+      </c>
+      <c r="B337" s="20" t="inlineStr">
+        <is>
+          <t>Федеральный закон от 12.01.1996 № 10-ФЗ; Федеральный закон от 26.12.2008 № 294-ФЗ; Постановление Правительства РФ от 21.07.2021 № 1230</t>
+        </is>
+      </c>
+      <c r="C337" s="20" t="inlineStr">
+        <is>
+          <t>п. 50–51 Положения (ПП РФ № 1230)</t>
+        </is>
+      </c>
+      <c r="D337" s="20" t="inlineStr">
+        <is>
+          <t>Отчет (уведомление) об исполнении предписания с приложением подтверждающих документов</t>
+        </is>
+      </c>
+      <c r="E337" s="20" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F337" s="20" t="inlineStr">
+        <is>
+          <t>ДА (при выдаче предписания)</t>
+        </is>
+      </c>
+      <c r="G337" s="20" t="inlineStr">
+        <is>
+          <t>Реквизиты предписания; перечень устраненных нарушений; принятые меры; сроки исполнения; опись приложений (копии приказов, ЛНА, актов, журналов и др.)</t>
+        </is>
+      </c>
+      <c r="H337" s="20" t="inlineStr">
+        <is>
+          <t>Руководитель организации / уполномоченный представитель контролируемого лица</t>
+        </is>
+      </c>
+      <c r="I337" s="20" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J337" s="20" t="inlineStr">
+        <is>
+          <t>Подтверждение</t>
+        </is>
+      </c>
+      <c r="K337" s="20" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L337" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="20" t="inlineStr">
+        <is>
+          <t>Взаимодействие с надзорными органами</t>
+        </is>
+      </c>
+      <c r="B338" s="20" t="inlineStr">
+        <is>
+          <t>Федеральный закон от 12.01.1996 № 10-ФЗ; Федеральный закон от 26.12.2008 № 294-ФЗ; Постановление Правительства РФ от 21.07.2021 № 1230</t>
+        </is>
+      </c>
+      <c r="C338" s="20" t="inlineStr">
+        <is>
+          <t>п. 21–24 Положения (ПП РФ № 1230)</t>
+        </is>
+      </c>
+      <c r="D338" s="20" t="inlineStr">
+        <is>
+          <t>Предостережение о недопустимости нарушения обязательных требований</t>
+        </is>
+      </c>
+      <c r="E338" s="20" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F338" s="20" t="inlineStr">
+        <is>
+          <t>— (документ контрольного органа)</t>
+        </is>
+      </c>
+      <c r="G338" s="20" t="inlineStr">
+        <is>
+          <t>Указание на обязательные требования; сведения, послужившие основанием; предложение принять меры; разъяснение порядка подачи возражения</t>
+        </is>
+      </c>
+      <c r="H338" s="20" t="inlineStr">
+        <is>
+          <t>Уполномоченное должностное лицо Роструда / ГИТ</t>
+        </is>
+      </c>
+      <c r="I338" s="20" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J338" s="20" t="inlineStr">
+        <is>
+          <t>Уведомление</t>
+        </is>
+      </c>
+      <c r="K338" s="20" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="L338" s="20" t="inlineStr">
+        <is>
+          <t>Нет ограничений</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="20" t="inlineStr">
+        <is>
+          <t>Взаимодействие с надзорными органами</t>
+        </is>
+      </c>
+      <c r="B339" s="20" t="inlineStr">
+        <is>
+          <t>Федеральный закон от 12.01.1996 № 10-ФЗ; Федеральный закон от 26.12.2008 № 294-ФЗ; Постановление Правительства РФ от 21.07.2021 № 1230</t>
+        </is>
+      </c>
+      <c r="C339" s="20" t="inlineStr">
+        <is>
+          <t>п. 23 Положения (ПП РФ № 1230)</t>
+        </is>
+      </c>
+      <c r="D339" s="20" t="inlineStr">
+        <is>
+          <t>Возражение на предостережение о недопустимости нарушения обязательных требований</t>
+        </is>
+      </c>
+      <c r="E339" s="20" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F339" s="20" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="G339" s="20" t="inlineStr">
+        <is>
+          <t>Сведения о предостережении и должностном лице; доводы несогласия; приложения</t>
+        </is>
+      </c>
+      <c r="H339" s="20" t="inlineStr">
+        <is>
+          <t>Руководитель организации / уполномоченный представитель контролируемого лица</t>
+        </is>
+      </c>
+      <c r="I339" s="20" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J339" s="20" t="inlineStr">
+        <is>
+          <t>Заявление</t>
+        </is>
+      </c>
+      <c r="K339" s="20" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L339" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="20" t="inlineStr">
+        <is>
+          <t>Взаимодействие с надзорными органами</t>
+        </is>
+      </c>
+      <c r="B340" s="20" t="inlineStr">
+        <is>
+          <t>Федеральный закон от 12.01.1996 № 10-ФЗ; Федеральный закон от 26.12.2008 № 294-ФЗ; Постановление Правительства РФ от 21.07.2021 № 1230</t>
+        </is>
+      </c>
+      <c r="C340" s="20" t="inlineStr">
+        <is>
+          <t>раздел VI Положения (ПП РФ № 1230), п. 52–58</t>
+        </is>
+      </c>
+      <c r="D340" s="20" t="inlineStr">
+        <is>
+          <t>Жалоба в досудебном порядке на решения Роструда / ГИТ, действия (бездействие) должностных лиц</t>
+        </is>
+      </c>
+      <c r="E340" s="20" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F340" s="20" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="G340" s="20" t="inlineStr">
+        <is>
+          <t>Наименование органа; сведения о заявителе; реквизиты обжалуемого решения / описание действий (бездействия); доводы; требования заявителя; перечень приложений</t>
+        </is>
+      </c>
+      <c r="H340" s="20" t="inlineStr">
+        <is>
+          <t>Руководитель организации / уполномоченный представитель контролируемого лица</t>
+        </is>
+      </c>
+      <c r="I340" s="20" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J340" s="20" t="inlineStr">
+        <is>
+          <t>Заявление</t>
+        </is>
+      </c>
+      <c r="K340" s="20" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L340" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="20" t="inlineStr">
+        <is>
+          <t>Взаимодействие с надзорными органами</t>
+        </is>
+      </c>
+      <c r="B341" s="20" t="inlineStr">
+        <is>
+          <t>Федеральный закон от 12.01.1996 № 10-ФЗ; Федеральный закон от 26.12.2008 № 294-ФЗ; Постановление Правительства РФ от 21.07.2021 № 1230</t>
+        </is>
+      </c>
+      <c r="C341" s="20" t="inlineStr">
+        <is>
+          <t>п. 14 Положения (ПП РФ № 1230)</t>
+        </is>
+      </c>
+      <c r="D341" s="20" t="inlineStr">
+        <is>
+          <t>Заявление контролируемого лица об изменении категории риска объекта контроля</t>
+        </is>
+      </c>
+      <c r="E341" s="20" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F341" s="20" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="G341" s="20" t="inlineStr">
+        <is>
+          <t>Сведения об объекте контроля; действующая категория риска; обоснование изменения; документы и сведения, подтверждающие доводы</t>
+        </is>
+      </c>
+      <c r="H341" s="20" t="inlineStr">
+        <is>
+          <t>Руководитель организации / уполномоченный представитель контролируемого лица</t>
+        </is>
+      </c>
+      <c r="I341" s="20" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J341" s="20" t="inlineStr">
+        <is>
+          <t>Заявление</t>
+        </is>
+      </c>
+      <c r="K341" s="20" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L341" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="20" t="inlineStr">
+        <is>
+          <t>Взаимодействие с надзорными органами</t>
+        </is>
+      </c>
+      <c r="B342" s="20" t="inlineStr">
+        <is>
+          <t>Федеральный закон от 12.01.1996 № 10-ФЗ; Федеральный закон от 26.12.2008 № 294-ФЗ; Постановление Правительства РФ от 21.07.2021 № 1230</t>
+        </is>
+      </c>
+      <c r="C342" s="20" t="inlineStr">
+        <is>
+          <t>ст. 19 Федерального закона № 10-ФЗ</t>
+        </is>
+      </c>
+      <c r="D342" s="20" t="inlineStr">
+        <is>
+          <t>Требование профсоюза (профсоюзного органа) об устранении выявленных нарушений законодательства о труде</t>
+        </is>
+      </c>
+      <c r="E342" s="20" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F342" s="20" t="inlineStr">
+        <is>
+          <t>— (документ профсоюза)</t>
+        </is>
+      </c>
+      <c r="G342" s="20" t="inlineStr">
+        <is>
+          <t>Описание выявленных нарушений; ссылки на нормы; требование об устранении; срок рассмотрения</t>
+        </is>
+      </c>
+      <c r="H342" s="20" t="inlineStr">
+        <is>
+          <t>Профсоюзный орган / профсоюзный инспектор труда</t>
+        </is>
+      </c>
+      <c r="I342" s="20" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J342" s="20" t="inlineStr">
+        <is>
+          <t>Уведомление</t>
+        </is>
+      </c>
+      <c r="K342" s="20" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="L342" s="20" t="inlineStr">
+        <is>
+          <t>Нет ограничений</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="20" t="inlineStr">
+        <is>
+          <t>Взаимодействие с надзорными органами</t>
+        </is>
+      </c>
+      <c r="B343" s="20" t="inlineStr">
+        <is>
+          <t>Федеральный закон от 12.01.1996 № 10-ФЗ; Федеральный закон от 26.12.2008 № 294-ФЗ; Постановление Правительства РФ от 21.07.2021 № 1230</t>
+        </is>
+      </c>
+      <c r="C343" s="20" t="inlineStr">
+        <is>
+          <t>ч. 1 ст. 19 Федерального закона № 10-ФЗ</t>
+        </is>
+      </c>
+      <c r="D343" s="20" t="inlineStr">
+        <is>
+          <t>Письменное сообщение профсоюзу о результатах рассмотрения требования об устранении нарушений и о принятых мерах</t>
+        </is>
+      </c>
+      <c r="E343" s="20" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F343" s="20" t="inlineStr">
+        <is>
+          <t>ДА (при получении требования профсоюза)</t>
+        </is>
+      </c>
+      <c r="G343" s="20" t="inlineStr">
+        <is>
+          <t>Реквизиты требования; результаты рассмотрения; перечень принятых (планируемых) мер; сроки; ответственные; приложения</t>
+        </is>
+      </c>
+      <c r="H343" s="20" t="inlineStr">
+        <is>
+          <t>Работодатель / должностное лицо, рассмотревшее требование</t>
+        </is>
+      </c>
+      <c r="I343" s="20" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J343" s="20" t="inlineStr">
+        <is>
+          <t>Уведомление</t>
+        </is>
+      </c>
+      <c r="K343" s="20" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L343" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="20" t="inlineStr">
+        <is>
+          <t>Взаимодействие с надзорными органами</t>
+        </is>
+      </c>
+      <c r="B344" s="20" t="inlineStr">
+        <is>
+          <t>Федеральный закон от 12.01.1996 № 10-ФЗ; Федеральный закон от 26.12.2008 № 294-ФЗ; Постановление Правительства РФ от 21.07.2021 № 1230</t>
+        </is>
+      </c>
+      <c r="C344" s="20" t="inlineStr">
+        <is>
+          <t>ч. 2–3 ст. 20 Федерального закона № 10-ФЗ</t>
+        </is>
+      </c>
+      <c r="D344" s="20" t="inlineStr">
+        <is>
+          <t>Требование профсоюзного органа / профсоюзного инспектора по охране труда об устранении нарушений, угрожающих жизни и здоровью работников</t>
+        </is>
+      </c>
+      <c r="E344" s="20" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F344" s="20" t="inlineStr">
+        <is>
+          <t>— (документ профсоюза)</t>
+        </is>
+      </c>
+      <c r="G344" s="20" t="inlineStr">
+        <is>
+          <t>Описание нарушений, угрожающих жизни и здоровью; требование об устранении; указание на обращение в органы государственного надзора (при необходимости)</t>
+        </is>
+      </c>
+      <c r="H344" s="20" t="inlineStr">
+        <is>
+          <t>Профсоюзный орган в организации / профсоюзный инспектор по охране труда</t>
+        </is>
+      </c>
+      <c r="I344" s="20" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J344" s="20" t="inlineStr">
+        <is>
+          <t>Уведомление</t>
+        </is>
+      </c>
+      <c r="K344" s="20" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="L344" s="20" t="inlineStr">
+        <is>
+          <t>Нет ограничений</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="20" t="inlineStr">
+        <is>
+          <t>Взаимодействие с надзорными органами</t>
+        </is>
+      </c>
+      <c r="B345" s="20" t="inlineStr">
+        <is>
+          <t>Федеральный закон от 12.01.1996 № 10-ФЗ; Федеральный закон от 26.12.2008 № 294-ФЗ; Постановление Правительства РФ от 21.07.2021 № 1230</t>
+        </is>
+      </c>
+      <c r="C345" s="20" t="inlineStr">
+        <is>
+          <t>ч. 2–3 ст. 20 Федерального закона № 10-ФЗ</t>
+        </is>
+      </c>
+      <c r="D345" s="20" t="inlineStr">
+        <is>
+          <t>Сообщение (ответ) о мерах, принятых по требованию профсоюзного органа / профсоюзного инспектора по охране труда</t>
+        </is>
+      </c>
+      <c r="E345" s="20" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F345" s="20" t="inlineStr">
+        <is>
+          <t>ДА (при получении требования)</t>
+        </is>
+      </c>
+      <c r="G345" s="20" t="inlineStr">
+        <is>
+          <t>Реквизиты требования; перечень устраненных нарушений / принятых мер; сроки; подтверждение устранения угрозы жизни и здоровью работников</t>
+        </is>
+      </c>
+      <c r="H345" s="20" t="inlineStr">
+        <is>
+          <t>Работодатель / должностное лицо, ответственное за устранение нарушений</t>
+        </is>
+      </c>
+      <c r="I345" s="20" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J345" s="20" t="inlineStr">
+        <is>
+          <t>Уведомление</t>
+        </is>
+      </c>
+      <c r="K345" s="20" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L345" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="20" t="inlineStr">
+        <is>
+          <t>Взаимодействие с надзорными органами</t>
+        </is>
+      </c>
+      <c r="B346" s="20" t="inlineStr">
+        <is>
+          <t>Федеральный закон от 12.01.1996 № 10-ФЗ; Федеральный закон от 26.12.2008 № 294-ФЗ; Постановление Правительства РФ от 21.07.2021 № 1230</t>
+        </is>
+      </c>
+      <c r="C346" s="20" t="inlineStr">
+        <is>
+          <t>ст. 19–20 Федерального закона № 10-ФЗ</t>
+        </is>
+      </c>
+      <c r="D346" s="20" t="inlineStr">
+        <is>
+          <t>Комплект документов (материалов), представленных по запросу профсоюзных инспекторов труда / уполномоченных (доверенных) лиц по охране труда при осуществлении профсоюзного контроля</t>
+        </is>
+      </c>
+      <c r="E346" s="20" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F346" s="20" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="G346" s="20" t="inlineStr">
+        <is>
+          <t>Опись; копии ЛНА, документов по охране труда, коллективного договора / соглашения и иных материалов, необходимых для проверки соблюдения законодательства о труде и охране труда</t>
+        </is>
+      </c>
+      <c r="H346" s="20" t="inlineStr">
+        <is>
+          <t>Работодатель / уполномоченное должностное лицо</t>
+        </is>
+      </c>
+      <c r="I346" s="20" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J346" s="20" t="inlineStr">
+        <is>
+          <t>Подтверждение</t>
+        </is>
+      </c>
+      <c r="K346" s="20" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L346" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="20" t="inlineStr">
+        <is>
+          <t>Взаимодействие с надзорными органами</t>
+        </is>
+      </c>
+      <c r="B347" s="20" t="inlineStr">
+        <is>
+          <t>Федеральный закон от 12.01.1996 № 10-ФЗ; Федеральный закон от 26.12.2008 № 294-ФЗ; Постановление Правительства РФ от 21.07.2021 № 1230</t>
+        </is>
+      </c>
+      <c r="C347" s="20" t="inlineStr">
+        <is>
+          <t>ст. 19–20 Федерального закона № 10-ФЗ; п. 16–34, 35–51 Положения (ПП РФ № 1230); ст. 16, 25 Федерального закона № 294-ФЗ</t>
+        </is>
+      </c>
+      <c r="D347" s="20" t="inlineStr">
+        <is>
+          <t>Локальный регламент (порядок) взаимодействия организации с органами государственного контроля (надзора) и органами профсоюзного контроля</t>
+        </is>
+      </c>
+      <c r="E347" s="20" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F347" s="20" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="G347" s="20" t="inlineStr">
+        <is>
+          <t>Порядок приема решений / требований / актов; назначение представителей; сроки подготовки ответов и исполнения предписаний; порядок обжалования; порядок взаимодействия с профсоюзами и профсоюзными инспекторами; ответственные лица; документооборот и хранение материалов проверок</t>
+        </is>
+      </c>
+      <c r="H347" s="20" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I347" s="20" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J347" s="20" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K347" s="20" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L347" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:L299"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/presentations/Analiz_SUOT_podpisanty_skvoznaya.xlsx
+++ b/presentations/Analiz_SUOT_podpisanty_skvoznaya.xlsx
@@ -1109,7 +1109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L357"/>
+  <dimension ref="A1:L362"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8"/>
   <cols>
     <col width="16.44140625" customWidth="1" style="11" min="1" max="1"/>
@@ -23081,37 +23081,37 @@
       </c>
       <c r="B355" s="13" t="inlineStr">
         <is>
-          <t>Правила по охране труда, утв. приказами Минтруда России (по применимости к видам деятельности): № 928н, 914н, 903н, 886н, 883н, 882н, 881н, 872н, 871н, 875н, 867н, 866н, 859н, 858н, 836н, 835н, 833н, 832н, 815н, 780н, 782н, 814н, 776н, 758н, 753н, 746н, 721н, 652н, 644н, 343н, 924н, 922н, 915н, 902н, 901н, 887н, 884н, 849н, 834н, 781н</t>
+          <t>Приказ Минтруда России от 16.11.2020 № 782н "Об утверждении Правил по охране труда при работе на высоте"</t>
         </is>
       </c>
       <c r="C355" s="13" t="inlineStr">
         <is>
-          <t>Типовая конструкция Правил при выполнении работ подрядными (сторонними) организациями на территории (объекте) заказчика (напр. п. 15 Правил № 902н; аналогичные требования в Правилах № 883н и иных)</t>
+          <t>Правила № 782н (допуск к работам на высоте; приложения с рекомендуемыми образцами удостоверения и личной книжки учёта работ на высоте)</t>
         </is>
       </c>
       <c r="D355" s="13" t="inlineStr">
         <is>
-          <t>Акт-допуск для производства работ на территории (объекте) организации (для подрядных / сторонних организаций)</t>
+          <t>Удостоверение о допуске к работам на высоте и (или) личная книжка учёта работ на высоте</t>
         </is>
       </c>
       <c r="E355" s="13" t="inlineStr">
         <is>
-          <t>НЕТ</t>
+          <t>ДА (рекомендуемый образец — приложения к Правилам № 782н)</t>
         </is>
       </c>
       <c r="F355" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>НЕТ</t>
         </is>
       </c>
       <c r="G355" s="13" t="inlineStr">
         <is>
-          <t>Сведения о заказчике и подрядчике; территория (объект); срок; виды работ; организационно-технические мероприятия по обеспечению безопасности; ответственные представители сторон</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H355" s="13" t="inlineStr">
         <is>
-          <t>Ответственный представитель заказчика; ответственный представитель подрядчика</t>
+          <t>Уполномоченное должностное лицо работодателя (выдача / ведение учёта); работник (в части получения / предъявления)</t>
         </is>
       </c>
       <c r="I355" s="13" t="inlineStr">
@@ -23143,27 +23143,27 @@
       </c>
       <c r="B356" s="13" t="inlineStr">
         <is>
-          <t>Правила по охране труда, утв. приказами Минтруда России (по применимости к видам деятельности): № 928н, 914н, 903н, 886н, 883н, 882н, 881н, 872н, 871н, 875н, 867н, 866н, 859н, 858н, 836н, 835н, 833н, 832н, 815н, 780н, 782н, 814н, 776н, 758н, 753н, 746н, 721н, 652н, 644н, 343н, 924н, 922н, 915н, 902н, 901н, 887н, 884н, 849н, 834н, 781н</t>
+          <t>Приказ Минтруда России от 16.11.2020 № 782н "Об утверждении Правил по охране труда при работе на высоте"</t>
         </is>
       </c>
       <c r="C356" s="13" t="inlineStr">
         <is>
-          <t>Типовая конструкция Правил: работодатель вправе устанавливать дополнительные требования безопасности, не противоречащие Правилам; требования охраны труда доводятся распоряжениями, указаниями, инструкциями</t>
+          <t>Правила № 782н (журналы приёма и осмотра лесов и подмостей; учёта и осмотра такелажных средств — рекомендуемые образцы в приложениях)</t>
         </is>
       </c>
       <c r="D356" s="13" t="inlineStr">
         <is>
-          <t>Распоряжения (указания) работодателя о дополнительных требованиях безопасности при выполнении конкретных работ</t>
+          <t>Журнал приёма и осмотра лесов и подмостей; журнал учёта и осмотра такелажных средств, механизмов и устройств</t>
         </is>
       </c>
       <c r="E356" s="13" t="inlineStr">
         <is>
-          <t>НЕТ</t>
+          <t>ДА (рекомендуемый образец — приложения к Правилам № 782н)</t>
         </is>
       </c>
       <c r="F356" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>НЕТ</t>
         </is>
       </c>
       <c r="G356" s="13" t="inlineStr">
@@ -23173,17 +23173,17 @@
       </c>
       <c r="H356" s="13" t="inlineStr">
         <is>
-          <t>Работодатель (руководитель организации / уполномоченное лицо) / непосредственный руководитель работ</t>
+          <t>Уполномоченное должностное лицо работодателя (ведущее журнал)</t>
         </is>
       </c>
       <c r="I356" s="13" t="inlineStr">
         <is>
-          <t>Нет требований</t>
+          <t>Собственноручная или УКЭП</t>
         </is>
       </c>
       <c r="J356" s="13" t="inlineStr">
         <is>
-          <t>Утверждение</t>
+          <t>Подтверждение</t>
         </is>
       </c>
       <c r="K356" s="13" t="inlineStr">
@@ -23205,55 +23205,365 @@
       </c>
       <c r="B357" s="13" t="inlineStr">
         <is>
+          <t>Приказ Минтруда России от 15.12.2020 № 903н "Об утверждении Правил по охране труда при эксплуатации электроустановок"</t>
+        </is>
+      </c>
+      <c r="C357" s="13" t="inlineStr">
+        <is>
+          <t>Правила № 903н (перечень профессий / видов работ для присвоения I группы по электробезопасности; программа инструктажа; журнал учёта присвоения I группы)</t>
+        </is>
+      </c>
+      <c r="D357" s="13" t="inlineStr">
+        <is>
+          <t>Перечень профессий (должностей) и видов работ, требующих присвоения I группы по электробезопасности; программа инструктажа; журнал учёта присвоения I группы по электробезопасности</t>
+        </is>
+      </c>
+      <c r="E357" s="13" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F357" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G357" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H357" s="13" t="inlineStr">
+        <is>
+          <t>Работодатель (утверждение перечня / программы); работник из числа электротехнического персонала с группой не ниже III (ведение журнала / присвоение I группы)</t>
+        </is>
+      </c>
+      <c r="I357" s="13" t="inlineStr">
+        <is>
+          <t>Собственноручная или УКЭП</t>
+        </is>
+      </c>
+      <c r="J357" s="13" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K357" s="13" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L357" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="13" t="inlineStr">
+        <is>
+          <t>Обеспечение безопасности работников</t>
+        </is>
+      </c>
+      <c r="B358" s="13" t="inlineStr">
+        <is>
+          <t>Приказ Минтруда России от 27.11.2020 № 835н "Об утверждении Правил по охране труда при работе с инструментом и приспособлениями"</t>
+        </is>
+      </c>
+      <c r="C358" s="13" t="inlineStr">
+        <is>
+          <t>Правила № 835н (учёт результатов осмотров, ремонта, проверок, испытаний инструмента, за исключением ручного)</t>
+        </is>
+      </c>
+      <c r="D358" s="13" t="inlineStr">
+        <is>
+          <t>Журнал учёта результатов осмотров, ремонта, проверок, испытаний инструмента и приспособлений</t>
+        </is>
+      </c>
+      <c r="E358" s="13" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F358" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G358" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H358" s="13" t="inlineStr">
+        <is>
+          <t>Лицо, ответственное за исправное состояние инструмента и приспособлений</t>
+        </is>
+      </c>
+      <c r="I358" s="13" t="inlineStr">
+        <is>
+          <t>Собственноручная или УКЭП</t>
+        </is>
+      </c>
+      <c r="J358" s="13" t="inlineStr">
+        <is>
+          <t>Подтверждение</t>
+        </is>
+      </c>
+      <c r="K358" s="13" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L358" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="13" t="inlineStr">
+        <is>
+          <t>Обеспечение безопасности работников</t>
+        </is>
+      </c>
+      <c r="B359" s="13" t="inlineStr">
+        <is>
+          <t>Приказ Минтруда России от 28.10.2020 № 753н "Об утверждении Правил по охране труда при погрузочно-разгрузочных работах и размещении грузов"</t>
+        </is>
+      </c>
+      <c r="C359" s="13" t="inlineStr">
+        <is>
+          <t>Правила № 753н (технологические карты / ППР на погрузочно-разгрузочные работы с применением ПС; схемы строповки; технологические карты размещения грузов — при выполнении соответствующих работ)</t>
+        </is>
+      </c>
+      <c r="D359" s="13" t="inlineStr">
+        <is>
+          <t>Технологические карты (ППР) на погрузочно-разгрузочные работы; схемы строповки; технологические карты размещения грузов</t>
+        </is>
+      </c>
+      <c r="E359" s="13" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F359" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G359" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H359" s="13" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I359" s="13" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J359" s="13" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K359" s="13" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L359" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="13" t="inlineStr">
+        <is>
+          <t>Обеспечение безопасности работников</t>
+        </is>
+      </c>
+      <c r="B360" s="13" t="inlineStr">
+        <is>
           <t>Правила по охране труда, утв. приказами Минтруда России (по применимости к видам деятельности): № 928н, 914н, 903н, 886н, 883н, 882н, 881н, 872н, 871н, 875н, 867н, 866н, 859н, 858н, 836н, 835н, 833н, 832н, 815н, 780н, 782н, 814н, 776н, 758н, 753н, 746н, 721н, 652н, 644н, 343н, 924н, 922н, 915н, 902н, 901н, 887н, 884н, 849н, 834н, 781н</t>
         </is>
       </c>
-      <c r="C357" s="13" t="inlineStr">
+      <c r="C360" s="13" t="inlineStr">
+        <is>
+          <t>Типовая конструкция Правил при выполнении работ подрядными (сторонними) организациями на территории (объекте) заказчика (напр. п. 15 Правил № 902н; аналогичные требования в Правилах № 883н и иных)</t>
+        </is>
+      </c>
+      <c r="D360" s="13" t="inlineStr">
+        <is>
+          <t>Акт-допуск для производства работ на территории (объекте) организации (для подрядных / сторонних организаций)</t>
+        </is>
+      </c>
+      <c r="E360" s="13" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F360" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G360" s="13" t="inlineStr">
+        <is>
+          <t>Сведения о заказчике и подрядчике; территория (объект); срок; виды работ; организационно-технические мероприятия по обеспечению безопасности; ответственные представители сторон</t>
+        </is>
+      </c>
+      <c r="H360" s="13" t="inlineStr">
+        <is>
+          <t>Ответственный представитель заказчика; ответственный представитель подрядчика</t>
+        </is>
+      </c>
+      <c r="I360" s="13" t="inlineStr">
+        <is>
+          <t>Собственноручная или УКЭП</t>
+        </is>
+      </c>
+      <c r="J360" s="13" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K360" s="13" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L360" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="13" t="inlineStr">
+        <is>
+          <t>Обеспечение безопасности работников</t>
+        </is>
+      </c>
+      <c r="B361" s="13" t="inlineStr">
+        <is>
+          <t>Правила по охране труда, утв. приказами Минтруда России (по применимости к видам деятельности): № 928н, 914н, 903н, 886н, 883н, 882н, 881н, 872н, 871н, 875н, 867н, 866н, 859н, 858н, 836н, 835н, 833н, 832н, 815н, 780н, 782н, 814н, 776н, 758н, 753н, 746н, 721н, 652н, 644н, 343н, 924н, 922н, 915н, 902н, 901н, 887н, 884н, 849н, 834н, 781н</t>
+        </is>
+      </c>
+      <c r="C361" s="13" t="inlineStr">
+        <is>
+          <t>Типовая конструкция Правил: работодатель вправе устанавливать дополнительные требования безопасности, не противоречащие Правилам; требования охраны труда доводятся распоряжениями, указаниями, инструкциями</t>
+        </is>
+      </c>
+      <c r="D361" s="13" t="inlineStr">
+        <is>
+          <t>Распоряжения (указания) работодателя о дополнительных требованиях безопасности при выполнении конкретных работ</t>
+        </is>
+      </c>
+      <c r="E361" s="13" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F361" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G361" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H361" s="13" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо) / непосредственный руководитель работ</t>
+        </is>
+      </c>
+      <c r="I361" s="13" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J361" s="13" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K361" s="13" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L361" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="13" t="inlineStr">
+        <is>
+          <t>Обеспечение безопасности работников</t>
+        </is>
+      </c>
+      <c r="B362" s="13" t="inlineStr">
+        <is>
+          <t>Правила по охране труда, утв. приказами Минтруда России (по применимости к видам деятельности): № 928н, 914н, 903н, 886н, 883н, 882н, 881н, 872н, 871н, 875н, 867н, 866н, 859н, 858н, 836н, 835н, 833н, 832н, 815н, 780н, 782н, 814н, 776н, 758н, 753н, 746н, 721н, 652н, 644н, 343н, 924н, 922н, 915н, 902н, 901н, 887н, 884н, 849н, 834н, 781н</t>
+        </is>
+      </c>
+      <c r="C362" s="13" t="inlineStr">
         <is>
           <t>Общие положения Правил (сфера применения): работодатель определяет применимые Правила по охране труда исходя из видов выполняемых работ и эксплуатируемого оборудования</t>
         </is>
       </c>
-      <c r="D357" s="13" t="inlineStr">
+      <c r="D362" s="13" t="inlineStr">
         <is>
           <t>Приказ (распоряжение) об определении перечня Правил по охране труда, применяемых в организации, и ответственных за контроль их соблюдения</t>
         </is>
       </c>
-      <c r="E357" s="13" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="F357" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G357" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H357" s="13" t="inlineStr">
+      <c r="E362" s="13" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F362" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G362" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H362" s="13" t="inlineStr">
         <is>
           <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
         </is>
       </c>
-      <c r="I357" s="13" t="inlineStr">
-        <is>
-          <t>Нет требований</t>
-        </is>
-      </c>
-      <c r="J357" s="13" t="inlineStr">
+      <c r="I362" s="13" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J362" s="13" t="inlineStr">
         <is>
           <t>Утверждение</t>
         </is>
       </c>
-      <c r="K357" s="13" t="inlineStr">
-        <is>
-          <t>НЕТ</t>
-        </is>
-      </c>
-      <c r="L357" s="21" t="inlineStr">
+      <c r="K362" s="13" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L362" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/presentations/Analiz_SUOT_podpisanty_skvoznaya.xlsx
+++ b/presentations/Analiz_SUOT_podpisanty_skvoznaya.xlsx
@@ -22027,7 +22027,7 @@
       </c>
       <c r="B338" s="13" t="inlineStr">
         <is>
-          <t>Правила по охране труда, утв. приказами Минтруда России (по применимости к видам деятельности): № 928н, 914н, 903н, 886н, 883н, 882н, 881н, 872н, 871н, 875н, 867н, 866н, 859н, 858н, 836н, 835н, 833н, 832н, 815н, 780н, 782н, 814н, 776н, 758н, 753н, 746н, 721н, 652н, 644н, 343н, 924н, 922н, 915н, 902н, 901н, 887н, 884н, 849н, 834н, 781н</t>
+          <t>Правила по охране труда, утв. приказами Минтруда России (только приказы, где документ прямо предусмотрен): № 343н, № 644н, № 652н, № 721н, № 746н, № 753н, № 758н, № 776н, № 780н, № 781н, № 814н, № 815н, № 832н, № 833н, № 834н, № 835н, № 836н, № 849н, № 858н, № 859н, № 866н, № 867н, № 871н, № 872н, № 875н, № 881н, № 882н, № 883н, № 884н, № 886н, № 887н, № 901н, № 902н, № 914н, № 915н, № 922н, № 924н, № 928н</t>
         </is>
       </c>
       <c r="C338" s="13" t="inlineStr">
@@ -22089,7 +22089,7 @@
       </c>
       <c r="B339" s="13" t="inlineStr">
         <is>
-          <t>Правила по охране труда, утв. приказами Минтруда России (по применимости к видам деятельности): № 928н, 914н, 903н, 886н, 883н, 882н, 881н, 872н, 871н, 875н, 867н, 866н, 859н, 858н, 836н, 835н, 833н, 832н, 815н, 780н, 782н, 814н, 776н, 758н, 753н, 746н, 721н, 652н, 644н, 343н, 924н, 922н, 915н, 902н, 901н, 887н, 884н, 849н, 834н, 781н</t>
+          <t>Правила по охране труда, утв. приказами Минтруда России (только приказы, где документ прямо предусмотрен): № 343н, № 644н, № 652н, № 721н, № 746н, № 753н, № 758н, № 776н, № 780н, № 781н, № 814н, № 815н, № 832н, № 833н, № 834н, № 835н, № 836н, № 849н, № 858н, № 859н, № 866н, № 867н, № 871н, № 872н, № 875н, № 881н, № 882н, № 883н, № 884н, № 886н, № 887н, № 901н, № 902н, № 914н, № 915н, № 922н, № 924н, № 928н</t>
         </is>
       </c>
       <c r="C339" s="13" t="inlineStr">
@@ -22151,7 +22151,7 @@
       </c>
       <c r="B340" s="13" t="inlineStr">
         <is>
-          <t>Правила по охране труда, утв. приказами Минтруда России (по применимости к видам деятельности): № 928н, 914н, 903н, 886н, 883н, 882н, 881н, 872н, 871н, 875н, 867н, 866н, 859н, 858н, 836н, 835н, 833н, 832н, 815н, 780н, 782н, 814н, 776н, 758н, 753н, 746н, 721н, 652н, 644н, 343н, 924н, 922н, 915н, 902н, 901н, 887н, 884н, 849н, 834н, 781н</t>
+          <t>Правила по охране труда, утв. приказами Минтруда России (только приказы, где документ прямо предусмотрен): № 343н, № 644н, № 746н, № 753н, № 758н, № 776н, № 780н, № 781н, № 814н, № 815н, № 832н, № 833н, № 834н, № 835н, № 849н, № 858н, № 859н, № 866н, № 867н, № 871н, № 872н, № 875н, № 881н, № 882н, № 883н, № 884н, № 887н, № 901н, № 902н, № 914н, № 915н, № 924н, № 928н</t>
         </is>
       </c>
       <c r="C340" s="13" t="inlineStr">
@@ -22213,7 +22213,7 @@
       </c>
       <c r="B341" s="13" t="inlineStr">
         <is>
-          <t>Правила по охране труда, утв. приказами Минтруда России (по применимости к видам деятельности): № 928н, 914н, 903н, 886н, 883н, 882н, 881н, 872н, 871н, 875н, 867н, 866н, 859н, 858н, 836н, 835н, 833н, 832н, 815н, 780н, 782н, 814н, 776н, 758н, 753н, 746н, 721н, 652н, 644н, 343н, 924н, 922н, 915н, 902н, 901н, 887н, 884н, 849н, 834н, 781н</t>
+          <t>Правила по охране труда, утв. приказами Минтруда России (только приказы, где документ прямо предусмотрен): № 652н, № 746н, № 776н, № 836н, № 875н, № 915н, № 924н</t>
         </is>
       </c>
       <c r="C341" s="13" t="inlineStr">
@@ -22275,7 +22275,7 @@
       </c>
       <c r="B342" s="13" t="inlineStr">
         <is>
-          <t>Правила по охране труда, утв. приказами Минтруда России (по применимости к видам деятельности): № 928н, 914н, 903н, 886н, 883н, 882н, 881н, 872н, 871н, 875н, 867н, 866н, 859н, 858н, 836н, 835н, 833н, 832н, 815н, 780н, 782н, 814н, 776н, 758н, 753н, 746н, 721н, 652н, 644н, 343н, 924н, 922н, 915н, 902н, 901н, 887н, 884н, 849н, 834н, 781н</t>
+          <t>Правила по охране труда, утв. приказами Минтруда России (только приказы, где документ прямо предусмотрен): № 644н, № 721н, № 746н, № 758н, № 776н, № 780н, № 781н, № 832н, № 833н, № 834н, № 849н, № 858н, № 859н, № 866н, № 867н, № 871н, № 872н, № 875н, № 882н, № 883н, № 884н, № 915н, № 924н</t>
         </is>
       </c>
       <c r="C342" s="13" t="inlineStr">
@@ -22337,7 +22337,7 @@
       </c>
       <c r="B343" s="13" t="inlineStr">
         <is>
-          <t>Правила по охране труда, утв. приказами Минтруда России (по применимости к видам деятельности): № 928н, 914н, 903н, 886н, 883н, 882н, 881н, 872н, 871н, 875н, 867н, 866н, 859н, 858н, 836н, 835н, 833н, 832н, 815н, 780н, 782н, 814н, 776н, 758н, 753н, 746н, 721н, 652н, 644н, 343н, 924н, 922н, 915н, 902н, 901н, 887н, 884н, 849н, 834н, 781н</t>
+          <t>Правила по охране труда, утв. приказами Минтруда России (только приказы, где документ прямо предусмотрен): № 644н, № 721н, № 746н, № 758н, № 776н, № 780н, № 781н, № 782н, № 814н, № 833н, № 834н, № 836н, № 849н, № 858н, № 859н, № 866н, № 867н, № 871н, № 872н, № 875н, № 882н, № 883н, № 884н, № 902н, № 915н, № 922н, № 924н</t>
         </is>
       </c>
       <c r="C343" s="13" t="inlineStr">
@@ -22399,7 +22399,7 @@
       </c>
       <c r="B344" s="13" t="inlineStr">
         <is>
-          <t>Правила по охране труда, утв. приказами Минтруда России (по применимости к видам деятельности): № 928н, 914н, 903н, 886н, 883н, 882н, 881н, 872н, 871н, 875н, 867н, 866н, 859н, 858н, 836н, 835н, 833н, 832н, 815н, 780н, 782н, 814н, 776н, 758н, 753н, 746н, 721н, 652н, 644н, 343н, 924н, 922н, 915н, 902н, 901н, 887н, 884н, 849н, 834н, 781н</t>
+          <t>Правила по охране труда, утв. приказами Минтруда России (только приказы, где документ прямо предусмотрен): № 721н, № 746н, № 758н, № 776н, № 780н, № 781н, № 814н, № 832н, № 833н, № 834н, № 836н, № 849н, № 858н, № 859н, № 866н, № 867н, № 871н, № 875н, № 882н, № 883н, № 884н, № 915н, № 922н, № 924н</t>
         </is>
       </c>
       <c r="C344" s="13" t="inlineStr">
@@ -22461,7 +22461,7 @@
       </c>
       <c r="B345" s="13" t="inlineStr">
         <is>
-          <t>Правила по охране труда, утв. приказами Минтруда России (по применимости к видам деятельности): № 928н, 914н, 903н, 886н, 883н, 882н, 881н, 872н, 871н, 875н, 867н, 866н, 859н, 858н, 836н, 835н, 833н, 832н, 815н, 780н, 782н, 814н, 776н, 758н, 753н, 746н, 721н, 652н, 644н, 343н, 924н, 922н, 915н, 902н, 901н, 887н, 884н, 849н, 834н, 781н</t>
+          <t>Правила по охране труда, утв. приказами Минтруда России (только приказы, где документ прямо предусмотрен): № 644н, № 721н, № 746н, № 758н, № 776н, № 781н, № 782н, № 814н, № 832н, № 833н, № 834н, № 835н, № 836н, № 849н, № 858н, № 859н, № 866н, № 867н, № 871н, № 875н, № 882н, № 883н, № 902н, № 903н, № 915н, № 922н, № 924н</t>
         </is>
       </c>
       <c r="C345" s="13" t="inlineStr">
@@ -22523,7 +22523,7 @@
       </c>
       <c r="B346" s="13" t="inlineStr">
         <is>
-          <t>Правила по охране труда, утв. приказами Минтруда России (по применимости к видам деятельности): № 928н, 914н, 903н, 886н, 883н, 882н, 881н, 872н, 871н, 875н, 867н, 866н, 859н, 858н, 836н, 835н, 833н, 832н, 815н, 780н, 782н, 814н, 776н, 758н, 753н, 746н, 721н, 652н, 644н, 343н, 924н, 922н, 915н, 902н, 901н, 887н, 884н, 849н, 834н, 781н</t>
+          <t>Правила по охране труда, утв. приказами Минтруда России (только приказы, где документ прямо предусмотрен): № 644н, № 721н, № 746н, № 758н, № 776н, № 781н, № 782н, № 814н, № 832н, № 833н, № 834н, № 835н, № 836н, № 849н, № 858н, № 859н, № 866н, № 867н, № 871н, № 875н, № 882н, № 883н, № 902н, № 903н, № 915н, № 922н, № 924н</t>
         </is>
       </c>
       <c r="C346" s="13" t="inlineStr">
@@ -22585,7 +22585,7 @@
       </c>
       <c r="B347" s="13" t="inlineStr">
         <is>
-          <t>Правила по охране труда, утв. приказами Минтруда России (по применимости к видам деятельности): № 928н, 914н, 903н, 886н, 883н, 882н, 881н, 872н, 871н, 875н, 867н, 866н, 859н, 858н, 836н, 835н, 833н, 832н, 815н, 780н, 782н, 814н, 776н, 758н, 753н, 746н, 721н, 652н, 644н, 343н, 924н, 922н, 915н, 902н, 901н, 887н, 884н, 849н, 834н, 781н</t>
+          <t>Правила по охране труда, утв. приказами Минтруда России (только приказы, где документ прямо предусмотрен): № 644н, № 758н, № 776н, № 781н, № 782н, № 833н, № 834н, № 849н, № 858н, № 867н, № 875н, № 882н, № 903н, № 915н, № 924н</t>
         </is>
       </c>
       <c r="C347" s="13" t="inlineStr">
@@ -22647,7 +22647,7 @@
       </c>
       <c r="B348" s="13" t="inlineStr">
         <is>
-          <t>Правила по охране труда, утв. приказами Минтруда России (по применимости к видам деятельности): № 928н, 914н, 903н, 886н, 883н, 882н, 881н, 872н, 871н, 875н, 867н, 866н, 859н, 858н, 836н, 835н, 833н, 832н, 815н, 780н, 782н, 814н, 776н, 758н, 753н, 746н, 721н, 652н, 644н, 343н, 924н, 922н, 915н, 902н, 901н, 887н, 884н, 849н, 834н, 781н</t>
+          <t>Правила по охране труда, утв. приказами Минтруда России (только приказы, где документ прямо предусмотрен): № 644н, № 758н, № 776н, № 781н, № 782н, № 832н, № 833н, № 834н, № 849н, № 858н, № 866н, № 867н, № 871н, № 882н, № 884н, № 902н, № 915н, № 922н</t>
         </is>
       </c>
       <c r="C348" s="13" t="inlineStr">
@@ -22709,7 +22709,7 @@
       </c>
       <c r="B349" s="13" t="inlineStr">
         <is>
-          <t>Правила по охране труда, утв. приказами Минтруда России (по применимости к видам деятельности): № 928н, 914н, 903н, 886н, 883н, 882н, 881н, 872н, 871н, 875н, 867н, 866н, 859н, 858н, 836н, 835н, 833н, 832н, 815н, 780н, 782н, 814н, 776н, 758н, 753н, 746н, 721н, 652н, 644н, 343н, 924н, 922н, 915н, 902н, 901н, 887н, 884н, 849н, 834н, 781н</t>
+          <t>Правила по охране труда, утв. приказами Минтруда России (только приказы, где документ прямо предусмотрен): № 758н, № 782н, № 833н, № 872н, № 902н</t>
         </is>
       </c>
       <c r="C349" s="13" t="inlineStr">
@@ -22771,7 +22771,7 @@
       </c>
       <c r="B350" s="13" t="inlineStr">
         <is>
-          <t>Приказ Минтруда России от 16.11.2020 № 782н; Приказ Минтруда России от 15.12.2020 № 902н (и иные ПОТ, предусматривающие планы эвакуации / спасения)</t>
+          <t>Приказ Минтруда России от 16.11.2020 № 782н "Об утверждении Правил по охране труда при работе на высоте"; Приказ Минтруда России от 15.12.2020 № 902н "Об утверждении Правил по охране труда при работе в ограниченных и замкнутых пространствах"</t>
         </is>
       </c>
       <c r="C350" s="13" t="inlineStr">
@@ -23267,7 +23267,7 @@
       </c>
       <c r="B358" s="13" t="inlineStr">
         <is>
-          <t>Приказ Минтруда России от 27.11.2020 № 835н "Об утверждении Правил по охране труда при работе с инструментом и приспособлениями"</t>
+          <t>Приказ Минтруда России от 27.11.2020 № 835н "Об утверждении Правил по охране труда при работе с инструментом и приспособлениями"; Приказ Минтруда России от 17.12.2020 № 922н "Об утверждении Правил по охране труда при проведении водолазных работ"</t>
         </is>
       </c>
       <c r="C358" s="13" t="inlineStr">
@@ -23329,7 +23329,7 @@
       </c>
       <c r="B359" s="13" t="inlineStr">
         <is>
-          <t>Приказ Минтруда России от 28.10.2020 № 753н "Об утверждении Правил по охране труда при погрузочно-разгрузочных работах и размещении грузов"</t>
+          <t>Правила по охране труда, утв. приказами Минтруда России (только приказы, где документ прямо предусмотрен): № 343н, № 652н, № 753н, № 782н, № 866н, № 883н</t>
         </is>
       </c>
       <c r="C359" s="13" t="inlineStr">
@@ -23391,7 +23391,7 @@
       </c>
       <c r="B360" s="13" t="inlineStr">
         <is>
-          <t>Правила по охране труда, утв. приказами Минтруда России (по применимости к видам деятельности): № 928н, 914н, 903н, 886н, 883н, 882н, 881н, 872н, 871н, 875н, 867н, 866н, 859н, 858н, 836н, 835н, 833н, 832н, 815н, 780н, 782н, 814н, 776н, 758н, 753н, 746н, 721н, 652н, 644н, 343н, 924н, 922н, 915н, 902н, 901н, 887н, 884н, 849н, 834н, 781н</t>
+          <t>Правила по охране труда, утв. приказами Минтруда России (только приказы, где документ прямо предусмотрен): № 781н, № 833н, № 883н, № 902н, № 903н, № 924н</t>
         </is>
       </c>
       <c r="C360" s="13" t="inlineStr">
@@ -23453,7 +23453,7 @@
       </c>
       <c r="B361" s="13" t="inlineStr">
         <is>
-          <t>Правила по охране труда, утв. приказами Минтруда России (по применимости к видам деятельности): № 928н, 914н, 903н, 886н, 883н, 882н, 881н, 872н, 871н, 875н, 867н, 866н, 859н, 858н, 836н, 835н, 833н, 832н, 815н, 780н, 782н, 814н, 776н, 758н, 753н, 746н, 721н, 652н, 644н, 343н, 924н, 922н, 915н, 902н, 901н, 887н, 884н, 849н, 834н, 781н</t>
+          <t>Правила по охране труда, утв. приказами Минтруда России (только приказы, где документ прямо предусмотрен): № 343н, № 644н, № 652н, № 721н, № 746н, № 753н, № 758н, № 776н, № 780н, № 781н, № 782н, № 814н, № 815н, № 832н, № 833н, № 834н, № 835н, № 849н, № 858н, № 859н, № 866н, № 867н, № 871н, № 872н, № 875н, № 882н, № 883н, № 884н, № 886н, № 887н, № 902н, № 903н, № 914н, № 915н, № 922н, № 924н, № 928н</t>
         </is>
       </c>
       <c r="C361" s="13" t="inlineStr">
@@ -23515,7 +23515,7 @@
       </c>
       <c r="B362" s="13" t="inlineStr">
         <is>
-          <t>Правила по охране труда, утв. приказами Минтруда России (по применимости к видам деятельности): № 928н, 914н, 903н, 886н, 883н, 882н, 881н, 872н, 871н, 875н, 867н, 866н, 859н, 858н, 836н, 835н, 833н, 832н, 815н, 780н, 782н, 814н, 776н, 758н, 753н, 746н, 721н, 652н, 644н, 343н, 924н, 922н, 915н, 902н, 901н, 887н, 884н, 849н, 834н, 781н</t>
+          <t>В текстах перечисленных Правил по охране труда отдельное требование об издании данного документа не установлено (организационный документ по усмотрению работодателя)</t>
         </is>
       </c>
       <c r="C362" s="13" t="inlineStr">

--- a/presentations/Analiz_SUOT_podpisanty_skvoznaya.xlsx
+++ b/presentations/Analiz_SUOT_podpisanty_skvoznaya.xlsx
@@ -22399,12 +22399,12 @@
       </c>
       <c r="B344" s="13" t="inlineStr">
         <is>
-          <t>Правила по охране труда, утв. приказами Минтруда России (только приказы, где документ прямо предусмотрен): № 721н, № 746н, № 758н, № 776н, № 780н, № 781н, № 814н, № 832н, № 833н, № 834н, № 836н, № 849н, № 858н, № 859н, № 866н, № 867н, № 871н, № 875н, № 882н, № 883н, № 884н, № 915н, № 922н, № 924н</t>
+          <t>Приказ Минтруда России от 27.10.2020 № 746н "Об утверждении Правил по охране труда в сельском хозяйстве"; Приказ Минтруда России от 16.11.2020 № 782н "Об утверждении Правил по охране труда при работе на высоте"; Приказ Минтруда России от 9.12.2020 № 872н "Об утверждении Правил по охране труда при строительстве, реконструкции, ремонте и содержании мостов"; Приказ Минтруда России от 15.12.2020 № 902н "Об утверждении Правил по охране труда при работе в ограниченных и замкнутых пространствах"</t>
         </is>
       </c>
       <c r="C344" s="13" t="inlineStr">
         <is>
-          <t>Типовая конструкция Правил: работы повышенной опасности выполняются по наряду-допуску; наряд-допуск оформляют уполномоченные работодателем должностные лица</t>
+          <t>п. 20 Правил № 746н (НД выдаёт лицо, уполномоченное приказом работодателя); п. 17 Правил № 872н (приказом назначаются лица, имеющие право выдавать наряд-допуск, ответственный руководитель и исполнитель работ); п. 35 Правил № 782н; п. 37 Правил № 902н (назначение лиц, ответственных за организацию работ и выдачу наряда-допуска)</t>
         </is>
       </c>
       <c r="D344" s="13" t="inlineStr">
@@ -22585,7 +22585,7 @@
       </c>
       <c r="B347" s="13" t="inlineStr">
         <is>
-          <t>Правила по охране труда, утв. приказами Минтруда России (только приказы, где документ прямо предусмотрен): № 644н, № 758н, № 776н, № 781н, № 782н, № 833н, № 834н, № 849н, № 858н, № 867н, № 875н, № 882н, № 903н, № 915н, № 924н</t>
+          <t>Правила по охране труда, утв. приказами Минтруда России (только приказы, где документ прямо предусмотрен): № 644н, № 652н, № 758н, № 776н, № 781н, № 782н, № 833н, № 834н, № 849н, № 858н, № 867н, № 875н, № 882н, № 903н, № 915н, № 924н</t>
         </is>
       </c>
       <c r="C347" s="13" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="C354" s="13" t="inlineStr">
         <is>
-          <t>Правила № 903н (организация работ в электроустановках по наряду-допуску / распоряжению; назначение ответственных; учет работ)</t>
+          <t>Правила № 903н: организация работ в электроустановках по наряду-допуску и по распоряжению (разд. VI–VII); перечень работ, выполняемых в порядке текущей эксплуатации; перечень работ под напряжением; журнал учёта работ по нарядам-допускам и распоряжениям (п. 6.6, прил. 8). Отдельного «перечня работ по наряду / по распоряжению» как самостоятельного локального документа (по модели п. 48 Правил № 782н) не установлено</t>
         </is>
       </c>
       <c r="D354" s="13" t="inlineStr">
         <is>
-          <t>Перечень работ в электроустановках, выполняемых по наряду-допуску / распоряжению, и локальный порядок организации таких работ</t>
+          <t>Локальные перечни работ в электроустановках, выполняемых в порядке текущей эксплуатации и под напряжением; порядок организации работ по наряду-допуску и по распоряжению; журнал учёта работ по нарядам-допускам и распоряжениям</t>
         </is>
       </c>
       <c r="E354" s="13" t="inlineStr">
@@ -23143,17 +23143,17 @@
       </c>
       <c r="B356" s="13" t="inlineStr">
         <is>
-          <t>Приказ Минтруда России от 16.11.2020 № 782н "Об утверждении Правил по охране труда при работе на высоте"</t>
+          <t>Приказ Минтруда России от 16.11.2020 № 782н "Об утверждении Правил по охране труда при работе на высоте"; Приказ Минтруда России от 9.12.2020 № 872н "Об утверждении Правил по охране труда при строительстве, реконструкции, ремонте и содержании мостов"</t>
         </is>
       </c>
       <c r="C356" s="13" t="inlineStr">
         <is>
-          <t>Правила № 782н (журналы приёма и осмотра лесов и подмостей; учёта и осмотра такелажных средств — рекомендуемые образцы в приложениях)</t>
+          <t>п. 98–101, прил. 6–7 Правил № 782н (журнал приёма и осмотра лесов и подмостей; журнал учёта и осмотра такелажных средств); Правила № 872н (журнал приёмки и осмотра лесов и подмостей при испытаниях подвесных лесов)</t>
         </is>
       </c>
       <c r="D356" s="13" t="inlineStr">
         <is>
-          <t>Журнал приёма и осмотра лесов и подмостей; журнал учёта и осмотра такелажных средств, механизмов и устройств</t>
+          <t>Журнал приёма (приёмки) и осмотра лесов и подмостей; журнал учёта и осмотра такелажных средств, механизмов и устройств</t>
         </is>
       </c>
       <c r="E356" s="13" t="inlineStr">
@@ -23329,12 +23329,12 @@
       </c>
       <c r="B359" s="13" t="inlineStr">
         <is>
-          <t>Правила по охране труда, утв. приказами Минтруда России (только приказы, где документ прямо предусмотрен): № 343н, № 652н, № 753н, № 782н, № 866н, № 883н</t>
+          <t>Правила по охране труда, утв. приказами Минтруда России (только приказы, где документ прямо предусмотрен): № 343н, № 652н, № 753н, № 782н, № 866н, № 883н, № 886н</t>
         </is>
       </c>
       <c r="C359" s="13" t="inlineStr">
         <is>
-          <t>Правила № 753н (технологические карты / ППР на погрузочно-разгрузочные работы с применением ПС; схемы строповки; технологические карты размещения грузов — при выполнении соответствующих работ)</t>
+          <t>п. 14, 37, 105 Правил № 753н (техкарты/ППР на ПРР; схемы строповки; карты размещения грузов); также схемы строповки / техдокументация на ПРР: № 343н, 652н, 782н, 866н, 883н, 886н</t>
         </is>
       </c>
       <c r="D359" s="13" t="inlineStr">

--- a/presentations/Analiz_SUOT_podpisanty_skvoznaya.xlsx
+++ b/presentations/Analiz_SUOT_podpisanty_skvoznaya.xlsx
@@ -22027,7 +22027,7 @@
       </c>
       <c r="B338" s="13" t="inlineStr">
         <is>
-          <t>Правила по охране труда, утв. приказами Минтруда России (только приказы, где документ прямо предусмотрен): № 343н, № 644н, № 652н, № 721н, № 746н, № 753н, № 758н, № 776н, № 780н, № 781н, № 814н, № 815н, № 832н, № 833н, № 834н, № 835н, № 836н, № 849н, № 858н, № 859н, № 866н, № 867н, № 871н, № 872н, № 875н, № 881н, № 882н, № 883н, № 884н, № 886н, № 887н, № 901н, № 902н, № 914н, № 915н, № 922н, № 924н, № 928н</t>
+          <t>Правила по охране труда, утв. приказами Минтруда России (только приказы, где документ прямо предусмотрен): № 343н, № 644н, № 652н, № 721н, № 746н, № 753н, № 758н, № 776н, № 780н, № 781н, № 782н, № 814н, № 815н, № 832н, № 833н, № 834н, № 835н, № 836н, № 849н, № 858н, № 859н, № 866н, № 867н, № 871н, № 872н, № 875н, № 881н, № 882н, № 883н, № 884н, № 886н, № 887н, № 901н, № 902н, № 914н, № 915н, № 922н, № 924н, № 928н</t>
         </is>
       </c>
       <c r="C338" s="13" t="inlineStr">
@@ -22089,7 +22089,7 @@
       </c>
       <c r="B339" s="13" t="inlineStr">
         <is>
-          <t>Правила по охране труда, утв. приказами Минтруда России (только приказы, где документ прямо предусмотрен): № 343н, № 644н, № 652н, № 721н, № 746н, № 753н, № 758н, № 776н, № 780н, № 781н, № 814н, № 815н, № 832н, № 833н, № 834н, № 835н, № 836н, № 849н, № 858н, № 859н, № 866н, № 867н, № 871н, № 872н, № 875н, № 881н, № 882н, № 883н, № 884н, № 886н, № 887н, № 901н, № 902н, № 914н, № 915н, № 922н, № 924н, № 928н</t>
+          <t>Правила по охране труда, утв. приказами Минтруда России (только приказы, где документ прямо предусмотрен): № 343н, № 644н, № 652н, № 721н, № 746н, № 753н, № 758н, № 776н, № 780н, № 781н, № 782н, № 814н, № 815н, № 832н, № 833н, № 834н, № 835н, № 836н, № 849н, № 858н, № 859н, № 866н, № 867н, № 871н, № 872н, № 875н, № 881н, № 882н, № 883н, № 884н, № 886н, № 887н, № 901н, № 902н, № 914н, № 915н, № 922н, № 924н, № 928н</t>
         </is>
       </c>
       <c r="C339" s="13" t="inlineStr">
@@ -22151,7 +22151,7 @@
       </c>
       <c r="B340" s="13" t="inlineStr">
         <is>
-          <t>Правила по охране труда, утв. приказами Минтруда России (только приказы, где документ прямо предусмотрен): № 343н, № 644н, № 746н, № 753н, № 758н, № 776н, № 780н, № 781н, № 814н, № 815н, № 832н, № 833н, № 834н, № 835н, № 849н, № 858н, № 859н, № 866н, № 867н, № 871н, № 872н, № 875н, № 881н, № 882н, № 883н, № 884н, № 887н, № 901н, № 902н, № 914н, № 915н, № 924н, № 928н</t>
+          <t>Правила по охране труда, утв. приказами Минтруда России (только приказы, где документ прямо предусмотрен): № 343н, № 644н, № 652н, № 721н, № 746н, № 753н, № 758н, № 776н, № 780н, № 781н, № 814н, № 815н, № 832н, № 833н, № 834н, № 835н, № 836н, № 849н, № 858н, № 859н, № 866н, № 867н, № 871н, № 872н, № 875н, № 881н, № 882н, № 883н, № 884н, № 887н, № 901н, № 902н, № 914н, № 915н, № 924н, № 928н</t>
         </is>
       </c>
       <c r="C340" s="13" t="inlineStr">
@@ -22213,7 +22213,7 @@
       </c>
       <c r="B341" s="13" t="inlineStr">
         <is>
-          <t>Правила по охране труда, утв. приказами Минтруда России (только приказы, где документ прямо предусмотрен): № 652н, № 746н, № 776н, № 836н, № 875н, № 915н, № 924н</t>
+          <t>Правила по охране труда, утв. приказами Минтруда России (только приказы, где документ прямо предусмотрен): № 644н, № 652н, № 721н, № 746н, № 758н, № 776н, № 814н, № 836н, № 875н, № 883н, № 901н, № 915н, № 924н</t>
         </is>
       </c>
       <c r="C341" s="13" t="inlineStr">
@@ -22275,7 +22275,7 @@
       </c>
       <c r="B342" s="13" t="inlineStr">
         <is>
-          <t>Правила по охране труда, утв. приказами Минтруда России (только приказы, где документ прямо предусмотрен): № 644н, № 721н, № 746н, № 758н, № 776н, № 780н, № 781н, № 832н, № 833н, № 834н, № 849н, № 858н, № 859н, № 866н, № 867н, № 871н, № 872н, № 875н, № 882н, № 883н, № 884н, № 915н, № 924н</t>
+          <t>Правила по охране труда, утв. приказами Минтруда России (только приказы, где документ прямо предусмотрен): № 644н, № 721н, № 746н, № 758н, № 776н, № 780н, № 781н, № 832н, № 833н, № 834н, № 849н, № 858н, № 859н, № 866н, № 867н, № 871н, № 872н, № 875н, № 882н, № 883н, № 884н, № 902н, № 915н, № 924н</t>
         </is>
       </c>
       <c r="C342" s="13" t="inlineStr">
@@ -22461,7 +22461,7 @@
       </c>
       <c r="B345" s="13" t="inlineStr">
         <is>
-          <t>Правила по охране труда, утв. приказами Минтруда России (только приказы, где документ прямо предусмотрен): № 644н, № 721н, № 746н, № 758н, № 776н, № 781н, № 782н, № 814н, № 832н, № 833н, № 834н, № 835н, № 836н, № 849н, № 858н, № 859н, № 866н, № 867н, № 871н, № 875н, № 882н, № 883н, № 902н, № 903н, № 915н, № 922н, № 924н</t>
+          <t>Правила по охране труда, утв. приказами Минтруда России (только приказы, где документ прямо предусмотрен): № 644н, № 652н, № 721н, № 746н, № 758н, № 776н, № 780н, № 781н, № 782н, № 814н, № 832н, № 833н, № 834н, № 835н, № 836н, № 849н, № 858н, № 859н, № 866н, № 867н, № 871н, № 872н, № 875н, № 882н, № 883н, № 884н, № 887н, № 901н, № 902н, № 903н, № 915н, № 922н, № 924н</t>
         </is>
       </c>
       <c r="C345" s="13" t="inlineStr">
@@ -22523,7 +22523,7 @@
       </c>
       <c r="B346" s="13" t="inlineStr">
         <is>
-          <t>Правила по охране труда, утв. приказами Минтруда России (только приказы, где документ прямо предусмотрен): № 644н, № 721н, № 746н, № 758н, № 776н, № 781н, № 782н, № 814н, № 832н, № 833н, № 834н, № 835н, № 836н, № 849н, № 858н, № 859н, № 866н, № 867н, № 871н, № 875н, № 882н, № 883н, № 902н, № 903н, № 915н, № 922н, № 924н</t>
+          <t>Правила по охране труда, утв. приказами Минтруда России (только приказы, где документ прямо предусмотрен): № 644н, № 652н, № 721н, № 746н, № 758н, № 776н, № 780н, № 781н, № 782н, № 814н, № 832н, № 833н, № 834н, № 835н, № 836н, № 849н, № 858н, № 859н, № 866н, № 867н, № 871н, № 872н, № 875н, № 882н, № 883н, № 884н, № 887н, № 901н, № 902н, № 903н, № 915н, № 922н, № 924н</t>
         </is>
       </c>
       <c r="C346" s="13" t="inlineStr">
@@ -22585,7 +22585,7 @@
       </c>
       <c r="B347" s="13" t="inlineStr">
         <is>
-          <t>Правила по охране труда, утв. приказами Минтруда России (только приказы, где документ прямо предусмотрен): № 644н, № 652н, № 758н, № 776н, № 781н, № 782н, № 833н, № 834н, № 849н, № 858н, № 867н, № 875н, № 882н, № 903н, № 915н, № 924н</t>
+          <t>Правила по охране труда, утв. приказами Минтруда России (только приказы, где документ прямо предусмотрен): № 644н, № 652н, № 746н, № 758н, № 776н, № 781н, № 782н, № 832н, № 833н, № 834н, № 849н, № 858н, № 866н, № 867н, № 871н, № 872н, № 875н, № 882н, № 884н, № 902н, № 903н, № 915н, № 922н, № 924н</t>
         </is>
       </c>
       <c r="C347" s="13" t="inlineStr">
@@ -22647,7 +22647,7 @@
       </c>
       <c r="B348" s="13" t="inlineStr">
         <is>
-          <t>Правила по охране труда, утв. приказами Минтруда России (только приказы, где документ прямо предусмотрен): № 644н, № 758н, № 776н, № 781н, № 782н, № 832н, № 833н, № 834н, № 849н, № 858н, № 866н, № 867н, № 871н, № 882н, № 884н, № 902н, № 915н, № 922н</t>
+          <t>Правила по охране труда, утв. приказами Минтруда России (только приказы, где документ прямо предусмотрен): № 644н, № 758н, № 776н, № 781н, № 782н, № 832н, № 833н, № 834н, № 849н, № 858н, № 866н, № 867н, № 871н, № 882н, № 884н, № 902н, № 915н</t>
         </is>
       </c>
       <c r="C348" s="13" t="inlineStr">
@@ -22709,7 +22709,7 @@
       </c>
       <c r="B349" s="13" t="inlineStr">
         <is>
-          <t>Правила по охране труда, утв. приказами Минтруда России (только приказы, где документ прямо предусмотрен): № 758н, № 782н, № 833н, № 872н, № 902н</t>
+          <t>Правила по охране труда, утв. приказами Минтруда России (только приказы, где документ прямо предусмотрен): № 644н, № 652н, № 746н, № 758н, № 782н, № 833н, № 872н, № 886н, № 902н, № 922н</t>
         </is>
       </c>
       <c r="C349" s="13" t="inlineStr">
@@ -23453,7 +23453,7 @@
       </c>
       <c r="B361" s="13" t="inlineStr">
         <is>
-          <t>Правила по охране труда, утв. приказами Минтруда России (только приказы, где документ прямо предусмотрен): № 343н, № 644н, № 652н, № 721н, № 746н, № 753н, № 758н, № 776н, № 780н, № 781н, № 782н, № 814н, № 815н, № 832н, № 833н, № 834н, № 835н, № 849н, № 858н, № 859н, № 866н, № 867н, № 871н, № 872н, № 875н, № 882н, № 883н, № 884н, № 886н, № 887н, № 902н, № 903н, № 914н, № 915н, № 922н, № 924н, № 928н</t>
+          <t>Правила по охране труда, утв. приказами Минтруда России (только приказы, где документ прямо предусмотрен): № 343н, № 644н, № 652н, № 721н, № 746н, № 753н, № 758н, № 776н, № 780н, № 781н, № 782н, № 814н, № 815н, № 832н, № 833н, № 834н, № 835н, № 836н, № 849н, № 858н, № 859н, № 866н, № 867н, № 871н, № 872н, № 875н, № 881н, № 882н, № 883н, № 884н, № 886н, № 887н, № 901н, № 902н, № 903н, № 914н, № 915н, № 922н, № 924н, № 928н</t>
         </is>
       </c>
       <c r="C361" s="13" t="inlineStr">

--- a/presentations/Analiz_SUOT_podpisanty_skvoznaya.xlsx
+++ b/presentations/Analiz_SUOT_podpisanty_skvoznaya.xlsx
@@ -2710,12 +2710,12 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>Приказы Минтранса России от 04.05.2026 № 190, от 14.04.2026 № 160, от 14.04.2026 № 159, от 10.11.2025 № 381, от 30.04.2025 № 145, от 30.04.2025 № 144, от 21.03.2025 № 97, от 17.03.2025 № 93, от 14.03.2025 № 89, от 04.03.2025 № 75, от 11.10.2021 № 339, от 16.10.2020 № 424, от 02.10.2020 № 404, от 16.10.2020 № 423, от 30.01.2004 № 10; приказы МЧС России от 24.04.2026 № 308, от 24.04.2026 № 307, от 28.02.2020 № 136, от 04.09.2013 № 585; приказ Минздрава России от 13.03.2025 № 115н; приказ Минобрнауки России от 08.04.2025 № 318; приказ Минпросвещения России от 04.04.2025 № 268; приказ Минфина России от 31.03.2025 № 39н; приказ Минтруда России от 13.03.2025 № 107н; приказ ГФС России от 17.08.2009 № 264; приказ ФСБ России от 07.04.2007 № 161; приказ Росгидромета от 30.12.2003 № 272; приказ Минсвязи России от 08.09.2003 № 112; приказ Госкомрыболовства России от 08.08.2003 № 271; приказ Минобороны России от 16.05.2003 № 170; постановление Минтруда России от 12.07.1999 № 22</t>
+          <t>Приказ Минтранса России от 04.05.2026 № 190; приказ Минтранса России от 14.04.2026 № 160; приказ Минтранса России от 14.04.2026 № 159; приказ Минтранса России от 16.10.2020 № 423; приказ Минтранса России от 16.10.2020 № 424; приказ Минтранса России от 02.10.2020 № 404; приказ Минтранса России от 11.10.2021 № 339; приказ Минпросвещения России от 04.04.2025 № 268; приказ Минобрнауки России от 08.04.2025 № 318; приказ Минздрава России от 13.03.2025 № 115н; приказ МЧС России от 24.04.2026 № 307</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>п. 1 и аналог. положений Особенностей (в т.ч. приказы Минтранса № 190, № 160, № 159, № 339, № 424, № 404, № 423; Минпросвещения № 268; Минобрнауки № 318 и др.)</t>
+          <t>п. 1 Особенностей (приказы Минтранса № 190, № 160, № 159, № 423, № 424, № 404); п. 2 Особенностей (приказ Минтранса № 339); п. 2–3 Особенностей (приказ Минпросвещения № 268); п. 2–3 Особенностей (приказ Минобрнауки № 318); п. 1 Особенностей (приказ Минздрава № 115н); п. 7 Особенностей (приказ МЧС № 307) — порядок введения суммированного учета устанавливается ПВТР</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -2772,12 +2772,12 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>Приказы Минтранса России от 04.05.2026 № 190, от 14.04.2026 № 160, от 14.04.2026 № 159, от 10.11.2025 № 381, от 30.04.2025 № 145, от 30.04.2025 № 144, от 21.03.2025 № 97, от 17.03.2025 № 93, от 14.03.2025 № 89, от 04.03.2025 № 75, от 11.10.2021 № 339, от 16.10.2020 № 424, от 02.10.2020 № 404, от 16.10.2020 № 423, от 30.01.2004 № 10; приказы МЧС России от 24.04.2026 № 308, от 24.04.2026 № 307, от 28.02.2020 № 136, от 04.09.2013 № 585; приказ Минздрава России от 13.03.2025 № 115н; приказ Минобрнауки России от 08.04.2025 № 318; приказ Минпросвещения России от 04.04.2025 № 268; приказ Минфина России от 31.03.2025 № 39н; приказ Минтруда России от 13.03.2025 № 107н; приказ ГФС России от 17.08.2009 № 264; приказ ФСБ России от 07.04.2007 № 161; приказ Росгидромета от 30.12.2003 № 272; приказ Минсвязи России от 08.09.2003 № 112; приказ Госкомрыболовства России от 08.08.2003 № 271; приказ Минобороны России от 16.05.2003 № 170; постановление Минтруда России от 12.07.1999 № 22</t>
+          <t>Приказ Минпросвещения России от 04.04.2025 № 268; приказ Минобрнауки России от 08.04.2025 № 318</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>п. 3 Особенностей (приказ Минпросвещения № 268); аналог. нормы отраслевых Особенностей; ст. 190, 372 ТК РФ</t>
+          <t>п. 3 Особенностей (приказ Минпросвещения № 268); п. 3 Особенностей (приказ Минобрнауки № 318)</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
@@ -2834,12 +2834,12 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>Приказы Минтранса России от 04.05.2026 № 190, от 14.04.2026 № 160, от 14.04.2026 № 159, от 10.11.2025 № 381, от 30.04.2025 № 145, от 30.04.2025 № 144, от 21.03.2025 № 97, от 17.03.2025 № 93, от 14.03.2025 № 89, от 04.03.2025 № 75, от 11.10.2021 № 339, от 16.10.2020 № 424, от 02.10.2020 № 404, от 16.10.2020 № 423, от 30.01.2004 № 10; приказы МЧС России от 24.04.2026 № 308, от 24.04.2026 № 307, от 28.02.2020 № 136, от 04.09.2013 № 585; приказ Минздрава России от 13.03.2025 № 115н; приказ Минобрнауки России от 08.04.2025 № 318; приказ Минпросвещения России от 04.04.2025 № 268; приказ Минфина России от 31.03.2025 № 39н; приказ Минтруда России от 13.03.2025 № 107н; приказ ГФС России от 17.08.2009 № 264; приказ ФСБ России от 07.04.2007 № 161; приказ Росгидромета от 30.12.2003 № 272; приказ Минсвязи России от 08.09.2003 № 112; приказ Госкомрыболовства России от 08.08.2003 № 271; приказ Минобороны России от 16.05.2003 № 170; постановление Минтруда России от 12.07.1999 № 22</t>
+          <t>Трудовой кодекс Российской Федерации</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>ст. 68, 22 ТК РФ; отраслевые Особенности (обязанность работодателя ознакомить с ЛНА)</t>
+          <t>ст. 22, 68 ТК РФ</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>Приказы Минтранса России от 04.05.2026 № 190, от 14.04.2026 № 160, от 14.04.2026 № 159, от 10.11.2025 № 381, от 30.04.2025 № 145, от 30.04.2025 № 144, от 21.03.2025 № 97, от 17.03.2025 № 93, от 14.03.2025 № 89, от 04.03.2025 № 75, от 11.10.2021 № 339, от 16.10.2020 № 424, от 02.10.2020 № 404, от 16.10.2020 № 423, от 30.01.2004 № 10; приказы МЧС России от 24.04.2026 № 308, от 24.04.2026 № 307, от 28.02.2020 № 136, от 04.09.2013 № 585; приказ Минздрава России от 13.03.2025 № 115н; приказ Минобрнауки России от 08.04.2025 № 318; приказ Минпросвещения России от 04.04.2025 № 268; приказ Минфина России от 31.03.2025 № 39н; приказ Минтруда России от 13.03.2025 № 107н; приказ ГФС России от 17.08.2009 № 264; приказ ФСБ России от 07.04.2007 № 161; приказ Росгидромета от 30.12.2003 № 272; приказ Минсвязи России от 08.09.2003 № 112; приказ Госкомрыболовства России от 08.08.2003 № 271; приказ Минобороны России от 16.05.2003 № 170; постановление Минтруда России от 12.07.1999 № 22</t>
+          <t>Приказ Минтранса России от 11.10.2021 № 339; приказ Минпросвещения России от 04.04.2025 № 268; приказ Минобрнауки России от 08.04.2025 № 318; приказ МЧС России от 24.04.2026 № 307</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>п. 2 Особенностей (приказ Минтранса № 339); п. 2 Особенностей (приказ Минпросвещения № 268); ст. 100 ТК РФ</t>
+          <t>п. 2 Особенностей (приказ Минтранса № 339); п. 2 Особенностей (приказ Минпросвещения № 268); п. 2 Особенностей (приказ Минобрнауки № 318); п. 2 Особенностей (приказ МЧС № 307)</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
@@ -2958,12 +2958,12 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>Приказы Минтранса России от 04.05.2026 № 190, от 14.04.2026 № 160, от 14.04.2026 № 159, от 10.11.2025 № 381, от 30.04.2025 № 145, от 30.04.2025 № 144, от 21.03.2025 № 97, от 17.03.2025 № 93, от 14.03.2025 № 89, от 04.03.2025 № 75, от 11.10.2021 № 339, от 16.10.2020 № 424, от 02.10.2020 № 404, от 16.10.2020 № 423, от 30.01.2004 № 10; приказы МЧС России от 24.04.2026 № 308, от 24.04.2026 № 307, от 28.02.2020 № 136, от 04.09.2013 № 585; приказ Минздрава России от 13.03.2025 № 115н; приказ Минобрнауки России от 08.04.2025 № 318; приказ Минпросвещения России от 04.04.2025 № 268; приказ Минфина России от 31.03.2025 № 39н; приказ Минтруда России от 13.03.2025 № 107н; приказ ГФС России от 17.08.2009 № 264; приказ ФСБ России от 07.04.2007 № 161; приказ Росгидромета от 30.12.2003 № 272; приказ Минсвязи России от 08.09.2003 № 112; приказ Госкомрыболовства России от 08.08.2003 № 271; приказ Минобороны России от 16.05.2003 № 170; постановление Минтруда России от 12.07.1999 № 22</t>
+          <t>Приказ Минтранса России от 04.05.2026 № 190; приказ Минтранса России от 14.04.2026 № 160; приказ Минтранса России от 14.04.2026 № 159; приказ Минтранса России от 16.10.2020 № 423; приказ Минтранса России от 16.10.2020 № 424; приказ Минтранса России от 02.10.2020 № 404; приказ Минтранса России от 11.10.2021 № 339; приказ Минтранса России от 10.11.2025 № 381; приказ МЧС России от 24.04.2026 № 307; приказ МЧС России от 24.04.2026 № 308; приказ Минпросвещения России от 04.04.2025 № 268; приказ Минздрава России от 13.03.2025 № 115н</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>п. 1–2 Особенностей (приказы Минтранса № 190, № 160, № 159, № 339 и др.); ст. 103 ТК РФ</t>
+          <t>п. 1–2 Особенностей (приказы Минтранса № 190, № 160, № 159, № 423, № 424, № 404); п. 2, 11 Особенностей (приказ Минтранса № 339); п. 3, 59 Особенностей (приказ Минтранса № 381); п. 1 Особенностей (приказ МЧС № 307); п. 1 Особенностей (приказ МЧС № 308); п. 4, 20 Особенностей (приказ Минпросвещения № 268); п. 1 Особенностей (приказ Минздрава № 115н)</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>Приказы Минтранса России от 04.05.2026 № 190, от 14.04.2026 № 160, от 14.04.2026 № 159, от 10.11.2025 № 381, от 30.04.2025 № 145, от 30.04.2025 № 144, от 21.03.2025 № 97, от 17.03.2025 № 93, от 14.03.2025 № 89, от 04.03.2025 № 75, от 11.10.2021 № 339, от 16.10.2020 № 424, от 02.10.2020 № 404, от 16.10.2020 № 423, от 30.01.2004 № 10; приказы МЧС России от 24.04.2026 № 308, от 24.04.2026 № 307, от 28.02.2020 № 136, от 04.09.2013 № 585; приказ Минздрава России от 13.03.2025 № 115н; приказ Минобрнауки России от 08.04.2025 № 318; приказ Минпросвещения России от 04.04.2025 № 268; приказ Минфина России от 31.03.2025 № 39н; приказ Минтруда России от 13.03.2025 № 107н; приказ ГФС России от 17.08.2009 № 264; приказ ФСБ России от 07.04.2007 № 161; приказ Росгидромета от 30.12.2003 № 272; приказ Минсвязи России от 08.09.2003 № 112; приказ Госкомрыболовства России от 08.08.2003 № 271; приказ Минобороны России от 16.05.2003 № 170; постановление Минтруда России от 12.07.1999 № 22</t>
+          <t>Приказ Минтранса России от 04.05.2026 № 190; приказ Минтранса России от 11.10.2021 № 339; приказ Минтранса России от 10.11.2025 № 381; приказ Минздрава России от 13.03.2025 № 115н</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>п. 2 Особенностей (приказы Минтранса № 190, № 339 и др.); ст. 103 ТК РФ</t>
+          <t>п. 2 Особенностей (приказ Минтранса № 190); п. 2 Особенностей (приказ Минтранса № 339); п. 59 Особенностей (приказ Минтранса № 381); п. 1 Особенностей (приказ Минздрава № 115н)</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>Приказы Минтранса России от 04.05.2026 № 190, от 14.04.2026 № 160, от 14.04.2026 № 159, от 10.11.2025 № 381, от 30.04.2025 № 145, от 30.04.2025 № 144, от 21.03.2025 № 97, от 17.03.2025 № 93, от 14.03.2025 № 89, от 04.03.2025 № 75, от 11.10.2021 № 339, от 16.10.2020 № 424, от 02.10.2020 № 404, от 16.10.2020 № 423, от 30.01.2004 № 10; приказы МЧС России от 24.04.2026 № 308, от 24.04.2026 № 307, от 28.02.2020 № 136, от 04.09.2013 № 585; приказ Минздрава России от 13.03.2025 № 115н; приказ Минобрнауки России от 08.04.2025 № 318; приказ Минпросвещения России от 04.04.2025 № 268; приказ Минфина России от 31.03.2025 № 39н; приказ Минтруда России от 13.03.2025 № 107н; приказ ГФС России от 17.08.2009 № 264; приказ ФСБ России от 07.04.2007 № 161; приказ Росгидромета от 30.12.2003 № 272; приказ Минсвязи России от 08.09.2003 № 112; приказ Госкомрыболовства России от 08.08.2003 № 271; приказ Минобороны России от 16.05.2003 № 170; постановление Минтруда России от 12.07.1999 № 22</t>
+          <t>Приказ Минтранса России от 04.05.2026 № 190; приказ Минтранса России от 11.10.2021 № 339; приказ Минтранса России от 10.11.2025 № 381</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>п. 2 Особенностей (приказы Минтранса № 190, № 339 и др.); ст. 103 ТК РФ</t>
+          <t>п. 2 Особенностей (приказ Минтранса № 190); п. 2 Особенностей (приказ Минтранса № 339); п. 59 Особенностей (приказ Минтранса № 381); ст. 103 ТК РФ</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
@@ -3144,12 +3144,12 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>Приказы Минтранса России от 04.05.2026 № 190, от 14.04.2026 № 160, от 14.04.2026 № 159, от 10.11.2025 № 381, от 30.04.2025 № 145, от 30.04.2025 № 144, от 21.03.2025 № 97, от 17.03.2025 № 93, от 14.03.2025 № 89, от 04.03.2025 № 75, от 11.10.2021 № 339, от 16.10.2020 № 424, от 02.10.2020 № 404, от 16.10.2020 № 423, от 30.01.2004 № 10; приказы МЧС России от 24.04.2026 № 308, от 24.04.2026 № 307, от 28.02.2020 № 136, от 04.09.2013 № 585; приказ Минздрава России от 13.03.2025 № 115н; приказ Минобрнауки России от 08.04.2025 № 318; приказ Минпросвещения России от 04.04.2025 № 268; приказ Минфина России от 31.03.2025 № 39н; приказ Минтруда России от 13.03.2025 № 107н; приказ ГФС России от 17.08.2009 № 264; приказ ФСБ России от 07.04.2007 № 161; приказ Росгидромета от 30.12.2003 № 272; приказ Минсвязи России от 08.09.2003 № 112; приказ Госкомрыболовства России от 08.08.2003 № 271; приказ Минобороны России от 16.05.2003 № 170; постановление Минтруда России от 12.07.1999 № 22</t>
+          <t>Приказ Минтранса России от 04.05.2026 № 190; приказ Минтранса России от 11.10.2021 № 339; приказ Минтранса России от 10.11.2025 № 381</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>п. 2 Особенностей (приказ Минтранса № 190); п. 2 Особенностей (приказ Минтранса № 339)</t>
+          <t>п. 2 Особенностей (приказ Минтранса № 190); п. 2 Особенностей (приказ Минтранса № 339); п. 59 Особенностей (приказ Минтранса № 381)</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>Приказы Минтранса России от 04.05.2026 № 190, от 14.04.2026 № 160, от 14.04.2026 № 159, от 10.11.2025 № 381, от 30.04.2025 № 145, от 30.04.2025 № 144, от 21.03.2025 № 97, от 17.03.2025 № 93, от 14.03.2025 № 89, от 04.03.2025 № 75, от 11.10.2021 № 339, от 16.10.2020 № 424, от 02.10.2020 № 404, от 16.10.2020 № 423, от 30.01.2004 № 10; приказы МЧС России от 24.04.2026 № 308, от 24.04.2026 № 307, от 28.02.2020 № 136, от 04.09.2013 № 585; приказ Минздрава России от 13.03.2025 № 115н; приказ Минобрнауки России от 08.04.2025 № 318; приказ Минпросвещения России от 04.04.2025 № 268; приказ Минфина России от 31.03.2025 № 39н; приказ Минтруда России от 13.03.2025 № 107н; приказ ГФС России от 17.08.2009 № 264; приказ ФСБ России от 07.04.2007 № 161; приказ Росгидромета от 30.12.2003 № 272; приказ Минсвязи России от 08.09.2003 № 112; приказ Госкомрыболовства России от 08.08.2003 № 271; приказ Минобороны России от 16.05.2003 № 170; постановление Минтруда России от 12.07.1999 № 22</t>
+          <t>Приказ Минтранса России от 14.04.2026 № 160; приказ Минтранса России от 14.04.2026 № 159; приказ Минтранса России от 16.10.2020 № 424; приказ Минтранса России от 02.10.2020 № 404; приказ Минтранса России от 11.10.2021 № 339; приказ Минтранса России от 10.11.2025 № 381; приказ Минздрава России от 13.03.2025 № 115н; приказ Минпросвещения России от 04.04.2025 № 268; приказ МЧС России от 24.04.2026 № 307</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>п. 3 и аналог. положений Особенностей (приказы Минтранса № 160, № 339, № 381 и др.); ст. 104 ТК РФ</t>
+          <t>п. 3 Особенностей (приказ Минтранса № 160); п. 3 Особенностей (приказ Минтранса № 159); п. 3 Особенностей (приказ Минтранса № 424); п. 3 Особенностей (приказ Минтранса № 404); п. 3, 20 Особенностей (приказ Минтранса № 339); п. 6 Особенностей (приказ Минтранса № 381); п. 1 Особенностей (приказ Минздрава № 115н); п. 35 Особенностей (приказ Минпросвещения № 268); п. 7 Особенностей (приказ МЧС № 307); ст. 104 ТК РФ</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
@@ -3268,12 +3268,12 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>Приказы Минтранса России от 04.05.2026 № 190, от 14.04.2026 № 160, от 14.04.2026 № 159, от 10.11.2025 № 381, от 30.04.2025 № 145, от 30.04.2025 № 144, от 21.03.2025 № 97, от 17.03.2025 № 93, от 14.03.2025 № 89, от 04.03.2025 № 75, от 11.10.2021 № 339, от 16.10.2020 № 424, от 02.10.2020 № 404, от 16.10.2020 № 423, от 30.01.2004 № 10; приказы МЧС России от 24.04.2026 № 308, от 24.04.2026 № 307, от 28.02.2020 № 136, от 04.09.2013 № 585; приказ Минздрава России от 13.03.2025 № 115н; приказ Минобрнауки России от 08.04.2025 № 318; приказ Минпросвещения России от 04.04.2025 № 268; приказ Минфина России от 31.03.2025 № 39н; приказ Минтруда России от 13.03.2025 № 107н; приказ ГФС России от 17.08.2009 № 264; приказ ФСБ России от 07.04.2007 № 161; приказ Росгидромета от 30.12.2003 № 272; приказ Минсвязи России от 08.09.2003 № 112; приказ Госкомрыболовства России от 08.08.2003 № 271; приказ Минобороны России от 16.05.2003 № 170; постановление Минтруда России от 12.07.1999 № 22</t>
+          <t>Приказ Минтранса России от 14.04.2026 № 160; приказ Минтранса России от 10.11.2025 № 381</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>п. 3 Особенностей (приказ Минтранса № 160); п. 6 Особенностей (приказ Минтранса № 381); ст. 104 ТК РФ</t>
+          <t>п. 3 Особенностей (приказ Минтранса № 160); п. 6 Особенностей (приказ Минтранса № 381)</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
@@ -3330,7 +3330,7 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>Приказы Минтранса России от 04.05.2026 № 190, от 14.04.2026 № 160, от 14.04.2026 № 159, от 10.11.2025 № 381, от 30.04.2025 № 145, от 30.04.2025 № 144, от 21.03.2025 № 97, от 17.03.2025 № 93, от 14.03.2025 № 89, от 04.03.2025 № 75, от 11.10.2021 № 339, от 16.10.2020 № 424, от 02.10.2020 № 404, от 16.10.2020 № 423, от 30.01.2004 № 10; приказы МЧС России от 24.04.2026 № 308, от 24.04.2026 № 307, от 28.02.2020 № 136, от 04.09.2013 № 585; приказ Минздрава России от 13.03.2025 № 115н; приказ Минобрнауки России от 08.04.2025 № 318; приказ Минпросвещения России от 04.04.2025 № 268; приказ Минфина России от 31.03.2025 № 39н; приказ Минтруда России от 13.03.2025 № 107н; приказ ГФС России от 17.08.2009 № 264; приказ ФСБ России от 07.04.2007 № 161; приказ Росгидромета от 30.12.2003 № 272; приказ Минсвязи России от 08.09.2003 № 112; приказ Госкомрыболовства России от 08.08.2003 № 271; приказ Минобороны России от 16.05.2003 № 170; постановление Минтруда России от 12.07.1999 № 22</t>
+          <t>Приказ Минтранса России от 14.04.2026 № 160; приказ Минтранса России от 10.11.2025 № 381</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>Приказы Минтранса России от 04.05.2026 № 190, от 14.04.2026 № 160, от 14.04.2026 № 159, от 10.11.2025 № 381, от 30.04.2025 № 145, от 30.04.2025 № 144, от 21.03.2025 № 97, от 17.03.2025 № 93, от 14.03.2025 № 89, от 04.03.2025 № 75, от 11.10.2021 № 339, от 16.10.2020 № 424, от 02.10.2020 № 404, от 16.10.2020 № 423, от 30.01.2004 № 10; приказы МЧС России от 24.04.2026 № 308, от 24.04.2026 № 307, от 28.02.2020 № 136, от 04.09.2013 № 585; приказ Минздрава России от 13.03.2025 № 115н; приказ Минобрнауки России от 08.04.2025 № 318; приказ Минпросвещения России от 04.04.2025 № 268; приказ Минфина России от 31.03.2025 № 39н; приказ Минтруда России от 13.03.2025 № 107н; приказ ГФС России от 17.08.2009 № 264; приказ ФСБ России от 07.04.2007 № 161; приказ Росгидромета от 30.12.2003 № 272; приказ Минсвязи России от 08.09.2003 № 112; приказ Госкомрыболовства России от 08.08.2003 № 271; приказ Минобороны России от 16.05.2003 № 170; постановление Минтруда России от 12.07.1999 № 22</t>
+          <t>Приказ Минтранса России от 14.04.2026 № 160; приказ Минтранса России от 14.04.2026 № 159; приказ Минтранса России от 16.10.2020 № 424; приказ Минпросвещения России от 04.04.2025 № 268; приказ Минтранса России от 10.11.2025 № 381</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>п. 5 Особенностей (приказ Минтранса № 160); п. 22–23 Особенностей (приказ Минпросвещения № 268); аналог. нормы отраслевых Особенностей</t>
+          <t>п. 5 Особенностей (приказ Минтранса № 160); п. 5 Особенностей (приказ Минтранса № 159); п. 5 Особенностей (приказ Минтранса № 424); п. 22–23 Особенностей (приказ Минпросвещения № 268); положения Особенностей о разделении полетной смены на части (приказ Минтранса № 381)</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
@@ -3454,12 +3454,12 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>Приказы Минтранса России от 04.05.2026 № 190, от 14.04.2026 № 160, от 14.04.2026 № 159, от 10.11.2025 № 381, от 30.04.2025 № 145, от 30.04.2025 № 144, от 21.03.2025 № 97, от 17.03.2025 № 93, от 14.03.2025 № 89, от 04.03.2025 № 75, от 11.10.2021 № 339, от 16.10.2020 № 424, от 02.10.2020 № 404, от 16.10.2020 № 423, от 30.01.2004 № 10; приказы МЧС России от 24.04.2026 № 308, от 24.04.2026 № 307, от 28.02.2020 № 136, от 04.09.2013 № 585; приказ Минздрава России от 13.03.2025 № 115н; приказ Минобрнауки России от 08.04.2025 № 318; приказ Минпросвещения России от 04.04.2025 № 268; приказ Минфина России от 31.03.2025 № 39н; приказ Минтруда России от 13.03.2025 № 107н; приказ ГФС России от 17.08.2009 № 264; приказ ФСБ России от 07.04.2007 № 161; приказ Росгидромета от 30.12.2003 № 272; приказ Минсвязи России от 08.09.2003 № 112; приказ Госкомрыболовства России от 08.08.2003 № 271; приказ Минобороны России от 16.05.2003 № 170; постановление Минтруда России от 12.07.1999 № 22</t>
+          <t>Приказ Минтранса России от 14.04.2026 № 160; приказ Минпросвещения России от 04.04.2025 № 268; приказ Минтранса России от 10.11.2025 № 381</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>п. 5 Особенностей (приказ Минтранса № 160); п. 23 Особенностей (приказ Минпросвещения № 268)</t>
+          <t>п. 5 Особенностей (приказ Минтранса № 160); п. 23 Особенностей (приказ Минпросвещения № 268); положения Особенностей о разделении полетной смены на части (приказ Минтранса № 381)</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>Приказы Минтранса России от 04.05.2026 № 190, от 14.04.2026 № 160, от 14.04.2026 № 159, от 10.11.2025 № 381, от 30.04.2025 № 145, от 30.04.2025 № 144, от 21.03.2025 № 97, от 17.03.2025 № 93, от 14.03.2025 № 89, от 04.03.2025 № 75, от 11.10.2021 № 339, от 16.10.2020 № 424, от 02.10.2020 № 404, от 16.10.2020 № 423, от 30.01.2004 № 10; приказы МЧС России от 24.04.2026 № 308, от 24.04.2026 № 307, от 28.02.2020 № 136, от 04.09.2013 № 585; приказ Минздрава России от 13.03.2025 № 115н; приказ Минобрнауки России от 08.04.2025 № 318; приказ Минпросвещения России от 04.04.2025 № 268; приказ Минфина России от 31.03.2025 № 39н; приказ Минтруда России от 13.03.2025 № 107н; приказ ГФС России от 17.08.2009 № 264; приказ ФСБ России от 07.04.2007 № 161; приказ Росгидромета от 30.12.2003 № 272; приказ Минсвязи России от 08.09.2003 № 112; приказ Госкомрыболовства России от 08.08.2003 № 271; приказ Минобороны России от 16.05.2003 № 170; постановление Минтруда России от 12.07.1999 № 22</t>
+          <t>Приказ Минтранса России от 14.04.2026 № 160; приказ Минтранса России от 11.10.2021 № 339; приказ Минпросвещения России от 04.04.2025 № 268; приказ Минтранса России от 10.11.2025 № 381</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>п. 5 Особенностей (приказ Минтранса № 160); п. 8 Особенностей (приказ Минтранса № 339); п. 16 Особенностей (приказ Минпросвещения № 268)</t>
+          <t>п. 5 Особенностей (приказ Минтранса № 160); п. 8 Особенностей (приказ Минтранса № 339); п. 2, 11, 16 Особенностей (приказ Минпросвещения № 268); п. 7, 10 Особенностей (приказ Минтранса № 381)</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
@@ -3578,12 +3578,12 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>Приказы Минтранса России от 04.05.2026 № 190, от 14.04.2026 № 160, от 14.04.2026 № 159, от 10.11.2025 № 381, от 30.04.2025 № 145, от 30.04.2025 № 144, от 21.03.2025 № 97, от 17.03.2025 № 93, от 14.03.2025 № 89, от 04.03.2025 № 75, от 11.10.2021 № 339, от 16.10.2020 № 424, от 02.10.2020 № 404, от 16.10.2020 № 423, от 30.01.2004 № 10; приказы МЧС России от 24.04.2026 № 308, от 24.04.2026 № 307, от 28.02.2020 № 136, от 04.09.2013 № 585; приказ Минздрава России от 13.03.2025 № 115н; приказ Минобрнауки России от 08.04.2025 № 318; приказ Минпросвещения России от 04.04.2025 № 268; приказ Минфина России от 31.03.2025 № 39н; приказ Минтруда России от 13.03.2025 № 107н; приказ ГФС России от 17.08.2009 № 264; приказ ФСБ России от 07.04.2007 № 161; приказ Росгидромета от 30.12.2003 № 272; приказ Минсвязи России от 08.09.2003 № 112; приказ Госкомрыболовства России от 08.08.2003 № 271; приказ Минобороны России от 16.05.2003 № 170; постановление Минтруда России от 12.07.1999 № 22</t>
+          <t>Приказ Минтранса России от 10.11.2025 № 381; Трудовой кодекс Российской Федерации</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>ст. 91 ТК РФ; п. 3 Особенностей (приказ Минздрава № 115н); п. 60 Особенностей (приказ Минтранса № 381); отраслевые Особенности</t>
+          <t>п. 60 Особенностей (приказ Минтранса № 381); ст. 91 ТК РФ</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>Приказы Минтранса России от 04.05.2026 № 190, от 14.04.2026 № 160, от 14.04.2026 № 159, от 10.11.2025 № 381, от 30.04.2025 № 145, от 30.04.2025 № 144, от 21.03.2025 № 97, от 17.03.2025 № 93, от 14.03.2025 № 89, от 04.03.2025 № 75, от 11.10.2021 № 339, от 16.10.2020 № 424, от 02.10.2020 № 404, от 16.10.2020 № 423, от 30.01.2004 № 10; приказы МЧС России от 24.04.2026 № 308, от 24.04.2026 № 307, от 28.02.2020 № 136, от 04.09.2013 № 585; приказ Минздрава России от 13.03.2025 № 115н; приказ Минобрнауки России от 08.04.2025 № 318; приказ Минпросвещения России от 04.04.2025 № 268; приказ Минфина России от 31.03.2025 № 39н; приказ Минтруда России от 13.03.2025 № 107н; приказ ГФС России от 17.08.2009 № 264; приказ ФСБ России от 07.04.2007 № 161; приказ Росгидромета от 30.12.2003 № 272; приказ Минсвязи России от 08.09.2003 № 112; приказ Госкомрыболовства России от 08.08.2003 № 271; приказ Минобороны России от 16.05.2003 № 170; постановление Минтруда России от 12.07.1999 № 22</t>
+          <t>Приказ Минпросвещения России от 04.04.2025 № 268; приказ МЧС России от 24.04.2026 № 307; приказ Минтранса России от 14.04.2026 № 160; Трудовой кодекс Российской Федерации</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>ст. 57, 100 ТК РФ; п. 16 Особенностей (приказ Минпросвещения № 268); отраслевые Особенности</t>
+          <t>п. 16 Особенностей (приказ Минпросвещения № 268); п. 2 Особенностей (приказ МЧС № 307); п. 12 Особенностей (приказ Минтранса № 160); ст. 57, 100 ТК РФ</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
@@ -3702,12 +3702,12 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>Приказы Минтранса России от 04.05.2026 № 190, от 14.04.2026 № 160, от 14.04.2026 № 159, от 10.11.2025 № 381, от 30.04.2025 № 145, от 30.04.2025 № 144, от 21.03.2025 № 97, от 17.03.2025 № 93, от 14.03.2025 № 89, от 04.03.2025 № 75, от 11.10.2021 № 339, от 16.10.2020 № 424, от 02.10.2020 № 404, от 16.10.2020 № 423, от 30.01.2004 № 10; приказы МЧС России от 24.04.2026 № 308, от 24.04.2026 № 307, от 28.02.2020 № 136, от 04.09.2013 № 585; приказ Минздрава России от 13.03.2025 № 115н; приказ Минобрнауки России от 08.04.2025 № 318; приказ Минпросвещения России от 04.04.2025 № 268; приказ Минфина России от 31.03.2025 № 39н; приказ Минтруда России от 13.03.2025 № 107н; приказ ГФС России от 17.08.2009 № 264; приказ ФСБ России от 07.04.2007 № 161; приказ Росгидромета от 30.12.2003 № 272; приказ Минсвязи России от 08.09.2003 № 112; приказ Госкомрыболовства России от 08.08.2003 № 271; приказ Минобороны России от 16.05.2003 № 170; постановление Минтруда России от 12.07.1999 № 22</t>
+          <t>Приказ Минтранса России от 11.10.2021 № 339</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>п. 6 Особенностей (приказ Минтранса № 339); аналог. нормы отраслевых Особенностей</t>
+          <t>п. 6 Особенностей (приказ Минтранса № 339)</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>Приказы Минтранса России от 04.05.2026 № 190, от 14.04.2026 № 160, от 14.04.2026 № 159, от 10.11.2025 № 381, от 30.04.2025 № 145, от 30.04.2025 № 144, от 21.03.2025 № 97, от 17.03.2025 № 93, от 14.03.2025 № 89, от 04.03.2025 № 75, от 11.10.2021 № 339, от 16.10.2020 № 424, от 02.10.2020 № 404, от 16.10.2020 № 423, от 30.01.2004 № 10; приказы МЧС России от 24.04.2026 № 308, от 24.04.2026 № 307, от 28.02.2020 № 136, от 04.09.2013 № 585; приказ Минздрава России от 13.03.2025 № 115н; приказ Минобрнауки России от 08.04.2025 № 318; приказ Минпросвещения России от 04.04.2025 № 268; приказ Минфина России от 31.03.2025 № 39н; приказ Минтруда России от 13.03.2025 № 107н; приказ ГФС России от 17.08.2009 № 264; приказ ФСБ России от 07.04.2007 № 161; приказ Росгидромета от 30.12.2003 № 272; приказ Минсвязи России от 08.09.2003 № 112; приказ Госкомрыболовства России от 08.08.2003 № 271; приказ Минобороны России от 16.05.2003 № 170; постановление Минтруда России от 12.07.1999 № 22</t>
+          <t>Приказ Минздрава России от 13.03.2025 № 115н</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>п. 1–3 Особенностей (приказ Минздрава № 115н)</t>
+          <t>п. 1 Особенностей (приказ Минздрава № 115н)</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>Приказы Минтранса России от 04.05.2026 № 190, от 14.04.2026 № 160, от 14.04.2026 № 159, от 10.11.2025 № 381, от 30.04.2025 № 145, от 30.04.2025 № 144, от 21.03.2025 № 97, от 17.03.2025 № 93, от 14.03.2025 № 89, от 04.03.2025 № 75, от 11.10.2021 № 339, от 16.10.2020 № 424, от 02.10.2020 № 404, от 16.10.2020 № 423, от 30.01.2004 № 10; приказы МЧС России от 24.04.2026 № 308, от 24.04.2026 № 307, от 28.02.2020 № 136, от 04.09.2013 № 585; приказ Минздрава России от 13.03.2025 № 115н; приказ Минобрнауки России от 08.04.2025 № 318; приказ Минпросвещения России от 04.04.2025 № 268; приказ Минфина России от 31.03.2025 № 39н; приказ Минтруда России от 13.03.2025 № 107н; приказ ГФС России от 17.08.2009 № 264; приказ ФСБ России от 07.04.2007 № 161; приказ Росгидромета от 30.12.2003 № 272; приказ Минсвязи России от 08.09.2003 № 112; приказ Госкомрыболовства России от 08.08.2003 № 271; приказ Минобороны России от 16.05.2003 № 170; постановление Минтруда России от 12.07.1999 № 22</t>
+          <t>Приказ Минздрава России от 13.03.2025 № 115н</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
@@ -3888,7 +3888,7 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>Приказы Минтранса России от 04.05.2026 № 190, от 14.04.2026 № 160, от 14.04.2026 № 159, от 10.11.2025 № 381, от 30.04.2025 № 145, от 30.04.2025 № 144, от 21.03.2025 № 97, от 17.03.2025 № 93, от 14.03.2025 № 89, от 04.03.2025 № 75, от 11.10.2021 № 339, от 16.10.2020 № 424, от 02.10.2020 № 404, от 16.10.2020 № 423, от 30.01.2004 № 10; приказы МЧС России от 24.04.2026 № 308, от 24.04.2026 № 307, от 28.02.2020 № 136, от 04.09.2013 № 585; приказ Минздрава России от 13.03.2025 № 115н; приказ Минобрнауки России от 08.04.2025 № 318; приказ Минпросвещения России от 04.04.2025 № 268; приказ Минфина России от 31.03.2025 № 39н; приказ Минтруда России от 13.03.2025 № 107н; приказ ГФС России от 17.08.2009 № 264; приказ ФСБ России от 07.04.2007 № 161; приказ Росгидромета от 30.12.2003 № 272; приказ Минсвязи России от 08.09.2003 № 112; приказ Госкомрыболовства России от 08.08.2003 № 271; приказ Минобороны России от 16.05.2003 № 170; постановление Минтруда России от 12.07.1999 № 22</t>
+          <t>Приказ Минздрава России от 13.03.2025 № 115н</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>Приказы Минтранса России от 04.05.2026 № 190, от 14.04.2026 № 160, от 14.04.2026 № 159, от 10.11.2025 № 381, от 30.04.2025 № 145, от 30.04.2025 № 144, от 21.03.2025 № 97, от 17.03.2025 № 93, от 14.03.2025 № 89, от 04.03.2025 № 75, от 11.10.2021 № 339, от 16.10.2020 № 424, от 02.10.2020 № 404, от 16.10.2020 № 423, от 30.01.2004 № 10; приказы МЧС России от 24.04.2026 № 308, от 24.04.2026 № 307, от 28.02.2020 № 136, от 04.09.2013 № 585; приказ Минздрава России от 13.03.2025 № 115н; приказ Минобрнауки России от 08.04.2025 № 318; приказ Минпросвещения России от 04.04.2025 № 268; приказ Минфина России от 31.03.2025 № 39н; приказ Минтруда России от 13.03.2025 № 107н; приказ ГФС России от 17.08.2009 № 264; приказ ФСБ России от 07.04.2007 № 161; приказ Росгидромета от 30.12.2003 № 272; приказ Минсвязи России от 08.09.2003 № 112; приказ Госкомрыболовства России от 08.08.2003 № 271; приказ Минобороны России от 16.05.2003 № 170; постановление Минтруда России от 12.07.1999 № 22</t>
+          <t>Приказ Минздрава России от 13.03.2025 № 115н</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
@@ -4012,7 +4012,7 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>Приказы Минтранса России от 04.05.2026 № 190, от 14.04.2026 № 160, от 14.04.2026 № 159, от 10.11.2025 № 381, от 30.04.2025 № 145, от 30.04.2025 № 144, от 21.03.2025 № 97, от 17.03.2025 № 93, от 14.03.2025 № 89, от 04.03.2025 № 75, от 11.10.2021 № 339, от 16.10.2020 № 424, от 02.10.2020 № 404, от 16.10.2020 № 423, от 30.01.2004 № 10; приказы МЧС России от 24.04.2026 № 308, от 24.04.2026 № 307, от 28.02.2020 № 136, от 04.09.2013 № 585; приказ Минздрава России от 13.03.2025 № 115н; приказ Минобрнауки России от 08.04.2025 № 318; приказ Минпросвещения России от 04.04.2025 № 268; приказ Минфина России от 31.03.2025 № 39н; приказ Минтруда России от 13.03.2025 № 107н; приказ ГФС России от 17.08.2009 № 264; приказ ФСБ России от 07.04.2007 № 161; приказ Росгидромета от 30.12.2003 № 272; приказ Минсвязи России от 08.09.2003 № 112; приказ Госкомрыболовства России от 08.08.2003 № 271; приказ Минобороны России от 16.05.2003 № 170; постановление Минтруда России от 12.07.1999 № 22</t>
+          <t>Приказ Минздрава России от 13.03.2025 № 115н</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
@@ -4074,12 +4074,12 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>Приказы Минтранса России от 04.05.2026 № 190, от 14.04.2026 № 160, от 14.04.2026 № 159, от 10.11.2025 № 381, от 30.04.2025 № 145, от 30.04.2025 № 144, от 21.03.2025 № 97, от 17.03.2025 № 93, от 14.03.2025 № 89, от 04.03.2025 № 75, от 11.10.2021 № 339, от 16.10.2020 № 424, от 02.10.2020 № 404, от 16.10.2020 № 423, от 30.01.2004 № 10; приказы МЧС России от 24.04.2026 № 308, от 24.04.2026 № 307, от 28.02.2020 № 136, от 04.09.2013 № 585; приказ Минздрава России от 13.03.2025 № 115н; приказ Минобрнауки России от 08.04.2025 № 318; приказ Минпросвещения России от 04.04.2025 № 268; приказ Минфина России от 31.03.2025 № 39н; приказ Минтруда России от 13.03.2025 № 107н; приказ ГФС России от 17.08.2009 № 264; приказ ФСБ России от 07.04.2007 № 161; приказ Росгидромета от 30.12.2003 № 272; приказ Минсвязи России от 08.09.2003 № 112; приказ Госкомрыболовства России от 08.08.2003 № 271; приказ Минобороны России от 16.05.2003 № 170; постановление Минтруда России от 12.07.1999 № 22</t>
+          <t>Приказ Минпросвещения России от 04.04.2025 № 268; приказ Минобрнауки России от 08.04.2025 № 318</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>п. 2, 13 Особенностей (приказ Минпросвещения № 268); аналог. нормы приказа Минобрнауки № 318</t>
+          <t>п. 13 Особенностей (приказ Минпросвещения № 268); п. 2 Особенностей (приказ Минобрнауки № 318) — режим устанавливается в т.ч. расписанием занятий</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>Приказы Минтранса России от 04.05.2026 № 190, от 14.04.2026 № 160, от 14.04.2026 № 159, от 10.11.2025 № 381, от 30.04.2025 № 145, от 30.04.2025 № 144, от 21.03.2025 № 97, от 17.03.2025 № 93, от 14.03.2025 № 89, от 04.03.2025 № 75, от 11.10.2021 № 339, от 16.10.2020 № 424, от 02.10.2020 № 404, от 16.10.2020 № 423, от 30.01.2004 № 10; приказы МЧС России от 24.04.2026 № 308, от 24.04.2026 № 307, от 28.02.2020 № 136, от 04.09.2013 № 585; приказ Минздрава России от 13.03.2025 № 115н; приказ Минобрнауки России от 08.04.2025 № 318; приказ Минпросвещения России от 04.04.2025 № 268; приказ Минфина России от 31.03.2025 № 39н; приказ Минтруда России от 13.03.2025 № 107н; приказ ГФС России от 17.08.2009 № 264; приказ ФСБ России от 07.04.2007 № 161; приказ Росгидромета от 30.12.2003 № 272; приказ Минсвязи России от 08.09.2003 № 112; приказ Госкомрыболовства России от 08.08.2003 № 271; приказ Минобороны России от 16.05.2003 № 170; постановление Минтруда России от 12.07.1999 № 22</t>
+          <t>Приказ Минпросвещения России от 04.04.2025 № 268</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
@@ -4198,7 +4198,7 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>Приказы Минтранса России от 04.05.2026 № 190, от 14.04.2026 № 160, от 14.04.2026 № 159, от 10.11.2025 № 381, от 30.04.2025 № 145, от 30.04.2025 № 144, от 21.03.2025 № 97, от 17.03.2025 № 93, от 14.03.2025 № 89, от 04.03.2025 № 75, от 11.10.2021 № 339, от 16.10.2020 № 424, от 02.10.2020 № 404, от 16.10.2020 № 423, от 30.01.2004 № 10; приказы МЧС России от 24.04.2026 № 308, от 24.04.2026 № 307, от 28.02.2020 № 136, от 04.09.2013 № 585; приказ Минздрава России от 13.03.2025 № 115н; приказ Минобрнауки России от 08.04.2025 № 318; приказ Минпросвещения России от 04.04.2025 № 268; приказ Минфина России от 31.03.2025 № 39н; приказ Минтруда России от 13.03.2025 № 107н; приказ ГФС России от 17.08.2009 № 264; приказ ФСБ России от 07.04.2007 № 161; приказ Росгидромета от 30.12.2003 № 272; приказ Минсвязи России от 08.09.2003 № 112; приказ Госкомрыболовства России от 08.08.2003 № 271; приказ Минобороны России от 16.05.2003 № 170; постановление Минтруда России от 12.07.1999 № 22</t>
+          <t>Приказ Минпросвещения России от 04.04.2025 № 268</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>Приказы Минтранса России от 04.05.2026 № 190, от 14.04.2026 № 160, от 14.04.2026 № 159, от 10.11.2025 № 381, от 30.04.2025 № 145, от 30.04.2025 № 144, от 21.03.2025 № 97, от 17.03.2025 № 93, от 14.03.2025 № 89, от 04.03.2025 № 75, от 11.10.2021 № 339, от 16.10.2020 № 424, от 02.10.2020 № 404, от 16.10.2020 № 423, от 30.01.2004 № 10; приказы МЧС России от 24.04.2026 № 308, от 24.04.2026 № 307, от 28.02.2020 № 136, от 04.09.2013 № 585; приказ Минздрава России от 13.03.2025 № 115н; приказ Минобрнауки России от 08.04.2025 № 318; приказ Минпросвещения России от 04.04.2025 № 268; приказ Минфина России от 31.03.2025 № 39н; приказ Минтруда России от 13.03.2025 № 107н; приказ ГФС России от 17.08.2009 № 264; приказ ФСБ России от 07.04.2007 № 161; приказ Росгидромета от 30.12.2003 № 272; приказ Минсвязи России от 08.09.2003 № 112; приказ Госкомрыболовства России от 08.08.2003 № 271; приказ Минобороны России от 16.05.2003 № 170; постановление Минтруда России от 12.07.1999 № 22</t>
+          <t>Приказ Минпросвещения России от 04.04.2025 № 268</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
@@ -4322,7 +4322,7 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>Приказы Минтранса России от 04.05.2026 № 190, от 14.04.2026 № 160, от 14.04.2026 № 159, от 10.11.2025 № 381, от 30.04.2025 № 145, от 30.04.2025 № 144, от 21.03.2025 № 97, от 17.03.2025 № 93, от 14.03.2025 № 89, от 04.03.2025 № 75, от 11.10.2021 № 339, от 16.10.2020 № 424, от 02.10.2020 № 404, от 16.10.2020 № 423, от 30.01.2004 № 10; приказы МЧС России от 24.04.2026 № 308, от 24.04.2026 № 307, от 28.02.2020 № 136, от 04.09.2013 № 585; приказ Минздрава России от 13.03.2025 № 115н; приказ Минобрнауки России от 08.04.2025 № 318; приказ Минпросвещения России от 04.04.2025 № 268; приказ Минфина России от 31.03.2025 № 39н; приказ Минтруда России от 13.03.2025 № 107н; приказ ГФС России от 17.08.2009 № 264; приказ ФСБ России от 07.04.2007 № 161; приказ Росгидромета от 30.12.2003 № 272; приказ Минсвязи России от 08.09.2003 № 112; приказ Госкомрыболовства России от 08.08.2003 № 271; приказ Минобороны России от 16.05.2003 № 170; постановление Минтруда России от 12.07.1999 № 22</t>
+          <t>Приказ Минпросвещения России от 04.04.2025 № 268</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
@@ -4384,7 +4384,7 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>Приказы Минтранса России от 04.05.2026 № 190, от 14.04.2026 № 160, от 14.04.2026 № 159, от 10.11.2025 № 381, от 30.04.2025 № 145, от 30.04.2025 № 144, от 21.03.2025 № 97, от 17.03.2025 № 93, от 14.03.2025 № 89, от 04.03.2025 № 75, от 11.10.2021 № 339, от 16.10.2020 № 424, от 02.10.2020 № 404, от 16.10.2020 № 423, от 30.01.2004 № 10; приказы МЧС России от 24.04.2026 № 308, от 24.04.2026 № 307, от 28.02.2020 № 136, от 04.09.2013 № 585; приказ Минздрава России от 13.03.2025 № 115н; приказ Минобрнауки России от 08.04.2025 № 318; приказ Минпросвещения России от 04.04.2025 № 268; приказ Минфина России от 31.03.2025 № 39н; приказ Минтруда России от 13.03.2025 № 107н; приказ ГФС России от 17.08.2009 № 264; приказ ФСБ России от 07.04.2007 № 161; приказ Росгидромета от 30.12.2003 № 272; приказ Минсвязи России от 08.09.2003 № 112; приказ Госкомрыболовства России от 08.08.2003 № 271; приказ Минобороны России от 16.05.2003 № 170; постановление Минтруда России от 12.07.1999 № 22</t>
+          <t>Приказ Минпросвещения России от 04.04.2025 № 268</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>Приказы Минтранса России от 04.05.2026 № 190, от 14.04.2026 № 160, от 14.04.2026 № 159, от 10.11.2025 № 381, от 30.04.2025 № 145, от 30.04.2025 № 144, от 21.03.2025 № 97, от 17.03.2025 № 93, от 14.03.2025 № 89, от 04.03.2025 № 75, от 11.10.2021 № 339, от 16.10.2020 № 424, от 02.10.2020 № 404, от 16.10.2020 № 423, от 30.01.2004 № 10; приказы МЧС России от 24.04.2026 № 308, от 24.04.2026 № 307, от 28.02.2020 № 136, от 04.09.2013 № 585; приказ Минздрава России от 13.03.2025 № 115н; приказ Минобрнауки России от 08.04.2025 № 318; приказ Минпросвещения России от 04.04.2025 № 268; приказ Минфина России от 31.03.2025 № 39н; приказ Минтруда России от 13.03.2025 № 107н; приказ ГФС России от 17.08.2009 № 264; приказ ФСБ России от 07.04.2007 № 161; приказ Росгидромета от 30.12.2003 № 272; приказ Минсвязи России от 08.09.2003 № 112; приказ Госкомрыболовства России от 08.08.2003 № 271; приказ Минобороны России от 16.05.2003 № 170; постановление Минтруда России от 12.07.1999 № 22</t>
+          <t>Приказ Минтранса России от 11.10.2021 № 339</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
@@ -4508,7 +4508,7 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>Приказы Минтранса России от 04.05.2026 № 190, от 14.04.2026 № 160, от 14.04.2026 № 159, от 10.11.2025 № 381, от 30.04.2025 № 145, от 30.04.2025 № 144, от 21.03.2025 № 97, от 17.03.2025 № 93, от 14.03.2025 № 89, от 04.03.2025 № 75, от 11.10.2021 № 339, от 16.10.2020 № 424, от 02.10.2020 № 404, от 16.10.2020 № 423, от 30.01.2004 № 10; приказы МЧС России от 24.04.2026 № 308, от 24.04.2026 № 307, от 28.02.2020 № 136, от 04.09.2013 № 585; приказ Минздрава России от 13.03.2025 № 115н; приказ Минобрнауки России от 08.04.2025 № 318; приказ Минпросвещения России от 04.04.2025 № 268; приказ Минфина России от 31.03.2025 № 39н; приказ Минтруда России от 13.03.2025 № 107н; приказ ГФС России от 17.08.2009 № 264; приказ ФСБ России от 07.04.2007 № 161; приказ Росгидромета от 30.12.2003 № 272; приказ Минсвязи России от 08.09.2003 № 112; приказ Госкомрыболовства России от 08.08.2003 № 271; приказ Минобороны России от 16.05.2003 № 170; постановление Минтруда России от 12.07.1999 № 22</t>
+          <t>Приказ Минтранса России от 11.10.2021 № 339</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
@@ -4570,7 +4570,7 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>Приказы Минтранса России от 04.05.2026 № 190, от 14.04.2026 № 160, от 14.04.2026 № 159, от 10.11.2025 № 381, от 30.04.2025 № 145, от 30.04.2025 № 144, от 21.03.2025 № 97, от 17.03.2025 № 93, от 14.03.2025 № 89, от 04.03.2025 № 75, от 11.10.2021 № 339, от 16.10.2020 № 424, от 02.10.2020 № 404, от 16.10.2020 № 423, от 30.01.2004 № 10; приказы МЧС России от 24.04.2026 № 308, от 24.04.2026 № 307, от 28.02.2020 № 136, от 04.09.2013 № 585; приказ Минздрава России от 13.03.2025 № 115н; приказ Минобрнауки России от 08.04.2025 № 318; приказ Минпросвещения России от 04.04.2025 № 268; приказ Минфина России от 31.03.2025 № 39н; приказ Минтруда России от 13.03.2025 № 107н; приказ ГФС России от 17.08.2009 № 264; приказ ФСБ России от 07.04.2007 № 161; приказ Росгидромета от 30.12.2003 № 272; приказ Минсвязи России от 08.09.2003 № 112; приказ Госкомрыболовства России от 08.08.2003 № 271; приказ Минобороны России от 16.05.2003 № 170; постановление Минтруда России от 12.07.1999 № 22</t>
+          <t>Приказ Минтранса России от 11.10.2021 № 339</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>Приказы Минтранса России от 04.05.2026 № 190, от 14.04.2026 № 160, от 14.04.2026 № 159, от 10.11.2025 № 381, от 30.04.2025 № 145, от 30.04.2025 № 144, от 21.03.2025 № 97, от 17.03.2025 № 93, от 14.03.2025 № 89, от 04.03.2025 № 75, от 11.10.2021 № 339, от 16.10.2020 № 424, от 02.10.2020 № 404, от 16.10.2020 № 423, от 30.01.2004 № 10; приказы МЧС России от 24.04.2026 № 308, от 24.04.2026 № 307, от 28.02.2020 № 136, от 04.09.2013 № 585; приказ Минздрава России от 13.03.2025 № 115н; приказ Минобрнауки России от 08.04.2025 № 318; приказ Минпросвещения России от 04.04.2025 № 268; приказ Минфина России от 31.03.2025 № 39н; приказ Минтруда России от 13.03.2025 № 107н; приказ ГФС России от 17.08.2009 № 264; приказ ФСБ России от 07.04.2007 № 161; приказ Росгидромета от 30.12.2003 № 272; приказ Минсвязи России от 08.09.2003 № 112; приказ Госкомрыболовства России от 08.08.2003 № 271; приказ Минобороны России от 16.05.2003 № 170; постановление Минтруда России от 12.07.1999 № 22</t>
+          <t>Приказ Минтранса России от 11.10.2021 № 339</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
@@ -4694,7 +4694,7 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>Приказы Минтранса России от 04.05.2026 № 190, от 14.04.2026 № 160, от 14.04.2026 № 159, от 10.11.2025 № 381, от 30.04.2025 № 145, от 30.04.2025 № 144, от 21.03.2025 № 97, от 17.03.2025 № 93, от 14.03.2025 № 89, от 04.03.2025 № 75, от 11.10.2021 № 339, от 16.10.2020 № 424, от 02.10.2020 № 404, от 16.10.2020 № 423, от 30.01.2004 № 10; приказы МЧС России от 24.04.2026 № 308, от 24.04.2026 № 307, от 28.02.2020 № 136, от 04.09.2013 № 585; приказ Минздрава России от 13.03.2025 № 115н; приказ Минобрнауки России от 08.04.2025 № 318; приказ Минпросвещения России от 04.04.2025 № 268; приказ Минфина России от 31.03.2025 № 39н; приказ Минтруда России от 13.03.2025 № 107н; приказ ГФС России от 17.08.2009 № 264; приказ ФСБ России от 07.04.2007 № 161; приказ Росгидромета от 30.12.2003 № 272; приказ Минсвязи России от 08.09.2003 № 112; приказ Госкомрыболовства России от 08.08.2003 № 271; приказ Минобороны России от 16.05.2003 № 170; постановление Минтруда России от 12.07.1999 № 22</t>
+          <t>Приказ Минтранса России от 11.10.2021 № 339</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>Приказы Минтранса России от 04.05.2026 № 190, от 14.04.2026 № 160, от 14.04.2026 № 159, от 10.11.2025 № 381, от 30.04.2025 № 145, от 30.04.2025 № 144, от 21.03.2025 № 97, от 17.03.2025 № 93, от 14.03.2025 № 89, от 04.03.2025 № 75, от 11.10.2021 № 339, от 16.10.2020 № 424, от 02.10.2020 № 404, от 16.10.2020 № 423, от 30.01.2004 № 10; приказы МЧС России от 24.04.2026 № 308, от 24.04.2026 № 307, от 28.02.2020 № 136, от 04.09.2013 № 585; приказ Минздрава России от 13.03.2025 № 115н; приказ Минобрнауки России от 08.04.2025 № 318; приказ Минпросвещения России от 04.04.2025 № 268; приказ Минфина России от 31.03.2025 № 39н; приказ Минтруда России от 13.03.2025 № 107н; приказ ГФС России от 17.08.2009 № 264; приказ ФСБ России от 07.04.2007 № 161; приказ Росгидромета от 30.12.2003 № 272; приказ Минсвязи России от 08.09.2003 № 112; приказ Госкомрыболовства России от 08.08.2003 № 271; приказ Минобороны России от 16.05.2003 № 170; постановление Минтруда России от 12.07.1999 № 22</t>
+          <t>Приказ Минтранса России от 10.11.2025 № 381</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>п. 1 Особенностей (приказ Минтранса № 381); руководство по производству полетов</t>
+          <t>п. 3 Особенностей (приказ Минтранса № 381)</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
@@ -4818,12 +4818,12 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>Приказы Минтранса России от 04.05.2026 № 190, от 14.04.2026 № 160, от 14.04.2026 № 159, от 10.11.2025 № 381, от 30.04.2025 № 145, от 30.04.2025 № 144, от 21.03.2025 № 97, от 17.03.2025 № 93, от 14.03.2025 № 89, от 04.03.2025 № 75, от 11.10.2021 № 339, от 16.10.2020 № 424, от 02.10.2020 № 404, от 16.10.2020 № 423, от 30.01.2004 № 10; приказы МЧС России от 24.04.2026 № 308, от 24.04.2026 № 307, от 28.02.2020 № 136, от 04.09.2013 № 585; приказ Минздрава России от 13.03.2025 № 115н; приказ Минобрнауки России от 08.04.2025 № 318; приказ Минпросвещения России от 04.04.2025 № 268; приказ Минфина России от 31.03.2025 № 39н; приказ Минтруда России от 13.03.2025 № 107н; приказ ГФС России от 17.08.2009 № 264; приказ ФСБ России от 07.04.2007 № 161; приказ Росгидромета от 30.12.2003 № 272; приказ Минсвязи России от 08.09.2003 № 112; приказ Госкомрыболовства России от 08.08.2003 № 271; приказ Минобороны России от 16.05.2003 № 170; постановление Минтруда России от 12.07.1999 № 22</t>
+          <t>Приказ Минтранса России от 10.11.2025 № 381</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>п. 1, 60 Особенностей (приказ Минтранса № 381)</t>
+          <t>п. 3, 59 Особенностей (приказ Минтранса № 381)</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
@@ -4880,12 +4880,12 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>Приказы Минтранса России от 04.05.2026 № 190, от 14.04.2026 № 160, от 14.04.2026 № 159, от 10.11.2025 № 381, от 30.04.2025 № 145, от 30.04.2025 № 144, от 21.03.2025 № 97, от 17.03.2025 № 93, от 14.03.2025 № 89, от 04.03.2025 № 75, от 11.10.2021 № 339, от 16.10.2020 № 424, от 02.10.2020 № 404, от 16.10.2020 № 423, от 30.01.2004 № 10; приказы МЧС России от 24.04.2026 № 308, от 24.04.2026 № 307, от 28.02.2020 № 136, от 04.09.2013 № 585; приказ Минздрава России от 13.03.2025 № 115н; приказ Минобрнауки России от 08.04.2025 № 318; приказ Минпросвещения России от 04.04.2025 № 268; приказ Минфина России от 31.03.2025 № 39н; приказ Минтруда России от 13.03.2025 № 107н; приказ ГФС России от 17.08.2009 № 264; приказ ФСБ России от 07.04.2007 № 161; приказ Росгидромета от 30.12.2003 № 272; приказ Минсвязи России от 08.09.2003 № 112; приказ Госкомрыболовства России от 08.08.2003 № 271; приказ Минобороны России от 16.05.2003 № 170; постановление Минтруда России от 12.07.1999 № 22</t>
+          <t>Приказ Минтранса России от 10.11.2025 № 381</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>п. 60 Особенностей (приказ Минтранса № 381)</t>
+          <t>п. 59–60 Особенностей (приказ Минтранса № 381)</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
@@ -4942,12 +4942,12 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>Приказы Минтранса России от 04.05.2026 № 190, от 14.04.2026 № 160, от 14.04.2026 № 159, от 10.11.2025 № 381, от 30.04.2025 № 145, от 30.04.2025 № 144, от 21.03.2025 № 97, от 17.03.2025 № 93, от 14.03.2025 № 89, от 04.03.2025 № 75, от 11.10.2021 № 339, от 16.10.2020 № 424, от 02.10.2020 № 404, от 16.10.2020 № 423, от 30.01.2004 № 10; приказы МЧС России от 24.04.2026 № 308, от 24.04.2026 № 307, от 28.02.2020 № 136, от 04.09.2013 № 585; приказ Минздрава России от 13.03.2025 № 115н; приказ Минобрнауки России от 08.04.2025 № 318; приказ Минпросвещения России от 04.04.2025 № 268; приказ Минфина России от 31.03.2025 № 39н; приказ Минтруда России от 13.03.2025 № 107н; приказ ГФС России от 17.08.2009 № 264; приказ ФСБ России от 07.04.2007 № 161; приказ Росгидромета от 30.12.2003 № 272; приказ Минсвязи России от 08.09.2003 № 112; приказ Госкомрыболовства России от 08.08.2003 № 271; приказ Минобороны России от 16.05.2003 № 170; постановление Минтруда России от 12.07.1999 № 22</t>
+          <t>Приказ Минтранса России от 30.04.2025 № 145; приказ Минтранса России от 30.04.2025 № 144; приказ Минтранса России от 04.03.2025 № 75; приказ ФСБ России от 07.04.2007 № 161; приказ Минобороны России от 16.05.2003 № 170</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>приказы Минтранса № 145, № 144, № 75; приказ ФСБ № 161; приказ Минобороны № 170</t>
+          <t>положения Особенностей / Положений о режиме рабочего времени и времени отдыха членов экипажей (вахтенное расписание / графики вахт) — приказы Минтранса № 145, № 144, № 75; приказ ФСБ № 161; приказ Минобороны № 170</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>Приказы Минтранса России от 04.05.2026 № 190, от 14.04.2026 № 160, от 14.04.2026 № 159, от 10.11.2025 № 381, от 30.04.2025 № 145, от 30.04.2025 № 144, от 21.03.2025 № 97, от 17.03.2025 № 93, от 14.03.2025 № 89, от 04.03.2025 № 75, от 11.10.2021 № 339, от 16.10.2020 № 424, от 02.10.2020 № 404, от 16.10.2020 № 423, от 30.01.2004 № 10; приказы МЧС России от 24.04.2026 № 308, от 24.04.2026 № 307, от 28.02.2020 № 136, от 04.09.2013 № 585; приказ Минздрава России от 13.03.2025 № 115н; приказ Минобрнауки России от 08.04.2025 № 318; приказ Минпросвещения России от 04.04.2025 № 268; приказ Минфина России от 31.03.2025 № 39н; приказ Минтруда России от 13.03.2025 № 107н; приказ ГФС России от 17.08.2009 № 264; приказ ФСБ России от 07.04.2007 № 161; приказ Росгидромета от 30.12.2003 № 272; приказ Минсвязи России от 08.09.2003 № 112; приказ Госкомрыболовства России от 08.08.2003 № 271; приказ Минобороны России от 16.05.2003 № 170; постановление Минтруда России от 12.07.1999 № 22</t>
+          <t>Приказ Минтранса России от 14.04.2026 № 160; приказ Минтранса России от 16.10.2020 № 424</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>п. 12 и аналог. положений Особенностей (приказ Минтранса № 160)</t>
+          <t>п. 12 Особенностей (приказ Минтранса № 160); п. 15 Особенностей (приказ Минтранса № 424)</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
@@ -5066,12 +5066,12 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>Приказы Минтранса России от 04.05.2026 № 190, от 14.04.2026 № 160, от 14.04.2026 № 159, от 10.11.2025 № 381, от 30.04.2025 № 145, от 30.04.2025 № 144, от 21.03.2025 № 97, от 17.03.2025 № 93, от 14.03.2025 № 89, от 04.03.2025 № 75, от 11.10.2021 № 339, от 16.10.2020 № 424, от 02.10.2020 № 404, от 16.10.2020 № 423, от 30.01.2004 № 10; приказы МЧС России от 24.04.2026 № 308, от 24.04.2026 № 307, от 28.02.2020 № 136, от 04.09.2013 № 585; приказ Минздрава России от 13.03.2025 № 115н; приказ Минобрнауки России от 08.04.2025 № 318; приказ Минпросвещения России от 04.04.2025 № 268; приказ Минфина России от 31.03.2025 № 39н; приказ Минтруда России от 13.03.2025 № 107н; приказ ГФС России от 17.08.2009 № 264; приказ ФСБ России от 07.04.2007 № 161; приказ Росгидромета от 30.12.2003 № 272; приказ Минсвязи России от 08.09.2003 № 112; приказ Госкомрыболовства России от 08.08.2003 № 271; приказ Минобороны России от 16.05.2003 № 170; постановление Минтруда России от 12.07.1999 № 22</t>
+          <t>Приказ Минтранса России от 14.04.2026 № 160; приказ Минтранса России от 16.10.2020 № 424</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>п. 18 Особенностей (приказ Минтранса № 160)</t>
+          <t>п. 18 Особенностей (приказ Минтранса № 160); соответствующие положения Особенностей (приказ Минтранса № 424)</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
@@ -5128,17 +5128,17 @@
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>Приказы Минтранса России от 04.05.2026 № 190, от 14.04.2026 № 160, от 14.04.2026 № 159, от 10.11.2025 № 381, от 30.04.2025 № 145, от 30.04.2025 № 144, от 21.03.2025 № 97, от 17.03.2025 № 93, от 14.03.2025 № 89, от 04.03.2025 № 75, от 11.10.2021 № 339, от 16.10.2020 № 424, от 02.10.2020 № 404, от 16.10.2020 № 423, от 30.01.2004 № 10; приказы МЧС России от 24.04.2026 № 308, от 24.04.2026 № 307, от 28.02.2020 № 136, от 04.09.2013 № 585; приказ Минздрава России от 13.03.2025 № 115н; приказ Минобрнауки России от 08.04.2025 № 318; приказ Минпросвещения России от 04.04.2025 № 268; приказ Минфина России от 31.03.2025 № 39н; приказ Минтруда России от 13.03.2025 № 107н; приказ ГФС России от 17.08.2009 № 264; приказ ФСБ России от 07.04.2007 № 161; приказ Росгидромета от 30.12.2003 № 272; приказ Минсвязи России от 08.09.2003 № 112; приказ Госкомрыболовства России от 08.08.2003 № 271; приказ Минобороны России от 16.05.2003 № 170; постановление Минтруда России от 12.07.1999 № 22</t>
+          <t>Приказ ГФС России от 17.08.2009 № 264</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>приказ ГФС России № 264; приказы МЧС № 308, № 307, № 136, № 585; приказ Минтруда № 107н; приказ Минфина № 39н; приказы Минтранса № 97, № 93; приказы Росгидромета № 272, Минсвязи № 112, Госкомрыболовства № 271</t>
+          <t>Положение о порядке учета рабочего времени и времени отдыха лиц начальствующего состава федеральной фельдъегерской связи (приказ ГФС № 264)</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>Локальный нормативный акт (положение) об особенностях учета рабочего времени и времени отдыха отдельных категорий работников с особым характером работы</t>
+          <t>Положение (локальный порядок) учета рабочего времени и времени отдыха лиц начальствующего состава федеральной фельдъегерской связи</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
@@ -5190,12 +5190,12 @@
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>Приказы Минтранса России от 04.05.2026 № 190, от 14.04.2026 № 160, от 14.04.2026 № 159, от 10.11.2025 № 381, от 30.04.2025 № 145, от 30.04.2025 № 144, от 21.03.2025 № 97, от 17.03.2025 № 93, от 14.03.2025 № 89, от 04.03.2025 № 75, от 11.10.2021 № 339, от 16.10.2020 № 424, от 02.10.2020 № 404, от 16.10.2020 № 423, от 30.01.2004 № 10; приказы МЧС России от 24.04.2026 № 308, от 24.04.2026 № 307, от 28.02.2020 № 136, от 04.09.2013 № 585; приказ Минздрава России от 13.03.2025 № 115н; приказ Минобрнауки России от 08.04.2025 № 318; приказ Минпросвещения России от 04.04.2025 № 268; приказ Минфина России от 31.03.2025 № 39н; приказ Минтруда России от 13.03.2025 № 107н; приказ ГФС России от 17.08.2009 № 264; приказ ФСБ России от 07.04.2007 № 161; приказ Росгидромета от 30.12.2003 № 272; приказ Минсвязи России от 08.09.2003 № 112; приказ Госкомрыболовства России от 08.08.2003 № 271; приказ Минобороны России от 16.05.2003 № 170; постановление Минтруда России от 12.07.1999 № 22</t>
+          <t>Постановление Минтруда России от 12.07.1999 № 22</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>постановление Минтруда России от 12.07.1999 № 22; приказ Минтранса № 381</t>
+          <t>п. 1 постановления Минтруда России от 12.07.1999 № 22</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>Приказы Минтранса России от 04.05.2026 № 190, от 14.04.2026 № 160, от 14.04.2026 № 159, от 10.11.2025 № 381, от 30.04.2025 № 145, от 30.04.2025 № 144, от 21.03.2025 № 97, от 17.03.2025 № 93, от 14.03.2025 № 89, от 04.03.2025 № 75, от 11.10.2021 № 339, от 16.10.2020 № 424, от 02.10.2020 № 404, от 16.10.2020 № 423, от 30.01.2004 № 10; приказы МЧС России от 24.04.2026 № 308, от 24.04.2026 № 307, от 28.02.2020 № 136, от 04.09.2013 № 585; приказ Минздрава России от 13.03.2025 № 115н; приказ Минобрнауки России от 08.04.2025 № 318; приказ Минпросвещения России от 04.04.2025 № 268; приказ Минфина России от 31.03.2025 № 39н; приказ Минтруда России от 13.03.2025 № 107н; приказ ГФС России от 17.08.2009 № 264; приказ ФСБ России от 07.04.2007 № 161; приказ Росгидромета от 30.12.2003 № 272; приказ Минсвязи России от 08.09.2003 № 112; приказ Госкомрыболовства России от 08.08.2003 № 271; приказ Минобороны России от 16.05.2003 № 170; постановление Минтруда России от 12.07.1999 № 22</t>
+          <t>Трудовой кодекс Российской Федерации</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>ст. 372 ТК РФ; отраслевые Особенности (учет мнения представительного органа)</t>
+          <t>ст. 372 ТК РФ (учет мнения выборного органа первичной профсоюзной организации при принятии ЛНА); отраслевые Особенности требуют учета мнения, не устанавливая отдельную форму документа</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">

--- a/presentations/Analiz_SUOT_podpisanty_skvoznaya.xlsx
+++ b/presentations/Analiz_SUOT_podpisanty_skvoznaya.xlsx
@@ -514,7 +514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L77"/>
+  <dimension ref="A1:L205"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.85546875" defaultRowHeight="12.75"/>
   <cols>
     <col width="10" customWidth="1" style="4" min="1" max="1"/>
@@ -2710,17 +2710,17 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>Приказ Минтранса России от 04.05.2026 № 190; приказ Минтранса России от 14.04.2026 № 160; приказ Минтранса России от 14.04.2026 № 159; приказ Минтранса России от 16.10.2020 № 423; приказ Минтранса России от 16.10.2020 № 424; приказ Минтранса России от 02.10.2020 № 404; приказ Минтранса России от 11.10.2021 № 339; приказ Минпросвещения России от 04.04.2025 № 268; приказ Минобрнауки России от 08.04.2025 № 318; приказ Минздрава России от 13.03.2025 № 115н; приказ МЧС России от 24.04.2026 № 307</t>
+          <t>Приказ Минтранса России от 04.05.2026 № 190 "Об утверждении Особенностей режима рабочего времени и времени отдыха работников метрополитена"</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>п. 1 Особенностей (приказы Минтранса № 190, № 160, № 159, № 423, № 424, № 404); п. 2 Особенностей (приказ Минтранса № 339); п. 2–3 Особенностей (приказ Минпросвещения № 268); п. 2–3 Особенностей (приказ Минобрнауки № 318); п. 1 Особенностей (приказ Минздрава № 115н); п. 7 Особенностей (приказ МЧС № 307) — порядок введения суммированного учета устанавливается ПВТР</t>
+          <t>п. 1 Особенностей</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>Правила внутреннего трудового распорядка (с особенностями режима рабочего времени и времени отдыха соответствующих категорий работников)</t>
+          <t>Правила внутреннего трудового распорядка (с особенностями режима рабочего времени и времени отдыха работников метрополитена)</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>Продолжительность рабочей недели / смены; время начала и окончания работы; перерывы; число смен; чередование рабочих и нерабочих дней; порядок суммированного учета; иные особенности режима по применимому отраслевому НПА</t>
+          <t>Продолжительность рабочей недели / смены; время начала и окончания работы; перерывы; число смен; чередование рабочих и нерабочих дней; иные особенности режима</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr">
@@ -2772,17 +2772,17 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>Приказ Минпросвещения России от 04.04.2025 № 268; приказ Минобрнауки России от 08.04.2025 № 318</t>
+          <t>Приказ Минтранса России от 04.05.2026 № 190 "Об утверждении Особенностей режима рабочего времени и времени отдыха работников метрополитена"</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>п. 3 Особенностей (приказ Минпросвещения № 268); п. 3 Особенностей (приказ Минобрнауки № 318)</t>
+          <t>п. 1–2 Особенностей</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>Правила внутреннего трудового распорядка (с особенностями режима рабочего времени и времени отдыха)</t>
+          <t>Графики работы и (или) графики сменности работников метрополитена</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ФИО (должности) работников; даты; время начала и окончания работы (смены); перерывы; выходные; срок, на который составлен график; составляются не менее чем на 1 месяц</t>
         </is>
       </c>
       <c r="H37" s="6" t="inlineStr">
         <is>
-          <t>Выборный орган первичной профсоюзной организации / иной представительный орган работников (учет мнения)</t>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
         </is>
       </c>
       <c r="I37" s="6" t="inlineStr">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
-          <t>Согласование</t>
+          <t>Утверждение</t>
         </is>
       </c>
       <c r="K37" s="6" t="inlineStr">
@@ -2834,17 +2834,17 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>Трудовой кодекс Российской Федерации</t>
+          <t>Приказ Минтранса России от 04.05.2026 № 190 "Об утверждении Особенностей режима рабочего времени и времени отдыха работников метрополитена"</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>ст. 22, 68 ТК РФ</t>
+          <t>п. 2 Особенностей</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>Правила внутреннего трудового распорядка (с особенностями режима рабочего времени и времени отдыха)</t>
+          <t>Графики работы и (или) графики сменности работников метрополитена</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
@@ -2864,7 +2864,7 @@
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>Работник</t>
+          <t>Выборный орган первичной профсоюзной организации / иной представительный орган работников</t>
         </is>
       </c>
       <c r="I38" s="6" t="inlineStr">
@@ -2874,7 +2874,7 @@
       </c>
       <c r="J38" s="6" t="inlineStr">
         <is>
-          <t>Ознакомление</t>
+          <t>Согласование</t>
         </is>
       </c>
       <c r="K38" s="6" t="inlineStr">
@@ -2896,17 +2896,17 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>Приказ Минтранса России от 11.10.2021 № 339; приказ Минпросвещения России от 04.04.2025 № 268; приказ Минобрнауки России от 08.04.2025 № 318; приказ МЧС России от 24.04.2026 № 307</t>
+          <t>Приказ Минтранса России от 04.05.2026 № 190 "Об утверждении Особенностей режима рабочего времени и времени отдыха работников метрополитена"</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>п. 2 Особенностей (приказ Минтранса № 339); п. 2 Особенностей (приказ Минпросвещения № 268); п. 2 Особенностей (приказ Минобрнауки № 318); п. 2 Особенностей (приказ МЧС № 307)</t>
+          <t>п. 2 Особенностей</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>Коллективный договор (положения о режиме рабочего времени и времени отдыха)</t>
+          <t>Лист ознакомления (отметки о доведении) графиков работы / графиков сменности до сведения работников</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
@@ -2916,17 +2916,17 @@
       </c>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>УСЛОВНО</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>Продолжительность рабочей недели; ненормированный рабочий день; продолжительность смены; перерывы; сменность; учетный период; компенсации неудобного режима; иные условия режима труда и отдыха</t>
+          <t>ФИО работника; дата ознакомления; подпись; реквизиты графика; доведение не позднее чем за 1 месяц до введения в действие</t>
         </is>
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
-          <t>Стороны коллективного договора (представители работодателя и работников)</t>
+          <t>Работник</t>
         </is>
       </c>
       <c r="I39" s="6" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
-          <t>Утверждение</t>
+          <t>Ознакомление</t>
         </is>
       </c>
       <c r="K39" s="6" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>Приказ Минтранса России от 04.05.2026 № 190; приказ Минтранса России от 14.04.2026 № 160; приказ Минтранса России от 14.04.2026 № 159; приказ Минтранса России от 16.10.2020 № 423; приказ Минтранса России от 16.10.2020 № 424; приказ Минтранса России от 02.10.2020 № 404; приказ Минтранса России от 11.10.2021 № 339; приказ Минтранса России от 10.11.2025 № 381; приказ МЧС России от 24.04.2026 № 307; приказ МЧС России от 24.04.2026 № 308; приказ Минпросвещения России от 04.04.2025 № 268; приказ Минздрава России от 13.03.2025 № 115н</t>
+          <t>Приказ Минтранса России от 04.05.2026 № 190 "Об утверждении Особенностей режима рабочего времени и времени отдыха работников метрополитена"</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>п. 1–2 Особенностей (приказы Минтранса № 190, № 160, № 159, № 423, № 424, № 404); п. 2, 11 Особенностей (приказ Минтранса № 339); п. 3, 59 Особенностей (приказ Минтранса № 381); п. 1 Особенностей (приказ МЧС № 307); п. 1 Особенностей (приказ МЧС № 308); п. 4, 20 Особенностей (приказ Минпросвещения № 268); п. 1 Особенностей (приказ Минздрава № 115н)</t>
+          <t>п. 2 Особенностей</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>Графики работы и (или) графики сменности</t>
+          <t>Измененные графики работы / графики сменности и уведомление работников об изменении в течение учетного периода</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
@@ -2978,12 +2978,12 @@
       </c>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>УСЛОВНО</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>Фамилии (должности) работников; даты; время начала и окончания работы (смены); перерывы; выходные; учетный период; срок, на который составлен график (как правило, не менее 1 месяца)</t>
+          <t>Изменения режима; дата введения; доведение не позднее чем за 3 дня до введения</t>
         </is>
       </c>
       <c r="H40" s="6" t="inlineStr">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="J40" s="6" t="inlineStr">
         <is>
-          <t>Утверждение</t>
+          <t>Уведомление</t>
         </is>
       </c>
       <c r="K40" s="6" t="inlineStr">
@@ -3020,17 +3020,17 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>Приказ Минтранса России от 04.05.2026 № 190; приказ Минтранса России от 11.10.2021 № 339; приказ Минтранса России от 10.11.2025 № 381; приказ Минздрава России от 13.03.2025 № 115н</t>
+          <t>Приказ Минтранса России от 04.05.2026 № 190 "Об утверждении Особенностей режима рабочего времени и времени отдыха работников метрополитена"</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>п. 2 Особенностей (приказ Минтранса № 190); п. 2 Особенностей (приказ Минтранса № 339); п. 59 Особенностей (приказ Минтранса № 381); п. 1 Особенностей (приказ Минздрава № 115н)</t>
+          <t>п. 2 Особенностей</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>Графики работы и (или) графики сменности</t>
+          <t>Измененные графики работы / графики сменности</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
@@ -3040,7 +3040,7 @@
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>УСЛОВНО</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="H41" s="6" t="inlineStr">
         <is>
-          <t>Представительный орган работников / выборный орган первичной профсоюзной организации (учет мнения)</t>
+          <t>Работник</t>
         </is>
       </c>
       <c r="I41" s="6" t="inlineStr">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
-          <t>Согласование</t>
+          <t>Ознакомление</t>
         </is>
       </c>
       <c r="K41" s="6" t="inlineStr">
@@ -3082,17 +3082,17 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>Приказ Минтранса России от 04.05.2026 № 190; приказ Минтранса России от 11.10.2021 № 339; приказ Минтранса России от 10.11.2025 № 381</t>
+          <t>Приказ МЧС России от 24.04.2026 № 308 "Об утверждении Особенностей режима служебного времени и времени отдыха сотрудников федеральной противопожарной службы Государственной противопожарной службы при сменной работе"</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>п. 2 Особенностей (приказ Минтранса № 190); п. 2 Особенностей (приказ Минтранса № 339); п. 59 Особенностей (приказ Минтранса № 381); ст. 103 ТК РФ</t>
+          <t>п. 1–3 Особенностей</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>Лист ознакомления (отметки о доведении) графиков работы / графиков сменности до сведения работников</t>
+          <t>График сменности сотрудников федеральной противопожарной службы</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>ФИО работника; дата ознакомления; подпись; реквизиты графика; срок доведения (как правило, не позднее чем за 1 месяц до введения в действие)</t>
+          <t>ФИО (должности) работников; даты; время начала и окончания работы (смены); перерывы; выходные; срок, на который составлен график; учетный период (полугодие или год); продолжительность смены</t>
         </is>
       </c>
       <c r="H42" s="6" t="inlineStr">
         <is>
-          <t>Работник</t>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
         </is>
       </c>
       <c r="I42" s="6" t="inlineStr">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="J42" s="6" t="inlineStr">
         <is>
-          <t>Ознакомление</t>
+          <t>Утверждение</t>
         </is>
       </c>
       <c r="K42" s="6" t="inlineStr">
@@ -3144,17 +3144,17 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>Приказ Минтранса России от 04.05.2026 № 190; приказ Минтранса России от 11.10.2021 № 339; приказ Минтранса России от 10.11.2025 № 381</t>
+          <t>Приказ МЧС России от 24.04.2026 № 308 "Об утверждении Особенностей режима служебного времени и времени отдыха сотрудников федеральной противопожарной службы Государственной противопожарной службы при сменной работе"</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>п. 2 Особенностей (приказ Минтранса № 190); п. 2 Особенностей (приказ Минтранса № 339); п. 59 Особенностей (приказ Минтранса № 381)</t>
+          <t>положения Особенностей</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>Измененные графики работы / графики сменности (при изменении в течение учетного периода) и уведомление работников</t>
+          <t>Распорядок дня / локальный акт о режиме служебного времени при сменной работе сотрудников</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>Изменения режима; дата введения; срок уведомления работников (в т.ч. не позднее чем за 3 дня — по отдельным отраслевым нормам)</t>
+          <t>Режим служебного времени; структура смены; перерывы</t>
         </is>
       </c>
       <c r="H43" s="6" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
-          <t>Уведомление</t>
+          <t>Утверждение</t>
         </is>
       </c>
       <c r="K43" s="6" t="inlineStr">
@@ -3206,17 +3206,17 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>Приказ Минтранса России от 14.04.2026 № 160; приказ Минтранса России от 14.04.2026 № 159; приказ Минтранса России от 16.10.2020 № 424; приказ Минтранса России от 02.10.2020 № 404; приказ Минтранса России от 11.10.2021 № 339; приказ Минтранса России от 10.11.2025 № 381; приказ Минздрава России от 13.03.2025 № 115н; приказ Минпросвещения России от 04.04.2025 № 268; приказ МЧС России от 24.04.2026 № 307</t>
+          <t>Приказ МЧС России от 24.04.2026 № 307 "Об утверждении Особенностей режима рабочего времени и времени отдыха лиц, не имеющих специальных или воинских званий, федеральной противопожарной службы Государственной противопожарной службы при сменной работе"</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>п. 3 Особенностей (приказ Минтранса № 160); п. 3 Особенностей (приказ Минтранса № 159); п. 3 Особенностей (приказ Минтранса № 424); п. 3 Особенностей (приказ Минтранса № 404); п. 3, 20 Особенностей (приказ Минтранса № 339); п. 6 Особенностей (приказ Минтранса № 381); п. 1 Особенностей (приказ Минздрава № 115н); п. 35 Особенностей (приказ Минпросвещения № 268); п. 7 Особенностей (приказ МЧС № 307); ст. 104 ТК РФ</t>
+          <t>п. 1 Особенностей</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>Приказ (локальный нормативный акт) о введении суммированного учета рабочего времени</t>
+          <t>График сменности работников федеральной противопожарной службы (без специальных или воинских званий)</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
@@ -3226,12 +3226,12 @@
       </c>
       <c r="F44" s="6" t="inlineStr">
         <is>
-          <t>УСЛОВНО</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>Категории работников; учетный период; порядок учета; основание введения; дата введения</t>
+          <t>ФИО (должности) работников; даты; время начала и окончания работы (смены); перерывы; выходные; срок, на который составлен график; продолжительность смены (как правило, исходя из 24 часов)</t>
         </is>
       </c>
       <c r="H44" s="6" t="inlineStr">
@@ -3268,17 +3268,17 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>Приказ Минтранса России от 14.04.2026 № 160; приказ Минтранса России от 10.11.2025 № 381</t>
+          <t>Приказ МЧС России от 24.04.2026 № 307 "Об утверждении Особенностей режима рабочего времени и времени отдыха лиц, не имеющих специальных или воинских званий, федеральной противопожарной службы Государственной противопожарной службы при сменной работе"</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>п. 3 Особенностей (приказ Минтранса № 160); п. 6 Особенностей (приказ Минтранса № 381)</t>
+          <t>п. 2 Особенностей</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>Приказ (локальный нормативный акт) об увеличении учетного периода суммированного учета рабочего времени</t>
+          <t>Распорядок дня при несении дежурства</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
@@ -3288,17 +3288,17 @@
       </c>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>УСЛОВНО</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>Новая продолжительность учетного периода; категории работников; основание; учет мнения представительного органа работников</t>
+          <t>Режим работы при несении дежурства; структура рабочего дня смены</t>
         </is>
       </c>
       <c r="H45" s="6" t="inlineStr">
         <is>
-          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+          <t>Руководитель подразделения федеральной противопожарной службы</t>
         </is>
       </c>
       <c r="I45" s="6" t="inlineStr">
@@ -3330,17 +3330,17 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>Приказ Минтранса России от 14.04.2026 № 160; приказ Минтранса России от 10.11.2025 № 381</t>
+          <t>Приказ МЧС России от 24.04.2026 № 307 "Об утверждении Особенностей режима рабочего времени и времени отдыха лиц, не имеющих специальных или воинских званий, федеральной противопожарной службы Государственной противопожарной службы при сменной работе"</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>п. 3 Особенностей (приказ Минтранса № 160); п. 6 Особенностей (приказ Минтранса № 381)</t>
+          <t>п. 2 Особенностей</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>Приказ (локальный нормативный акт) об увеличении учетного периода суммированного учета рабочего времени</t>
+          <t>Коллективный договор / соглашение / локальный нормативный акт / трудовой договор (закрепление режима работы при несении дежурства)</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
@@ -3355,12 +3355,12 @@
       </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Закрепление распорядка дня и режима дежурства</t>
         </is>
       </c>
       <c r="H46" s="6" t="inlineStr">
         <is>
-          <t>Выборный орган первичной профсоюзной организации / представительный орган работников (учет мнения)</t>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
         </is>
       </c>
       <c r="I46" s="6" t="inlineStr">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="J46" s="6" t="inlineStr">
         <is>
-          <t>Согласование</t>
+          <t>Утверждение</t>
         </is>
       </c>
       <c r="K46" s="6" t="inlineStr">
@@ -3392,17 +3392,17 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>Приказ Минтранса России от 14.04.2026 № 160; приказ Минтранса России от 14.04.2026 № 159; приказ Минтранса России от 16.10.2020 № 424; приказ Минпросвещения России от 04.04.2025 № 268; приказ Минтранса России от 10.11.2025 № 381</t>
+          <t>Приказ МЧС России от 24.04.2026 № 307 "Об утверждении Особенностей режима рабочего времени и времени отдыха лиц, не имеющих специальных или воинских званий, федеральной противопожарной службы Государственной противопожарной службы при сменной работе"</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>п. 5 Особенностей (приказ Минтранса № 160); п. 5 Особенностей (приказ Минтранса № 159); п. 5 Особенностей (приказ Минтранса № 424); п. 22–23 Особенностей (приказ Минпросвещения № 268); положения Особенностей о разделении полетной смены на части (приказ Минтранса № 381)</t>
+          <t>п. 7 Особенностей</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>Локальный нормативный акт о разделении рабочего дня (смены) на части</t>
+          <t>Правила внутреннего трудового распорядка (порядок введения суммированного учета рабочего времени)</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
@@ -3412,12 +3412,12 @@
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>УСЛОВНО</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>Категории работников; порядок разделения дня (смены); продолжительность частей и перерывов; компенсации неудобного режима (при наличии)</t>
+          <t>Порядок введения суммированного учета; учетный период (три месяца, полугодие или год)</t>
         </is>
       </c>
       <c r="H47" s="6" t="inlineStr">
@@ -3454,17 +3454,17 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>Приказ Минтранса России от 14.04.2026 № 160; приказ Минпросвещения России от 04.04.2025 № 268; приказ Минтранса России от 10.11.2025 № 381</t>
+          <t>Приказ Минтранса России от 14.04.2026 № 160 "Об утверждении Особенностей режима рабочего времени и времени отдыха водителей автомобилей"</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>п. 5 Особенностей (приказ Минтранса № 160); п. 23 Особенностей (приказ Минпросвещения № 268); положения Особенностей о разделении полетной смены на части (приказ Минтранса № 381)</t>
+          <t>п. 1 Особенностей</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>Локальный нормативный акт о разделении рабочего дня (смены) на части</t>
+          <t>Правила внутреннего трудового распорядка (с особенностями режима рабочего времени и времени отдыха водителей автомобилей)</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
@@ -3474,17 +3474,17 @@
       </c>
       <c r="F48" s="6" t="inlineStr">
         <is>
-          <t>УСЛОВНО</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Продолжительность рабочей недели / смены; время начала и окончания работы; перерывы; число смен; чередование рабочих и нерабочих дней; иные особенности режима</t>
         </is>
       </c>
       <c r="H48" s="6" t="inlineStr">
         <is>
-          <t>Выборный орган первичной профсоюзной организации / представительный орган работников (учет мнения)</t>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
         </is>
       </c>
       <c r="I48" s="6" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="J48" s="6" t="inlineStr">
         <is>
-          <t>Согласование</t>
+          <t>Утверждение</t>
         </is>
       </c>
       <c r="K48" s="6" t="inlineStr">
@@ -3516,17 +3516,17 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>Приказ Минтранса России от 14.04.2026 № 160; приказ Минтранса России от 11.10.2021 № 339; приказ Минпросвещения России от 04.04.2025 № 268; приказ Минтранса России от 10.11.2025 № 381</t>
+          <t>Приказ Минтранса России от 14.04.2026 № 160 "Об утверждении Особенностей режима рабочего времени и времени отдыха водителей автомобилей"</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>п. 5 Особенностей (приказ Минтранса № 160); п. 8 Особенностей (приказ Минтранса № 339); п. 2, 11, 16 Особенностей (приказ Минпросвещения № 268); п. 7, 10 Особенностей (приказ Минтранса № 381)</t>
+          <t>п. 1 Особенностей</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>Письменное согласие работника на разделение рабочего дня (смены) на части / на дежурство / на дополнительные виды работ</t>
+          <t>Графики работы и (или) графики сменности водителей автомобилей</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
@@ -3536,17 +3536,17 @@
       </c>
       <c r="F49" s="6" t="inlineStr">
         <is>
-          <t>УСЛОВНО</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>ФИО работника; вид согласия; период; условия; дата; подпись работника</t>
+          <t>ФИО (должности) работников; даты; время начала и окончания работы (смены); перерывы; выходные; срок, на который составлен график</t>
         </is>
       </c>
       <c r="H49" s="6" t="inlineStr">
         <is>
-          <t>Работник</t>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
         </is>
       </c>
       <c r="I49" s="6" t="inlineStr">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="J49" s="6" t="inlineStr">
         <is>
-          <t>Подтверждение (?)</t>
+          <t>Утверждение</t>
         </is>
       </c>
       <c r="K49" s="6" t="inlineStr">
@@ -3578,37 +3578,37 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>Приказ Минтранса России от 10.11.2025 № 381; Трудовой кодекс Российской Федерации</t>
+          <t>Приказ Минтранса России от 14.04.2026 № 160 "Об утверждении Особенностей режима рабочего времени и времени отдыха водителей автомобилей"</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>п. 60 Особенностей (приказ Минтранса № 381); ст. 91 ТК РФ</t>
+          <t>п. 3 Особенностей</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>Табель учета рабочего времени</t>
+          <t>Приказ (локальный нормативный акт) о введении суммированного учета рабочего времени водителей</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>ДА (формы Т-12 / Т-13 либо иные применяемые работодателем)</t>
+          <t>НЕТ</t>
         </is>
       </c>
       <c r="F50" s="6" t="inlineStr">
         <is>
-          <t>ДА</t>
+          <t>УСЛОВНО</t>
         </is>
       </c>
       <c r="G50" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Категории водителей; учетный период (1 месяц); порядок учета; дата введения</t>
         </is>
       </c>
       <c r="H50" s="6" t="inlineStr">
         <is>
-          <t>Работодатель (руководитель организации / уполномоченное лицо); лицо, ведущее учет рабочего времени</t>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
         </is>
       </c>
       <c r="I50" s="6" t="inlineStr">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="J50" s="6" t="inlineStr">
         <is>
-          <t>Подтверждение (?)</t>
+          <t>Утверждение</t>
         </is>
       </c>
       <c r="K50" s="6" t="inlineStr">
@@ -3640,17 +3640,17 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>Приказ Минпросвещения России от 04.04.2025 № 268; приказ МЧС России от 24.04.2026 № 307; приказ Минтранса России от 14.04.2026 № 160; Трудовой кодекс Российской Федерации</t>
+          <t>Приказ Минтранса России от 14.04.2026 № 160 "Об утверждении Особенностей режима рабочего времени и времени отдыха водителей автомобилей"</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>п. 16 Особенностей (приказ Минпросвещения № 268); п. 2 Особенностей (приказ МЧС № 307); п. 12 Особенностей (приказ Минтранса № 160); ст. 57, 100 ТК РФ</t>
+          <t>п. 3 Особенностей</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>Трудовой договор (дополнительное соглашение) с условиями режима рабочего времени и времени отдыха</t>
+          <t>Приказ (локальный нормативный акт) об увеличении учетного периода суммированного учета рабочего времени водителей до 3 месяцев</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
@@ -3660,17 +3660,17 @@
       </c>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>ДА</t>
+          <t>УСЛОВНО</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>Режим рабочего времени; характер работы; дополнительные виды работ (содержание, срок, оплата — при наличии); иные условия, связанные с особым характером работы</t>
+          <t>Новая продолжительность учетного периода; категории водителей; основание</t>
         </is>
       </c>
       <c r="H51" s="6" t="inlineStr">
         <is>
-          <t>Работодатель (руководитель организации / уполномоченное лицо); работник</t>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
         </is>
       </c>
       <c r="I51" s="6" t="inlineStr">
@@ -3702,17 +3702,17 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>Приказ Минтранса России от 11.10.2021 № 339</t>
+          <t>Приказ Минтранса России от 14.04.2026 № 160 "Об утверждении Особенностей режима рабочего времени и времени отдыха водителей автомобилей"</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>п. 6 Особенностей (приказ Минтранса № 339)</t>
+          <t>п. 3 Особенностей</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>Перечень работ, на которых по условиям производства невозможно предоставление перерыва для отдыха и питания, и места для отдыха и приема пищи (в составе ПВТР / отдельным ЛНА)</t>
+          <t>Приказ (локальный нормативный акт) об увеличении учетного периода суммированного учета рабочего времени водителей до 3 месяцев</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>Перечень работ; места для отдыха и приема пищи; порядок обеспечения возможности отдыха и приема пищи в рабочее время</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H52" s="6" t="inlineStr">
         <is>
-          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+          <t>Выборный орган первичной профсоюзной организации / иной представительный орган работников</t>
         </is>
       </c>
       <c r="I52" s="6" t="inlineStr">
@@ -3742,7 +3742,7 @@
       </c>
       <c r="J52" s="6" t="inlineStr">
         <is>
-          <t>Утверждение</t>
+          <t>Согласование</t>
         </is>
       </c>
       <c r="K52" s="6" t="inlineStr">
@@ -3764,17 +3764,17 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>Приказ Минздрава России от 13.03.2025 № 115н</t>
+          <t>Приказ Минтранса России от 14.04.2026 № 160 "Об утверждении Особенностей режима рабочего времени и времени отдыха водителей автомобилей"</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>п. 1 Особенностей (приказ Минздрава № 115н)</t>
+          <t>п. 4 Особенностей</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>График работы (график дежурств на дому) медицинских работников</t>
+          <t>Локальный нормативный акт об увеличении продолжительности ежедневной работы (смены) водителей регулярных перевозок до 12 часов</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
@@ -3789,7 +3789,7 @@
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>ФИО медицинских работников; время начала и окончания дежурства на дому; период; учет суммированного учета рабочего времени</t>
+          <t>Категории водителей; условия увеличения смены до 12 часов</t>
         </is>
       </c>
       <c r="H53" s="6" t="inlineStr">
@@ -3826,17 +3826,17 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>Приказ Минздрава России от 13.03.2025 № 115н</t>
+          <t>Приказ Минтранса России от 14.04.2026 № 160 "Об утверждении Особенностей режима рабочего времени и времени отдыха водителей автомобилей"</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>п. 1 Особенностей (приказ Минздрава № 115н)</t>
+          <t>п. 4 Особенностей</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>График работы (график дежурств на дому) медицинских работников</t>
+          <t>Локальный нормативный акт об увеличении продолжительности ежедневной работы (смены) водителей регулярных перевозок до 12 часов</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="H54" s="6" t="inlineStr">
         <is>
-          <t>Представительный орган работников (учет мнения)</t>
+          <t>Выборный орган первичной профсоюзной организации / иной представительный орган работников</t>
         </is>
       </c>
       <c r="I54" s="6" t="inlineStr">
@@ -3888,17 +3888,17 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>Приказ Минздрава России от 13.03.2025 № 115н</t>
+          <t>Приказ Минтранса России от 14.04.2026 № 160 "Об утверждении Особенностей режима рабочего времени и времени отдыха водителей автомобилей"</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>п. 2 Особенностей (приказ Минздрава № 115н)</t>
+          <t>п. 5 Особенностей</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>Локальный нормативный акт о порядке учета времени следования медицинского работника при дежурстве на дому</t>
+          <t>Локальный нормативный акт о разделении рабочего дня (смены) водителя на части</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
@@ -3913,7 +3913,7 @@
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>Порядок фиксации времени следования от дома до места оказания помощи и обратно; единицы учета; ответственные; формы учета</t>
+          <t>Порядок разделения дня (смены); продолжительность частей и перерывов; места перерывов</t>
         </is>
       </c>
       <c r="H55" s="6" t="inlineStr">
@@ -3950,17 +3950,17 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>Приказ Минздрава России от 13.03.2025 № 115н</t>
+          <t>Приказ Минтранса России от 14.04.2026 № 160 "Об утверждении Особенностей режима рабочего времени и времени отдыха водителей автомобилей"</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>п. 2 Особенностей (приказ Минздрава № 115н)</t>
+          <t>п. 5 Особенностей</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>Локальный нормативный акт о порядке учета времени следования медицинского работника при дежурстве на дому</t>
+          <t>Локальный нормативный акт о разделении рабочего дня (смены) водителя на части</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="H56" s="6" t="inlineStr">
         <is>
-          <t>Представительный орган работников (согласование)</t>
+          <t>Выборный орган первичной профсоюзной организации / иной представительный орган работников</t>
         </is>
       </c>
       <c r="I56" s="6" t="inlineStr">
@@ -4012,17 +4012,17 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>Приказ Минздрава России от 13.03.2025 № 115н</t>
+          <t>Приказ Минтранса России от 14.04.2026 № 160 "Об утверждении Особенностей режима рабочего времени и времени отдыха водителей автомобилей"</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>п. 3 Особенностей (приказ Минздрава № 115н)</t>
+          <t>п. 5 Особенностей</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>Документы (журналы / формы) учета времени дежурства на дому, времени оказания медицинской помощи и времени следования</t>
+          <t>Письменное согласие водителя на разделение рабочего дня (смены) на части</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
@@ -4032,17 +4032,17 @@
       </c>
       <c r="F57" s="6" t="inlineStr">
         <is>
-          <t>ДА (при дежурствах на дому)</t>
+          <t>УСЛОВНО</t>
         </is>
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>Время пребывания дома в режиме ожидания вызова; время оказания помощи; время следования; ФИО работника; даты</t>
+          <t>ФИО водителя; период; условия разделения смены; дата; подпись</t>
         </is>
       </c>
       <c r="H57" s="6" t="inlineStr">
         <is>
-          <t>Работодатель / лицо, ведущее учет рабочего времени</t>
+          <t>Работник</t>
         </is>
       </c>
       <c r="I57" s="6" t="inlineStr">
@@ -4074,17 +4074,17 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>Приказ Минпросвещения России от 04.04.2025 № 268; приказ Минобрнауки России от 08.04.2025 № 318</t>
+          <t>Приказ Минтранса России от 14.04.2026 № 160 "Об утверждении Особенностей режима рабочего времени и времени отдыха водителей автомобилей"</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>п. 13 Особенностей (приказ Минпросвещения № 268); п. 2 Особенностей (приказ Минобрнауки № 318) — режим устанавливается в т.ч. расписанием занятий</t>
+          <t>п. 12 Особенностей</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>Расписание учебных занятий</t>
+          <t>Локальный нормативный акт о составе и продолжительности иных видов времени, включаемых в рабочее время водителя</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
@@ -4094,12 +4094,12 @@
       </c>
       <c r="F58" s="6" t="inlineStr">
         <is>
-          <t>ДА (для педагогических работников, ведущих преподавательскую работу)</t>
+          <t>УСЛОВНО</t>
         </is>
       </c>
       <c r="G58" s="6" t="inlineStr">
         <is>
-          <t>Учебные занятия; продолжительность; перерывы (перемены); закрепление педагогических работников; дни недели</t>
+          <t>Виды времени (подготовка, медосмотр, охрана груза и др.); продолжительность</t>
         </is>
       </c>
       <c r="H58" s="6" t="inlineStr">
@@ -4136,17 +4136,17 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>Приказ Минпросвещения России от 04.04.2025 № 268</t>
+          <t>Приказ Минтранса России от 14.04.2026 № 160 "Об утверждении Особенностей режима рабочего времени и времени отдыха водителей автомобилей"</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>п. 13 Особенностей (приказ Минпросвещения № 268)</t>
+          <t>п. 12 Особенностей</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>Устав и (или) локальный нормативный акт о продолжительности занятий и перерывов (перемен) между ними</t>
+          <t>Локальный нормативный акт о составе и продолжительности иных видов времени, включаемых в рабочее время водителя</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
@@ -4156,17 +4156,17 @@
       </c>
       <c r="F59" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>УСЛОВНО</t>
         </is>
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>Продолжительность занятий; перерывы (перемены); возможность спаренных занятий; учет санитарных правил</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H59" s="6" t="inlineStr">
         <is>
-          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+          <t>Выборный орган первичной профсоюзной организации / иной представительный орган работников</t>
         </is>
       </c>
       <c r="I59" s="6" t="inlineStr">
@@ -4176,7 +4176,7 @@
       </c>
       <c r="J59" s="6" t="inlineStr">
         <is>
-          <t>Утверждение</t>
+          <t>Согласование</t>
         </is>
       </c>
       <c r="K59" s="6" t="inlineStr">
@@ -4198,17 +4198,17 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>Приказ Минпросвещения России от 04.04.2025 № 268</t>
+          <t>Приказ Минтранса России от 14.04.2026 № 160 "Об утверждении Особенностей режима рабочего времени и времени отдыха водителей автомобилей"</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>п. 14–15 Особенностей (приказ Минпросвещения № 268)</t>
+          <t>п. 15 Особенностей</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>График дежурств педагогических работников в организации</t>
+          <t>Правила внутреннего трудового распорядка (время предоставления и продолжительность перерыва для отдыха и питания водителей)</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="F60" s="6" t="inlineStr">
         <is>
-          <t>УСЛОВНО</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G60" s="6" t="inlineStr">
         <is>
-          <t>ФИО работников; время дежурства (не ранее чем за 20 минут до начала и не позднее 20 минут после окончания занятий); даты</t>
+          <t>Время предоставления перерыва; продолжительность (в т.ч. при смене более 8 часов — два перерыва)</t>
         </is>
       </c>
       <c r="H60" s="6" t="inlineStr">
@@ -4260,17 +4260,17 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>Приказ Минпросвещения России от 04.04.2025 № 268</t>
+          <t>Приказ Минтранса России от 14.04.2026 № 160 "Об утверждении Особенностей режима рабочего времени и времени отдыха водителей автомобилей"</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>п. 14, 16 Особенностей (приказ Минпросвещения № 268)</t>
+          <t>п. 18 Особенностей</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>Планы и графики организации (методические советы, родительские собрания, мероприятия), утверждаемые локальными актами</t>
+          <t>Локальный нормативный акт / коллективный договор о размере дополнительного вознаграждения за время нахождения в экипаже без управления автомобилем</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
@@ -4285,7 +4285,7 @@
       </c>
       <c r="G61" s="6" t="inlineStr">
         <is>
-          <t>Виды мероприятий; сроки; участники; связь с должностными обязанностями педагогических работников</t>
+          <t>Размер дополнительного вознаграждения; порядок выплаты</t>
         </is>
       </c>
       <c r="H61" s="6" t="inlineStr">
@@ -4322,17 +4322,17 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>Приказ Минпросвещения России от 04.04.2025 № 268</t>
+          <t>Приказ Минтранса России от 14.04.2026 № 160 "Об утверждении Особенностей режима рабочего времени и времени отдыха водителей автомобилей"</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>п. 34–35 Особенностей (приказ Минпросвещения № 268)</t>
+          <t>п. 18 Особенностей</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>Локальные нормативные акты и графики работы в каникулярное время</t>
+          <t>Локальный нормативный акт / коллективный договор о размере дополнительного вознаграждения за время нахождения в экипаже без управления автомобилем</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
@@ -4347,12 +4347,12 @@
       </c>
       <c r="G62" s="6" t="inlineStr">
         <is>
-          <t>Характер и особенности работы в каникулярное время; режим; категории работников; при необходимости — суммированный учет</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H62" s="6" t="inlineStr">
         <is>
-          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+          <t>Выборный орган первичной профсоюзной организации / иной представительный орган работников</t>
         </is>
       </c>
       <c r="I62" s="6" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="J62" s="6" t="inlineStr">
         <is>
-          <t>Утверждение</t>
+          <t>Согласование</t>
         </is>
       </c>
       <c r="K62" s="6" t="inlineStr">
@@ -4384,17 +4384,17 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>Приказ Минпросвещения России от 04.04.2025 № 268</t>
+          <t>Приказ Минтранса России от 14.04.2026 № 159 "Об утверждении Особенностей режима рабочего времени и времени отдыха водителей трамвая и троллейбуса"</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>п. 22 Особенностей (приказ Минпросвещения № 268)</t>
+          <t>п. 1 Особенностей</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>Письменное заявление педагогического работника о допущении длительных перерывов между занятиями при составлении расписания</t>
+          <t>Правила внутреннего трудового распорядка (с особенностями режима рабочего времени и времени отдыха водителей трамвая и троллейбуса)</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
@@ -4404,17 +4404,17 @@
       </c>
       <c r="F63" s="6" t="inlineStr">
         <is>
-          <t>УСЛОВНО</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>Просьба о длительных перерывах; основания; период; подпись работника</t>
+          <t>Продолжительность рабочей недели / смены; время начала и окончания работы; перерывы; число смен; чередование рабочих и нерабочих дней; иные особенности режима</t>
         </is>
       </c>
       <c r="H63" s="6" t="inlineStr">
         <is>
-          <t>Педагогический работник, ведущий преподавательскую работу</t>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
         </is>
       </c>
       <c r="I63" s="6" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="J63" s="6" t="inlineStr">
         <is>
-          <t>Заявление</t>
+          <t>Утверждение</t>
         </is>
       </c>
       <c r="K63" s="6" t="inlineStr">
@@ -4446,17 +4446,17 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>Приказ Минтранса России от 11.10.2021 № 339</t>
+          <t>Приказ Минтранса России от 14.04.2026 № 159 "Об утверждении Особенностей режима рабочего времени и времени отдыха водителей трамвая и троллейбуса"</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>п. 8 Особенностей (приказ Минтранса № 339)</t>
+          <t>п. 1 Особенностей</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>Положение о дежурстве (на дому / в специально оборудованной комнате / в купе вагона)</t>
+          <t>Графики работы и (или) графики сменности водителей трамвая и троллейбуса</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="F64" s="6" t="inlineStr">
         <is>
-          <t>УСЛОВНО</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G64" s="6" t="inlineStr">
         <is>
-          <t>Порядок дежурства; категории работников; учет рабочего времени; условия вызова на работу</t>
+          <t>ФИО (должности) работников; даты; время начала и окончания работы (смены); перерывы; выходные; срок, на который составлен график</t>
         </is>
       </c>
       <c r="H64" s="6" t="inlineStr">
@@ -4508,17 +4508,17 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>Приказ Минтранса России от 11.10.2021 № 339</t>
+          <t>Приказ Минтранса России от 14.04.2026 № 159 "Об утверждении Особенностей режима рабочего времени и времени отдыха водителей трамвая и троллейбуса"</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>п. 8 Особенностей (приказ Минтранса № 339)</t>
+          <t>п. 3 Особенностей</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>Положение о дежурстве (на дому / в специально оборудованной комнате / в купе вагона)</t>
+          <t>Локальный нормативный акт о продолжительности времени медицинских осмотров и подготовительно-заключительного времени водителей трамвая и троллейбуса</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
@@ -4528,17 +4528,17 @@
       </c>
       <c r="F65" s="6" t="inlineStr">
         <is>
-          <t>УСЛОВНО</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Продолжительность медосмотров; продолжительность подготовительно-заключительного времени</t>
         </is>
       </c>
       <c r="H65" s="6" t="inlineStr">
         <is>
-          <t>Представительный орган работников (учет мнения)</t>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
         </is>
       </c>
       <c r="I65" s="6" t="inlineStr">
@@ -4548,7 +4548,7 @@
       </c>
       <c r="J65" s="6" t="inlineStr">
         <is>
-          <t>Согласование</t>
+          <t>Утверждение</t>
         </is>
       </c>
       <c r="K65" s="6" t="inlineStr">
@@ -4570,17 +4570,17 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>Приказ Минтранса России от 11.10.2021 № 339</t>
+          <t>Приказ Минтранса России от 14.04.2026 № 159 "Об утверждении Особенностей режима рабочего времени и времени отдыха водителей трамвая и троллейбуса"</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>п. 5 Особенностей (приказ Минтранса № 339)</t>
+          <t>п. 3 Особенностей</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>Локальный нормативный акт — перечень железнодорожных линий (участков инфраструктуры), ремонт и ТО которых организованы преимущественно в ночное время</t>
+          <t>Локальный нормативный акт о продолжительности времени медицинских осмотров и подготовительно-заключительного времени водителей трамвая и троллейбуса</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
@@ -4590,17 +4590,17 @@
       </c>
       <c r="F66" s="6" t="inlineStr">
         <is>
-          <t>УСЛОВНО</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G66" s="6" t="inlineStr">
         <is>
-          <t>Перечень линий (участков); обоснование ночного режима работ</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H66" s="6" t="inlineStr">
         <is>
-          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+          <t>Выборный орган первичной профсоюзной организации / иной представительный орган работников</t>
         </is>
       </c>
       <c r="I66" s="6" t="inlineStr">
@@ -4610,7 +4610,7 @@
       </c>
       <c r="J66" s="6" t="inlineStr">
         <is>
-          <t>Утверждение</t>
+          <t>Согласование</t>
         </is>
       </c>
       <c r="K66" s="6" t="inlineStr">
@@ -4632,17 +4632,17 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>Приказ Минтранса России от 11.10.2021 № 339</t>
+          <t>Приказ Минтранса России от 14.04.2026 № 159 "Об утверждении Особенностей режима рабочего времени и времени отдыха водителей трамвая и троллейбуса"</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>п. 22–23 Особенностей (приказ Минтранса № 339)</t>
+          <t>п. 2 Особенностей</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>Графики сменности / графики дежурств работников поездных бригад пассажирских поездов (на каждый поезд)</t>
+          <t>Локальный нормативный акт о перечне простейших неисправностей подвижного состава, устраняемых водителем на линии</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="G67" s="6" t="inlineStr">
         <is>
-          <t>Состав бригады; продолжительность смен / дежурств в рейсе; местные условия; учет мнения представительного органа</t>
+          <t>Перечень простейших неисправностей; порядок учета времени работ по устранению</t>
         </is>
       </c>
       <c r="H67" s="6" t="inlineStr">
@@ -4694,17 +4694,17 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>Приказ Минтранса России от 11.10.2021 № 339</t>
+          <t>Приказ Минтранса России от 14.04.2026 № 159 "Об утверждении Особенностей режима рабочего времени и времени отдыха водителей трамвая и троллейбуса"</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>п. 10, 12–13 Особенностей (приказ Минтранса № 339)</t>
+          <t>п. 5 Особенностей</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>Наряд / вызов работников (в т.ч. локомотивных бригад) и порядок вызова (в ПВТР / отдельном порядке)</t>
+          <t>Приказ (локальный нормативный акт) о введении суммированного учета рабочего времени водителей трамвая и троллейбуса</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
@@ -4719,12 +4719,12 @@
       </c>
       <c r="G68" s="6" t="inlineStr">
         <is>
-          <t>Время явки; место явки; работник; основание вызова; порядок вызова другого работника</t>
+          <t>Учетный период (1 месяц); категории водителей; порядок учета</t>
         </is>
       </c>
       <c r="H68" s="6" t="inlineStr">
         <is>
-          <t>Работодатель / уполномоченное должностное лицо</t>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
         </is>
       </c>
       <c r="I68" s="6" t="inlineStr">
@@ -4756,17 +4756,17 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>Приказ Минтранса России от 10.11.2025 № 381</t>
+          <t>Приказ Минтранса России от 14.04.2026 № 159 "Об утверждении Особенностей режима рабочего времени и времени отдыха водителей трамвая и троллейбуса"</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>п. 3 Особенностей (приказ Минтранса № 381)</t>
+          <t>п. 5 Особенностей</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>Руководство по производству полетов (РПП) в части режима рабочего времени и времени отдыха авиационного персонала</t>
+          <t>Приказ (локальный нормативный акт) об увеличении учетного периода суммированного учета до 3 месяцев</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="G69" s="6" t="inlineStr">
         <is>
-          <t>Нормы рабочего / полетного времени и отдыха; порядок планирования; контроль соблюдения режимов</t>
+          <t>Новая продолжительность учетного периода; основание</t>
         </is>
       </c>
       <c r="H69" s="6" t="inlineStr">
@@ -4818,17 +4818,17 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>Приказ Минтранса России от 10.11.2025 № 381</t>
+          <t>Приказ Минтранса России от 14.04.2026 № 159 "Об утверждении Особенностей режима рабочего времени и времени отдыха водителей трамвая и троллейбуса"</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>п. 3, 59 Особенностей (приказ Минтранса № 381)</t>
+          <t>п. 5 Особенностей</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>Графики работы членов экипажей / расписания движения (в части планирования рабочего и полетного времени)</t>
+          <t>Приказ (локальный нормативный акт) об увеличении учетного периода суммированного учета до 3 месяцев</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
@@ -4843,12 +4843,12 @@
       </c>
       <c r="G70" s="6" t="inlineStr">
         <is>
-          <t>Планируемое рабочее и полетное время; время отдыха; состав экипажа; рейсы / задания</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H70" s="6" t="inlineStr">
         <is>
-          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+          <t>Выборный орган первичной профсоюзной организации / иной представительный орган работников</t>
         </is>
       </c>
       <c r="I70" s="6" t="inlineStr">
@@ -4858,7 +4858,7 @@
       </c>
       <c r="J70" s="6" t="inlineStr">
         <is>
-          <t>Утверждение</t>
+          <t>Согласование</t>
         </is>
       </c>
       <c r="K70" s="6" t="inlineStr">
@@ -4880,17 +4880,17 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>Приказ Минтранса России от 10.11.2025 № 381</t>
+          <t>Приказ Минтранса России от 14.04.2026 № 159 "Об утверждении Особенностей режима рабочего времени и времени отдыха водителей трамвая и троллейбуса"</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>п. 59–60 Особенностей (приказ Минтранса № 381)</t>
+          <t>п. 6 Особенностей</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>Документы (система) учета запланированного и фактического рабочего времени, полетного времени и времени отдыха членов экипажей</t>
+          <t>Локальный нормативный акт об увеличении продолжительности ежедневной работы (смены) водителя до 12 часов</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
@@ -4900,17 +4900,17 @@
       </c>
       <c r="F71" s="6" t="inlineStr">
         <is>
-          <t>ДА (для авиационного персонала по приказу № 381)</t>
+          <t>УСЛОВНО</t>
         </is>
       </c>
       <c r="G71" s="6" t="inlineStr">
         <is>
-          <t>Запланированные и фактические показатели рабочего / полетного времени и отдыха; отклонения; период учета</t>
+          <t>Условия увеличения смены до 12 часов</t>
         </is>
       </c>
       <c r="H71" s="6" t="inlineStr">
         <is>
-          <t>Работодатель / лицо, обеспечивающее учет</t>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
         </is>
       </c>
       <c r="I71" s="6" t="inlineStr">
@@ -4920,7 +4920,7 @@
       </c>
       <c r="J71" s="6" t="inlineStr">
         <is>
-          <t>Подтверждение (?)</t>
+          <t>Утверждение</t>
         </is>
       </c>
       <c r="K71" s="6" t="inlineStr">
@@ -4942,17 +4942,17 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>Приказ Минтранса России от 30.04.2025 № 145; приказ Минтранса России от 30.04.2025 № 144; приказ Минтранса России от 04.03.2025 № 75; приказ ФСБ России от 07.04.2007 № 161; приказ Минобороны России от 16.05.2003 № 170</t>
+          <t>Приказ Минтранса России от 14.04.2026 № 159 "Об утверждении Особенностей режима рабочего времени и времени отдыха водителей трамвая и троллейбуса"</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>положения Особенностей / Положений о режиме рабочего времени и времени отдыха членов экипажей (вахтенное расписание / графики вахт) — приказы Минтранса № 145, № 144, № 75; приказ ФСБ № 161; приказ Минобороны № 170</t>
+          <t>п. 6 Особенностей</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>Вахтенное расписание / графики вахт членов экипажей судов (морских, внутреннего водного транспорта, обеспечения и др.)</t>
+          <t>Локальный нормативный акт об увеличении продолжительности ежедневной работы (смены) водителя до 12 часов</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
@@ -4967,12 +4967,12 @@
       </c>
       <c r="G72" s="6" t="inlineStr">
         <is>
-          <t>Состав вахт; продолжительность; чередование вахт и отдыха; категории работников плавсостава / лоцманов</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H72" s="6" t="inlineStr">
         <is>
-          <t>Работодатель (капитан / руководитель организации / уполномоченное лицо)</t>
+          <t>Выборный орган первичной профсоюзной организации / иной представительный орган работников</t>
         </is>
       </c>
       <c r="I72" s="6" t="inlineStr">
@@ -4982,7 +4982,7 @@
       </c>
       <c r="J72" s="6" t="inlineStr">
         <is>
-          <t>Утверждение</t>
+          <t>Согласование</t>
         </is>
       </c>
       <c r="K72" s="6" t="inlineStr">
@@ -5004,17 +5004,17 @@
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>Приказ Минтранса России от 14.04.2026 № 160; приказ Минтранса России от 16.10.2020 № 424</t>
+          <t>Приказ Минтранса России от 14.04.2026 № 159 "Об утверждении Особенностей режима рабочего времени и времени отдыха водителей трамвая и троллейбуса"</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>п. 12 Особенностей (приказ Минтранса № 160); п. 15 Особенностей (приказ Минтранса № 424)</t>
+          <t>п. 7 Особенностей</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>Локальный нормативный акт о составе и продолжительности иных видов времени, включаемых в рабочее время водителя</t>
+          <t>Локальный нормативный акт о разделении рабочего дня (смены) водителя на части</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
@@ -5029,7 +5029,7 @@
       </c>
       <c r="G73" s="6" t="inlineStr">
         <is>
-          <t>Виды времени (подготовка, медосмотр, охрана груза и др.); продолжительность; порядок установления с учетом мнения представительного органа</t>
+          <t>Порядок разделения; перерывы между частями; места перерывов</t>
         </is>
       </c>
       <c r="H73" s="6" t="inlineStr">
@@ -5066,17 +5066,17 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>Приказ Минтранса России от 14.04.2026 № 160; приказ Минтранса России от 16.10.2020 № 424</t>
+          <t>Приказ Минтранса России от 14.04.2026 № 159 "Об утверждении Особенностей режима рабочего времени и времени отдыха водителей трамвая и троллейбуса"</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>п. 18 Особенностей (приказ Минтранса № 160); соответствующие положения Особенностей (приказ Минтранса № 424)</t>
+          <t>п. 7 Особенностей</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>Локальный нормативный акт / коллективный договор о размере дополнительного вознаграждения за время нахождения в экипаже без управления автомобилем</t>
+          <t>Локальный нормативный акт о разделении рабочего дня (смены) водителя на части</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="G74" s="6" t="inlineStr">
         <is>
-          <t>Размер дополнительного вознаграждения; порядок выплаты; категории водителей</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H74" s="6" t="inlineStr">
         <is>
-          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+          <t>Выборный орган первичной профсоюзной организации / иной представительный орган работников</t>
         </is>
       </c>
       <c r="I74" s="6" t="inlineStr">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="J74" s="6" t="inlineStr">
         <is>
-          <t>Утверждение</t>
+          <t>Согласование</t>
         </is>
       </c>
       <c r="K74" s="6" t="inlineStr">
@@ -5128,17 +5128,17 @@
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>Приказ ГФС России от 17.08.2009 № 264</t>
+          <t>Приказ Минтранса России от 14.04.2026 № 159 "Об утверждении Особенностей режима рабочего времени и времени отдыха водителей трамвая и троллейбуса"</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>Положение о порядке учета рабочего времени и времени отдыха лиц начальствующего состава федеральной фельдъегерской связи (приказ ГФС № 264)</t>
+          <t>п. 7 Особенностей</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>Положение (локальный порядок) учета рабочего времени и времени отдыха лиц начальствующего состава федеральной фельдъегерской связи</t>
+          <t>Письменное согласие водителя на разделение рабочего дня (смены) на части</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="G75" s="6" t="inlineStr">
         <is>
-          <t>Категории работников; порядок учета служебного / рабочего времени; особенности сменной работы; перерывы и отдых</t>
+          <t>ФИО водителя; период; условия; дата; подпись</t>
         </is>
       </c>
       <c r="H75" s="6" t="inlineStr">
         <is>
-          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+          <t>Работник</t>
         </is>
       </c>
       <c r="I75" s="6" t="inlineStr">
@@ -5168,7 +5168,7 @@
       </c>
       <c r="J75" s="6" t="inlineStr">
         <is>
-          <t>Утверждение</t>
+          <t>Подтверждение (?)</t>
         </is>
       </c>
       <c r="K75" s="6" t="inlineStr">
@@ -5190,17 +5190,17 @@
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>Постановление Минтруда России от 12.07.1999 № 22</t>
+          <t>Приказ Минтранса России от 14.04.2026 № 159 "Об утверждении Особенностей режима рабочего времени и времени отдыха водителей трамвая и троллейбуса"</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>п. 1 постановления Минтруда России от 12.07.1999 № 22</t>
+          <t>п. 10 Особенностей</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
         <is>
-          <t>Локальный нормативный акт / ПВТР об установлении продолжительности рабочей недели членам экипажей воздушных судов гражданской авиации</t>
+          <t>Письменное заявление водителя о сокращении ежедневного (междусменного) отдыха</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
@@ -5215,12 +5215,12 @@
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
-          <t>Продолжительность рабочей недели (36 часов — по постановлению № 22); категории работников; порядок применения</t>
+          <t>Просьба о сокращении отдыха; период; условия компенсации</t>
         </is>
       </c>
       <c r="H76" s="6" t="inlineStr">
         <is>
-          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+          <t>Работник</t>
         </is>
       </c>
       <c r="I76" s="6" t="inlineStr">
@@ -5230,7 +5230,7 @@
       </c>
       <c r="J76" s="6" t="inlineStr">
         <is>
-          <t>Утверждение</t>
+          <t>Заявление</t>
         </is>
       </c>
       <c r="K76" s="6" t="inlineStr">
@@ -5252,17 +5252,17 @@
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>Трудовой кодекс Российской Федерации</t>
+          <t>Приказ Минтранса России от 14.04.2026 № 159 "Об утверждении Особенностей режима рабочего времени и времени отдыха водителей трамвая и троллейбуса"</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>ст. 372 ТК РФ (учет мнения выборного органа первичной профсоюзной организации при принятии ЛНА); отраслевые Особенности требуют учета мнения, не устанавливая отдельную форму документа</t>
+          <t>п. 10 Особенностей</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>Мотивированное мнение (документ учета мнения) выборного органа первичной профсоюзной организации / представительного органа работников</t>
+          <t>Согласование сокращения ежедневного (междусменного) отдыха водителя</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
@@ -5277,12 +5277,12 @@
       </c>
       <c r="G77" s="6" t="inlineStr">
         <is>
-          <t>Реквизиты проекта ЛНА / графика; позиция представительного органа; дата; подписи</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H77" s="6" t="inlineStr">
         <is>
-          <t>Председатель (уполномоченное лицо) представительного органа работников</t>
+          <t>Выборный орган первичной профсоюзной организации / иной представительный орган работников</t>
         </is>
       </c>
       <c r="I77" s="6" t="inlineStr">
@@ -5301,6 +5301,7942 @@
         </is>
       </c>
       <c r="L77" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтранса России от 10.11.2025 № 381 "Об утверждении Особенностей режима рабочего времени и времени отдыха специалистов авиационного персонала гражданской авиации, труд которых непосредственно связан с движением гражданских воздушных судов"</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>п. 3 Особенностей</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>Руководство по производству полетов (РПП) в части режима рабочего времени и времени отдыха авиационного персонала</t>
+        </is>
+      </c>
+      <c r="E78" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F78" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G78" s="6" t="inlineStr">
+        <is>
+          <t>Нормы рабочего / полетного времени и отдыха; порядок планирования; контроль соблюдения режимов</t>
+        </is>
+      </c>
+      <c r="H78" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I78" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J78" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K78" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L78" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтранса России от 10.11.2025 № 381 "Об утверждении Особенностей режима рабочего времени и времени отдыха специалистов авиационного персонала гражданской авиации, труд которых непосредственно связан с движением гражданских воздушных судов"</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>п. 3 Особенностей</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>Руководство по производству полетов (РПП) в части режима рабочего времени и времени отдыха авиационного персонала</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F79" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G79" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H79" s="6" t="inlineStr">
+        <is>
+          <t>Выборный орган первичной профсоюзной организации / иной представительный орган работников</t>
+        </is>
+      </c>
+      <c r="I79" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J79" s="6" t="inlineStr">
+        <is>
+          <t>Согласование</t>
+        </is>
+      </c>
+      <c r="K79" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L79" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтранса России от 10.11.2025 № 381 "Об утверждении Особенностей режима рабочего времени и времени отдыха специалистов авиационного персонала гражданской авиации, труд которых непосредственно связан с движением гражданских воздушных судов"</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>п. 6 Особенностей</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>Локальный нормативный акт о введении суммированного учета рабочего времени членов экипажей / внешних пилотов</t>
+        </is>
+      </c>
+      <c r="E80" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F80" s="6" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="G80" s="6" t="inlineStr">
+        <is>
+          <t>Учетный период (не более 1 месяца); категории работников</t>
+        </is>
+      </c>
+      <c r="H80" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I80" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J80" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K80" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L80" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтранса России от 10.11.2025 № 381 "Об утверждении Особенностей режима рабочего времени и времени отдыха специалистов авиационного персонала гражданской авиации, труд которых непосредственно связан с движением гражданских воздушных судов"</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>п. 6 Особенностей</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>Локальный нормативный акт о введении суммированного учета рабочего времени членов экипажей / внешних пилотов</t>
+        </is>
+      </c>
+      <c r="E81" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F81" s="6" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="G81" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H81" s="6" t="inlineStr">
+        <is>
+          <t>Выборный орган первичной профсоюзной организации / иной представительный орган работников</t>
+        </is>
+      </c>
+      <c r="I81" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J81" s="6" t="inlineStr">
+        <is>
+          <t>Согласование</t>
+        </is>
+      </c>
+      <c r="K81" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L81" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтранса России от 10.11.2025 № 381 "Об утверждении Особенностей режима рабочего времени и времени отдыха специалистов авиационного персонала гражданской авиации, труд которых непосредственно связан с движением гражданских воздушных судов"</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>п. 6 Особенностей</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t>Локальный нормативный акт об увеличении учетного периода суммированного учета до одного квартала</t>
+        </is>
+      </c>
+      <c r="E82" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F82" s="6" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="G82" s="6" t="inlineStr">
+        <is>
+          <t>Новая продолжительность учетного периода; основание</t>
+        </is>
+      </c>
+      <c r="H82" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I82" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J82" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K82" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L82" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтранса России от 10.11.2025 № 381 "Об утверждении Особенностей режима рабочего времени и времени отдыха специалистов авиационного персонала гражданской авиации, труд которых непосредственно связан с движением гражданских воздушных судов"</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>п. 6 Особенностей</t>
+        </is>
+      </c>
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t>Локальный нормативный акт об увеличении учетного периода суммированного учета до одного квартала</t>
+        </is>
+      </c>
+      <c r="E83" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F83" s="6" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="G83" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H83" s="6" t="inlineStr">
+        <is>
+          <t>Выборный орган первичной профсоюзной организации / иной представительный орган работников</t>
+        </is>
+      </c>
+      <c r="I83" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J83" s="6" t="inlineStr">
+        <is>
+          <t>Согласование</t>
+        </is>
+      </c>
+      <c r="K83" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L83" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтранса России от 10.11.2025 № 381 "Об утверждении Особенностей режима рабочего времени и времени отдыха специалистов авиационного персонала гражданской авиации, труд которых непосредственно связан с движением гражданских воздушных судов"</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>положения Особенностей о разделении полетной смены</t>
+        </is>
+      </c>
+      <c r="D84" s="6" t="inlineStr">
+        <is>
+          <t>Локальный нормативный акт о разделении полетной смены на части</t>
+        </is>
+      </c>
+      <c r="E84" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F84" s="6" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="G84" s="6" t="inlineStr">
+        <is>
+          <t>Порядок разделения полетной смены; продолжительность частей</t>
+        </is>
+      </c>
+      <c r="H84" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I84" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J84" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K84" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L84" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтранса России от 10.11.2025 № 381 "Об утверждении Особенностей режима рабочего времени и времени отдыха специалистов авиационного персонала гражданской авиации, труд которых непосредственно связан с движением гражданских воздушных судов"</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>положения Особенностей о разделении полетной смены</t>
+        </is>
+      </c>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t>Локальный нормативный акт о разделении полетной смены на части</t>
+        </is>
+      </c>
+      <c r="E85" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F85" s="6" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="G85" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H85" s="6" t="inlineStr">
+        <is>
+          <t>Выборный орган первичной профсоюзной организации / иной представительный орган работников</t>
+        </is>
+      </c>
+      <c r="I85" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J85" s="6" t="inlineStr">
+        <is>
+          <t>Согласование</t>
+        </is>
+      </c>
+      <c r="K85" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L85" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтранса России от 10.11.2025 № 381 "Об утверждении Особенностей режима рабочего времени и времени отдыха специалистов авиационного персонала гражданской авиации, труд которых непосредственно связан с движением гражданских воздушных судов"</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>п. 7 Особенностей</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>Письменное согласие члена экипажа / внешнего пилота на привлечение к сверхурочной работе</t>
+        </is>
+      </c>
+      <c r="E86" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F86" s="6" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="G86" s="6" t="inlineStr">
+        <is>
+          <t>ФИО; период; условия привлечения; дата; подпись</t>
+        </is>
+      </c>
+      <c r="H86" s="6" t="inlineStr">
+        <is>
+          <t>Работник</t>
+        </is>
+      </c>
+      <c r="I86" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J86" s="6" t="inlineStr">
+        <is>
+          <t>Подтверждение (?)</t>
+        </is>
+      </c>
+      <c r="K86" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L86" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтранса России от 10.11.2025 № 381 "Об утверждении Особенностей режима рабочего времени и времени отдыха специалистов авиационного персонала гражданской авиации, труд которых непосредственно связан с движением гражданских воздушных судов"</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>п. 59 Особенностей</t>
+        </is>
+      </c>
+      <c r="D87" s="6" t="inlineStr">
+        <is>
+          <t>Графики работы членов экипажей / внешних пилотов</t>
+        </is>
+      </c>
+      <c r="E87" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F87" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G87" s="6" t="inlineStr">
+        <is>
+          <t>Планируемое рабочее и полетное время; время отдыха; состав экипажа; составляются не менее чем на 1 календарный месяц</t>
+        </is>
+      </c>
+      <c r="H87" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I87" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J87" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K87" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L87" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтранса России от 10.11.2025 № 381 "Об утверждении Особенностей режима рабочего времени и времени отдыха специалистов авиационного персонала гражданской авиации, труд которых непосредственно связан с движением гражданских воздушных судов"</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>п. 59 Особенностей</t>
+        </is>
+      </c>
+      <c r="D88" s="6" t="inlineStr">
+        <is>
+          <t>Графики работы членов экипажей / внешних пилотов</t>
+        </is>
+      </c>
+      <c r="E88" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F88" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G88" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H88" s="6" t="inlineStr">
+        <is>
+          <t>Выборный орган первичной профсоюзной организации / иной представительный орган работников</t>
+        </is>
+      </c>
+      <c r="I88" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J88" s="6" t="inlineStr">
+        <is>
+          <t>Согласование</t>
+        </is>
+      </c>
+      <c r="K88" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L88" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтранса России от 10.11.2025 № 381 "Об утверждении Особенностей режима рабочего времени и времени отдыха специалистов авиационного персонала гражданской авиации, труд которых непосредственно связан с движением гражданских воздушных судов"</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>п. 59 Особенностей</t>
+        </is>
+      </c>
+      <c r="D89" s="6" t="inlineStr">
+        <is>
+          <t>Лист ознакомления (отметки о доведении) графиков работы членов экипажей до сведения работников</t>
+        </is>
+      </c>
+      <c r="E89" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F89" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G89" s="6" t="inlineStr">
+        <is>
+          <t>ФИО; дата; подпись; доведение не позднее чем за 1 календарный месяц</t>
+        </is>
+      </c>
+      <c r="H89" s="6" t="inlineStr">
+        <is>
+          <t>Работник</t>
+        </is>
+      </c>
+      <c r="I89" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J89" s="6" t="inlineStr">
+        <is>
+          <t>Ознакомление</t>
+        </is>
+      </c>
+      <c r="K89" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L89" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтранса России от 10.11.2025 № 381 "Об утверждении Особенностей режима рабочего времени и времени отдыха специалистов авиационного персонала гражданской авиации, труд которых непосредственно связан с движением гражданских воздушных судов"</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>п. 59 Особенностей</t>
+        </is>
+      </c>
+      <c r="D90" s="6" t="inlineStr">
+        <is>
+          <t>Измененные графики работы членов экипажей и уведомление работников</t>
+        </is>
+      </c>
+      <c r="E90" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F90" s="6" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="G90" s="6" t="inlineStr">
+        <is>
+          <t>Изменения; доведение не позднее чем за пять рабочих дней</t>
+        </is>
+      </c>
+      <c r="H90" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I90" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J90" s="6" t="inlineStr">
+        <is>
+          <t>Уведомление</t>
+        </is>
+      </c>
+      <c r="K90" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L90" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтранса России от 10.11.2025 № 381 "Об утверждении Особенностей режима рабочего времени и времени отдыха специалистов авиационного персонала гражданской авиации, труд которых непосредственно связан с движением гражданских воздушных судов"</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="inlineStr">
+        <is>
+          <t>п. 59 Особенностей</t>
+        </is>
+      </c>
+      <c r="D91" s="6" t="inlineStr">
+        <is>
+          <t>Измененные графики работы членов экипажей</t>
+        </is>
+      </c>
+      <c r="E91" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F91" s="6" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="G91" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H91" s="6" t="inlineStr">
+        <is>
+          <t>Работник</t>
+        </is>
+      </c>
+      <c r="I91" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J91" s="6" t="inlineStr">
+        <is>
+          <t>Ознакомление</t>
+        </is>
+      </c>
+      <c r="K91" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L91" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B92" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтранса России от 10.11.2025 № 381 "Об утверждении Особенностей режима рабочего времени и времени отдыха специалистов авиационного персонала гражданской авиации, труд которых непосредственно связан с движением гражданских воздушных судов"</t>
+        </is>
+      </c>
+      <c r="C92" s="6" t="inlineStr">
+        <is>
+          <t>п. 3 Особенностей</t>
+        </is>
+      </c>
+      <c r="D92" s="6" t="inlineStr">
+        <is>
+          <t>Расписания движения гражданских воздушных судов (в части планирования рабочего и полетного времени)</t>
+        </is>
+      </c>
+      <c r="E92" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F92" s="6" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="G92" s="6" t="inlineStr">
+        <is>
+          <t>Рейсы; время; связь с графиками работы экипажей</t>
+        </is>
+      </c>
+      <c r="H92" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I92" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J92" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K92" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L92" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтранса России от 10.11.2025 № 381 "Об утверждении Особенностей режима рабочего времени и времени отдыха специалистов авиационного персонала гражданской авиации, труд которых непосредственно связан с движением гражданских воздушных судов"</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>п. 64–67 Особенностей</t>
+        </is>
+      </c>
+      <c r="D93" s="6" t="inlineStr">
+        <is>
+          <t>Графики сменности диспетчеров УВД</t>
+        </is>
+      </c>
+      <c r="E93" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F93" s="6" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="G93" s="6" t="inlineStr">
+        <is>
+          <t>ФИО (должности) работников; даты; время начала и окончания работы (смены); перерывы; выходные; срок, на который составлен график</t>
+        </is>
+      </c>
+      <c r="H93" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I93" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J93" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K93" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L93" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтранса России от 10.11.2025 № 381 "Об утверждении Особенностей режима рабочего времени и времени отдыха специалистов авиационного персонала гражданской авиации, труд которых непосредственно связан с движением гражданских воздушных судов"</t>
+        </is>
+      </c>
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>п. 64–67 Особенностей</t>
+        </is>
+      </c>
+      <c r="D94" s="6" t="inlineStr">
+        <is>
+          <t>Графики сменности диспетчеров УВД</t>
+        </is>
+      </c>
+      <c r="E94" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F94" s="6" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="G94" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H94" s="6" t="inlineStr">
+        <is>
+          <t>Выборный орган первичной профсоюзной организации / иной представительный орган работников</t>
+        </is>
+      </c>
+      <c r="I94" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J94" s="6" t="inlineStr">
+        <is>
+          <t>Согласование</t>
+        </is>
+      </c>
+      <c r="K94" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L94" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтранса России от 10.11.2025 № 381 "Об утверждении Особенностей режима рабочего времени и времени отдыха специалистов авиационного персонала гражданской авиации, труд которых непосредственно связан с движением гражданских воздушных судов"</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>п. 64–67 Особенностей</t>
+        </is>
+      </c>
+      <c r="D95" s="6" t="inlineStr">
+        <is>
+          <t>Лист ознакомления (отметки о доведении) графиков сменности диспетчеров УВД</t>
+        </is>
+      </c>
+      <c r="E95" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F95" s="6" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="G95" s="6" t="inlineStr">
+        <is>
+          <t>ФИО; дата; подпись; доведение не позднее чем за 1 календарный месяц</t>
+        </is>
+      </c>
+      <c r="H95" s="6" t="inlineStr">
+        <is>
+          <t>Работник</t>
+        </is>
+      </c>
+      <c r="I95" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J95" s="6" t="inlineStr">
+        <is>
+          <t>Ознакомление</t>
+        </is>
+      </c>
+      <c r="K95" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L95" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтранса России от 10.11.2025 № 381 "Об утверждении Особенностей режима рабочего времени и времени отдыха специалистов авиационного персонала гражданской авиации, труд которых непосредственно связан с движением гражданских воздушных судов"</t>
+        </is>
+      </c>
+      <c r="C96" s="6" t="inlineStr">
+        <is>
+          <t>п. 59–60 Особенностей</t>
+        </is>
+      </c>
+      <c r="D96" s="6" t="inlineStr">
+        <is>
+          <t>Документы (система) учета запланированного и фактического рабочего времени, полетного времени и времени отдыха членов экипажей</t>
+        </is>
+      </c>
+      <c r="E96" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F96" s="6" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="G96" s="6" t="inlineStr">
+        <is>
+          <t>Запланированные и фактические показатели; отклонения; период учета</t>
+        </is>
+      </c>
+      <c r="H96" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I96" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J96" s="6" t="inlineStr">
+        <is>
+          <t>Подтверждение (?)</t>
+        </is>
+      </c>
+      <c r="K96" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L96" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B97" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтранса России от 10.11.2025 № 381 "Об утверждении Особенностей режима рабочего времени и времени отдыха специалистов авиационного персонала гражданской авиации, труд которых непосредственно связан с движением гражданских воздушных судов"</t>
+        </is>
+      </c>
+      <c r="C97" s="6" t="inlineStr">
+        <is>
+          <t>п. 60 Особенностей</t>
+        </is>
+      </c>
+      <c r="D97" s="6" t="inlineStr">
+        <is>
+          <t>Табель учета рабочего времени</t>
+        </is>
+      </c>
+      <c r="E97" s="6" t="inlineStr">
+        <is>
+          <t>ДА (форма Т-12 / Т-13 либо иная применяемая работодателем)</t>
+        </is>
+      </c>
+      <c r="F97" s="6" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="G97" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H97" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I97" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J97" s="6" t="inlineStr">
+        <is>
+          <t>Подтверждение (?)</t>
+        </is>
+      </c>
+      <c r="K97" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L97" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B98" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтранса России от 10.11.2025 № 381 "Об утверждении Особенностей режима рабочего времени и времени отдыха специалистов авиационного персонала гражданской авиации, труд которых непосредственно связан с движением гражданских воздушных судов"</t>
+        </is>
+      </c>
+      <c r="C98" s="6" t="inlineStr">
+        <is>
+          <t>п. 60 Особенностей</t>
+        </is>
+      </c>
+      <c r="D98" s="6" t="inlineStr">
+        <is>
+          <t>Табель учета рабочего времени</t>
+        </is>
+      </c>
+      <c r="E98" s="6" t="inlineStr">
+        <is>
+          <t>ДА (форма Т-12 / Т-13 либо иная применяемая работодателем)</t>
+        </is>
+      </c>
+      <c r="F98" s="6" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="G98" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H98" s="6" t="inlineStr">
+        <is>
+          <t>Лицо, ведущее учет рабочего времени</t>
+        </is>
+      </c>
+      <c r="I98" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J98" s="6" t="inlineStr">
+        <is>
+          <t>Подтверждение (?)</t>
+        </is>
+      </c>
+      <c r="K98" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L98" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B99" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минздрава России от 13.03.2025 № 115н "Об утверждении Особенностей режима рабочего времени и учета рабочего времени при осуществлении медицинскими работниками медицинских организаций дежурств на дому"</t>
+        </is>
+      </c>
+      <c r="C99" s="6" t="inlineStr">
+        <is>
+          <t>п. 1 Особенностей</t>
+        </is>
+      </c>
+      <c r="D99" s="6" t="inlineStr">
+        <is>
+          <t>Правила внутреннего трудового распорядка (суммированный учет рабочего времени медицинских работников, осуществляющих дежурство на дому)</t>
+        </is>
+      </c>
+      <c r="E99" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F99" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G99" s="6" t="inlineStr">
+        <is>
+          <t>Установление суммированного учета рабочего времени для медицинских работников, осуществляющих дежурство на дому</t>
+        </is>
+      </c>
+      <c r="H99" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I99" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J99" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K99" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L99" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B100" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минздрава России от 13.03.2025 № 115н "Об утверждении Особенностей режима рабочего времени и учета рабочего времени при осуществлении медицинскими работниками медицинских организаций дежурств на дому"</t>
+        </is>
+      </c>
+      <c r="C100" s="6" t="inlineStr">
+        <is>
+          <t>п. 1 Особенностей</t>
+        </is>
+      </c>
+      <c r="D100" s="6" t="inlineStr">
+        <is>
+          <t>График работы (график дежурств на дому) медицинских работников</t>
+        </is>
+      </c>
+      <c r="E100" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F100" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G100" s="6" t="inlineStr">
+        <is>
+          <t>ФИО медицинских работников; время начала и окончания дежурства на дому; период</t>
+        </is>
+      </c>
+      <c r="H100" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I100" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J100" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K100" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L100" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B101" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минздрава России от 13.03.2025 № 115н "Об утверждении Особенностей режима рабочего времени и учета рабочего времени при осуществлении медицинскими работниками медицинских организаций дежурств на дому"</t>
+        </is>
+      </c>
+      <c r="C101" s="6" t="inlineStr">
+        <is>
+          <t>п. 1 Особенностей</t>
+        </is>
+      </c>
+      <c r="D101" s="6" t="inlineStr">
+        <is>
+          <t>График работы (график дежурств на дому) медицинских работников</t>
+        </is>
+      </c>
+      <c r="E101" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F101" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G101" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H101" s="6" t="inlineStr">
+        <is>
+          <t>Выборный орган первичной профсоюзной организации / иной представительный орган работников</t>
+        </is>
+      </c>
+      <c r="I101" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J101" s="6" t="inlineStr">
+        <is>
+          <t>Согласование</t>
+        </is>
+      </c>
+      <c r="K101" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L101" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B102" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минздрава России от 13.03.2025 № 115н "Об утверждении Особенностей режима рабочего времени и учета рабочего времени при осуществлении медицинскими работниками медицинских организаций дежурств на дому"</t>
+        </is>
+      </c>
+      <c r="C102" s="6" t="inlineStr">
+        <is>
+          <t>п. 2 Особенностей</t>
+        </is>
+      </c>
+      <c r="D102" s="6" t="inlineStr">
+        <is>
+          <t>Локальный нормативный акт о порядке учета времени следования медицинского работника при дежурстве на дому</t>
+        </is>
+      </c>
+      <c r="E102" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F102" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G102" s="6" t="inlineStr">
+        <is>
+          <t>Порядок фиксации времени следования от дома до места оказания помощи и обратно; единицы учета; ответственные</t>
+        </is>
+      </c>
+      <c r="H102" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I102" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J102" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K102" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L102" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B103" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минздрава России от 13.03.2025 № 115н "Об утверждении Особенностей режима рабочего времени и учета рабочего времени при осуществлении медицинскими работниками медицинских организаций дежурств на дому"</t>
+        </is>
+      </c>
+      <c r="C103" s="6" t="inlineStr">
+        <is>
+          <t>п. 2 Особенностей</t>
+        </is>
+      </c>
+      <c r="D103" s="6" t="inlineStr">
+        <is>
+          <t>Локальный нормативный акт о порядке учета времени следования медицинского работника при дежурстве на дому</t>
+        </is>
+      </c>
+      <c r="E103" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F103" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G103" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H103" s="6" t="inlineStr">
+        <is>
+          <t>Выборный орган первичной профсоюзной организации / иной представительный орган работников</t>
+        </is>
+      </c>
+      <c r="I103" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J103" s="6" t="inlineStr">
+        <is>
+          <t>Согласование</t>
+        </is>
+      </c>
+      <c r="K103" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L103" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B104" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минздрава России от 13.03.2025 № 115н "Об утверждении Особенностей режима рабочего времени и учета рабочего времени при осуществлении медицинскими работниками медицинских организаций дежурств на дому"</t>
+        </is>
+      </c>
+      <c r="C104" s="6" t="inlineStr">
+        <is>
+          <t>п. 3 Особенностей</t>
+        </is>
+      </c>
+      <c r="D104" s="6" t="inlineStr">
+        <is>
+          <t>Документы (журналы / формы) учета времени дежурства на дому, времени оказания медицинской помощи и времени следования</t>
+        </is>
+      </c>
+      <c r="E104" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F104" s="6" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="G104" s="6" t="inlineStr">
+        <is>
+          <t>Время пребывания дома в режиме ожидания вызова; время оказания помощи; время следования; ФИО; даты</t>
+        </is>
+      </c>
+      <c r="H104" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I104" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J104" s="6" t="inlineStr">
+        <is>
+          <t>Подтверждение (?)</t>
+        </is>
+      </c>
+      <c r="K104" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L104" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B105" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минздрава России от 13.03.2025 № 115н "Об утверждении Особенностей режима рабочего времени и учета рабочего времени при осуществлении медицинскими работниками медицинских организаций дежурств на дому"</t>
+        </is>
+      </c>
+      <c r="C105" s="6" t="inlineStr">
+        <is>
+          <t>п. 3 Особенностей</t>
+        </is>
+      </c>
+      <c r="D105" s="6" t="inlineStr">
+        <is>
+          <t>Документы (журналы / формы) учета времени дежурства на дому, времени оказания медицинской помощи и времени следования</t>
+        </is>
+      </c>
+      <c r="E105" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F105" s="6" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="G105" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H105" s="6" t="inlineStr">
+        <is>
+          <t>Лицо, ведущее учет рабочего времени</t>
+        </is>
+      </c>
+      <c r="I105" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J105" s="6" t="inlineStr">
+        <is>
+          <t>Подтверждение (?)</t>
+        </is>
+      </c>
+      <c r="K105" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L105" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B106" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтранса России от 30.04.2025 № 145 "Об утверждении Особенностей режима рабочего времени и времени отдыха членов экипажей морских судов и судов смешанного (река-море) плавания"</t>
+        </is>
+      </c>
+      <c r="C106" s="6" t="inlineStr">
+        <is>
+          <t>п. 1 Особенностей (Положения)</t>
+        </is>
+      </c>
+      <c r="D106" s="6" t="inlineStr">
+        <is>
+          <t>Правила внутреннего трудового распорядка (с особенностями режима рабочего времени и времени отдыха членов экипажей морских судов и судов смешанного (река-море) плавания)</t>
+        </is>
+      </c>
+      <c r="E106" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F106" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G106" s="6" t="inlineStr">
+        <is>
+          <t>Продолжительность рабочей недели / смены; время начала и окончания работы; перерывы; число смен; чередование рабочих и нерабочих дней; иные особенности режима</t>
+        </is>
+      </c>
+      <c r="H106" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I106" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J106" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K106" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L106" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B107" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтранса России от 30.04.2025 № 145 "Об утверждении Особенностей режима рабочего времени и времени отдыха членов экипажей морских судов и судов смешанного (река-море) плавания"</t>
+        </is>
+      </c>
+      <c r="C107" s="6" t="inlineStr">
+        <is>
+          <t>п. 1 Особенностей (Положения)</t>
+        </is>
+      </c>
+      <c r="D107" s="6" t="inlineStr">
+        <is>
+          <t>Графики работы и (или) графики сменности (членов экипажей морских судов и судов смешанного (река-море) плавания)</t>
+        </is>
+      </c>
+      <c r="E107" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F107" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G107" s="6" t="inlineStr">
+        <is>
+          <t>ФИО (должности) работников; даты; время начала и окончания работы (смены); перерывы; выходные; срок, на который составлен график</t>
+        </is>
+      </c>
+      <c r="H107" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I107" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J107" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K107" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L107" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B108" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтранса России от 30.04.2025 № 145 "Об утверждении Особенностей режима рабочего времени и времени отдыха членов экипажей морских судов и судов смешанного (река-море) плавания"</t>
+        </is>
+      </c>
+      <c r="C108" s="6" t="inlineStr">
+        <is>
+          <t>положения Особенностей</t>
+        </is>
+      </c>
+      <c r="D108" s="6" t="inlineStr">
+        <is>
+          <t>Вахтенное расписание / графики вахт членов экипажей морских судов и судов смешанного (река-море) плавания</t>
+        </is>
+      </c>
+      <c r="E108" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F108" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G108" s="6" t="inlineStr">
+        <is>
+          <t>Состав вахт; продолжительность; чередование вахт и отдыха</t>
+        </is>
+      </c>
+      <c r="H108" s="6" t="inlineStr">
+        <is>
+          <t>Капитан судна / руководитель организации / уполномоченное лицо</t>
+        </is>
+      </c>
+      <c r="I108" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J108" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K108" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L108" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B109" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтранса России от 30.04.2025 № 144 "Об утверждении Особенностей режима рабочего времени и времени отдыха работников плавающего состава судов внутреннего водного транспорта"</t>
+        </is>
+      </c>
+      <c r="C109" s="6" t="inlineStr">
+        <is>
+          <t>п. 1 Особенностей (Положения)</t>
+        </is>
+      </c>
+      <c r="D109" s="6" t="inlineStr">
+        <is>
+          <t>Правила внутреннего трудового распорядка (с особенностями режима рабочего времени и времени отдыха работников плавающего состава судов внутреннего водного транспорта)</t>
+        </is>
+      </c>
+      <c r="E109" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F109" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G109" s="6" t="inlineStr">
+        <is>
+          <t>Продолжительность рабочей недели / смены; время начала и окончания работы; перерывы; число смен; чередование рабочих и нерабочих дней; иные особенности режима</t>
+        </is>
+      </c>
+      <c r="H109" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I109" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J109" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K109" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L109" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B110" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтранса России от 30.04.2025 № 144 "Об утверждении Особенностей режима рабочего времени и времени отдыха работников плавающего состава судов внутреннего водного транспорта"</t>
+        </is>
+      </c>
+      <c r="C110" s="6" t="inlineStr">
+        <is>
+          <t>п. 1 Особенностей (Положения)</t>
+        </is>
+      </c>
+      <c r="D110" s="6" t="inlineStr">
+        <is>
+          <t>Графики работы и (или) графики сменности (работников плавающего состава судов внутреннего водного транспорта)</t>
+        </is>
+      </c>
+      <c r="E110" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F110" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G110" s="6" t="inlineStr">
+        <is>
+          <t>ФИО (должности) работников; даты; время начала и окончания работы (смены); перерывы; выходные; срок, на который составлен график</t>
+        </is>
+      </c>
+      <c r="H110" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I110" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J110" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K110" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L110" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B111" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтранса России от 30.04.2025 № 144 "Об утверждении Особенностей режима рабочего времени и времени отдыха работников плавающего состава судов внутреннего водного транспорта"</t>
+        </is>
+      </c>
+      <c r="C111" s="6" t="inlineStr">
+        <is>
+          <t>положения Особенностей</t>
+        </is>
+      </c>
+      <c r="D111" s="6" t="inlineStr">
+        <is>
+          <t>Вахтенное расписание / графики вахт работников плавающего состава судов внутреннего водного транспорта</t>
+        </is>
+      </c>
+      <c r="E111" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F111" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G111" s="6" t="inlineStr">
+        <is>
+          <t>Состав вахт; продолжительность; чередование вахт и отдыха</t>
+        </is>
+      </c>
+      <c r="H111" s="6" t="inlineStr">
+        <is>
+          <t>Капитан судна / руководитель организации / уполномоченное лицо</t>
+        </is>
+      </c>
+      <c r="I111" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J111" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K111" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L111" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B112" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минобрнауки России от 08.04.2025 № 318 "Об утверждении Особенностей режима рабочего времени и времени отдыха педагогических и иных работников организаций, осуществляющих образовательную деятельность по образовательным программам высшего образования и дополнительным профессиональным программам"</t>
+        </is>
+      </c>
+      <c r="C112" s="6" t="inlineStr">
+        <is>
+          <t>п. 2 Особенностей</t>
+        </is>
+      </c>
+      <c r="D112" s="6" t="inlineStr">
+        <is>
+          <t>Коллективный договор (положения о режиме рабочего времени и времени отдыха педагогических и иных работников)</t>
+        </is>
+      </c>
+      <c r="E112" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F112" s="6" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="G112" s="6" t="inlineStr">
+        <is>
+          <t>Режим рабочего времени и времени отдыха; графики работы; расписание занятий</t>
+        </is>
+      </c>
+      <c r="H112" s="6" t="inlineStr">
+        <is>
+          <t>Стороны коллективного договора (представители работодателя и работников)</t>
+        </is>
+      </c>
+      <c r="I112" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J112" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K112" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L112" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B113" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минобрнауки России от 08.04.2025 № 318 "Об утверждении Особенностей режима рабочего времени и времени отдыха педагогических и иных работников организаций, осуществляющих образовательную деятельность по образовательным программам высшего образования и дополнительным профессиональным программам"</t>
+        </is>
+      </c>
+      <c r="C113" s="6" t="inlineStr">
+        <is>
+          <t>п. 2–3 Особенностей</t>
+        </is>
+      </c>
+      <c r="D113" s="6" t="inlineStr">
+        <is>
+          <t>Правила внутреннего трудового распорядка (с особенностями режима рабочего времени и времени отдыха педагогических и иных работников)</t>
+        </is>
+      </c>
+      <c r="E113" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F113" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G113" s="6" t="inlineStr">
+        <is>
+          <t>Продолжительность рабочей недели / смены; время начала и окончания работы; перерывы; число смен; чередование рабочих и нерабочих дней; иные особенности режима</t>
+        </is>
+      </c>
+      <c r="H113" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I113" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J113" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K113" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L113" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B114" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минобрнауки России от 08.04.2025 № 318 "Об утверждении Особенностей режима рабочего времени и времени отдыха педагогических и иных работников организаций, осуществляющих образовательную деятельность по образовательным программам высшего образования и дополнительным профессиональным программам"</t>
+        </is>
+      </c>
+      <c r="C114" s="6" t="inlineStr">
+        <is>
+          <t>п. 3 Особенностей</t>
+        </is>
+      </c>
+      <c r="D114" s="6" t="inlineStr">
+        <is>
+          <t>Правила внутреннего трудового распорядка (с особенностями режима рабочего времени и времени отдыха педагогических и иных работников)</t>
+        </is>
+      </c>
+      <c r="E114" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F114" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G114" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H114" s="6" t="inlineStr">
+        <is>
+          <t>Выборный орган первичной профсоюзной организации / иной представительный орган работников</t>
+        </is>
+      </c>
+      <c r="I114" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J114" s="6" t="inlineStr">
+        <is>
+          <t>Согласование</t>
+        </is>
+      </c>
+      <c r="K114" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L114" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B115" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минобрнауки России от 08.04.2025 № 318 "Об утверждении Особенностей режима рабочего времени и времени отдыха педагогических и иных работников организаций, осуществляющих образовательную деятельность по образовательным программам высшего образования и дополнительным профессиональным программам"</t>
+        </is>
+      </c>
+      <c r="C115" s="6" t="inlineStr">
+        <is>
+          <t>п. 2 Особенностей</t>
+        </is>
+      </c>
+      <c r="D115" s="6" t="inlineStr">
+        <is>
+          <t>Графики работы педагогических и иных работников</t>
+        </is>
+      </c>
+      <c r="E115" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F115" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G115" s="6" t="inlineStr">
+        <is>
+          <t>ФИО (должности) работников; даты; время начала и окончания работы (смены); перерывы; выходные; срок, на который составлен график</t>
+        </is>
+      </c>
+      <c r="H115" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I115" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J115" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K115" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L115" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B116" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минобрнауки России от 08.04.2025 № 318 "Об утверждении Особенностей режима рабочего времени и времени отдыха педагогических и иных работников организаций, осуществляющих образовательную деятельность по образовательным программам высшего образования и дополнительным профессиональным программам"</t>
+        </is>
+      </c>
+      <c r="C116" s="6" t="inlineStr">
+        <is>
+          <t>п. 2 Особенностей</t>
+        </is>
+      </c>
+      <c r="D116" s="6" t="inlineStr">
+        <is>
+          <t>Расписание учебных занятий</t>
+        </is>
+      </c>
+      <c r="E116" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F116" s="6" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="G116" s="6" t="inlineStr">
+        <is>
+          <t>Учебные занятия; продолжительность; закрепление педагогических работников</t>
+        </is>
+      </c>
+      <c r="H116" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I116" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J116" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K116" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L116" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B117" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минобрнауки России от 08.04.2025 № 318 "Об утверждении Особенностей режима рабочего времени и времени отдыха педагогических и иных работников организаций, осуществляющих образовательную деятельность по образовательным программам высшего образования и дополнительным профессиональным программам"</t>
+        </is>
+      </c>
+      <c r="C117" s="6" t="inlineStr">
+        <is>
+          <t>п. 2 Особенностей</t>
+        </is>
+      </c>
+      <c r="D117" s="6" t="inlineStr">
+        <is>
+          <t>Трудовой договор (условия режима рабочего времени и времени отдыха)</t>
+        </is>
+      </c>
+      <c r="E117" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F117" s="6" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="G117" s="6" t="inlineStr">
+        <is>
+          <t>Режим рабочего времени; особенности педагогической работы</t>
+        </is>
+      </c>
+      <c r="H117" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I117" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J117" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K117" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L117" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B118" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минобрнауки России от 08.04.2025 № 318 "Об утверждении Особенностей режима рабочего времени и времени отдыха педагогических и иных работников организаций, осуществляющих образовательную деятельность по образовательным программам высшего образования и дополнительным профессиональным программам"</t>
+        </is>
+      </c>
+      <c r="C118" s="6" t="inlineStr">
+        <is>
+          <t>п. 2 Особенностей</t>
+        </is>
+      </c>
+      <c r="D118" s="6" t="inlineStr">
+        <is>
+          <t>Трудовой договор (условия режима рабочего времени и времени отдыха)</t>
+        </is>
+      </c>
+      <c r="E118" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F118" s="6" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="G118" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H118" s="6" t="inlineStr">
+        <is>
+          <t>Работник</t>
+        </is>
+      </c>
+      <c r="I118" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J118" s="6" t="inlineStr">
+        <is>
+          <t>Подтверждение (?)</t>
+        </is>
+      </c>
+      <c r="K118" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L118" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B119" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минобрнауки России от 08.04.2025 № 318 "Об утверждении Особенностей режима рабочего времени и времени отдыха педагогических и иных работников организаций, осуществляющих образовательную деятельность по образовательным программам высшего образования и дополнительным профессиональным программам"</t>
+        </is>
+      </c>
+      <c r="C119" s="6" t="inlineStr">
+        <is>
+          <t>п. 2 Особенностей</t>
+        </is>
+      </c>
+      <c r="D119" s="6" t="inlineStr">
+        <is>
+          <t>Иные локальные нормативные акты организации о режиме рабочего времени и времени отдыха</t>
+        </is>
+      </c>
+      <c r="E119" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F119" s="6" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="G119" s="6" t="inlineStr">
+        <is>
+          <t>Особенности режима применительно к организации</t>
+        </is>
+      </c>
+      <c r="H119" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I119" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J119" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K119" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L119" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B120" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минпросвещения России от 04.04.2025 № 268 "Об утверждении Особенностей режима рабочего времени и времени отдыха педагогических и иных работников организаций, осуществляющих образовательную деятельность по основным и дополнительным общеобразовательным программам, образовательным программам среднего профессионального образования и соответствующим дополнительным профессиональным программам, основным программам профессионального обучения"</t>
+        </is>
+      </c>
+      <c r="C120" s="6" t="inlineStr">
+        <is>
+          <t>п. 2 Особенностей</t>
+        </is>
+      </c>
+      <c r="D120" s="6" t="inlineStr">
+        <is>
+          <t>Коллективный договор (положения о режиме рабочего времени и времени отдыха педагогических и иных работников)</t>
+        </is>
+      </c>
+      <c r="E120" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F120" s="6" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="G120" s="6" t="inlineStr">
+        <is>
+          <t>Режим рабочего времени и времени отдыха; дополнительные виды работ; компенсации</t>
+        </is>
+      </c>
+      <c r="H120" s="6" t="inlineStr">
+        <is>
+          <t>Стороны коллективного договора (представители работодателя и работников)</t>
+        </is>
+      </c>
+      <c r="I120" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J120" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K120" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L120" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B121" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минпросвещения России от 04.04.2025 № 268 "Об утверждении Особенностей режима рабочего времени и времени отдыха педагогических и иных работников организаций, осуществляющих образовательную деятельность по основным и дополнительным общеобразовательным программам, образовательным программам среднего профессионального образования и соответствующим дополнительным профессиональным программам, основным программам профессионального обучения"</t>
+        </is>
+      </c>
+      <c r="C121" s="6" t="inlineStr">
+        <is>
+          <t>п. 2–3 Особенностей</t>
+        </is>
+      </c>
+      <c r="D121" s="6" t="inlineStr">
+        <is>
+          <t>Правила внутреннего трудового распорядка (с особенностями режима рабочего времени и времени отдыха педагогических и иных работников)</t>
+        </is>
+      </c>
+      <c r="E121" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F121" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G121" s="6" t="inlineStr">
+        <is>
+          <t>Продолжительность рабочей недели / смены; время начала и окончания работы; перерывы; число смен; чередование рабочих и нерабочих дней; иные особенности режима; перерывы для отдыха и питания; порядок дополнительной работы</t>
+        </is>
+      </c>
+      <c r="H121" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I121" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J121" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K121" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L121" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B122" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минпросвещения России от 04.04.2025 № 268 "Об утверждении Особенностей режима рабочего времени и времени отдыха педагогических и иных работников организаций, осуществляющих образовательную деятельность по основным и дополнительным общеобразовательным программам, образовательным программам среднего профессионального образования и соответствующим дополнительным профессиональным программам, основным программам профессионального обучения"</t>
+        </is>
+      </c>
+      <c r="C122" s="6" t="inlineStr">
+        <is>
+          <t>п. 3 Особенностей</t>
+        </is>
+      </c>
+      <c r="D122" s="6" t="inlineStr">
+        <is>
+          <t>Правила внутреннего трудового распорядка (с особенностями режима рабочего времени и времени отдыха педагогических и иных работников)</t>
+        </is>
+      </c>
+      <c r="E122" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F122" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G122" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H122" s="6" t="inlineStr">
+        <is>
+          <t>Выборный орган первичной профсоюзной организации / иной представительный орган работников</t>
+        </is>
+      </c>
+      <c r="I122" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J122" s="6" t="inlineStr">
+        <is>
+          <t>Согласование</t>
+        </is>
+      </c>
+      <c r="K122" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L122" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B123" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минпросвещения России от 04.04.2025 № 268 "Об утверждении Особенностей режима рабочего времени и времени отдыха педагогических и иных работников организаций, осуществляющих образовательную деятельность по основным и дополнительным общеобразовательным программам, образовательным программам среднего профессионального образования и соответствующим дополнительным профессиональным программам, основным программам профессионального обучения"</t>
+        </is>
+      </c>
+      <c r="C123" s="6" t="inlineStr">
+        <is>
+          <t>п. 4 Особенностей</t>
+        </is>
+      </c>
+      <c r="D123" s="6" t="inlineStr">
+        <is>
+          <t>График работы руководителей образовательной организации</t>
+        </is>
+      </c>
+      <c r="E123" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F123" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G123" s="6" t="inlineStr">
+        <is>
+          <t>Режим работы руководителя с учетом функций по руководству организацией</t>
+        </is>
+      </c>
+      <c r="H123" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I123" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J123" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K123" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L123" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B124" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минпросвещения России от 04.04.2025 № 268 "Об утверждении Особенностей режима рабочего времени и времени отдыха педагогических и иных работников организаций, осуществляющих образовательную деятельность по основным и дополнительным общеобразовательным программам, образовательным программам среднего профессионального образования и соответствующим дополнительным профессиональным программам, основным программам профессионального обучения"</t>
+        </is>
+      </c>
+      <c r="C124" s="6" t="inlineStr">
+        <is>
+          <t>п. 13 Особенностей</t>
+        </is>
+      </c>
+      <c r="D124" s="6" t="inlineStr">
+        <is>
+          <t>Устав и (или) локальный нормативный акт о продолжительности занятий и перерывов (перемен) между ними</t>
+        </is>
+      </c>
+      <c r="E124" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F124" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G124" s="6" t="inlineStr">
+        <is>
+          <t>Продолжительность занятий; перерывы (перемены); возможность спаренных занятий</t>
+        </is>
+      </c>
+      <c r="H124" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I124" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J124" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K124" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L124" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B125" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минпросвещения России от 04.04.2025 № 268 "Об утверждении Особенностей режима рабочего времени и времени отдыха педагогических и иных работников организаций, осуществляющих образовательную деятельность по основным и дополнительным общеобразовательным программам, образовательным программам среднего профессионального образования и соответствующим дополнительным профессиональным программам, основным программам профессионального обучения"</t>
+        </is>
+      </c>
+      <c r="C125" s="6" t="inlineStr">
+        <is>
+          <t>п. 13 Особенностей</t>
+        </is>
+      </c>
+      <c r="D125" s="6" t="inlineStr">
+        <is>
+          <t>Расписание учебных занятий</t>
+        </is>
+      </c>
+      <c r="E125" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F125" s="6" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="G125" s="6" t="inlineStr">
+        <is>
+          <t>Учебные занятия; продолжительность; перерывы; закрепление педагогических работников</t>
+        </is>
+      </c>
+      <c r="H125" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I125" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J125" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K125" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L125" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B126" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минпросвещения России от 04.04.2025 № 268 "Об утверждении Особенностей режима рабочего времени и времени отдыха педагогических и иных работников организаций, осуществляющих образовательную деятельность по основным и дополнительным общеобразовательным программам, образовательным программам среднего профессионального образования и соответствующим дополнительным профессиональным программам, основным программам профессионального обучения"</t>
+        </is>
+      </c>
+      <c r="C126" s="6" t="inlineStr">
+        <is>
+          <t>п. 14–15 Особенностей</t>
+        </is>
+      </c>
+      <c r="D126" s="6" t="inlineStr">
+        <is>
+          <t>График дежурств педагогических работников в организации</t>
+        </is>
+      </c>
+      <c r="E126" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F126" s="6" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="G126" s="6" t="inlineStr">
+        <is>
+          <t>ФИО работников; время дежурства; даты</t>
+        </is>
+      </c>
+      <c r="H126" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I126" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J126" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K126" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L126" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B127" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минпросвещения России от 04.04.2025 № 268 "Об утверждении Особенностей режима рабочего времени и времени отдыха педагогических и иных работников организаций, осуществляющих образовательную деятельность по основным и дополнительным общеобразовательным программам, образовательным программам среднего профессионального образования и соответствующим дополнительным профессиональным программам, основным программам профессионального обучения"</t>
+        </is>
+      </c>
+      <c r="C127" s="6" t="inlineStr">
+        <is>
+          <t>п. 14, 16 Особенностей</t>
+        </is>
+      </c>
+      <c r="D127" s="6" t="inlineStr">
+        <is>
+          <t>Планы и графики организации (методические советы, родительские собрания, мероприятия)</t>
+        </is>
+      </c>
+      <c r="E127" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F127" s="6" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="G127" s="6" t="inlineStr">
+        <is>
+          <t>Виды мероприятий; сроки; участники</t>
+        </is>
+      </c>
+      <c r="H127" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I127" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J127" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K127" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L127" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B128" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минпросвещения России от 04.04.2025 № 268 "Об утверждении Особенностей режима рабочего времени и времени отдыха педагогических и иных работников организаций, осуществляющих образовательную деятельность по основным и дополнительным общеобразовательным программам, образовательным программам среднего профессионального образования и соответствующим дополнительным профессиональным программам, основным программам профессионального обучения"</t>
+        </is>
+      </c>
+      <c r="C128" s="6" t="inlineStr">
+        <is>
+          <t>п. 16 Особенностей</t>
+        </is>
+      </c>
+      <c r="D128" s="6" t="inlineStr">
+        <is>
+          <t>Письменное согласие педагогического работника на выполнение дополнительных видов работ за дополнительную оплату</t>
+        </is>
+      </c>
+      <c r="E128" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F128" s="6" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="G128" s="6" t="inlineStr">
+        <is>
+          <t>Вид дополнительной работы; срок; размер оплаты; дата; подпись</t>
+        </is>
+      </c>
+      <c r="H128" s="6" t="inlineStr">
+        <is>
+          <t>Работник</t>
+        </is>
+      </c>
+      <c r="I128" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J128" s="6" t="inlineStr">
+        <is>
+          <t>Подтверждение (?)</t>
+        </is>
+      </c>
+      <c r="K128" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L128" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B129" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минпросвещения России от 04.04.2025 № 268 "Об утверждении Особенностей режима рабочего времени и времени отдыха педагогических и иных работников организаций, осуществляющих образовательную деятельность по основным и дополнительным общеобразовательным программам, образовательным программам среднего профессионального образования и соответствующим дополнительным профессиональным программам, основным программам профессионального обучения"</t>
+        </is>
+      </c>
+      <c r="C129" s="6" t="inlineStr">
+        <is>
+          <t>п. 16 Особенностей</t>
+        </is>
+      </c>
+      <c r="D129" s="6" t="inlineStr">
+        <is>
+          <t>Трудовой договор (дополнительное соглашение) с указанием содержания, срока и оплаты дополнительной работы</t>
+        </is>
+      </c>
+      <c r="E129" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F129" s="6" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="G129" s="6" t="inlineStr">
+        <is>
+          <t>Содержание дополнительной работы; срок выполнения; размер оплаты</t>
+        </is>
+      </c>
+      <c r="H129" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I129" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J129" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K129" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L129" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B130" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минпросвещения России от 04.04.2025 № 268 "Об утверждении Особенностей режима рабочего времени и времени отдыха педагогических и иных работников организаций, осуществляющих образовательную деятельность по основным и дополнительным общеобразовательным программам, образовательным программам среднего профессионального образования и соответствующим дополнительным профессиональным программам, основным программам профессионального обучения"</t>
+        </is>
+      </c>
+      <c r="C130" s="6" t="inlineStr">
+        <is>
+          <t>п. 16 Особенностей</t>
+        </is>
+      </c>
+      <c r="D130" s="6" t="inlineStr">
+        <is>
+          <t>Трудовой договор (дополнительное соглашение) с указанием содержания, срока и оплаты дополнительной работы</t>
+        </is>
+      </c>
+      <c r="E130" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F130" s="6" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="G130" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H130" s="6" t="inlineStr">
+        <is>
+          <t>Работник</t>
+        </is>
+      </c>
+      <c r="I130" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J130" s="6" t="inlineStr">
+        <is>
+          <t>Подтверждение (?)</t>
+        </is>
+      </c>
+      <c r="K130" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L130" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B131" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минпросвещения России от 04.04.2025 № 268 "Об утверждении Особенностей режима рабочего времени и времени отдыха педагогических и иных работников организаций, осуществляющих образовательную деятельность по основным и дополнительным общеобразовательным программам, образовательным программам среднего профессионального образования и соответствующим дополнительным профессиональным программам, основным программам профессионального обучения"</t>
+        </is>
+      </c>
+      <c r="C131" s="6" t="inlineStr">
+        <is>
+          <t>п. 20 Особенностей</t>
+        </is>
+      </c>
+      <c r="D131" s="6" t="inlineStr">
+        <is>
+          <t>Графики работы педагогических и иных работников</t>
+        </is>
+      </c>
+      <c r="E131" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F131" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G131" s="6" t="inlineStr">
+        <is>
+          <t>ФИО (должности) работников; даты; время начала и окончания работы (смены); перерывы; выходные; срок, на который составлен график</t>
+        </is>
+      </c>
+      <c r="H131" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I131" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J131" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K131" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L131" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B132" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минпросвещения России от 04.04.2025 № 268 "Об утверждении Особенностей режима рабочего времени и времени отдыха педагогических и иных работников организаций, осуществляющих образовательную деятельность по основным и дополнительным общеобразовательным программам, образовательным программам среднего профессионального образования и соответствующим дополнительным профессиональным программам, основным программам профессионального обучения"</t>
+        </is>
+      </c>
+      <c r="C132" s="6" t="inlineStr">
+        <is>
+          <t>п. 22 Особенностей</t>
+        </is>
+      </c>
+      <c r="D132" s="6" t="inlineStr">
+        <is>
+          <t>Письменное заявление педагогического работника о допущении длительных перерывов между занятиями при составлении расписания</t>
+        </is>
+      </c>
+      <c r="E132" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F132" s="6" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="G132" s="6" t="inlineStr">
+        <is>
+          <t>Просьба о длительных перерывах; период; подпись работника</t>
+        </is>
+      </c>
+      <c r="H132" s="6" t="inlineStr">
+        <is>
+          <t>Работник</t>
+        </is>
+      </c>
+      <c r="I132" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J132" s="6" t="inlineStr">
+        <is>
+          <t>Заявление</t>
+        </is>
+      </c>
+      <c r="K132" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L132" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B133" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минпросвещения России от 04.04.2025 № 268 "Об утверждении Особенностей режима рабочего времени и времени отдыха педагогических и иных работников организаций, осуществляющих образовательную деятельность по основным и дополнительным общеобразовательным программам, образовательным программам среднего профессионального образования и соответствующим дополнительным профессиональным программам, основным программам профессионального обучения"</t>
+        </is>
+      </c>
+      <c r="C133" s="6" t="inlineStr">
+        <is>
+          <t>п. 23 Особенностей</t>
+        </is>
+      </c>
+      <c r="D133" s="6" t="inlineStr">
+        <is>
+          <t>Локальный нормативный акт о режиме рабочего дня с разделением на части для воспитателей (круглосуточное пребывание обучающихся)</t>
+        </is>
+      </c>
+      <c r="E133" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F133" s="6" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="G133" s="6" t="inlineStr">
+        <is>
+          <t>Порядок разделения дня; компенсация неудобного режима</t>
+        </is>
+      </c>
+      <c r="H133" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I133" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J133" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K133" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L133" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B134" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минпросвещения России от 04.04.2025 № 268 "Об утверждении Особенностей режима рабочего времени и времени отдыха педагогических и иных работников организаций, осуществляющих образовательную деятельность по основным и дополнительным общеобразовательным программам, образовательным программам среднего профессионального образования и соответствующим дополнительным профессиональным программам, основным программам профессионального обучения"</t>
+        </is>
+      </c>
+      <c r="C134" s="6" t="inlineStr">
+        <is>
+          <t>п. 23 Особенностей</t>
+        </is>
+      </c>
+      <c r="D134" s="6" t="inlineStr">
+        <is>
+          <t>Локальный нормативный акт о режиме рабочего дня с разделением на части для воспитателей (круглосуточное пребывание обучающихся)</t>
+        </is>
+      </c>
+      <c r="E134" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F134" s="6" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="G134" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H134" s="6" t="inlineStr">
+        <is>
+          <t>Выборный орган первичной профсоюзной организации / иной представительный орган работников</t>
+        </is>
+      </c>
+      <c r="I134" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J134" s="6" t="inlineStr">
+        <is>
+          <t>Согласование</t>
+        </is>
+      </c>
+      <c r="K134" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L134" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B135" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минпросвещения России от 04.04.2025 № 268 "Об утверждении Особенностей режима рабочего времени и времени отдыха педагогических и иных работников организаций, осуществляющих образовательную деятельность по основным и дополнительным общеобразовательным программам, образовательным программам среднего профессионального образования и соответствующим дополнительным профессиональным программам, основным программам профессионального обучения"</t>
+        </is>
+      </c>
+      <c r="C135" s="6" t="inlineStr">
+        <is>
+          <t>п. 34–35 Особенностей</t>
+        </is>
+      </c>
+      <c r="D135" s="6" t="inlineStr">
+        <is>
+          <t>Локальные нормативные акты и графики работы в каникулярное время</t>
+        </is>
+      </c>
+      <c r="E135" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F135" s="6" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="G135" s="6" t="inlineStr">
+        <is>
+          <t>Характер и особенности работы в каникулярное время; режим; категории работников</t>
+        </is>
+      </c>
+      <c r="H135" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I135" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J135" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K135" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L135" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B136" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минпросвещения России от 04.04.2025 № 268 "Об утверждении Особенностей режима рабочего времени и времени отдыха педагогических и иных работников организаций, осуществляющих образовательную деятельность по основным и дополнительным общеобразовательным программам, образовательным программам среднего профессионального образования и соответствующим дополнительным профессиональным программам, основным программам профессионального обучения"</t>
+        </is>
+      </c>
+      <c r="C136" s="6" t="inlineStr">
+        <is>
+          <t>п. 35 Особенностей</t>
+        </is>
+      </c>
+      <c r="D136" s="6" t="inlineStr">
+        <is>
+          <t>Письменное согласие педагогического работника на введение суммированного учета рабочего времени в каникулярное время</t>
+        </is>
+      </c>
+      <c r="E136" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F136" s="6" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="G136" s="6" t="inlineStr">
+        <is>
+          <t>ФИО; период; условия; дата; подпись</t>
+        </is>
+      </c>
+      <c r="H136" s="6" t="inlineStr">
+        <is>
+          <t>Работник</t>
+        </is>
+      </c>
+      <c r="I136" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J136" s="6" t="inlineStr">
+        <is>
+          <t>Подтверждение (?)</t>
+        </is>
+      </c>
+      <c r="K136" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L136" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B137" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минфина России от 31.03.2025 № 39н "Об утверждении Особенностей режима рабочего времени и времени отдыха работников субъектов добычи драгоценных металлов и субъектов добычи драгоценных камней, осуществляющих добычу драгоценных металлов и драгоценных камней из коренных (рудных), россыпных и техногенных месторождений"</t>
+        </is>
+      </c>
+      <c r="C137" s="6" t="inlineStr">
+        <is>
+          <t>п. 1 Особенностей</t>
+        </is>
+      </c>
+      <c r="D137" s="6" t="inlineStr">
+        <is>
+          <t>Правила внутреннего трудового распорядка (с особенностями режима рабочего времени и времени отдыха работников субъектов добычи драгоценных металлов и драгоценных камней)</t>
+        </is>
+      </c>
+      <c r="E137" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F137" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G137" s="6" t="inlineStr">
+        <is>
+          <t>Продолжительность рабочей недели / смены; время начала и окончания работы; перерывы; число смен; чередование рабочих и нерабочих дней; иные особенности режима</t>
+        </is>
+      </c>
+      <c r="H137" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I137" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J137" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K137" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L137" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B138" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минфина России от 31.03.2025 № 39н "Об утверждении Особенностей режима рабочего времени и времени отдыха работников субъектов добычи драгоценных металлов и субъектов добычи драгоценных камней, осуществляющих добычу драгоценных металлов и драгоценных камней из коренных (рудных), россыпных и техногенных месторождений"</t>
+        </is>
+      </c>
+      <c r="C138" s="6" t="inlineStr">
+        <is>
+          <t>п. 1 Особенностей</t>
+        </is>
+      </c>
+      <c r="D138" s="6" t="inlineStr">
+        <is>
+          <t>Графики работы и (или) графики сменности работников субъектов добычи драгоценных металлов и драгоценных камней</t>
+        </is>
+      </c>
+      <c r="E138" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F138" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G138" s="6" t="inlineStr">
+        <is>
+          <t>ФИО (должности) работников; даты; время начала и окончания работы (смены); перерывы; выходные; срок, на который составлен график</t>
+        </is>
+      </c>
+      <c r="H138" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I138" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J138" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K138" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L138" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B139" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтранса России от 21.03.2025 № 97 "Об утверждении Особенностей режима рабочего времени и времени отдыха отдельных категорий работников федерального государственного унитарного предприятия "Управление ведомственной охраны Министерства транспорта Российской Федерации", имеющих особый характер работы"</t>
+        </is>
+      </c>
+      <c r="C139" s="6" t="inlineStr">
+        <is>
+          <t>п. 1 Особенностей (Положения)</t>
+        </is>
+      </c>
+      <c r="D139" s="6" t="inlineStr">
+        <is>
+          <t>Правила внутреннего трудового распорядка (с особенностями режима рабочего времени и времени отдыха работников ведомственной охраны Минтранса России)</t>
+        </is>
+      </c>
+      <c r="E139" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F139" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G139" s="6" t="inlineStr">
+        <is>
+          <t>Продолжительность рабочей недели / смены; время начала и окончания работы; перерывы; число смен; чередование рабочих и нерабочих дней; иные особенности режима</t>
+        </is>
+      </c>
+      <c r="H139" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I139" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J139" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K139" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L139" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B140" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтранса России от 21.03.2025 № 97 "Об утверждении Особенностей режима рабочего времени и времени отдыха отдельных категорий работников федерального государственного унитарного предприятия "Управление ведомственной охраны Министерства транспорта Российской Федерации", имеющих особый характер работы"</t>
+        </is>
+      </c>
+      <c r="C140" s="6" t="inlineStr">
+        <is>
+          <t>п. 1 Особенностей (Положения)</t>
+        </is>
+      </c>
+      <c r="D140" s="6" t="inlineStr">
+        <is>
+          <t>Графики работы и (или) графики сменности (работников ведомственной охраны Минтранса России)</t>
+        </is>
+      </c>
+      <c r="E140" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F140" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G140" s="6" t="inlineStr">
+        <is>
+          <t>ФИО (должности) работников; даты; время начала и окончания работы (смены); перерывы; выходные; срок, на который составлен график</t>
+        </is>
+      </c>
+      <c r="H140" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I140" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J140" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K140" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L140" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B141" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтранса России от 17.03.2025 № 93 "Об утверждении Особенностей режима рабочего времени и времени отдыха отдельных категорий работников федерального государственного предприятия "Ведомственная охрана железнодорожного транспорта Российской Федерации", имеющих особый характер работы"</t>
+        </is>
+      </c>
+      <c r="C141" s="6" t="inlineStr">
+        <is>
+          <t>п. 1 Особенностей (Положения)</t>
+        </is>
+      </c>
+      <c r="D141" s="6" t="inlineStr">
+        <is>
+          <t>Правила внутреннего трудового распорядка (с особенностями режима рабочего времени и времени отдыха работников ведомственной охраны железнодорожного транспорта)</t>
+        </is>
+      </c>
+      <c r="E141" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F141" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G141" s="6" t="inlineStr">
+        <is>
+          <t>Продолжительность рабочей недели / смены; время начала и окончания работы; перерывы; число смен; чередование рабочих и нерабочих дней; иные особенности режима</t>
+        </is>
+      </c>
+      <c r="H141" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I141" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J141" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K141" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L141" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B142" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтранса России от 17.03.2025 № 93 "Об утверждении Особенностей режима рабочего времени и времени отдыха отдельных категорий работников федерального государственного предприятия "Ведомственная охрана железнодорожного транспорта Российской Федерации", имеющих особый характер работы"</t>
+        </is>
+      </c>
+      <c r="C142" s="6" t="inlineStr">
+        <is>
+          <t>п. 1 Особенностей (Положения)</t>
+        </is>
+      </c>
+      <c r="D142" s="6" t="inlineStr">
+        <is>
+          <t>Графики работы и (или) графики сменности (работников ведомственной охраны железнодорожного транспорта)</t>
+        </is>
+      </c>
+      <c r="E142" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F142" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G142" s="6" t="inlineStr">
+        <is>
+          <t>ФИО (должности) работников; даты; время начала и окончания работы (смены); перерывы; выходные; срок, на который составлен график</t>
+        </is>
+      </c>
+      <c r="H142" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I142" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J142" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K142" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L142" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B143" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтранса России от 14.03.2025 № 89 "Об утверждении Особенностей режима рабочего времени и времени отдыха работников, занятых на погрузочно-разгрузочных работах на морском (речном) транспорте"</t>
+        </is>
+      </c>
+      <c r="C143" s="6" t="inlineStr">
+        <is>
+          <t>п. 1 Особенностей (Положения)</t>
+        </is>
+      </c>
+      <c r="D143" s="6" t="inlineStr">
+        <is>
+          <t>Правила внутреннего трудового распорядка (с особенностями режима рабочего времени и времени отдыха работников, занятых на погрузочно-разгрузочных работах на морском (речном) транспорте)</t>
+        </is>
+      </c>
+      <c r="E143" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F143" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G143" s="6" t="inlineStr">
+        <is>
+          <t>Продолжительность рабочей недели / смены; время начала и окончания работы; перерывы; число смен; чередование рабочих и нерабочих дней; иные особенности режима</t>
+        </is>
+      </c>
+      <c r="H143" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I143" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J143" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K143" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L143" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B144" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтранса России от 14.03.2025 № 89 "Об утверждении Особенностей режима рабочего времени и времени отдыха работников, занятых на погрузочно-разгрузочных работах на морском (речном) транспорте"</t>
+        </is>
+      </c>
+      <c r="C144" s="6" t="inlineStr">
+        <is>
+          <t>п. 1 Особенностей (Положения)</t>
+        </is>
+      </c>
+      <c r="D144" s="6" t="inlineStr">
+        <is>
+          <t>Графики работы и (или) графики сменности (работников, занятых на погрузочно-разгрузочных работах на морском (речном) транспорте)</t>
+        </is>
+      </c>
+      <c r="E144" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F144" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G144" s="6" t="inlineStr">
+        <is>
+          <t>ФИО (должности) работников; даты; время начала и окончания работы (смены); перерывы; выходные; срок, на который составлен график</t>
+        </is>
+      </c>
+      <c r="H144" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I144" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J144" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K144" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L144" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B145" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтруда России от 13.03.2025 № 107н "Об утверждении Особенностей режима рабочего времени и времени отдыха сотрудников Следственного комитета Российской Федерации, замещающих должности, по которым предусмотрено присвоение специальных званий, при сменной работе"</t>
+        </is>
+      </c>
+      <c r="C145" s="6" t="inlineStr">
+        <is>
+          <t>положения Особенностей</t>
+        </is>
+      </c>
+      <c r="D145" s="6" t="inlineStr">
+        <is>
+          <t>График сменности сотрудников Следственного комитета Российской Федерации</t>
+        </is>
+      </c>
+      <c r="E145" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F145" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G145" s="6" t="inlineStr">
+        <is>
+          <t>ФИО (должности) работников; даты; время начала и окончания работы (смены); перерывы; выходные; срок, на который составлен график</t>
+        </is>
+      </c>
+      <c r="H145" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I145" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J145" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K145" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L145" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B146" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтруда России от 13.03.2025 № 107н "Об утверждении Особенностей режима рабочего времени и времени отдыха сотрудников Следственного комитета Российской Федерации, замещающих должности, по которым предусмотрено присвоение специальных званий, при сменной работе"</t>
+        </is>
+      </c>
+      <c r="C146" s="6" t="inlineStr">
+        <is>
+          <t>положения Особенностей</t>
+        </is>
+      </c>
+      <c r="D146" s="6" t="inlineStr">
+        <is>
+          <t>Локальный нормативный акт / служебный распорядок о режиме служебного времени при сменной работе</t>
+        </is>
+      </c>
+      <c r="E146" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F146" s="6" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="G146" s="6" t="inlineStr">
+        <is>
+          <t>Режим служебного времени; структура смены; перерывы и отдых</t>
+        </is>
+      </c>
+      <c r="H146" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I146" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J146" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K146" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L146" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B147" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтранса России от 04.03.2025 № 75 "Об утверждении Особенностей режима рабочего времени и времени отдыха морских лоцманов и кандидатов в морские лоцманы"</t>
+        </is>
+      </c>
+      <c r="C147" s="6" t="inlineStr">
+        <is>
+          <t>п. 1 Особенностей (Положения)</t>
+        </is>
+      </c>
+      <c r="D147" s="6" t="inlineStr">
+        <is>
+          <t>Правила внутреннего трудового распорядка (с особенностями режима рабочего времени и времени отдыха морских лоцманов и кандидатов в морские лоцманы)</t>
+        </is>
+      </c>
+      <c r="E147" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F147" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G147" s="6" t="inlineStr">
+        <is>
+          <t>Продолжительность рабочей недели / смены; время начала и окончания работы; перерывы; число смен; чередование рабочих и нерабочих дней; иные особенности режима</t>
+        </is>
+      </c>
+      <c r="H147" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I147" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J147" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K147" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L147" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B148" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтранса России от 04.03.2025 № 75 "Об утверждении Особенностей режима рабочего времени и времени отдыха морских лоцманов и кандидатов в морские лоцманы"</t>
+        </is>
+      </c>
+      <c r="C148" s="6" t="inlineStr">
+        <is>
+          <t>п. 1 Особенностей (Положения)</t>
+        </is>
+      </c>
+      <c r="D148" s="6" t="inlineStr">
+        <is>
+          <t>Графики работы и (или) графики сменности (морских лоцманов и кандидатов в морские лоцманы)</t>
+        </is>
+      </c>
+      <c r="E148" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F148" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G148" s="6" t="inlineStr">
+        <is>
+          <t>ФИО (должности) работников; даты; время начала и окончания работы (смены); перерывы; выходные; срок, на который составлен график</t>
+        </is>
+      </c>
+      <c r="H148" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I148" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J148" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K148" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L148" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B149" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтранса России от 04.03.2025 № 75 "Об утверждении Особенностей режима рабочего времени и времени отдыха морских лоцманов и кандидатов в морские лоцманы"</t>
+        </is>
+      </c>
+      <c r="C149" s="6" t="inlineStr">
+        <is>
+          <t>положения Особенностей</t>
+        </is>
+      </c>
+      <c r="D149" s="6" t="inlineStr">
+        <is>
+          <t>Графики работы (вахт / дежурств) морских лоцманов и кандидатов в морские лоцманы</t>
+        </is>
+      </c>
+      <c r="E149" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F149" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G149" s="6" t="inlineStr">
+        <is>
+          <t>ФИО (должности) работников; даты; время начала и окончания работы (смены); перерывы; выходные; срок, на который составлен график</t>
+        </is>
+      </c>
+      <c r="H149" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I149" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J149" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K149" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L149" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B150" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтранса России от 11.10.2021 № 339 "Об утверждении Особенностей режима рабочего времени и времени отдыха, условий труда отдельных категорий работников железнодорожного транспорта общего пользования, работа которых непосредственно связана с движением поездов"</t>
+        </is>
+      </c>
+      <c r="C150" s="6" t="inlineStr">
+        <is>
+          <t>п. 2 Особенностей</t>
+        </is>
+      </c>
+      <c r="D150" s="6" t="inlineStr">
+        <is>
+          <t>Коллективный договор (положения о режиме рабочего времени и времени отдыха работников железнодорожного транспорта)</t>
+        </is>
+      </c>
+      <c r="E150" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F150" s="6" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="G150" s="6" t="inlineStr">
+        <is>
+          <t>Продолжительность рабочей недели; ненормированный рабочий день; продолжительность смены; перерывы; сменность</t>
+        </is>
+      </c>
+      <c r="H150" s="6" t="inlineStr">
+        <is>
+          <t>Стороны коллективного договора (представители работодателя и работников)</t>
+        </is>
+      </c>
+      <c r="I150" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J150" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K150" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L150" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B151" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтранса России от 11.10.2021 № 339 "Об утверждении Особенностей режима рабочего времени и времени отдыха, условий труда отдельных категорий работников железнодорожного транспорта общего пользования, работа которых непосредственно связана с движением поездов"</t>
+        </is>
+      </c>
+      <c r="C151" s="6" t="inlineStr">
+        <is>
+          <t>п. 2 Особенностей</t>
+        </is>
+      </c>
+      <c r="D151" s="6" t="inlineStr">
+        <is>
+          <t>Правила внутреннего трудового распорядка (с особенностями режима рабочего времени и времени отдыха работников железнодорожного транспорта)</t>
+        </is>
+      </c>
+      <c r="E151" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F151" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G151" s="6" t="inlineStr">
+        <is>
+          <t>Продолжительность рабочей недели / смены; время начала и окончания работы; перерывы; число смен; чередование рабочих и нерабочих дней; иные особенности режима</t>
+        </is>
+      </c>
+      <c r="H151" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I151" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J151" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K151" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L151" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B152" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтранса России от 11.10.2021 № 339 "Об утверждении Особенностей режима рабочего времени и времени отдыха, условий труда отдельных категорий работников железнодорожного транспорта общего пользования, работа которых непосредственно связана с движением поездов"</t>
+        </is>
+      </c>
+      <c r="C152" s="6" t="inlineStr">
+        <is>
+          <t>п. 2 Особенностей</t>
+        </is>
+      </c>
+      <c r="D152" s="6" t="inlineStr">
+        <is>
+          <t>Графики сменности работников железнодорожного транспорта</t>
+        </is>
+      </c>
+      <c r="E152" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F152" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G152" s="6" t="inlineStr">
+        <is>
+          <t>ФИО (должности) работников; даты; время начала и окончания работы (смены); перерывы; выходные; срок, на который составлен график; режим на месяц / квартал / год при соответствующем учете</t>
+        </is>
+      </c>
+      <c r="H152" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I152" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J152" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K152" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L152" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B153" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтранса России от 11.10.2021 № 339 "Об утверждении Особенностей режима рабочего времени и времени отдыха, условий труда отдельных категорий работников железнодорожного транспорта общего пользования, работа которых непосредственно связана с движением поездов"</t>
+        </is>
+      </c>
+      <c r="C153" s="6" t="inlineStr">
+        <is>
+          <t>п. 2 Особенностей</t>
+        </is>
+      </c>
+      <c r="D153" s="6" t="inlineStr">
+        <is>
+          <t>Графики сменности работников железнодорожного транспорта</t>
+        </is>
+      </c>
+      <c r="E153" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F153" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G153" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H153" s="6" t="inlineStr">
+        <is>
+          <t>Выборный орган первичной профсоюзной организации / иной представительный орган работников</t>
+        </is>
+      </c>
+      <c r="I153" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J153" s="6" t="inlineStr">
+        <is>
+          <t>Согласование</t>
+        </is>
+      </c>
+      <c r="K153" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L153" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B154" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтранса России от 11.10.2021 № 339 "Об утверждении Особенностей режима рабочего времени и времени отдыха, условий труда отдельных категорий работников железнодорожного транспорта общего пользования, работа которых непосредственно связана с движением поездов"</t>
+        </is>
+      </c>
+      <c r="C154" s="6" t="inlineStr">
+        <is>
+          <t>п. 2 Особенностей</t>
+        </is>
+      </c>
+      <c r="D154" s="6" t="inlineStr">
+        <is>
+          <t>Лист ознакомления (отметки о доведении) графиков сменности до сведения работников</t>
+        </is>
+      </c>
+      <c r="E154" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F154" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G154" s="6" t="inlineStr">
+        <is>
+          <t>ФИО работника; дата; подпись; доведение не позднее чем за 1 месяц до введения в действие</t>
+        </is>
+      </c>
+      <c r="H154" s="6" t="inlineStr">
+        <is>
+          <t>Работник</t>
+        </is>
+      </c>
+      <c r="I154" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J154" s="6" t="inlineStr">
+        <is>
+          <t>Ознакомление</t>
+        </is>
+      </c>
+      <c r="K154" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L154" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B155" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтранса России от 11.10.2021 № 339 "Об утверждении Особенностей режима рабочего времени и времени отдыха, условий труда отдельных категорий работников железнодорожного транспорта общего пользования, работа которых непосредственно связана с движением поездов"</t>
+        </is>
+      </c>
+      <c r="C155" s="6" t="inlineStr">
+        <is>
+          <t>п. 3 Особенностей</t>
+        </is>
+      </c>
+      <c r="D155" s="6" t="inlineStr">
+        <is>
+          <t>Приказ (локальный нормативный акт) / ПВТР о порядке введения суммированного учета рабочего времени</t>
+        </is>
+      </c>
+      <c r="E155" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F155" s="6" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="G155" s="6" t="inlineStr">
+        <is>
+          <t>Учетный период; категории работников; порядок введения суммированного учета</t>
+        </is>
+      </c>
+      <c r="H155" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I155" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J155" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K155" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L155" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B156" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтранса России от 11.10.2021 № 339 "Об утверждении Особенностей режима рабочего времени и времени отдыха, условий труда отдельных категорий работников железнодорожного транспорта общего пользования, работа которых непосредственно связана с движением поездов"</t>
+        </is>
+      </c>
+      <c r="C156" s="6" t="inlineStr">
+        <is>
+          <t>п. 5 Особенностей</t>
+        </is>
+      </c>
+      <c r="D156" s="6" t="inlineStr">
+        <is>
+          <t>Локальный нормативный акт — перечень железнодорожных линий (участков инфраструктуры), ремонт и техническое обслуживание которых организованы преимущественно в ночное время</t>
+        </is>
+      </c>
+      <c r="E156" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F156" s="6" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="G156" s="6" t="inlineStr">
+        <is>
+          <t>Перечень линий (участков); обоснование ночного режима работ</t>
+        </is>
+      </c>
+      <c r="H156" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I156" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J156" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K156" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L156" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B157" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтранса России от 11.10.2021 № 339 "Об утверждении Особенностей режима рабочего времени и времени отдыха, условий труда отдельных категорий работников железнодорожного транспорта общего пользования, работа которых непосредственно связана с движением поездов"</t>
+        </is>
+      </c>
+      <c r="C157" s="6" t="inlineStr">
+        <is>
+          <t>п. 5 Особенностей</t>
+        </is>
+      </c>
+      <c r="D157" s="6" t="inlineStr">
+        <is>
+          <t>Локальный нормативный акт — перечень железнодорожных линий (участков инфраструктуры), ремонт и техническое обслуживание которых организованы преимущественно в ночное время</t>
+        </is>
+      </c>
+      <c r="E157" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F157" s="6" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="G157" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H157" s="6" t="inlineStr">
+        <is>
+          <t>Выборный орган первичной профсоюзной организации / иной представительный орган работников</t>
+        </is>
+      </c>
+      <c r="I157" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J157" s="6" t="inlineStr">
+        <is>
+          <t>Согласование</t>
+        </is>
+      </c>
+      <c r="K157" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L157" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B158" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтранса России от 11.10.2021 № 339 "Об утверждении Особенностей режима рабочего времени и времени отдыха, условий труда отдельных категорий работников железнодорожного транспорта общего пользования, работа которых непосредственно связана с движением поездов"</t>
+        </is>
+      </c>
+      <c r="C158" s="6" t="inlineStr">
+        <is>
+          <t>п. 6 Особенностей</t>
+        </is>
+      </c>
+      <c r="D158" s="6" t="inlineStr">
+        <is>
+          <t>Перечень работ, на которых невозможно предоставление перерыва для отдыха и питания, и места для отдыха и приема пищи (в составе ПВТР)</t>
+        </is>
+      </c>
+      <c r="E158" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F158" s="6" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="G158" s="6" t="inlineStr">
+        <is>
+          <t>Перечень работ; места для отдыха и приема пищи</t>
+        </is>
+      </c>
+      <c r="H158" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I158" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J158" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K158" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L158" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B159" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтранса России от 11.10.2021 № 339 "Об утверждении Особенностей режима рабочего времени и времени отдыха, условий труда отдельных категорий работников железнодорожного транспорта общего пользования, работа которых непосредственно связана с движением поездов"</t>
+        </is>
+      </c>
+      <c r="C159" s="6" t="inlineStr">
+        <is>
+          <t>п. 8 Особенностей</t>
+        </is>
+      </c>
+      <c r="D159" s="6" t="inlineStr">
+        <is>
+          <t>Положение о дежурстве (на дому / в специально оборудованной комнате / в купе вагона)</t>
+        </is>
+      </c>
+      <c r="E159" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F159" s="6" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="G159" s="6" t="inlineStr">
+        <is>
+          <t>Порядок дежурства; категории работников; учет рабочего времени; условия вызова на работу</t>
+        </is>
+      </c>
+      <c r="H159" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I159" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J159" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K159" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L159" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B160" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтранса России от 11.10.2021 № 339 "Об утверждении Особенностей режима рабочего времени и времени отдыха, условий труда отдельных категорий работников железнодорожного транспорта общего пользования, работа которых непосредственно связана с движением поездов"</t>
+        </is>
+      </c>
+      <c r="C160" s="6" t="inlineStr">
+        <is>
+          <t>п. 8 Особенностей</t>
+        </is>
+      </c>
+      <c r="D160" s="6" t="inlineStr">
+        <is>
+          <t>Положение о дежурстве (на дому / в специально оборудованной комнате / в купе вагона)</t>
+        </is>
+      </c>
+      <c r="E160" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F160" s="6" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="G160" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H160" s="6" t="inlineStr">
+        <is>
+          <t>Выборный орган первичной профсоюзной организации / иной представительный орган работников</t>
+        </is>
+      </c>
+      <c r="I160" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J160" s="6" t="inlineStr">
+        <is>
+          <t>Согласование</t>
+        </is>
+      </c>
+      <c r="K160" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L160" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B161" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтранса России от 11.10.2021 № 339 "Об утверждении Особенностей режима рабочего времени и времени отдыха, условий труда отдельных категорий работников железнодорожного транспорта общего пользования, работа которых непосредственно связана с движением поездов"</t>
+        </is>
+      </c>
+      <c r="C161" s="6" t="inlineStr">
+        <is>
+          <t>п. 8 Особенностей</t>
+        </is>
+      </c>
+      <c r="D161" s="6" t="inlineStr">
+        <is>
+          <t>Письменное согласие работника на дежурство на дому / в специально оборудованной комнате / в купе вагона</t>
+        </is>
+      </c>
+      <c r="E161" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F161" s="6" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="G161" s="6" t="inlineStr">
+        <is>
+          <t>ФИО работника; вид дежурства; период; дата; подпись</t>
+        </is>
+      </c>
+      <c r="H161" s="6" t="inlineStr">
+        <is>
+          <t>Работник</t>
+        </is>
+      </c>
+      <c r="I161" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J161" s="6" t="inlineStr">
+        <is>
+          <t>Подтверждение (?)</t>
+        </is>
+      </c>
+      <c r="K161" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L161" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B162" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтранса России от 11.10.2021 № 339 "Об утверждении Особенностей режима рабочего времени и времени отдыха, условий труда отдельных категорий работников железнодорожного транспорта общего пользования, работа которых непосредственно связана с движением поездов"</t>
+        </is>
+      </c>
+      <c r="C162" s="6" t="inlineStr">
+        <is>
+          <t>п. 10, 12–13 Особенностей</t>
+        </is>
+      </c>
+      <c r="D162" s="6" t="inlineStr">
+        <is>
+          <t>Наряд / вызов работников (в т.ч. локомотивных бригад) и порядок вызова</t>
+        </is>
+      </c>
+      <c r="E162" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F162" s="6" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="G162" s="6" t="inlineStr">
+        <is>
+          <t>Время явки; место явки; работник; основание вызова</t>
+        </is>
+      </c>
+      <c r="H162" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель / уполномоченное должностное лицо</t>
+        </is>
+      </c>
+      <c r="I162" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J162" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K162" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L162" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B163" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтранса России от 11.10.2021 № 339 "Об утверждении Особенностей режима рабочего времени и времени отдыха, условий труда отдельных категорий работников железнодорожного транспорта общего пользования, работа которых непосредственно связана с движением поездов"</t>
+        </is>
+      </c>
+      <c r="C163" s="6" t="inlineStr">
+        <is>
+          <t>п. 15 Особенностей</t>
+        </is>
+      </c>
+      <c r="D163" s="6" t="inlineStr">
+        <is>
+          <t>Локальный нормативный акт об установлении предельно допустимого времени нахождения локомотивных бригад на работе с момента явки</t>
+        </is>
+      </c>
+      <c r="E163" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F163" s="6" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="G163" s="6" t="inlineStr">
+        <is>
+          <t>Пункт явки; предельно допустимое время нахождения; запрет отправления по его истечении</t>
+        </is>
+      </c>
+      <c r="H163" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I163" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J163" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K163" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L163" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B164" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтранса России от 11.10.2021 № 339 "Об утверждении Особенностей режима рабочего времени и времени отдыха, условий труда отдельных категорий работников железнодорожного транспорта общего пользования, работа которых непосредственно связана с движением поездов"</t>
+        </is>
+      </c>
+      <c r="C164" s="6" t="inlineStr">
+        <is>
+          <t>п. 15 Особенностей</t>
+        </is>
+      </c>
+      <c r="D164" s="6" t="inlineStr">
+        <is>
+          <t>Локальный нормативный акт об установлении предельно допустимого времени нахождения локомотивных бригад на работе с момента явки</t>
+        </is>
+      </c>
+      <c r="E164" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F164" s="6" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="G164" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H164" s="6" t="inlineStr">
+        <is>
+          <t>Выборный орган первичной профсоюзной организации / иной представительный орган работников</t>
+        </is>
+      </c>
+      <c r="I164" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J164" s="6" t="inlineStr">
+        <is>
+          <t>Согласование</t>
+        </is>
+      </c>
+      <c r="K164" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L164" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B165" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтранса России от 11.10.2021 № 339 "Об утверждении Особенностей режима рабочего времени и времени отдыха, условий труда отдельных категорий работников железнодорожного транспорта общего пользования, работа которых непосредственно связана с движением поездов"</t>
+        </is>
+      </c>
+      <c r="C165" s="6" t="inlineStr">
+        <is>
+          <t>п. 16 Особенностей</t>
+        </is>
+      </c>
+      <c r="D165" s="6" t="inlineStr">
+        <is>
+          <t>Порядок установления продолжительности непрерывной работы локомотивных бригад / изменения режима в период действия графика сменности</t>
+        </is>
+      </c>
+      <c r="E165" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F165" s="6" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="G165" s="6" t="inlineStr">
+        <is>
+          <t>Условия увеличения непрерывной работы; порядок изменения режима</t>
+        </is>
+      </c>
+      <c r="H165" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I165" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J165" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K165" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L165" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B166" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтранса России от 11.10.2021 № 339 "Об утверждении Особенностей режима рабочего времени и времени отдыха, условий труда отдельных категорий работников железнодорожного транспорта общего пользования, работа которых непосредственно связана с движением поездов"</t>
+        </is>
+      </c>
+      <c r="C166" s="6" t="inlineStr">
+        <is>
+          <t>п. 16 Особенностей</t>
+        </is>
+      </c>
+      <c r="D166" s="6" t="inlineStr">
+        <is>
+          <t>Порядок установления продолжительности непрерывной работы локомотивных бригад / изменения режима в период действия графика сменности</t>
+        </is>
+      </c>
+      <c r="E166" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F166" s="6" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="G166" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H166" s="6" t="inlineStr">
+        <is>
+          <t>Выборный орган первичной профсоюзной организации / иной представительный орган работников</t>
+        </is>
+      </c>
+      <c r="I166" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J166" s="6" t="inlineStr">
+        <is>
+          <t>Согласование</t>
+        </is>
+      </c>
+      <c r="K166" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L166" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B167" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтранса России от 11.10.2021 № 339 "Об утверждении Особенностей режима рабочего времени и времени отдыха, условий труда отдельных категорий работников железнодорожного транспорта общего пользования, работа которых непосредственно связана с движением поездов"</t>
+        </is>
+      </c>
+      <c r="C167" s="6" t="inlineStr">
+        <is>
+          <t>п. 22 Особенностей</t>
+        </is>
+      </c>
+      <c r="D167" s="6" t="inlineStr">
+        <is>
+          <t>Графики сменности работников поездных бригад пассажирских поездов (на каждый поезд)</t>
+        </is>
+      </c>
+      <c r="E167" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F167" s="6" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="G167" s="6" t="inlineStr">
+        <is>
+          <t>Состав бригады; продолжительность смен в рейсе; местные условия</t>
+        </is>
+      </c>
+      <c r="H167" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I167" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J167" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K167" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L167" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B168" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтранса России от 11.10.2021 № 339 "Об утверждении Особенностей режима рабочего времени и времени отдыха, условий труда отдельных категорий работников железнодорожного транспорта общего пользования, работа которых непосредственно связана с движением поездов"</t>
+        </is>
+      </c>
+      <c r="C168" s="6" t="inlineStr">
+        <is>
+          <t>п. 22 Особенностей</t>
+        </is>
+      </c>
+      <c r="D168" s="6" t="inlineStr">
+        <is>
+          <t>Графики сменности работников поездных бригад пассажирских поездов (на каждый поезд)</t>
+        </is>
+      </c>
+      <c r="E168" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F168" s="6" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="G168" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H168" s="6" t="inlineStr">
+        <is>
+          <t>Выборный орган первичной профсоюзной организации / иной представительный орган работников</t>
+        </is>
+      </c>
+      <c r="I168" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J168" s="6" t="inlineStr">
+        <is>
+          <t>Согласование</t>
+        </is>
+      </c>
+      <c r="K168" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L168" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B169" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтранса России от 11.10.2021 № 339 "Об утверждении Особенностей режима рабочего времени и времени отдыха, условий труда отдельных категорий работников железнодорожного транспорта общего пользования, работа которых непосредственно связана с движением поездов"</t>
+        </is>
+      </c>
+      <c r="C169" s="6" t="inlineStr">
+        <is>
+          <t>п. 23 Особенностей</t>
+        </is>
+      </c>
+      <c r="D169" s="6" t="inlineStr">
+        <is>
+          <t>Графики дежурств в рейсе работников поездных бригад пассажирских поездов (на каждый поезд)</t>
+        </is>
+      </c>
+      <c r="E169" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F169" s="6" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="G169" s="6" t="inlineStr">
+        <is>
+          <t>Состав; продолжительность дежурств в рейсе; местные условия</t>
+        </is>
+      </c>
+      <c r="H169" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I169" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J169" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K169" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L169" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B170" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтранса России от 11.10.2021 № 339 "Об утверждении Особенностей режима рабочего времени и времени отдыха, условий труда отдельных категорий работников железнодорожного транспорта общего пользования, работа которых непосредственно связана с движением поездов"</t>
+        </is>
+      </c>
+      <c r="C170" s="6" t="inlineStr">
+        <is>
+          <t>п. 23 Особенностей</t>
+        </is>
+      </c>
+      <c r="D170" s="6" t="inlineStr">
+        <is>
+          <t>Графики дежурств в рейсе работников поездных бригад пассажирских поездов (на каждый поезд)</t>
+        </is>
+      </c>
+      <c r="E170" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F170" s="6" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="G170" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H170" s="6" t="inlineStr">
+        <is>
+          <t>Выборный орган первичной профсоюзной организации / иной представительный орган работников</t>
+        </is>
+      </c>
+      <c r="I170" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J170" s="6" t="inlineStr">
+        <is>
+          <t>Согласование</t>
+        </is>
+      </c>
+      <c r="K170" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L170" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B171" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтранса России от 11.10.2021 № 339 "Об утверждении Особенностей режима рабочего времени и времени отдыха, условий труда отдельных категорий работников железнодорожного транспорта общего пользования, работа которых непосредственно связана с движением поездов"</t>
+        </is>
+      </c>
+      <c r="C171" s="6" t="inlineStr">
+        <is>
+          <t>п. 25 Особенностей</t>
+        </is>
+      </c>
+      <c r="D171" s="6" t="inlineStr">
+        <is>
+          <t>Локальный нормативный акт о продолжительности поездки и порядке ее увеличения</t>
+        </is>
+      </c>
+      <c r="E171" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F171" s="6" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="G171" s="6" t="inlineStr">
+        <is>
+          <t>Продолжительность поездки; порядок увеличения срока</t>
+        </is>
+      </c>
+      <c r="H171" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I171" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J171" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K171" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L171" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B172" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтранса России от 11.10.2021 № 339 "Об утверждении Особенностей режима рабочего времени и времени отдыха, условий труда отдельных категорий работников железнодорожного транспорта общего пользования, работа которых непосредственно связана с движением поездов"</t>
+        </is>
+      </c>
+      <c r="C172" s="6" t="inlineStr">
+        <is>
+          <t>п. 25 Особенностей</t>
+        </is>
+      </c>
+      <c r="D172" s="6" t="inlineStr">
+        <is>
+          <t>Локальный нормативный акт о продолжительности поездки и порядке ее увеличения</t>
+        </is>
+      </c>
+      <c r="E172" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F172" s="6" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="G172" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H172" s="6" t="inlineStr">
+        <is>
+          <t>Выборный орган первичной профсоюзной организации / иной представительный орган работников</t>
+        </is>
+      </c>
+      <c r="I172" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J172" s="6" t="inlineStr">
+        <is>
+          <t>Согласование</t>
+        </is>
+      </c>
+      <c r="K172" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L172" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B173" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтранса России от 11.10.2021 № 339 "Об утверждении Особенностей режима рабочего времени и времени отдыха, условий труда отдельных категорий работников железнодорожного транспорта общего пользования, работа которых непосредственно связана с движением поездов"</t>
+        </is>
+      </c>
+      <c r="C173" s="6" t="inlineStr">
+        <is>
+          <t>п. 25 Особенностей</t>
+        </is>
+      </c>
+      <c r="D173" s="6" t="inlineStr">
+        <is>
+          <t>Письменное согласие работников поездных бригад на увеличение продолжительности поездки</t>
+        </is>
+      </c>
+      <c r="E173" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F173" s="6" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="G173" s="6" t="inlineStr">
+        <is>
+          <t>ФИО работников; срок увеличения; дата; подпись</t>
+        </is>
+      </c>
+      <c r="H173" s="6" t="inlineStr">
+        <is>
+          <t>Работник</t>
+        </is>
+      </c>
+      <c r="I173" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J173" s="6" t="inlineStr">
+        <is>
+          <t>Подтверждение (?)</t>
+        </is>
+      </c>
+      <c r="K173" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L173" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B174" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтранса России от 16.10.2020 № 424 "Об утверждении Особенностей режима рабочего времени и времени отдыха, условий труда водителей автомобилей"</t>
+        </is>
+      </c>
+      <c r="C174" s="6" t="inlineStr">
+        <is>
+          <t>п. 1 Особенностей</t>
+        </is>
+      </c>
+      <c r="D174" s="6" t="inlineStr">
+        <is>
+          <t>Правила внутреннего трудового распорядка (с особенностями режима рабочего времени и времени отдыха водителей автомобилей)</t>
+        </is>
+      </c>
+      <c r="E174" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F174" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G174" s="6" t="inlineStr">
+        <is>
+          <t>Продолжительность рабочей недели / смены; время начала и окончания работы; перерывы; число смен; чередование рабочих и нерабочих дней; иные особенности режима</t>
+        </is>
+      </c>
+      <c r="H174" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I174" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J174" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K174" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L174" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B175" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтранса России от 16.10.2020 № 424 "Об утверждении Особенностей режима рабочего времени и времени отдыха, условий труда водителей автомобилей"</t>
+        </is>
+      </c>
+      <c r="C175" s="6" t="inlineStr">
+        <is>
+          <t>п. 1 Особенностей</t>
+        </is>
+      </c>
+      <c r="D175" s="6" t="inlineStr">
+        <is>
+          <t>Графики работы и (или) графики сменности водителей автомобилей</t>
+        </is>
+      </c>
+      <c r="E175" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F175" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G175" s="6" t="inlineStr">
+        <is>
+          <t>ФИО (должности) работников; даты; время начала и окончания работы (смены); перерывы; выходные; срок, на который составлен график</t>
+        </is>
+      </c>
+      <c r="H175" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I175" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J175" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K175" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L175" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B176" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтранса России от 16.10.2020 № 424 "Об утверждении Особенностей режима рабочего времени и времени отдыха, условий труда водителей автомобилей"</t>
+        </is>
+      </c>
+      <c r="C176" s="6" t="inlineStr">
+        <is>
+          <t>п. 3 Особенностей</t>
+        </is>
+      </c>
+      <c r="D176" s="6" t="inlineStr">
+        <is>
+          <t>Приказ (локальный нормативный акт) о введении суммированного учета рабочего времени водителей</t>
+        </is>
+      </c>
+      <c r="E176" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F176" s="6" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="G176" s="6" t="inlineStr">
+        <is>
+          <t>Учетный период; категории водителей; порядок учета</t>
+        </is>
+      </c>
+      <c r="H176" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I176" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J176" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K176" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L176" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B177" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтранса России от 16.10.2020 № 424 "Об утверждении Особенностей режима рабочего времени и времени отдыха, условий труда водителей автомобилей"</t>
+        </is>
+      </c>
+      <c r="C177" s="6" t="inlineStr">
+        <is>
+          <t>п. 5 Особенностей</t>
+        </is>
+      </c>
+      <c r="D177" s="6" t="inlineStr">
+        <is>
+          <t>Локальный нормативный акт о разделении рабочего дня (смены) водителя на части</t>
+        </is>
+      </c>
+      <c r="E177" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F177" s="6" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="G177" s="6" t="inlineStr">
+        <is>
+          <t>Порядок разделения дня (смены); перерывы</t>
+        </is>
+      </c>
+      <c r="H177" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I177" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J177" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K177" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L177" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B178" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтранса России от 16.10.2020 № 424 "Об утверждении Особенностей режима рабочего времени и времени отдыха, условий труда водителей автомобилей"</t>
+        </is>
+      </c>
+      <c r="C178" s="6" t="inlineStr">
+        <is>
+          <t>п. 5 Особенностей</t>
+        </is>
+      </c>
+      <c r="D178" s="6" t="inlineStr">
+        <is>
+          <t>Локальный нормативный акт о разделении рабочего дня (смены) водителя на части</t>
+        </is>
+      </c>
+      <c r="E178" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F178" s="6" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="G178" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H178" s="6" t="inlineStr">
+        <is>
+          <t>Выборный орган первичной профсоюзной организации / иной представительный орган работников</t>
+        </is>
+      </c>
+      <c r="I178" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J178" s="6" t="inlineStr">
+        <is>
+          <t>Согласование</t>
+        </is>
+      </c>
+      <c r="K178" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L178" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B179" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтранса России от 16.10.2020 № 424 "Об утверждении Особенностей режима рабочего времени и времени отдыха, условий труда водителей автомобилей"</t>
+        </is>
+      </c>
+      <c r="C179" s="6" t="inlineStr">
+        <is>
+          <t>п. 5 Особенностей</t>
+        </is>
+      </c>
+      <c r="D179" s="6" t="inlineStr">
+        <is>
+          <t>Письменное согласие водителя на разделение рабочего дня (смены) на части</t>
+        </is>
+      </c>
+      <c r="E179" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F179" s="6" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="G179" s="6" t="inlineStr">
+        <is>
+          <t>ФИО водителя; период; условия; дата; подпись</t>
+        </is>
+      </c>
+      <c r="H179" s="6" t="inlineStr">
+        <is>
+          <t>Работник</t>
+        </is>
+      </c>
+      <c r="I179" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J179" s="6" t="inlineStr">
+        <is>
+          <t>Подтверждение (?)</t>
+        </is>
+      </c>
+      <c r="K179" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L179" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B180" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтранса России от 16.10.2020 № 424 "Об утверждении Особенностей режима рабочего времени и времени отдыха, условий труда водителей автомобилей"</t>
+        </is>
+      </c>
+      <c r="C180" s="6" t="inlineStr">
+        <is>
+          <t>п. 15 Особенностей</t>
+        </is>
+      </c>
+      <c r="D180" s="6" t="inlineStr">
+        <is>
+          <t>Локальный нормативный акт о составе и продолжительности иных видов времени, включаемых в рабочее время водителя</t>
+        </is>
+      </c>
+      <c r="E180" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F180" s="6" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="G180" s="6" t="inlineStr">
+        <is>
+          <t>Виды времени; продолжительность</t>
+        </is>
+      </c>
+      <c r="H180" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I180" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J180" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K180" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L180" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B181" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтранса России от 16.10.2020 № 424 "Об утверждении Особенностей режима рабочего времени и времени отдыха, условий труда водителей автомобилей"</t>
+        </is>
+      </c>
+      <c r="C181" s="6" t="inlineStr">
+        <is>
+          <t>п. 15 Особенностей</t>
+        </is>
+      </c>
+      <c r="D181" s="6" t="inlineStr">
+        <is>
+          <t>Локальный нормативный акт о составе и продолжительности иных видов времени, включаемых в рабочее время водителя</t>
+        </is>
+      </c>
+      <c r="E181" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F181" s="6" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="G181" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H181" s="6" t="inlineStr">
+        <is>
+          <t>Выборный орган первичной профсоюзной организации / иной представительный орган работников</t>
+        </is>
+      </c>
+      <c r="I181" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J181" s="6" t="inlineStr">
+        <is>
+          <t>Согласование</t>
+        </is>
+      </c>
+      <c r="K181" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L181" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B182" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтранса России от 02.10.2020 № 404 "Об утверждении Особенностей режима рабочего времени и времени отдыха водителей трамвая и троллейбуса"</t>
+        </is>
+      </c>
+      <c r="C182" s="6" t="inlineStr">
+        <is>
+          <t>п. 1 Особенностей</t>
+        </is>
+      </c>
+      <c r="D182" s="6" t="inlineStr">
+        <is>
+          <t>Правила внутреннего трудового распорядка (с особенностями режима рабочего времени и времени отдыха водителей трамвая и троллейбуса)</t>
+        </is>
+      </c>
+      <c r="E182" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F182" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G182" s="6" t="inlineStr">
+        <is>
+          <t>Продолжительность рабочей недели / смены; время начала и окончания работы; перерывы; число смен; чередование рабочих и нерабочих дней; иные особенности режима</t>
+        </is>
+      </c>
+      <c r="H182" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I182" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J182" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K182" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L182" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B183" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтранса России от 02.10.2020 № 404 "Об утверждении Особенностей режима рабочего времени и времени отдыха водителей трамвая и троллейбуса"</t>
+        </is>
+      </c>
+      <c r="C183" s="6" t="inlineStr">
+        <is>
+          <t>п. 1 Особенностей</t>
+        </is>
+      </c>
+      <c r="D183" s="6" t="inlineStr">
+        <is>
+          <t>Графики работы и (или) графики сменности водителей трамвая и троллейбуса</t>
+        </is>
+      </c>
+      <c r="E183" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F183" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G183" s="6" t="inlineStr">
+        <is>
+          <t>ФИО (должности) работников; даты; время начала и окончания работы (смены); перерывы; выходные; срок, на который составлен график</t>
+        </is>
+      </c>
+      <c r="H183" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I183" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J183" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K183" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L183" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B184" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтранса России от 02.10.2020 № 404 "Об утверждении Особенностей режима рабочего времени и времени отдыха водителей трамвая и троллейбуса"</t>
+        </is>
+      </c>
+      <c r="C184" s="6" t="inlineStr">
+        <is>
+          <t>п. 3 Особенностей</t>
+        </is>
+      </c>
+      <c r="D184" s="6" t="inlineStr">
+        <is>
+          <t>Приказ (локальный нормативный акт) о введении суммированного учета рабочего времени водителей трамвая и троллейбуса</t>
+        </is>
+      </c>
+      <c r="E184" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F184" s="6" t="inlineStr">
+        <is>
+          <t>УСЛОВНО</t>
+        </is>
+      </c>
+      <c r="G184" s="6" t="inlineStr">
+        <is>
+          <t>Учетный период; категории водителей; порядок учета</t>
+        </is>
+      </c>
+      <c r="H184" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I184" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J184" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K184" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L184" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B185" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтранса России от 16.10.2020 № 423 "Об утверждении Особенностей режима рабочего времени и времени отдыха работников метрополитена"</t>
+        </is>
+      </c>
+      <c r="C185" s="6" t="inlineStr">
+        <is>
+          <t>п. 1 Особенностей</t>
+        </is>
+      </c>
+      <c r="D185" s="6" t="inlineStr">
+        <is>
+          <t>Правила внутреннего трудового распорядка (с особенностями режима рабочего времени и времени отдыха работников метрополитена)</t>
+        </is>
+      </c>
+      <c r="E185" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F185" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G185" s="6" t="inlineStr">
+        <is>
+          <t>Продолжительность рабочей недели / смены; время начала и окончания работы; перерывы; число смен; чередование рабочих и нерабочих дней; иные особенности режима</t>
+        </is>
+      </c>
+      <c r="H185" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I185" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J185" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K185" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L185" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B186" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтранса России от 16.10.2020 № 423 "Об утверждении Особенностей режима рабочего времени и времени отдыха работников метрополитена"</t>
+        </is>
+      </c>
+      <c r="C186" s="6" t="inlineStr">
+        <is>
+          <t>п. 1 Особенностей</t>
+        </is>
+      </c>
+      <c r="D186" s="6" t="inlineStr">
+        <is>
+          <t>Графики работы и (или) графики сменности работников метрополитена</t>
+        </is>
+      </c>
+      <c r="E186" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F186" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G186" s="6" t="inlineStr">
+        <is>
+          <t>ФИО (должности) работников; даты; время начала и окончания работы (смены); перерывы; выходные; срок, на который составлен график</t>
+        </is>
+      </c>
+      <c r="H186" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I186" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J186" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K186" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L186" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B187" s="6" t="inlineStr">
+        <is>
+          <t>Приказ МЧС России от 28.02.2020 № 136 "Об утверждении Положения об особенностях режима рабочего времени и времени отдыха работников аварийно-спасательных и поисково-спасательных формирований Министерства Российской Федерации по делам гражданской обороны, чрезвычайным ситуациям и ликвидации последствий стихийных бедствий, работа которых непосредственно связана с проведением аварийно-спасательных работ"</t>
+        </is>
+      </c>
+      <c r="C187" s="6" t="inlineStr">
+        <is>
+          <t>положения Положения</t>
+        </is>
+      </c>
+      <c r="D187" s="6" t="inlineStr">
+        <is>
+          <t>Правила внутреннего трудового распорядка (с особенностями режима рабочего времени и времени отдыха работников аварийно-спасательных формирований)</t>
+        </is>
+      </c>
+      <c r="E187" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F187" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G187" s="6" t="inlineStr">
+        <is>
+          <t>Продолжительность рабочей недели / смены; время начала и окончания работы; перерывы; число смен; чередование рабочих и нерабочих дней; иные особенности режима</t>
+        </is>
+      </c>
+      <c r="H187" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I187" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J187" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K187" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L187" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B188" s="6" t="inlineStr">
+        <is>
+          <t>Приказ МЧС России от 28.02.2020 № 136 "Об утверждении Положения об особенностях режима рабочего времени и времени отдыха работников аварийно-спасательных и поисково-спасательных формирований Министерства Российской Федерации по делам гражданской обороны, чрезвычайным ситуациям и ликвидации последствий стихийных бедствий, работа которых непосредственно связана с проведением аварийно-спасательных работ"</t>
+        </is>
+      </c>
+      <c r="C188" s="6" t="inlineStr">
+        <is>
+          <t>положения Положения</t>
+        </is>
+      </c>
+      <c r="D188" s="6" t="inlineStr">
+        <is>
+          <t>Графики работы и (или) графики сменности работников аварийно-спасательных формирований</t>
+        </is>
+      </c>
+      <c r="E188" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F188" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G188" s="6" t="inlineStr">
+        <is>
+          <t>ФИО (должности) работников; даты; время начала и окончания работы (смены); перерывы; выходные; срок, на который составлен график</t>
+        </is>
+      </c>
+      <c r="H188" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I188" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J188" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K188" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L188" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B189" s="6" t="inlineStr">
+        <is>
+          <t>Приказ МЧС России от 04.09.2013 № 585 "Об утверждении Положения об особенностях регулирования работы, режимов труда и отдыха отдельных категорий работников военизированных горноспасательных частей, находящихся в ведении МЧС России"</t>
+        </is>
+      </c>
+      <c r="C189" s="6" t="inlineStr">
+        <is>
+          <t>положения Положения</t>
+        </is>
+      </c>
+      <c r="D189" s="6" t="inlineStr">
+        <is>
+          <t>Правила внутреннего трудового распорядка (с особенностями режимов труда и отдыха работников военизированных горноспасательных частей)</t>
+        </is>
+      </c>
+      <c r="E189" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F189" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G189" s="6" t="inlineStr">
+        <is>
+          <t>Продолжительность рабочей недели / смены; время начала и окончания работы; перерывы; число смен; чередование рабочих и нерабочих дней; иные особенности режима</t>
+        </is>
+      </c>
+      <c r="H189" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I189" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J189" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K189" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L189" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B190" s="6" t="inlineStr">
+        <is>
+          <t>Приказ МЧС России от 04.09.2013 № 585 "Об утверждении Положения об особенностях регулирования работы, режимов труда и отдыха отдельных категорий работников военизированных горноспасательных частей, находящихся в ведении МЧС России"</t>
+        </is>
+      </c>
+      <c r="C190" s="6" t="inlineStr">
+        <is>
+          <t>положения Положения</t>
+        </is>
+      </c>
+      <c r="D190" s="6" t="inlineStr">
+        <is>
+          <t>Графики работы и (или) графики сменности работников военизированных горноспасательных частей</t>
+        </is>
+      </c>
+      <c r="E190" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F190" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G190" s="6" t="inlineStr">
+        <is>
+          <t>ФИО (должности) работников; даты; время начала и окончания работы (смены); перерывы; выходные; срок, на который составлен график</t>
+        </is>
+      </c>
+      <c r="H190" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I190" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J190" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K190" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L190" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B191" s="6" t="inlineStr">
+        <is>
+          <t>Приказ ГФС России от 17.08.2009 № 264 "Об утверждении Положения о порядке учета рабочего времени и времени отдыха лиц начальствующего состава федеральной фельдъегерской связи"</t>
+        </is>
+      </c>
+      <c r="C191" s="6" t="inlineStr">
+        <is>
+          <t>Положение (приказ ГФС № 264)</t>
+        </is>
+      </c>
+      <c r="D191" s="6" t="inlineStr">
+        <is>
+          <t>Документы учета рабочего времени и времени отдыха лиц начальствующего состава федеральной фельдъегерской связи</t>
+        </is>
+      </c>
+      <c r="E191" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F191" s="6" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="G191" s="6" t="inlineStr">
+        <is>
+          <t>Учет рабочего времени и времени отдыха в порядке, установленном Положением</t>
+        </is>
+      </c>
+      <c r="H191" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I191" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J191" s="6" t="inlineStr">
+        <is>
+          <t>Подтверждение (?)</t>
+        </is>
+      </c>
+      <c r="K191" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L191" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B192" s="6" t="inlineStr">
+        <is>
+          <t>Приказ ГФС России от 17.08.2009 № 264 "Об утверждении Положения о порядке учета рабочего времени и времени отдыха лиц начальствующего состава федеральной фельдъегерской связи"</t>
+        </is>
+      </c>
+      <c r="C192" s="6" t="inlineStr">
+        <is>
+          <t>Положение (приказ ГФС № 264)</t>
+        </is>
+      </c>
+      <c r="D192" s="6" t="inlineStr">
+        <is>
+          <t>Документы учета рабочего времени и времени отдыха лиц начальствующего состава федеральной фельдъегерской связи</t>
+        </is>
+      </c>
+      <c r="E192" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F192" s="6" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
+      <c r="G192" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H192" s="6" t="inlineStr">
+        <is>
+          <t>Лицо, ведущее учет рабочего времени</t>
+        </is>
+      </c>
+      <c r="I192" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J192" s="6" t="inlineStr">
+        <is>
+          <t>Подтверждение (?)</t>
+        </is>
+      </c>
+      <c r="K192" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L192" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B193" s="6" t="inlineStr">
+        <is>
+          <t>Приказ ФСБ России от 07.04.2007 № 161 "Об утверждении Положения об особенностях режима рабочего времени и времени отдыха членов экипажей из числа гражданского персонала пограничных патрульных судов, катеров"</t>
+        </is>
+      </c>
+      <c r="C193" s="6" t="inlineStr">
+        <is>
+          <t>положения Положения</t>
+        </is>
+      </c>
+      <c r="D193" s="6" t="inlineStr">
+        <is>
+          <t>Правила внутреннего трудового распорядка (с особенностями режима рабочего времени и времени отдыха членов экипажей пограничных патрульных судов, катеров)</t>
+        </is>
+      </c>
+      <c r="E193" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F193" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G193" s="6" t="inlineStr">
+        <is>
+          <t>Продолжительность рабочей недели / смены; время начала и окончания работы; перерывы; число смен; чередование рабочих и нерабочих дней; иные особенности режима</t>
+        </is>
+      </c>
+      <c r="H193" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I193" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J193" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K193" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L193" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B194" s="6" t="inlineStr">
+        <is>
+          <t>Приказ ФСБ России от 07.04.2007 № 161 "Об утверждении Положения об особенностях режима рабочего времени и времени отдыха членов экипажей из числа гражданского персонала пограничных патрульных судов, катеров"</t>
+        </is>
+      </c>
+      <c r="C194" s="6" t="inlineStr">
+        <is>
+          <t>положения Положения</t>
+        </is>
+      </c>
+      <c r="D194" s="6" t="inlineStr">
+        <is>
+          <t>Вахтенное расписание / графики вахт членов экипажей пограничных патрульных судов, катеров</t>
+        </is>
+      </c>
+      <c r="E194" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F194" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G194" s="6" t="inlineStr">
+        <is>
+          <t>Состав вахт; продолжительность; чередование вахт и отдыха</t>
+        </is>
+      </c>
+      <c r="H194" s="6" t="inlineStr">
+        <is>
+          <t>Капитан судна / руководитель организации / уполномоченное лицо</t>
+        </is>
+      </c>
+      <c r="I194" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J194" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K194" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L194" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B195" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтранса России от 30.01.2004 № 10 "Об утверждении Положения об особенностях режима рабочего времени и времени отдыха работников, осуществляющих управление воздушным движением гражданской авиации Российской Федерации"</t>
+        </is>
+      </c>
+      <c r="C195" s="6" t="inlineStr">
+        <is>
+          <t>положения Положения</t>
+        </is>
+      </c>
+      <c r="D195" s="6" t="inlineStr">
+        <is>
+          <t>Правила внутреннего трудового распорядка (с особенностями режима рабочего времени и времени отдыха работников УВД)</t>
+        </is>
+      </c>
+      <c r="E195" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F195" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G195" s="6" t="inlineStr">
+        <is>
+          <t>Продолжительность рабочей недели / смены; время начала и окончания работы; перерывы; число смен; чередование рабочих и нерабочих дней; иные особенности режима</t>
+        </is>
+      </c>
+      <c r="H195" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I195" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J195" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K195" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L195" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B196" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минтранса России от 30.01.2004 № 10 "Об утверждении Положения об особенностях режима рабочего времени и времени отдыха работников, осуществляющих управление воздушным движением гражданской авиации Российской Федерации"</t>
+        </is>
+      </c>
+      <c r="C196" s="6" t="inlineStr">
+        <is>
+          <t>положения Положения</t>
+        </is>
+      </c>
+      <c r="D196" s="6" t="inlineStr">
+        <is>
+          <t>Графики сменности работников, осуществляющих управление воздушным движением</t>
+        </is>
+      </c>
+      <c r="E196" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F196" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G196" s="6" t="inlineStr">
+        <is>
+          <t>ФИО (должности) работников; даты; время начала и окончания работы (смены); перерывы; выходные; срок, на который составлен график</t>
+        </is>
+      </c>
+      <c r="H196" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I196" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J196" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K196" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L196" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B197" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Росгидромета от 30.12.2003 № 272 "Об утверждении Положения об особенностях режима рабочего времени и времени отдыха работников оперативно-производственных организаций Росгидромета, их структурных подразделений, имеющих особый характер работы"</t>
+        </is>
+      </c>
+      <c r="C197" s="6" t="inlineStr">
+        <is>
+          <t>положения Положения</t>
+        </is>
+      </c>
+      <c r="D197" s="6" t="inlineStr">
+        <is>
+          <t>Правила внутреннего трудового распорядка (с особенностями режима рабочего времени и времени отдыха работников оперативно-производственных организаций Росгидромета)</t>
+        </is>
+      </c>
+      <c r="E197" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F197" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G197" s="6" t="inlineStr">
+        <is>
+          <t>Продолжительность рабочей недели / смены; время начала и окончания работы; перерывы; число смен; чередование рабочих и нерабочих дней; иные особенности режима</t>
+        </is>
+      </c>
+      <c r="H197" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I197" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J197" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K197" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L197" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B198" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Росгидромета от 30.12.2003 № 272 "Об утверждении Положения об особенностях режима рабочего времени и времени отдыха работников оперативно-производственных организаций Росгидромета, их структурных подразделений, имеющих особый характер работы"</t>
+        </is>
+      </c>
+      <c r="C198" s="6" t="inlineStr">
+        <is>
+          <t>положения Положения</t>
+        </is>
+      </c>
+      <c r="D198" s="6" t="inlineStr">
+        <is>
+          <t>Графики работы и (или) графики сменности работников оперативно-производственных организаций Росгидромета</t>
+        </is>
+      </c>
+      <c r="E198" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F198" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G198" s="6" t="inlineStr">
+        <is>
+          <t>ФИО (должности) работников; даты; время начала и окончания работы (смены); перерывы; выходные; срок, на который составлен график</t>
+        </is>
+      </c>
+      <c r="H198" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I198" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J198" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K198" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L198" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B199" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минсвязи России от 08.09.2003 № 112 "Об утверждении Положения об особенностях режима рабочего времени и времени отдыха работников связи, имеющих особый характер работы"</t>
+        </is>
+      </c>
+      <c r="C199" s="6" t="inlineStr">
+        <is>
+          <t>положения Положения</t>
+        </is>
+      </c>
+      <c r="D199" s="6" t="inlineStr">
+        <is>
+          <t>Правила внутреннего трудового распорядка (с особенностями режима рабочего времени и времени отдыха работников связи)</t>
+        </is>
+      </c>
+      <c r="E199" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F199" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G199" s="6" t="inlineStr">
+        <is>
+          <t>Продолжительность рабочей недели / смены; время начала и окончания работы; перерывы; число смен; чередование рабочих и нерабочих дней; иные особенности режима</t>
+        </is>
+      </c>
+      <c r="H199" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I199" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J199" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K199" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L199" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B200" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минсвязи России от 08.09.2003 № 112 "Об утверждении Положения об особенностях режима рабочего времени и времени отдыха работников связи, имеющих особый характер работы"</t>
+        </is>
+      </c>
+      <c r="C200" s="6" t="inlineStr">
+        <is>
+          <t>положения Положения</t>
+        </is>
+      </c>
+      <c r="D200" s="6" t="inlineStr">
+        <is>
+          <t>Графики работы и (или) графики сменности работников связи</t>
+        </is>
+      </c>
+      <c r="E200" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F200" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G200" s="6" t="inlineStr">
+        <is>
+          <t>ФИО (должности) работников; даты; время начала и окончания работы (смены); перерывы; выходные; срок, на который составлен график</t>
+        </is>
+      </c>
+      <c r="H200" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I200" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J200" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K200" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L200" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B201" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Госкомрыболовства России от 08.08.2003 № 271 "Об утверждении Положения об особенностях режима рабочего времени и времени отдыха отдельных категорий работников рыбохозяйственного комплекса, имеющих особый характер работы"</t>
+        </is>
+      </c>
+      <c r="C201" s="6" t="inlineStr">
+        <is>
+          <t>положения Положения</t>
+        </is>
+      </c>
+      <c r="D201" s="6" t="inlineStr">
+        <is>
+          <t>Правила внутреннего трудового распорядка (с особенностями режима рабочего времени и времени отдыха работников рыбохозяйственного комплекса)</t>
+        </is>
+      </c>
+      <c r="E201" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F201" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G201" s="6" t="inlineStr">
+        <is>
+          <t>Продолжительность рабочей недели / смены; время начала и окончания работы; перерывы; число смен; чередование рабочих и нерабочих дней; иные особенности режима</t>
+        </is>
+      </c>
+      <c r="H201" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I201" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J201" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K201" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L201" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B202" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Госкомрыболовства России от 08.08.2003 № 271 "Об утверждении Положения об особенностях режима рабочего времени и времени отдыха отдельных категорий работников рыбохозяйственного комплекса, имеющих особый характер работы"</t>
+        </is>
+      </c>
+      <c r="C202" s="6" t="inlineStr">
+        <is>
+          <t>положения Положения</t>
+        </is>
+      </c>
+      <c r="D202" s="6" t="inlineStr">
+        <is>
+          <t>Графики работы и (или) графики сменности работников рыбохозяйственного комплекса</t>
+        </is>
+      </c>
+      <c r="E202" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F202" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G202" s="6" t="inlineStr">
+        <is>
+          <t>ФИО (должности) работников; даты; время начала и окончания работы (смены); перерывы; выходные; срок, на который составлен график</t>
+        </is>
+      </c>
+      <c r="H202" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I202" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J202" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K202" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L202" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B203" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минобороны России от 16.05.2003 № 170 "Об утверждении Положения об особенностях режима рабочего времени и времени отдыха членов экипажей (гражданского персонала) судов обеспечения Вооруженных Сил Российской Федерации"</t>
+        </is>
+      </c>
+      <c r="C203" s="6" t="inlineStr">
+        <is>
+          <t>положения Положения</t>
+        </is>
+      </c>
+      <c r="D203" s="6" t="inlineStr">
+        <is>
+          <t>Правила внутреннего трудового распорядка (с особенностями режима рабочего времени и времени отдыха членов экипажей судов обеспечения ВС РФ)</t>
+        </is>
+      </c>
+      <c r="E203" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F203" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G203" s="6" t="inlineStr">
+        <is>
+          <t>Продолжительность рабочей недели / смены; время начала и окончания работы; перерывы; число смен; чередование рабочих и нерабочих дней; иные особенности режима</t>
+        </is>
+      </c>
+      <c r="H203" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I203" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J203" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K203" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L203" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B204" s="6" t="inlineStr">
+        <is>
+          <t>Приказ Минобороны России от 16.05.2003 № 170 "Об утверждении Положения об особенностях режима рабочего времени и времени отдыха членов экипажей (гражданского персонала) судов обеспечения Вооруженных Сил Российской Федерации"</t>
+        </is>
+      </c>
+      <c r="C204" s="6" t="inlineStr">
+        <is>
+          <t>положения Положения</t>
+        </is>
+      </c>
+      <c r="D204" s="6" t="inlineStr">
+        <is>
+          <t>Вахтенное расписание / графики вахт членов экипажей судов обеспечения ВС РФ</t>
+        </is>
+      </c>
+      <c r="E204" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F204" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G204" s="6" t="inlineStr">
+        <is>
+          <t>Состав вахт; продолжительность; чередование вахт и отдыха</t>
+        </is>
+      </c>
+      <c r="H204" s="6" t="inlineStr">
+        <is>
+          <t>Капитан судна / руководитель организации / уполномоченное лицо</t>
+        </is>
+      </c>
+      <c r="I204" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J204" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K204" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L204" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="6" t="inlineStr">
+        <is>
+          <t>Режимы труда и отдыха</t>
+        </is>
+      </c>
+      <c r="B205" s="6" t="inlineStr">
+        <is>
+          <t>Постановление Минтруда России от 12.07.1999 № 22 "Об установлении продолжительности рабочей недели членам экипажей воздушных судов гражданской авиации"</t>
+        </is>
+      </c>
+      <c r="C205" s="6" t="inlineStr">
+        <is>
+          <t>п. 1 постановления</t>
+        </is>
+      </c>
+      <c r="D205" s="6" t="inlineStr">
+        <is>
+          <t>Правила внутреннего трудового распорядка / локальный нормативный акт об установлении продолжительности рабочей недели членам экипажей воздушных судов гражданской авиации (36 часов)</t>
+        </is>
+      </c>
+      <c r="E205" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="F205" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G205" s="6" t="inlineStr">
+        <is>
+          <t>Продолжительность рабочей недели 36 часов; категории членов экипажей воздушных судов</t>
+        </is>
+      </c>
+      <c r="H205" s="6" t="inlineStr">
+        <is>
+          <t>Работодатель (руководитель организации / уполномоченное лицо)</t>
+        </is>
+      </c>
+      <c r="I205" s="6" t="inlineStr">
+        <is>
+          <t>Нет требований</t>
+        </is>
+      </c>
+      <c r="J205" s="6" t="inlineStr">
+        <is>
+          <t>Утверждение</t>
+        </is>
+      </c>
+      <c r="K205" s="6" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
+      <c r="L205" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
